--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -2784,86 +2784,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3476,6 +3396,86 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3490,92 +3490,92 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V159">
     <sortCondition ref="I2:I159"/>
   </sortState>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A09E4D62-1B60-46F0-8D10-9D2989A1E1DD}" name="haModel" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{965DA40D-EBE9-42CF-B56F-A6A77EF637F0}" name="haDescription" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{130CAF40-E0C6-4E3E-B004-85850140B916}" name="BiNuralMSRP w/Charger" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{A09E4D62-1B60-46F0-8D10-9D2989A1E1DD}" name="haModel" dataDxfId="51"/>
+    <tableColumn id="15" xr3:uid="{965DA40D-EBE9-42CF-B56F-A6A77EF637F0}" name="haDescription" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{130CAF40-E0C6-4E3E-B004-85850140B916}" name="BiNuralMSRP w/Charger" dataDxfId="49">
       <calculatedColumnFormula>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BA070518-7526-4FCA-A727-C48F8CD389F1}" name="haMSRP" dataDxfId="54" dataCellStyle="Comma"/>
-    <tableColumn id="17" xr3:uid="{00383612-0531-419F-BDF0-C61ADC5A5242}" name="Discount Type 1" dataDxfId="53" dataCellStyle="Comma"/>
-    <tableColumn id="18" xr3:uid="{238DF570-BCC6-441D-86CE-1CD2C0CBB0A4}" name="Discount Amount 1" dataDxfId="52" dataCellStyle="Comma">
+    <tableColumn id="3" xr3:uid="{BA070518-7526-4FCA-A727-C48F8CD389F1}" name="haMSRP" dataDxfId="48" dataCellStyle="Comma"/>
+    <tableColumn id="17" xr3:uid="{00383612-0531-419F-BDF0-C61ADC5A5242}" name="Discount Type 1" dataDxfId="47" dataCellStyle="Comma"/>
+    <tableColumn id="18" xr3:uid="{238DF570-BCC6-441D-86CE-1CD2C0CBB0A4}" name="Discount Amount 1" dataDxfId="46" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[haMSRP]]-((HearingAids[[#This Row],[ListPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{5D29F2AF-C8F8-440E-80A9-37F68ED6526A}" name="HAListPrice" dataDxfId="51" dataCellStyle="Comma">
+    <tableColumn id="14" xr3:uid="{5D29F2AF-C8F8-440E-80A9-37F68ED6526A}" name="HAListPrice" dataDxfId="45" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{790802D5-161D-4A7E-805F-7E74CEEFF06C}" name="ListPriceBinural" dataDxfId="50" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{A443216B-20E9-4998-AF64-4AF2D830D488}" name="Discount Type 2" dataDxfId="49" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{97DC0668-F1BB-4221-B66A-0541EE63F239}" name="Discount Amount 2" dataDxfId="48" dataCellStyle="Comma">
+    <tableColumn id="8" xr3:uid="{790802D5-161D-4A7E-805F-7E74CEEFF06C}" name="ListPriceBinural" dataDxfId="44" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{A443216B-20E9-4998-AF64-4AF2D830D488}" name="Discount Type 2" dataDxfId="43" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{97DC0668-F1BB-4221-B66A-0541EE63F239}" name="Discount Amount 2" dataDxfId="42" dataCellStyle="Comma">
       <calculatedColumnFormula>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BA3E2B5E-A0AC-4615-8DC5-9BDA41C1C791}" name="haNetPrice" dataDxfId="47" dataCellStyle="Comma">
+    <tableColumn id="7" xr3:uid="{BA3E2B5E-A0AC-4615-8DC5-9BDA41C1C791}" name="haNetPrice" dataDxfId="41" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{38CF1B18-CDB5-4976-B47F-965816542466}" name="haNetPriceBinural" dataDxfId="46" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{7FD8661B-3CB2-4419-B4E4-F4B466463008}" name="Discount Type 3" dataDxfId="45" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{F690564D-67FB-47A7-BB92-4594973E8684}" name="Discount Amount 3" dataDxfId="44" dataCellStyle="Comma">
+    <tableColumn id="20" xr3:uid="{38CF1B18-CDB5-4976-B47F-965816542466}" name="haNetPriceBinural" dataDxfId="40" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{7FD8661B-3CB2-4419-B4E4-F4B466463008}" name="Discount Type 3" dataDxfId="39" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{F690564D-67FB-47A7-BB92-4594973E8684}" name="Discount Amount 3" dataDxfId="38" dataCellStyle="Comma">
       <calculatedColumnFormula>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{70079D27-1688-482B-B7CE-C08CD0692376}" name="haNetPrice2" dataDxfId="43" dataCellStyle="Comma">
+    <tableColumn id="22" xr3:uid="{70079D27-1688-482B-B7CE-C08CD0692376}" name="haNetPrice2" dataDxfId="37" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{86E09452-1856-484B-8B87-A189C8CD8DFB}" name="haNetPriceBinural2" dataDxfId="42" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{C584D592-9121-42BD-ADD1-A997B12ADB03}" name="paFittingFee" dataDxfId="41" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{D4BCCF1D-8129-4502-AE64-888D352A8485}" name="chargerType" dataDxfId="40" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{8D61B71A-686D-41F5-A2BF-54F259932C23}" name="chargerPrice" dataDxfId="39" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{8C0379A7-F346-4094-953F-A4AB4D0878CB}" name="haReceiverType" dataDxfId="38" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{5D6BB6BD-447F-4911-B6E4-986FB62F14A1}" name="haReceiverPrice" dataDxfId="37" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{E1863ADB-80F5-499D-B829-43F23A36EF68}" name="haReceiverDiscountDescription" dataDxfId="36" dataCellStyle="Comma"/>
+    <tableColumn id="16" xr3:uid="{86E09452-1856-484B-8B87-A189C8CD8DFB}" name="haNetPriceBinural2" dataDxfId="36" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{C584D592-9121-42BD-ADD1-A997B12ADB03}" name="paFittingFee" dataDxfId="35" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{D4BCCF1D-8129-4502-AE64-888D352A8485}" name="chargerType" dataDxfId="34" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{8D61B71A-686D-41F5-A2BF-54F259932C23}" name="chargerPrice" dataDxfId="33" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{8C0379A7-F346-4094-953F-A4AB4D0878CB}" name="haReceiverType" dataDxfId="32" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{5D6BB6BD-447F-4911-B6E4-986FB62F14A1}" name="haReceiverPrice" dataDxfId="31" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{E1863ADB-80F5-499D-B829-43F23A36EF68}" name="haReceiverDiscountDescription" dataDxfId="30" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="29">
   <autoFilter ref="A1:I260" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H286">
     <sortCondition ref="H1:H286"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="33">
+    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="27">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="32"/>
-    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57">
   <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H74">
     <sortCondition ref="H1:H74"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{FDC3E4DD-A231-46DD-8097-7C0DC18260BD}" name="barcodeName"/>
-    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="56">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{D0382781-2AC8-4DE6-BF59-9B38B78B1184}" name="remoteModel"/>
     <tableColumn id="4" xr3:uid="{9B080694-7BEA-4586-AA70-DDEC1D67D699}" name="remoteType"/>
     <tableColumn id="7" xr3:uid="{CCB41D66-8697-4FAF-A74F-5F54F6CCA4F8}" name="remoteListAmount"/>
-    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="20">
+    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="54">
       <calculatedColumnFormula>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{435AFC97-0382-475D-9332-93EDAB756C8B}" name="remoteDiscountDescription"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1168" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB2A2E54-06D7-409A-89D6-8527DEB169F4}"/>
+  <xr:revisionPtr revIDLastSave="1180" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAFA8165-B8F0-43C3-9B88-7358519A216B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3562,7 +3562,15 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57">
-  <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}"/>
+  <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Open House Gold Bundle"/>
+        <filter val="Open House Platinum Bundle"/>
+        <filter val="Open House Silver Bundle"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H74">
     <sortCondition ref="H1:H74"/>
   </sortState>
@@ -25315,7 +25323,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" hidden="1">
       <c r="A2" t="s">
         <v>408</v>
       </c>
@@ -25343,7 +25351,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" hidden="1">
       <c r="A3" t="s">
         <v>410</v>
       </c>
@@ -25371,7 +25379,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>409</v>
       </c>
@@ -25399,7 +25407,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" hidden="1">
       <c r="A5" t="s">
         <v>411</v>
       </c>
@@ -25427,7 +25435,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
         <v>318</v>
       </c>
@@ -25455,7 +25463,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
         <v>319</v>
       </c>
@@ -25483,7 +25491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
         <v>223</v>
       </c>
@@ -25511,7 +25519,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
         <v>224</v>
       </c>
@@ -25539,7 +25547,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
         <v>225</v>
       </c>
@@ -25567,7 +25575,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
         <v>240</v>
       </c>
@@ -25595,7 +25603,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
         <v>241</v>
       </c>
@@ -25623,7 +25631,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" hidden="1">
       <c r="A13" t="s">
         <v>242</v>
       </c>
@@ -25651,7 +25659,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
         <v>246</v>
       </c>
@@ -25679,7 +25687,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" t="s">
         <v>247</v>
       </c>
@@ -25707,7 +25715,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" t="s">
         <v>248</v>
       </c>
@@ -25735,7 +25743,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" hidden="1">
       <c r="A17" t="s">
         <v>243</v>
       </c>
@@ -25763,7 +25771,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" hidden="1">
       <c r="A18" t="s">
         <v>244</v>
       </c>
@@ -25791,7 +25799,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" hidden="1">
       <c r="A19" t="s">
         <v>245</v>
       </c>
@@ -25819,7 +25827,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" hidden="1">
       <c r="A20" t="s">
         <v>181</v>
       </c>
@@ -25847,7 +25855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" hidden="1">
       <c r="A21" t="s">
         <v>182</v>
       </c>
@@ -25875,7 +25883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" hidden="1">
       <c r="A22" t="s">
         <v>183</v>
       </c>
@@ -25903,7 +25911,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" hidden="1">
       <c r="A23" t="s">
         <v>178</v>
       </c>
@@ -25931,7 +25939,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" hidden="1">
       <c r="A24" t="s">
         <v>179</v>
       </c>
@@ -25959,7 +25967,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" t="s">
         <v>180</v>
       </c>
@@ -25987,7 +25995,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" hidden="1">
       <c r="A26" t="s">
         <v>428</v>
       </c>
@@ -26015,7 +26023,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" hidden="1">
       <c r="A27" t="s">
         <v>462</v>
       </c>
@@ -26043,7 +26051,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" hidden="1">
       <c r="A28" t="s">
         <v>284</v>
       </c>
@@ -26071,7 +26079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" hidden="1">
       <c r="A29" t="s">
         <v>285</v>
       </c>
@@ -26099,7 +26107,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" hidden="1">
       <c r="A30" t="s">
         <v>267</v>
       </c>
@@ -26127,7 +26135,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" hidden="1">
       <c r="A31" t="s">
         <v>268</v>
       </c>
@@ -26155,7 +26163,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" hidden="1">
       <c r="A32" t="s">
         <v>286</v>
       </c>
@@ -26183,7 +26191,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" hidden="1">
       <c r="A33" t="s">
         <v>287</v>
       </c>
@@ -26211,7 +26219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" hidden="1">
       <c r="A34" t="s">
         <v>249</v>
       </c>
@@ -26239,7 +26247,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" hidden="1">
       <c r="A35" t="s">
         <v>250</v>
       </c>
@@ -26267,7 +26275,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" hidden="1">
       <c r="A36" t="s">
         <v>251</v>
       </c>
@@ -26295,7 +26303,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" hidden="1">
       <c r="A37" t="s">
         <v>337</v>
       </c>
@@ -26323,7 +26331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" hidden="1">
       <c r="A38" t="s">
         <v>338</v>
       </c>
@@ -26351,7 +26359,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" hidden="1">
       <c r="A39" t="s">
         <v>336</v>
       </c>
@@ -26379,7 +26387,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" hidden="1">
       <c r="A40" t="s">
         <v>369</v>
       </c>
@@ -26407,7 +26415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" hidden="1">
       <c r="A41" t="s">
         <v>370</v>
       </c>
@@ -26453,11 +26461,11 @@
         <v>175</v>
       </c>
       <c r="F42" s="25">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G42" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H42" t="s">
         <v>425</v>
@@ -26481,11 +26489,11 @@
         <v>450</v>
       </c>
       <c r="F43" s="25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G43" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="H43" t="s">
         <v>425</v>
@@ -26509,11 +26517,11 @@
         <v>175</v>
       </c>
       <c r="F44" s="25">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G44" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H44" t="s">
         <v>468</v>
@@ -26537,11 +26545,11 @@
         <v>450</v>
       </c>
       <c r="F45" s="25">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G45" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="H45" t="s">
         <v>468</v>
@@ -26565,11 +26573,11 @@
         <v>450</v>
       </c>
       <c r="F46" s="25">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G46" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="H46" t="s">
         <v>468</v>
@@ -26593,11 +26601,11 @@
         <v>175</v>
       </c>
       <c r="F47" s="25">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G47" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H47" t="s">
         <v>467</v>
@@ -26621,17 +26629,17 @@
         <v>450</v>
       </c>
       <c r="F48" s="25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G48" s="25">
         <f>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</f>
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="H48" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" hidden="1">
       <c r="A49" t="s">
         <v>424</v>
       </c>
@@ -26659,7 +26667,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" t="s">
         <v>426</v>
       </c>
@@ -26687,7 +26695,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" t="s">
         <v>474</v>
       </c>
@@ -26715,7 +26723,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" t="s">
         <v>427</v>
       </c>
@@ -26743,7 +26751,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" t="s">
         <v>146</v>
       </c>
@@ -26771,7 +26779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" t="s">
         <v>148</v>
       </c>
@@ -26799,7 +26807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" hidden="1">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -26827,7 +26835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" t="s">
         <v>455</v>
       </c>
@@ -26855,7 +26863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" t="s">
         <v>149</v>
       </c>
@@ -26883,7 +26891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" hidden="1">
       <c r="A58" t="s">
         <v>150</v>
       </c>
@@ -26911,7 +26919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" t="s">
         <v>151</v>
       </c>
@@ -26939,7 +26947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" t="s">
         <v>152</v>
       </c>
@@ -26968,7 +26976,7 @@
       </c>
       <c r="J60" s="35"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" hidden="1">
       <c r="A61" t="s">
         <v>153</v>
       </c>
@@ -26997,7 +27005,7 @@
       </c>
       <c r="J61" s="35"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" hidden="1">
       <c r="A62" t="s">
         <v>154</v>
       </c>
@@ -27026,7 +27034,7 @@
       </c>
       <c r="J62" s="35"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" hidden="1">
       <c r="A63" t="s">
         <v>420</v>
       </c>
@@ -27055,7 +27063,7 @@
       </c>
       <c r="J63" s="35"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" t="s">
         <v>420</v>
       </c>
@@ -27084,7 +27092,7 @@
       </c>
       <c r="J64" s="35"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" hidden="1">
       <c r="A65" t="s">
         <v>153</v>
       </c>
@@ -27113,7 +27121,7 @@
       </c>
       <c r="J65" s="35"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" hidden="1">
       <c r="A66" t="s">
         <v>149</v>
       </c>
@@ -27142,7 +27150,7 @@
       </c>
       <c r="J66" s="35"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" t="s">
         <v>471</v>
       </c>
@@ -27171,7 +27179,7 @@
       </c>
       <c r="J67" s="35"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" hidden="1">
       <c r="B68" s="16" t="str">
         <f t="shared" si="2"/>
         <v>()</v>
@@ -27196,7 +27204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" hidden="1">
       <c r="B69" s="16" t="str">
         <f t="shared" si="2"/>
         <v>()</v>
@@ -27221,7 +27229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" hidden="1">
       <c r="B70" s="16" t="str">
         <f t="shared" si="2"/>
         <v>()</v>
@@ -27246,7 +27254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" t="s">
         <v>371</v>
       </c>
@@ -27274,7 +27282,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" hidden="1">
       <c r="A72" t="s">
         <v>372</v>
       </c>
@@ -27302,7 +27310,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" t="s">
         <v>388</v>
       </c>
@@ -27330,7 +27338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" t="s">
         <v>389</v>
       </c>
@@ -27358,7 +27366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" t="s">
         <v>540</v>
       </c>
@@ -27386,7 +27394,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" t="s">
         <v>541</v>
       </c>
@@ -27414,7 +27422,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" t="s">
         <v>542</v>
       </c>
@@ -27442,7 +27450,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" t="s">
         <v>543</v>
       </c>
@@ -27470,7 +27478,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" t="s">
         <v>544</v>
       </c>
@@ -27498,7 +27506,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" t="s">
         <v>545</v>
       </c>
@@ -27526,7 +27534,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" hidden="1">
       <c r="A81" t="s">
         <v>546</v>
       </c>
@@ -27554,7 +27562,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" hidden="1">
       <c r="A82" t="s">
         <v>547</v>
       </c>
@@ -27582,7 +27590,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" hidden="1">
       <c r="A83" t="s">
         <v>548</v>
       </c>
@@ -27610,7 +27618,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" hidden="1">
       <c r="A84" t="s">
         <v>549</v>
       </c>
@@ -27638,7 +27646,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" hidden="1">
       <c r="A85" t="s">
         <v>550</v>
       </c>
@@ -27666,7 +27674,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" hidden="1">
       <c r="A86" t="s">
         <v>550</v>
       </c>
@@ -27694,7 +27702,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" hidden="1">
       <c r="A87" t="s">
         <v>548</v>
       </c>
@@ -27722,7 +27730,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" hidden="1">
       <c r="A88" t="s">
         <v>544</v>
       </c>
@@ -27750,7 +27758,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" hidden="1">
       <c r="A89" t="s">
         <v>551</v>
       </c>
@@ -27778,7 +27786,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" hidden="1">
       <c r="A90" t="s">
         <v>552</v>
       </c>
@@ -27806,7 +27814,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" hidden="1">
       <c r="A91" t="s">
         <v>553</v>
       </c>
@@ -27834,7 +27842,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" hidden="1">
       <c r="A92" t="s">
         <v>554</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1180" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAFA8165-B8F0-43C3-9B88-7358519A216B}"/>
+  <xr:revisionPtr revIDLastSave="1181" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6633AB3-5C10-4419-9E8A-8B448F15EC55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -3565,9 +3565,11 @@
   <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}">
     <filterColumn colId="7">
       <filters>
+        <filter val="Gold Bundle"/>
         <filter val="Open House Gold Bundle"/>
         <filter val="Open House Platinum Bundle"/>
         <filter val="Open House Silver Bundle"/>
+        <filter val="Platinum Bundle"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -25995,7 +25997,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>428</v>
       </c>
@@ -26023,7 +26025,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>462</v>
       </c>
@@ -26667,7 +26669,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>426</v>
       </c>
@@ -26695,7 +26697,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>474</v>
       </c>
@@ -26723,7 +26725,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>427</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1181" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6633AB3-5C10-4419-9E8A-8B448F15EC55}"/>
+  <xr:revisionPtr revIDLastSave="1206" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E762FF-7D3C-41FA-9C7B-E380EEBCE296}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -1919,27 +1919,6 @@
     <t>Beltone RIE Digital Boost Max S 4 95-DWHC</t>
   </si>
   <si>
-    <t>Beltone Boost Max S 4 95-DWHC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone RIE Digital Boost Max S 17 95-DWHC</t>
-  </si>
-  <si>
-    <t>Beltone Boost Max S 17 95-DWHC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone RIE Digital Boost Max S 6 95-DWHC</t>
-  </si>
-  <si>
-    <t>Beltone Boost Max S 6 95-DWHC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone RIE Digital Boost Max S 9 95-DWHC</t>
-  </si>
-  <si>
-    <t>Beltone Boost Max S 9 95-DWHC Digital RIE</t>
-  </si>
-  <si>
     <t>UHCH Competitive</t>
   </si>
   <si>
@@ -1950,6 +1929,27 @@
   </si>
   <si>
     <t>Envision 9 Special</t>
+  </si>
+  <si>
+    <t>Beltone BTE Digital Boost Max S 17 95-DWHC</t>
+  </si>
+  <si>
+    <t>Beltone BTE Digital Boost Max S 6 95-DWHC</t>
+  </si>
+  <si>
+    <t>Beltone BTE Digital Boost Max S 9 95-DWHC</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 4 95-DWHC BTE Digital</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 17 95-DWHC BTE Digital</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 6 95-DWHC BTE Digital</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 9 95-DWHC BTE Digital</t>
   </si>
 </sst>
 </file>
@@ -3491,7 +3491,17 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
-  <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}"/>
+  <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Beltone Boost Max S 17 95-DWHC Digital BTE"/>
+        <filter val="Beltone Boost Max S 4 95-DWHC Digital BTE"/>
+        <filter val="Beltone Boost Max S 6 95-DWHC Digital BTE"/>
+        <filter val="Beltone Boost Max S 9 95-DWHC Digital BTE"/>
+        <filter val="Beltone Envision 4 62S-DRWC Digital RIE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V159">
     <sortCondition ref="I2:I159"/>
   </sortState>
@@ -3972,7 +3982,7 @@
         <v>61</v>
       </c>
       <c r="B7" s="171" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C7" s="172"/>
     </row>
@@ -4355,7 +4365,8 @@
   <dimension ref="A1:AF232"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
@@ -4458,7 +4469,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="12.75">
+    <row r="2" spans="1:31" ht="12.75" hidden="1">
       <c r="A2" s="37" t="s">
         <v>501</v>
       </c>
@@ -4522,7 +4533,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="12.75">
+    <row r="3" spans="1:31" ht="12.75" hidden="1">
       <c r="A3" s="37" t="s">
         <v>500</v>
       </c>
@@ -4648,7 +4659,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="12.75">
+    <row r="5" spans="1:31" ht="12.75" hidden="1">
       <c r="A5" s="37" t="s">
         <v>496</v>
       </c>
@@ -4717,7 +4728,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="12.75">
+    <row r="6" spans="1:31" ht="12.75" hidden="1">
       <c r="A6" s="37" t="s">
         <v>498</v>
       </c>
@@ -4787,7 +4798,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="12.75">
+    <row r="7" spans="1:31" ht="12.75" hidden="1">
       <c r="A7" s="37" t="s">
         <v>497</v>
       </c>
@@ -4857,7 +4868,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="12.75">
+    <row r="8" spans="1:31" ht="12.75" hidden="1">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -4926,7 +4937,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="12.75">
+    <row r="9" spans="1:31" ht="12.75" hidden="1">
       <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
@@ -4995,7 +5006,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="12.75">
+    <row r="10" spans="1:31" ht="12.75" hidden="1">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -5064,7 +5075,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="12.75">
+    <row r="11" spans="1:31" ht="12.75" hidden="1">
       <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
@@ -5133,7 +5144,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="12.75">
+    <row r="12" spans="1:31" ht="12.75" hidden="1">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -5202,7 +5213,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="12.75">
+    <row r="13" spans="1:31" ht="12.75" hidden="1">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -5271,7 +5282,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="12.75">
+    <row r="14" spans="1:31" ht="12.75" hidden="1">
       <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
@@ -5338,7 +5349,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="12.75">
+    <row r="15" spans="1:31" ht="12.75" hidden="1">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -5406,7 +5417,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="12.75">
+    <row r="16" spans="1:31" ht="12.75" hidden="1">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
@@ -5476,7 +5487,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="12.75">
+    <row r="17" spans="1:31" ht="12.75" hidden="1">
       <c r="A17" s="3" t="s">
         <v>406</v>
       </c>
@@ -5545,7 +5556,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="12.75">
+    <row r="18" spans="1:31" ht="12.75" hidden="1">
       <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
@@ -5614,7 +5625,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="12.75">
+    <row r="19" spans="1:31" ht="12.75" hidden="1">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
@@ -5683,7 +5694,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="12.75">
+    <row r="20" spans="1:31" ht="12.75" hidden="1">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -5752,7 +5763,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="12.75">
+    <row r="21" spans="1:31" ht="12.75" hidden="1">
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
@@ -5821,7 +5832,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="12.75">
+    <row r="22" spans="1:31" ht="12.75" hidden="1">
       <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
@@ -5890,7 +5901,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="12.75">
+    <row r="23" spans="1:31" ht="12.75" hidden="1">
       <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
@@ -5956,7 +5967,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="12.75">
+    <row r="24" spans="1:31" ht="12.75" hidden="1">
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
@@ -6023,7 +6034,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="12.75">
+    <row r="25" spans="1:31" ht="12.75" hidden="1">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -6091,7 +6102,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="12.75">
+    <row r="26" spans="1:31" ht="12.75" hidden="1">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -6161,7 +6172,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="12.75">
+    <row r="27" spans="1:31" ht="12.75" hidden="1">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -6231,7 +6242,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="12.75">
+    <row r="28" spans="1:31" ht="12.75" hidden="1">
       <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
@@ -6300,7 +6311,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="12.75">
+    <row r="29" spans="1:31" ht="12.75" hidden="1">
       <c r="A29" s="3" t="s">
         <v>19</v>
       </c>
@@ -6369,7 +6380,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="12.75">
+    <row r="30" spans="1:31" ht="12.75" hidden="1">
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
@@ -6438,7 +6449,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="12.75">
+    <row r="31" spans="1:31" ht="12.75" hidden="1">
       <c r="A31" s="3" t="s">
         <v>21</v>
       </c>
@@ -6507,7 +6518,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="12.75">
+    <row r="32" spans="1:31" ht="12.75" hidden="1">
       <c r="A32" s="3" t="s">
         <v>22</v>
       </c>
@@ -6574,7 +6585,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="12.75">
+    <row r="33" spans="1:31" ht="12.75" hidden="1">
       <c r="A33" s="3" t="s">
         <v>23</v>
       </c>
@@ -6641,7 +6652,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="12.75">
+    <row r="34" spans="1:31" ht="12.75" hidden="1">
       <c r="A34" s="3" t="s">
         <v>24</v>
       </c>
@@ -6712,8 +6723,8 @@
       <c r="A35" s="111" t="s">
         <v>617</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>618</v>
+      <c r="B35" s="142" t="s">
+        <v>625</v>
       </c>
       <c r="C35" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -6774,7 +6785,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="12.75">
+    <row r="36" spans="1:31" ht="12.75" hidden="1">
       <c r="A36" s="37" t="s">
         <v>500</v>
       </c>
@@ -6847,7 +6858,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="12.75">
+    <row r="37" spans="1:31" ht="12.75" hidden="1">
       <c r="A37" s="3" t="s">
         <v>413</v>
       </c>
@@ -6919,7 +6930,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="12.75">
+    <row r="38" spans="1:31" ht="12.75" hidden="1">
       <c r="A38" s="3" t="s">
         <v>414</v>
       </c>
@@ -6991,7 +7002,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="12.75">
+    <row r="39" spans="1:31" ht="12.75" hidden="1">
       <c r="A39" s="3" t="s">
         <v>415</v>
       </c>
@@ -7063,7 +7074,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="12.75">
+    <row r="40" spans="1:31" ht="12.75" hidden="1">
       <c r="A40" s="37" t="s">
         <v>496</v>
       </c>
@@ -7135,7 +7146,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="12.75">
+    <row r="41" spans="1:31" ht="12.75" hidden="1">
       <c r="A41" s="37" t="s">
         <v>498</v>
       </c>
@@ -7207,7 +7218,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="12.75">
+    <row r="42" spans="1:31" ht="12.75" hidden="1">
       <c r="A42" s="37" t="s">
         <v>497</v>
       </c>
@@ -7281,10 +7292,10 @@
     </row>
     <row r="43" spans="1:31" ht="12.75">
       <c r="A43" s="111" t="s">
-        <v>619</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
+      </c>
+      <c r="B43" s="142" t="s">
+        <v>626</v>
       </c>
       <c r="C43" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7350,10 +7361,10 @@
     </row>
     <row r="44" spans="1:31" ht="12.75">
       <c r="A44" s="111" t="s">
-        <v>621</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
+      </c>
+      <c r="B44" s="142" t="s">
+        <v>627</v>
       </c>
       <c r="C44" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7419,10 +7430,10 @@
     </row>
     <row r="45" spans="1:31" ht="12.75">
       <c r="A45" s="111" t="s">
-        <v>623</v>
-      </c>
-      <c r="B45" s="3" t="s">
         <v>624</v>
+      </c>
+      <c r="B45" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="C45" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7486,7 +7497,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="12.75">
+    <row r="46" spans="1:31" ht="12.75" hidden="1">
       <c r="A46" s="142" t="s">
         <v>496</v>
       </c>
@@ -7515,7 +7526,7 @@
         <v>9450</v>
       </c>
       <c r="I46" s="145" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="J46" s="2">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -7558,7 +7569,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="12.75">
+    <row r="47" spans="1:31" ht="12.75" hidden="1">
       <c r="A47" s="142" t="s">
         <v>498</v>
       </c>
@@ -7587,7 +7598,7 @@
         <v>7050</v>
       </c>
       <c r="I47" s="145" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="J47" s="2">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -7630,7 +7641,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="12.75">
+    <row r="48" spans="1:31" ht="12.75" hidden="1">
       <c r="A48" s="142" t="s">
         <v>497</v>
       </c>
@@ -7659,7 +7670,7 @@
         <v>8350</v>
       </c>
       <c r="I48" s="145" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="J48" s="2">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -7702,7 +7713,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="12.75">
+    <row r="49" spans="1:32" ht="12.75" hidden="1">
       <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
@@ -7775,7 +7786,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="12.75">
+    <row r="50" spans="1:32" ht="12.75" hidden="1">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7848,7 +7859,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="12.75">
+    <row r="51" spans="1:32" ht="12.75" hidden="1">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -7921,7 +7932,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="12.75">
+    <row r="52" spans="1:32" ht="12.75" hidden="1">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -7994,7 +8005,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="12.75">
+    <row r="53" spans="1:32" ht="12.75" hidden="1">
       <c r="A53" s="3" t="s">
         <v>55</v>
       </c>
@@ -8067,7 +8078,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="12.75">
+    <row r="54" spans="1:32" ht="12.75" hidden="1">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8140,7 +8151,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="12.75">
+    <row r="55" spans="1:32" ht="12.75" hidden="1">
       <c r="A55" s="37" t="s">
         <v>501</v>
       </c>
@@ -8213,7 +8224,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="12.75">
+    <row r="56" spans="1:32" ht="12.75" hidden="1">
       <c r="A56" s="37" t="s">
         <v>500</v>
       </c>
@@ -8359,7 +8370,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:32" ht="12.75">
+    <row r="58" spans="1:32" ht="12.75" hidden="1">
       <c r="A58" s="37" t="s">
         <v>496</v>
       </c>
@@ -8432,7 +8443,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:32" ht="12.75">
+    <row r="59" spans="1:32" ht="12.75" hidden="1">
       <c r="A59" s="37" t="s">
         <v>498</v>
       </c>
@@ -8505,7 +8516,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:32" ht="12.75">
+    <row r="60" spans="1:32" ht="12.75" hidden="1">
       <c r="A60" s="37" t="s">
         <v>497</v>
       </c>
@@ -8578,7 +8589,7 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:32" ht="12.75">
+    <row r="61" spans="1:32" ht="12.75" hidden="1">
       <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
@@ -8651,7 +8662,7 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:32" ht="12.75">
+    <row r="62" spans="1:32" ht="12.75" hidden="1">
       <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
@@ -8723,7 +8734,7 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:32" ht="12.75">
+    <row r="63" spans="1:32" ht="12.75" hidden="1">
       <c r="A63" s="3" t="s">
         <v>29</v>
       </c>
@@ -8795,7 +8806,7 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:32" ht="12.75">
+    <row r="64" spans="1:32" ht="12.75" hidden="1">
       <c r="A64" s="3" t="s">
         <v>30</v>
       </c>
@@ -8868,7 +8879,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="12.75">
+    <row r="65" spans="1:31" ht="12.75" hidden="1">
       <c r="A65" s="3" t="s">
         <v>31</v>
       </c>
@@ -8941,7 +8952,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="12.75">
+    <row r="66" spans="1:31" ht="12.75" hidden="1">
       <c r="A66" s="3" t="s">
         <v>32</v>
       </c>
@@ -9014,7 +9025,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="12.75">
+    <row r="67" spans="1:31" ht="12.75" hidden="1">
       <c r="A67" s="3" t="s">
         <v>38</v>
       </c>
@@ -9085,7 +9096,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="12.75">
+    <row r="68" spans="1:31" ht="12.75" hidden="1">
       <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
@@ -9156,7 +9167,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="12.75">
+    <row r="69" spans="1:31" ht="12.75" hidden="1">
       <c r="A69" s="3" t="s">
         <v>44</v>
       </c>
@@ -9229,7 +9240,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="12.75">
+    <row r="70" spans="1:31" ht="12.75" hidden="1">
       <c r="A70" s="3" t="s">
         <v>406</v>
       </c>
@@ -9302,7 +9313,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="12.75">
+    <row r="71" spans="1:31" ht="12.75" hidden="1">
       <c r="A71" s="3" t="s">
         <v>45</v>
       </c>
@@ -9375,7 +9386,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="12.75">
+    <row r="72" spans="1:31" ht="12.75" hidden="1">
       <c r="A72" s="3" t="s">
         <v>33</v>
       </c>
@@ -9448,7 +9459,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="12.75">
+    <row r="73" spans="1:31" ht="12.75" hidden="1">
       <c r="A73" s="3" t="s">
         <v>34</v>
       </c>
@@ -9521,7 +9532,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="12.75">
+    <row r="74" spans="1:31" ht="12.75" hidden="1">
       <c r="A74" s="3" t="s">
         <v>35</v>
       </c>
@@ -9594,7 +9605,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="12.75">
+    <row r="75" spans="1:31" ht="12.75" hidden="1">
       <c r="A75" s="3" t="s">
         <v>36</v>
       </c>
@@ -9667,7 +9678,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="12.75">
+    <row r="76" spans="1:31" ht="12.75" hidden="1">
       <c r="A76" s="3" t="s">
         <v>37</v>
       </c>
@@ -9738,7 +9749,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="12.75">
+    <row r="77" spans="1:31" ht="12.75" hidden="1">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -9809,7 +9820,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="12.75">
+    <row r="78" spans="1:31" ht="12.75" hidden="1">
       <c r="A78" s="3" t="s">
         <v>41</v>
       </c>
@@ -9880,7 +9891,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="12.75">
+    <row r="79" spans="1:31" ht="12.75" hidden="1">
       <c r="A79" s="3" t="s">
         <v>25</v>
       </c>
@@ -9953,7 +9964,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="12.75">
+    <row r="80" spans="1:31" ht="12.75" hidden="1">
       <c r="A80" s="3" t="s">
         <v>27</v>
       </c>
@@ -10026,7 +10037,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="12.75">
+    <row r="81" spans="1:31" ht="12.75" hidden="1">
       <c r="A81" s="3" t="s">
         <v>15</v>
       </c>
@@ -10099,7 +10110,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="12.75">
+    <row r="82" spans="1:31" ht="12.75" hidden="1">
       <c r="A82" s="3" t="s">
         <v>19</v>
       </c>
@@ -10172,7 +10183,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="12.75">
+    <row r="83" spans="1:31" ht="12.75" hidden="1">
       <c r="A83" s="3" t="s">
         <v>20</v>
       </c>
@@ -10245,7 +10256,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="12.75">
+    <row r="84" spans="1:31" ht="12.75" hidden="1">
       <c r="A84" s="3" t="s">
         <v>21</v>
       </c>
@@ -10318,7 +10329,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="12.75">
+    <row r="85" spans="1:31" ht="12.75" hidden="1">
       <c r="A85" s="3" t="s">
         <v>22</v>
       </c>
@@ -10389,7 +10400,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="12.75">
+    <row r="86" spans="1:31" ht="12.75" hidden="1">
       <c r="A86" s="3" t="s">
         <v>23</v>
       </c>
@@ -10460,7 +10471,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="12.75">
+    <row r="87" spans="1:31" ht="12.75" hidden="1">
       <c r="A87" s="3" t="s">
         <v>24</v>
       </c>
@@ -10531,7 +10542,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="12.75">
+    <row r="88" spans="1:31" ht="12.75" hidden="1">
       <c r="A88" s="3" t="s">
         <v>413</v>
       </c>
@@ -10604,7 +10615,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="12.75">
+    <row r="89" spans="1:31" ht="12.75" hidden="1">
       <c r="A89" s="3" t="s">
         <v>414</v>
       </c>
@@ -10677,7 +10688,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="12.75">
+    <row r="90" spans="1:31" ht="12.75" hidden="1">
       <c r="A90" s="3" t="s">
         <v>415</v>
       </c>
@@ -10752,10 +10763,10 @@
     </row>
     <row r="91" spans="1:31" ht="12.75">
       <c r="A91" s="111" t="s">
-        <v>619</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
+      </c>
+      <c r="B91" s="142" t="s">
+        <v>626</v>
       </c>
       <c r="C91" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10824,8 +10835,8 @@
       <c r="A92" s="111" t="s">
         <v>617</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>618</v>
+      <c r="B92" s="142" t="s">
+        <v>625</v>
       </c>
       <c r="C92" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10886,10 +10897,10 @@
     </row>
     <row r="93" spans="1:31" ht="12.75">
       <c r="A93" s="111" t="s">
-        <v>623</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
+      </c>
+      <c r="B93" s="142" t="s">
+        <v>627</v>
       </c>
       <c r="C93" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10956,10 +10967,10 @@
     </row>
     <row r="94" spans="1:31" ht="12.75">
       <c r="A94" s="111" t="s">
-        <v>621</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
+      </c>
+      <c r="B94" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="C94" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -11024,7 +11035,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="12.75">
+    <row r="95" spans="1:31" ht="12.75" hidden="1">
       <c r="A95" s="37" t="s">
         <v>500</v>
       </c>
@@ -11097,7 +11108,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="12.75">
+    <row r="96" spans="1:31" ht="12.75" hidden="1">
       <c r="A96" s="3" t="s">
         <v>413</v>
       </c>
@@ -11169,7 +11180,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="12.75">
+    <row r="97" spans="1:31" ht="12.75" hidden="1">
       <c r="A97" s="3" t="s">
         <v>414</v>
       </c>
@@ -11241,7 +11252,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="12.75">
+    <row r="98" spans="1:31" ht="12.75" hidden="1">
       <c r="A98" s="3" t="s">
         <v>415</v>
       </c>
@@ -11313,7 +11324,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="12.75">
+    <row r="99" spans="1:31" ht="12.75" hidden="1">
       <c r="A99" s="37" t="s">
         <v>500</v>
       </c>
@@ -11385,7 +11396,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="12.75">
+    <row r="100" spans="1:31" ht="12.75" hidden="1">
       <c r="A100" s="3" t="s">
         <v>413</v>
       </c>
@@ -11457,7 +11468,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="12.75">
+    <row r="101" spans="1:31" ht="12.75" hidden="1">
       <c r="A101" s="3" t="s">
         <v>414</v>
       </c>
@@ -11529,7 +11540,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="12.75">
+    <row r="102" spans="1:31" ht="12.75" hidden="1">
       <c r="A102" s="3" t="s">
         <v>415</v>
       </c>
@@ -11602,7 +11613,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="12.75">
+    <row r="103" spans="1:31" ht="12.75" hidden="1">
       <c r="A103" s="37" t="s">
         <v>500</v>
       </c>
@@ -11674,7 +11685,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="12.75">
+    <row r="104" spans="1:31" ht="12.75" hidden="1">
       <c r="A104" s="3" t="s">
         <v>413</v>
       </c>
@@ -11746,7 +11757,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="12.75">
+    <row r="105" spans="1:31" ht="12.75" hidden="1">
       <c r="A105" s="3" t="s">
         <v>414</v>
       </c>
@@ -11818,7 +11829,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="12.75">
+    <row r="106" spans="1:31" ht="12.75" hidden="1">
       <c r="A106" s="3" t="s">
         <v>415</v>
       </c>
@@ -11890,7 +11901,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="12.75">
+    <row r="107" spans="1:31" ht="12.75" hidden="1">
       <c r="A107" s="37" t="s">
         <v>500</v>
       </c>
@@ -11962,7 +11973,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="12.75">
+    <row r="108" spans="1:31" ht="12.75" hidden="1">
       <c r="A108" s="3" t="s">
         <v>413</v>
       </c>
@@ -12034,7 +12045,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="12.75">
+    <row r="109" spans="1:31" ht="12.75" hidden="1">
       <c r="A109" s="3" t="s">
         <v>414</v>
       </c>
@@ -12106,7 +12117,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="12.75">
+    <row r="110" spans="1:31" ht="12.75" hidden="1">
       <c r="A110" s="3" t="s">
         <v>415</v>
       </c>
@@ -12178,7 +12189,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="12.75">
+    <row r="111" spans="1:31" ht="12.75" hidden="1">
       <c r="A111" s="3" t="s">
         <v>51</v>
       </c>
@@ -12251,7 +12262,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="12.75">
+    <row r="112" spans="1:31" ht="12.75" hidden="1">
       <c r="A112" s="3" t="s">
         <v>52</v>
       </c>
@@ -12324,7 +12335,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="12.75">
+    <row r="113" spans="1:31" ht="12.75" hidden="1">
       <c r="A113" s="3" t="s">
         <v>53</v>
       </c>
@@ -12397,7 +12408,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="12.75">
+    <row r="114" spans="1:31" ht="12.75" hidden="1">
       <c r="A114" s="3" t="s">
         <v>54</v>
       </c>
@@ -12470,7 +12481,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="12.75">
+    <row r="115" spans="1:31" ht="12.75" hidden="1">
       <c r="A115" s="3" t="s">
         <v>55</v>
       </c>
@@ -12543,7 +12554,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="12.75">
+    <row r="116" spans="1:31" ht="12.75" hidden="1">
       <c r="A116" s="3" t="s">
         <v>56</v>
       </c>
@@ -12616,7 +12627,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.75">
+    <row r="117" spans="1:31" ht="12.75" hidden="1">
       <c r="A117" s="37" t="s">
         <v>496</v>
       </c>
@@ -12689,7 +12700,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.75">
+    <row r="118" spans="1:31" ht="12.75" hidden="1">
       <c r="A118" s="37" t="s">
         <v>498</v>
       </c>
@@ -12762,7 +12773,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.75">
+    <row r="119" spans="1:31" ht="12.75" hidden="1">
       <c r="A119" s="37" t="s">
         <v>497</v>
       </c>
@@ -12835,7 +12846,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="12.75">
+    <row r="120" spans="1:31" ht="12.75" hidden="1">
       <c r="A120" s="3" t="s">
         <v>413</v>
       </c>
@@ -12908,7 +12919,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="12.75">
+    <row r="121" spans="1:31" ht="12.75" hidden="1">
       <c r="A121" s="3" t="s">
         <v>414</v>
       </c>
@@ -12981,7 +12992,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="12.75">
+    <row r="122" spans="1:31" ht="12.75" hidden="1">
       <c r="A122" s="3" t="s">
         <v>415</v>
       </c>
@@ -13057,10 +13068,10 @@
     </row>
     <row r="123" spans="1:31" ht="12.75">
       <c r="A123" s="111" t="s">
-        <v>619</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
+      </c>
+      <c r="B123" s="142" t="s">
+        <v>626</v>
       </c>
       <c r="C123" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13130,10 +13141,10 @@
     </row>
     <row r="124" spans="1:31" ht="12.75">
       <c r="A124" s="111" t="s">
-        <v>621</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
+      </c>
+      <c r="B124" s="142" t="s">
+        <v>627</v>
       </c>
       <c r="C124" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13203,10 +13214,10 @@
     </row>
     <row r="125" spans="1:31" ht="12.75">
       <c r="A125" s="111" t="s">
-        <v>623</v>
-      </c>
-      <c r="B125" s="3" t="s">
         <v>624</v>
+      </c>
+      <c r="B125" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="C125" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13274,7 +13285,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.75">
+    <row r="126" spans="1:31" ht="12.75" hidden="1">
       <c r="A126" s="37" t="s">
         <v>500</v>
       </c>
@@ -13347,7 +13358,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="12.75">
+    <row r="127" spans="1:31" ht="12.75" hidden="1">
       <c r="A127" s="3" t="s">
         <v>413</v>
       </c>
@@ -13420,7 +13431,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="12.75">
+    <row r="128" spans="1:31" ht="12.75" hidden="1">
       <c r="A128" s="3" t="s">
         <v>414</v>
       </c>
@@ -13493,7 +13504,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="12.75">
+    <row r="129" spans="1:31" ht="12.75" hidden="1">
       <c r="A129" s="3" t="s">
         <v>415</v>
       </c>
@@ -13566,7 +13577,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="12.75">
+    <row r="130" spans="1:31" ht="12.75" hidden="1">
       <c r="A130" s="37" t="s">
         <v>500</v>
       </c>
@@ -13639,7 +13650,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="12.75">
+    <row r="131" spans="1:31" ht="12.75" hidden="1">
       <c r="A131" s="3" t="s">
         <v>413</v>
       </c>
@@ -13712,7 +13723,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="12.75">
+    <row r="132" spans="1:31" ht="12.75" hidden="1">
       <c r="A132" s="3" t="s">
         <v>414</v>
       </c>
@@ -13785,7 +13796,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="12.75">
+    <row r="133" spans="1:31" ht="12.75" hidden="1">
       <c r="A133" s="3" t="s">
         <v>415</v>
       </c>
@@ -13858,7 +13869,7 @@
       <c r="AD133"/>
       <c r="AE133"/>
     </row>
-    <row r="134" spans="1:31" ht="12.75">
+    <row r="134" spans="1:31" ht="12.75" hidden="1">
       <c r="A134" s="37" t="s">
         <v>496</v>
       </c>
@@ -13931,7 +13942,7 @@
       <c r="AD134"/>
       <c r="AE134"/>
     </row>
-    <row r="135" spans="1:31" ht="12.75">
+    <row r="135" spans="1:31" ht="12.75" hidden="1">
       <c r="A135" s="37" t="s">
         <v>498</v>
       </c>
@@ -14004,7 +14015,7 @@
       <c r="AD135"/>
       <c r="AE135"/>
     </row>
-    <row r="136" spans="1:31" ht="12.75">
+    <row r="136" spans="1:31" ht="12.75" hidden="1">
       <c r="A136" s="37" t="s">
         <v>497</v>
       </c>
@@ -14079,10 +14090,10 @@
     </row>
     <row r="137" spans="1:31" ht="12.75">
       <c r="A137" s="111" t="s">
-        <v>619</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
+      </c>
+      <c r="B137" s="142" t="s">
+        <v>626</v>
       </c>
       <c r="C137" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14152,10 +14163,10 @@
     </row>
     <row r="138" spans="1:31" ht="12.75">
       <c r="A138" s="111" t="s">
-        <v>621</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
+      </c>
+      <c r="B138" s="142" t="s">
+        <v>627</v>
       </c>
       <c r="C138" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14225,10 +14236,10 @@
     </row>
     <row r="139" spans="1:31" ht="12.75">
       <c r="A139" s="90" t="s">
-        <v>623</v>
-      </c>
-      <c r="B139" s="3" t="s">
         <v>624</v>
+      </c>
+      <c r="B139" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="C139" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14295,7 +14306,7 @@
       <c r="AC139" s="2"/>
       <c r="AD139" s="2"/>
     </row>
-    <row r="140" spans="1:31" ht="12.75">
+    <row r="140" spans="1:31" ht="12.75" hidden="1">
       <c r="A140" s="114" t="s">
         <v>500</v>
       </c>
@@ -14367,7 +14378,7 @@
       <c r="AC140" s="2"/>
       <c r="AD140" s="2"/>
     </row>
-    <row r="141" spans="1:31" ht="12.75">
+    <row r="141" spans="1:31" ht="12.75" hidden="1">
       <c r="A141" s="112" t="s">
         <v>413</v>
       </c>
@@ -14439,7 +14450,7 @@
       <c r="AC141" s="2"/>
       <c r="AD141" s="8"/>
     </row>
-    <row r="142" spans="1:31" ht="12.75">
+    <row r="142" spans="1:31" ht="12.75" hidden="1">
       <c r="A142" s="112" t="s">
         <v>414</v>
       </c>
@@ -14511,7 +14522,7 @@
       <c r="AC142" s="2"/>
       <c r="AD142" s="8"/>
     </row>
-    <row r="143" spans="1:31" ht="12.75">
+    <row r="143" spans="1:31" ht="12.75" hidden="1">
       <c r="A143" s="112" t="s">
         <v>415</v>
       </c>
@@ -14583,7 +14594,7 @@
       <c r="AC143" s="2"/>
       <c r="AD143" s="8"/>
     </row>
-    <row r="144" spans="1:31" ht="12.75">
+    <row r="144" spans="1:31" ht="12.75" hidden="1">
       <c r="A144" s="114" t="s">
         <v>500</v>
       </c>
@@ -14655,7 +14666,7 @@
       <c r="AC144" s="2"/>
       <c r="AD144" s="8"/>
     </row>
-    <row r="145" spans="1:31" ht="12.75">
+    <row r="145" spans="1:31" ht="12.75" hidden="1">
       <c r="A145" s="112" t="s">
         <v>413</v>
       </c>
@@ -14728,7 +14739,7 @@
       <c r="AD145" s="8"/>
       <c r="AE145" s="25"/>
     </row>
-    <row r="146" spans="1:31" ht="12.75">
+    <row r="146" spans="1:31" ht="12.75" hidden="1">
       <c r="A146" s="112" t="s">
         <v>414</v>
       </c>
@@ -14801,7 +14812,7 @@
       <c r="AD146" s="12"/>
       <c r="AE146" s="25"/>
     </row>
-    <row r="147" spans="1:31" ht="12.75">
+    <row r="147" spans="1:31" ht="12.75" hidden="1">
       <c r="A147" s="112" t="s">
         <v>415</v>
       </c>
@@ -14874,7 +14885,7 @@
       <c r="AD147" s="12"/>
       <c r="AE147" s="25"/>
     </row>
-    <row r="148" spans="1:31" ht="12.75">
+    <row r="148" spans="1:31" ht="12.75" hidden="1">
       <c r="A148" s="113" t="s">
         <v>500</v>
       </c>
@@ -14903,7 +14914,7 @@
         <v>3500</v>
       </c>
       <c r="I148" s="123" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="J148" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -14946,7 +14957,7 @@
       <c r="AC148" s="2"/>
       <c r="AD148" s="12"/>
     </row>
-    <row r="149" spans="1:31" ht="12.75">
+    <row r="149" spans="1:31" ht="12.75" hidden="1">
       <c r="A149" s="113" t="s">
         <v>413</v>
       </c>
@@ -14975,7 +14986,7 @@
         <v>9450</v>
       </c>
       <c r="I149" s="123" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="J149" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -15018,7 +15029,7 @@
       <c r="AC149" s="2"/>
       <c r="AD149" s="12"/>
     </row>
-    <row r="150" spans="1:31" ht="12.75">
+    <row r="150" spans="1:31" ht="12.75" hidden="1">
       <c r="A150" s="113" t="s">
         <v>414</v>
       </c>
@@ -15047,7 +15058,7 @@
         <v>7050</v>
       </c>
       <c r="I150" s="123" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="J150" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -15090,7 +15101,7 @@
       <c r="AC150" s="2"/>
       <c r="AD150" s="12"/>
     </row>
-    <row r="151" spans="1:31" ht="12.75">
+    <row r="151" spans="1:31" ht="12.75" hidden="1">
       <c r="A151" s="113" t="s">
         <v>415</v>
       </c>
@@ -15119,7 +15130,7 @@
         <v>8350</v>
       </c>
       <c r="I151" s="123" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="J151" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -15162,7 +15173,7 @@
       <c r="AC151" s="2"/>
       <c r="AD151" s="12"/>
     </row>
-    <row r="152" spans="1:31" ht="12.75">
+    <row r="152" spans="1:31" ht="12.75" hidden="1">
       <c r="A152" s="154" t="s">
         <v>500</v>
       </c>
@@ -15234,7 +15245,7 @@
       <c r="AC152" s="2"/>
       <c r="AD152" s="8"/>
     </row>
-    <row r="153" spans="1:31" ht="12.75">
+    <row r="153" spans="1:31" ht="12.75" hidden="1">
       <c r="A153" s="3" t="s">
         <v>413</v>
       </c>
@@ -15306,7 +15317,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="12.75">
+    <row r="154" spans="1:31" ht="12.75" hidden="1">
       <c r="A154" s="3" t="s">
         <v>414</v>
       </c>
@@ -15378,7 +15389,7 @@
       <c r="AD154"/>
       <c r="AE154"/>
     </row>
-    <row r="155" spans="1:31" ht="12.75">
+    <row r="155" spans="1:31" ht="12.75" hidden="1">
       <c r="A155" s="3" t="s">
         <v>415</v>
       </c>
@@ -15450,7 +15461,7 @@
       <c r="AD155"/>
       <c r="AE155"/>
     </row>
-    <row r="156" spans="1:31" ht="12.75">
+    <row r="156" spans="1:31" ht="12.75" hidden="1">
       <c r="A156" s="37" t="s">
         <v>500</v>
       </c>
@@ -15522,7 +15533,7 @@
       <c r="AD156"/>
       <c r="AE156"/>
     </row>
-    <row r="157" spans="1:31" ht="12.75">
+    <row r="157" spans="1:31" ht="12.75" hidden="1">
       <c r="A157" s="3" t="s">
         <v>413</v>
       </c>
@@ -15594,7 +15605,7 @@
       <c r="AD157"/>
       <c r="AE157"/>
     </row>
-    <row r="158" spans="1:31" ht="12.75">
+    <row r="158" spans="1:31" ht="12.75" hidden="1">
       <c r="A158" s="3" t="s">
         <v>414</v>
       </c>
@@ -15667,7 +15678,7 @@
       <c r="AD158"/>
       <c r="AE158"/>
     </row>
-    <row r="159" spans="1:31" ht="12.75">
+    <row r="159" spans="1:31" ht="12.75" hidden="1">
       <c r="A159" s="3" t="s">
         <v>415</v>
       </c>
@@ -28104,7 +28115,7 @@
     <row r="3" spans="1:5">
       <c r="A3" t="str" cm="1">
         <f t="array" ref="A3:A48">_xlfn.UNIQUE(_xlfn._xlws.SORT((HearingAids[haModel])))</f>
-        <v>Beltone BTE Digital Boost Ultra 17 86DWHT</v>
+        <v>Beltone BTE Digital Boost Max S 17 95-DWHC</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3:B22">_xlfn.UNIQUE(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(HearingAids[Discount Type 2], HearingAids[Discount Type 2]&lt;&gt;"")))</f>
@@ -28116,7 +28127,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="str">
-        <v>Beltone BTE Digital Boost Ultra 17 95DWT</v>
+        <v>Beltone BTE Digital Boost Max S 6 95-DWHC</v>
       </c>
       <c r="B4" t="str">
         <v>Amplifon Competitive</v>
@@ -28127,7 +28138,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="str">
-        <v>Beltone BTE Digital Boost Ultra 6 86DWHT</v>
+        <v>Beltone BTE Digital Boost Max S 9 95-DWHC</v>
       </c>
       <c r="B5" t="str">
         <v>Early Lease Upgrade</v>
@@ -28138,7 +28149,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="str">
-        <v>Beltone BTE Digital Boost Ultra 6 95DWT</v>
+        <v>Beltone BTE Digital Boost Ultra 17 86DWHT</v>
       </c>
       <c r="B6" t="str">
         <v>Envision 17 Special</v>
@@ -28149,7 +28160,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="str">
-        <v>Beltone BTE Digital Boost Ultra 9 86DWHT</v>
+        <v>Beltone BTE Digital Boost Ultra 17 95DWT</v>
       </c>
       <c r="B7" t="str">
         <v>Envision 6 Special</v>
@@ -28160,7 +28171,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="str">
-        <v>Beltone BTE Digital Boost Ultra 9 95DWT</v>
+        <v>Beltone BTE Digital Boost Ultra 6 86DWHT</v>
       </c>
       <c r="B8" t="str">
         <v>Envision 9 Special</v>
@@ -28168,7 +28179,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="str">
-        <v>Beltone BTE Digital Rely 2 66DW</v>
+        <v>Beltone BTE Digital Boost Ultra 6 95DWT</v>
       </c>
       <c r="B9" t="str">
         <v>Fast Funding</v>
@@ -28176,7 +28187,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="str">
-        <v>Beltone BTE Digital Rely 2 76DW</v>
+        <v>Beltone BTE Digital Boost Ultra 9 86DWHT</v>
       </c>
       <c r="B10" t="str">
         <v>GHB Competitive</v>
@@ -28184,7 +28195,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="str">
-        <v>Beltone BTE Digital Rely 2 86DWH</v>
+        <v>Beltone BTE Digital Boost Ultra 9 95DWT</v>
       </c>
       <c r="B11" t="str">
         <v>HCS Competitive</v>
@@ -28192,7 +28203,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="str">
-        <v>Beltone BTE Digital Rely 2 95DW</v>
+        <v>Beltone BTE Digital Rely 2 66DW</v>
       </c>
       <c r="B12" t="str">
         <v>HearUSA Competitive</v>
@@ -28200,7 +28211,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="str">
-        <v>Beltone BTE Digital Rely 3 66DW</v>
+        <v>Beltone BTE Digital Rely 2 76DW</v>
       </c>
       <c r="B13" t="str">
         <v>Humana</v>
@@ -28208,7 +28219,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="str">
-        <v>Beltone BTE Digital Rely 3 76DW</v>
+        <v>Beltone BTE Digital Rely 2 86DWH</v>
       </c>
       <c r="B14" t="str">
         <v>Marketing Offer</v>
@@ -28216,7 +28227,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="str">
-        <v>Beltone BTE Digital Rely 3 86DWH</v>
+        <v>Beltone BTE Digital Rely 2 95DW</v>
       </c>
       <c r="B15" t="str">
         <v>Martins Point Competitive</v>
@@ -28224,7 +28235,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="str">
-        <v>Beltone BTE Digital Rely 3 95DW</v>
+        <v>Beltone BTE Digital Rely 3 66DW</v>
       </c>
       <c r="B16" t="str">
         <v>Nations Hearing Competitive</v>
@@ -28232,7 +28243,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="str">
-        <v>Beltone BTE Digital Rely 4 66DW</v>
+        <v>Beltone BTE Digital Rely 3 76DW</v>
       </c>
       <c r="B17" t="str">
         <v>Open House Special</v>
@@ -28240,7 +28251,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="str">
-        <v>Beltone BTE Digital Rely 4 76DW</v>
+        <v>Beltone BTE Digital Rely 3 86DWH</v>
       </c>
       <c r="B18" t="str">
         <v>Tri-Care</v>
@@ -28248,7 +28259,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="str">
-        <v>Beltone BTE Digital Rely 4 86DWH</v>
+        <v>Beltone BTE Digital Rely 3 95DW</v>
       </c>
       <c r="B19" t="str">
         <v>TruHearing Competitive</v>
@@ -28256,7 +28267,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="str">
-        <v>Beltone BTE Digital Rely 4 95DW</v>
+        <v>Beltone BTE Digital Rely 4 66DW</v>
       </c>
       <c r="B20" t="str">
         <v>UHCH Competitive</v>
@@ -28264,7 +28275,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="str">
-        <v>Beltone CIC Digital Rely 3</v>
+        <v>Beltone BTE Digital Rely 4 76DW</v>
       </c>
       <c r="B21" t="str">
         <v>Veterans Discount</v>
@@ -28272,7 +28283,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="str">
-        <v>Beltone CIC Digital Rely 4</v>
+        <v>Beltone BTE Digital Rely 4 86DWH</v>
       </c>
       <c r="B22" t="str">
         <v>WellCare Competitive</v>
@@ -28280,52 +28291,52 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="str">
-        <v>Beltone ITC Digital Rely 2</v>
+        <v>Beltone BTE Digital Rely 4 95DW</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="str">
-        <v>Beltone ITC Digital Rely 3</v>
+        <v>Beltone CIC Digital Rely 3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="str">
-        <v>Beltone ITC Digital Rely 4</v>
+        <v>Beltone CIC Digital Rely 4</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="str">
-        <v>Beltone ITE Digital Rely 2</v>
+        <v>Beltone ITC Digital Rely 2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="str">
-        <v>Beltone ITE Digital Rely 3</v>
+        <v>Beltone ITC Digital Rely 3</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="str">
-        <v>Beltone ITE Digital Rely 4</v>
+        <v>Beltone ITC Digital Rely 4</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="str">
-        <v>Beltone RIE Digital Boost Max S 17 95-DWHC</v>
+        <v>Beltone ITE Digital Rely 2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="str">
-        <v>Beltone RIE Digital Boost Max S 4 95-DWHC</v>
+        <v>Beltone ITE Digital Rely 3</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="str">
-        <v>Beltone RIE Digital Boost Max S 6 95-DWHC</v>
+        <v>Beltone ITE Digital Rely 4</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="str">
-        <v>Beltone RIE Digital Boost Max S 9 95-DWHC</v>
+        <v>Beltone RIE Digital Boost Max S 4 95-DWHC</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1206" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E762FF-7D3C-41FA-9C7B-E380EEBCE296}"/>
+  <xr:revisionPtr revIDLastSave="1213" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42CB9F7B-7005-4F02-8742-7462BB1C99C4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -1916,9 +1916,6 @@
     <t>MO-REC-SF3-MP4</t>
   </si>
   <si>
-    <t>Beltone RIE Digital Boost Max S 4 95-DWHC</t>
-  </si>
-  <si>
     <t>UHCH Competitive</t>
   </si>
   <si>
@@ -1950,6 +1947,9 @@
   </si>
   <si>
     <t>Beltone Boost Max S 9 95-DWHC BTE Digital</t>
+  </si>
+  <si>
+    <t>Beltone BTE Digital Boost Max S 4 95-DWHC</t>
   </si>
 </sst>
 </file>
@@ -2784,6 +2784,86 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3396,86 +3476,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3490,15 +3490,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
   <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Beltone Boost Max S 17 95-DWHC Digital BTE"/>
-        <filter val="Beltone Boost Max S 4 95-DWHC Digital BTE"/>
-        <filter val="Beltone Boost Max S 6 95-DWHC Digital BTE"/>
-        <filter val="Beltone Boost Max S 9 95-DWHC Digital BTE"/>
-        <filter val="Beltone Envision 4 62S-DRWC Digital RIE"/>
+        <filter val="Beltone Boost Max S 17 95-DWHC BTE Digital"/>
+        <filter val="Beltone Boost Max S 4 95-DWHC BTE Digital"/>
+        <filter val="Beltone Boost Max S 6 95-DWHC BTE Digital"/>
+        <filter val="Beltone Boost Max S 9 95-DWHC BTE Digital"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3506,72 +3505,72 @@
     <sortCondition ref="I2:I159"/>
   </sortState>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A09E4D62-1B60-46F0-8D10-9D2989A1E1DD}" name="haModel" dataDxfId="51"/>
-    <tableColumn id="15" xr3:uid="{965DA40D-EBE9-42CF-B56F-A6A77EF637F0}" name="haDescription" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{130CAF40-E0C6-4E3E-B004-85850140B916}" name="BiNuralMSRP w/Charger" dataDxfId="49">
+    <tableColumn id="1" xr3:uid="{A09E4D62-1B60-46F0-8D10-9D2989A1E1DD}" name="haModel" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{965DA40D-EBE9-42CF-B56F-A6A77EF637F0}" name="haDescription" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{130CAF40-E0C6-4E3E-B004-85850140B916}" name="BiNuralMSRP w/Charger" dataDxfId="55">
       <calculatedColumnFormula>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BA070518-7526-4FCA-A727-C48F8CD389F1}" name="haMSRP" dataDxfId="48" dataCellStyle="Comma"/>
-    <tableColumn id="17" xr3:uid="{00383612-0531-419F-BDF0-C61ADC5A5242}" name="Discount Type 1" dataDxfId="47" dataCellStyle="Comma"/>
-    <tableColumn id="18" xr3:uid="{238DF570-BCC6-441D-86CE-1CD2C0CBB0A4}" name="Discount Amount 1" dataDxfId="46" dataCellStyle="Comma">
+    <tableColumn id="3" xr3:uid="{BA070518-7526-4FCA-A727-C48F8CD389F1}" name="haMSRP" dataDxfId="54" dataCellStyle="Comma"/>
+    <tableColumn id="17" xr3:uid="{00383612-0531-419F-BDF0-C61ADC5A5242}" name="Discount Type 1" dataDxfId="53" dataCellStyle="Comma"/>
+    <tableColumn id="18" xr3:uid="{238DF570-BCC6-441D-86CE-1CD2C0CBB0A4}" name="Discount Amount 1" dataDxfId="52" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[haMSRP]]-((HearingAids[[#This Row],[ListPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{5D29F2AF-C8F8-440E-80A9-37F68ED6526A}" name="HAListPrice" dataDxfId="45" dataCellStyle="Comma">
+    <tableColumn id="14" xr3:uid="{5D29F2AF-C8F8-440E-80A9-37F68ED6526A}" name="HAListPrice" dataDxfId="51" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{790802D5-161D-4A7E-805F-7E74CEEFF06C}" name="ListPriceBinural" dataDxfId="44" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{A443216B-20E9-4998-AF64-4AF2D830D488}" name="Discount Type 2" dataDxfId="43" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{97DC0668-F1BB-4221-B66A-0541EE63F239}" name="Discount Amount 2" dataDxfId="42" dataCellStyle="Comma">
+    <tableColumn id="8" xr3:uid="{790802D5-161D-4A7E-805F-7E74CEEFF06C}" name="ListPriceBinural" dataDxfId="50" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{A443216B-20E9-4998-AF64-4AF2D830D488}" name="Discount Type 2" dataDxfId="49" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{97DC0668-F1BB-4221-B66A-0541EE63F239}" name="Discount Amount 2" dataDxfId="48" dataCellStyle="Comma">
       <calculatedColumnFormula>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BA3E2B5E-A0AC-4615-8DC5-9BDA41C1C791}" name="haNetPrice" dataDxfId="41" dataCellStyle="Comma">
+    <tableColumn id="7" xr3:uid="{BA3E2B5E-A0AC-4615-8DC5-9BDA41C1C791}" name="haNetPrice" dataDxfId="47" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{38CF1B18-CDB5-4976-B47F-965816542466}" name="haNetPriceBinural" dataDxfId="40" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{7FD8661B-3CB2-4419-B4E4-F4B466463008}" name="Discount Type 3" dataDxfId="39" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{F690564D-67FB-47A7-BB92-4594973E8684}" name="Discount Amount 3" dataDxfId="38" dataCellStyle="Comma">
+    <tableColumn id="20" xr3:uid="{38CF1B18-CDB5-4976-B47F-965816542466}" name="haNetPriceBinural" dataDxfId="46" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{7FD8661B-3CB2-4419-B4E4-F4B466463008}" name="Discount Type 3" dataDxfId="45" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{F690564D-67FB-47A7-BB92-4594973E8684}" name="Discount Amount 3" dataDxfId="44" dataCellStyle="Comma">
       <calculatedColumnFormula>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{70079D27-1688-482B-B7CE-C08CD0692376}" name="haNetPrice2" dataDxfId="37" dataCellStyle="Comma">
+    <tableColumn id="22" xr3:uid="{70079D27-1688-482B-B7CE-C08CD0692376}" name="haNetPrice2" dataDxfId="43" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{86E09452-1856-484B-8B87-A189C8CD8DFB}" name="haNetPriceBinural2" dataDxfId="36" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{C584D592-9121-42BD-ADD1-A997B12ADB03}" name="paFittingFee" dataDxfId="35" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{D4BCCF1D-8129-4502-AE64-888D352A8485}" name="chargerType" dataDxfId="34" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{8D61B71A-686D-41F5-A2BF-54F259932C23}" name="chargerPrice" dataDxfId="33" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{8C0379A7-F346-4094-953F-A4AB4D0878CB}" name="haReceiverType" dataDxfId="32" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{5D6BB6BD-447F-4911-B6E4-986FB62F14A1}" name="haReceiverPrice" dataDxfId="31" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{E1863ADB-80F5-499D-B829-43F23A36EF68}" name="haReceiverDiscountDescription" dataDxfId="30" dataCellStyle="Comma"/>
+    <tableColumn id="16" xr3:uid="{86E09452-1856-484B-8B87-A189C8CD8DFB}" name="haNetPriceBinural2" dataDxfId="42" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{C584D592-9121-42BD-ADD1-A997B12ADB03}" name="paFittingFee" dataDxfId="41" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{D4BCCF1D-8129-4502-AE64-888D352A8485}" name="chargerType" dataDxfId="40" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{8D61B71A-686D-41F5-A2BF-54F259932C23}" name="chargerPrice" dataDxfId="39" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{8C0379A7-F346-4094-953F-A4AB4D0878CB}" name="haReceiverType" dataDxfId="38" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{5D6BB6BD-447F-4911-B6E4-986FB62F14A1}" name="haReceiverPrice" dataDxfId="37" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{E1863ADB-80F5-499D-B829-43F23A36EF68}" name="haReceiverDiscountDescription" dataDxfId="36" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="35">
   <autoFilter ref="A1:I260" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H286">
     <sortCondition ref="H1:H286"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="27">
+    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="33">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="26"/>
-    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23">
   <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}">
     <filterColumn colId="7">
       <filters>
@@ -3588,14 +3587,14 @@
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{FDC3E4DD-A231-46DD-8097-7C0DC18260BD}" name="barcodeName"/>
-    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="56">
+    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="22">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{D0382781-2AC8-4DE6-BF59-9B38B78B1184}" name="remoteModel"/>
     <tableColumn id="4" xr3:uid="{9B080694-7BEA-4586-AA70-DDEC1D67D699}" name="remoteType"/>
     <tableColumn id="7" xr3:uid="{CCB41D66-8697-4FAF-A74F-5F54F6CCA4F8}" name="remoteListAmount"/>
-    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="54">
+    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="20">
       <calculatedColumnFormula>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{435AFC97-0382-475D-9332-93EDAB756C8B}" name="remoteDiscountDescription"/>
@@ -3982,7 +3981,7 @@
         <v>61</v>
       </c>
       <c r="B7" s="171" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C7" s="172"/>
     </row>
@@ -4365,7 +4364,7 @@
   <dimension ref="A1:AF232"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -4596,7 +4595,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="12.75">
+    <row r="4" spans="1:31" ht="12.75" hidden="1">
       <c r="A4" s="37" t="s">
         <v>499</v>
       </c>
@@ -6720,11 +6719,11 @@
       <c r="AE34"/>
     </row>
     <row r="35" spans="1:31" ht="12.75">
-      <c r="A35" s="111" t="s">
-        <v>617</v>
+      <c r="A35" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="B35" s="142" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C35" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7292,10 +7291,10 @@
     </row>
     <row r="43" spans="1:31" ht="12.75">
       <c r="A43" s="111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B43" s="142" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C43" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7361,10 +7360,10 @@
     </row>
     <row r="44" spans="1:31" ht="12.75">
       <c r="A44" s="111" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B44" s="142" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C44" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7430,10 +7429,10 @@
     </row>
     <row r="45" spans="1:31" ht="12.75">
       <c r="A45" s="111" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B45" s="142" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C45" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7526,7 +7525,7 @@
         <v>9450</v>
       </c>
       <c r="I46" s="145" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J46" s="2">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -7598,7 +7597,7 @@
         <v>7050</v>
       </c>
       <c r="I47" s="145" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J47" s="2">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -7670,7 +7669,7 @@
         <v>8350</v>
       </c>
       <c r="I48" s="145" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J48" s="2">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -8297,7 +8296,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="12.75">
+    <row r="57" spans="1:32" ht="12.75" hidden="1">
       <c r="A57" s="37" t="s">
         <v>499</v>
       </c>
@@ -10763,10 +10762,10 @@
     </row>
     <row r="91" spans="1:31" ht="12.75">
       <c r="A91" s="111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B91" s="142" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C91" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10832,11 +10831,11 @@
       <c r="AE91"/>
     </row>
     <row r="92" spans="1:31" ht="12.75">
-      <c r="A92" s="111" t="s">
-        <v>617</v>
+      <c r="A92" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="B92" s="142" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C92" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10897,10 +10896,10 @@
     </row>
     <row r="93" spans="1:31" ht="12.75">
       <c r="A93" s="111" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B93" s="142" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C93" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10967,10 +10966,10 @@
     </row>
     <row r="94" spans="1:31" ht="12.75">
       <c r="A94" s="111" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B94" s="142" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C94" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13068,10 +13067,10 @@
     </row>
     <row r="123" spans="1:31" ht="12.75">
       <c r="A123" s="111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B123" s="142" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C123" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13141,10 +13140,10 @@
     </row>
     <row r="124" spans="1:31" ht="12.75">
       <c r="A124" s="111" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B124" s="142" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C124" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13214,10 +13213,10 @@
     </row>
     <row r="125" spans="1:31" ht="12.75">
       <c r="A125" s="111" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B125" s="142" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C125" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14090,10 +14089,10 @@
     </row>
     <row r="137" spans="1:31" ht="12.75">
       <c r="A137" s="111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B137" s="142" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C137" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14163,10 +14162,10 @@
     </row>
     <row r="138" spans="1:31" ht="12.75">
       <c r="A138" s="111" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B138" s="142" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C138" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14236,10 +14235,10 @@
     </row>
     <row r="139" spans="1:31" ht="12.75">
       <c r="A139" s="90" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B139" s="142" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C139" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14914,7 +14913,7 @@
         <v>3500</v>
       </c>
       <c r="I148" s="123" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J148" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -14986,7 +14985,7 @@
         <v>9450</v>
       </c>
       <c r="I149" s="123" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J149" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -15058,7 +15057,7 @@
         <v>7050</v>
       </c>
       <c r="I150" s="123" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J150" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -15130,7 +15129,7 @@
         <v>8350</v>
       </c>
       <c r="I151" s="123" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J151" s="97">
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
@@ -28127,7 +28126,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="str">
-        <v>Beltone BTE Digital Boost Max S 6 95-DWHC</v>
+        <v>Beltone BTE Digital Boost Max S 4 95-DWHC</v>
       </c>
       <c r="B4" t="str">
         <v>Amplifon Competitive</v>
@@ -28138,7 +28137,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="str">
-        <v>Beltone BTE Digital Boost Max S 9 95-DWHC</v>
+        <v>Beltone BTE Digital Boost Max S 6 95-DWHC</v>
       </c>
       <c r="B5" t="str">
         <v>Early Lease Upgrade</v>
@@ -28149,7 +28148,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="str">
-        <v>Beltone BTE Digital Boost Ultra 17 86DWHT</v>
+        <v>Beltone BTE Digital Boost Max S 9 95-DWHC</v>
       </c>
       <c r="B6" t="str">
         <v>Envision 17 Special</v>
@@ -28160,7 +28159,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="str">
-        <v>Beltone BTE Digital Boost Ultra 17 95DWT</v>
+        <v>Beltone BTE Digital Boost Ultra 17 86DWHT</v>
       </c>
       <c r="B7" t="str">
         <v>Envision 6 Special</v>
@@ -28171,7 +28170,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="str">
-        <v>Beltone BTE Digital Boost Ultra 6 86DWHT</v>
+        <v>Beltone BTE Digital Boost Ultra 17 95DWT</v>
       </c>
       <c r="B8" t="str">
         <v>Envision 9 Special</v>
@@ -28179,7 +28178,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="str">
-        <v>Beltone BTE Digital Boost Ultra 6 95DWT</v>
+        <v>Beltone BTE Digital Boost Ultra 6 86DWHT</v>
       </c>
       <c r="B9" t="str">
         <v>Fast Funding</v>
@@ -28187,7 +28186,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="str">
-        <v>Beltone BTE Digital Boost Ultra 9 86DWHT</v>
+        <v>Beltone BTE Digital Boost Ultra 6 95DWT</v>
       </c>
       <c r="B10" t="str">
         <v>GHB Competitive</v>
@@ -28195,7 +28194,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="str">
-        <v>Beltone BTE Digital Boost Ultra 9 95DWT</v>
+        <v>Beltone BTE Digital Boost Ultra 9 86DWHT</v>
       </c>
       <c r="B11" t="str">
         <v>HCS Competitive</v>
@@ -28203,7 +28202,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="str">
-        <v>Beltone BTE Digital Rely 2 66DW</v>
+        <v>Beltone BTE Digital Boost Ultra 9 95DWT</v>
       </c>
       <c r="B12" t="str">
         <v>HearUSA Competitive</v>
@@ -28211,7 +28210,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="str">
-        <v>Beltone BTE Digital Rely 2 76DW</v>
+        <v>Beltone BTE Digital Rely 2 66DW</v>
       </c>
       <c r="B13" t="str">
         <v>Humana</v>
@@ -28219,7 +28218,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="str">
-        <v>Beltone BTE Digital Rely 2 86DWH</v>
+        <v>Beltone BTE Digital Rely 2 76DW</v>
       </c>
       <c r="B14" t="str">
         <v>Marketing Offer</v>
@@ -28227,7 +28226,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="str">
-        <v>Beltone BTE Digital Rely 2 95DW</v>
+        <v>Beltone BTE Digital Rely 2 86DWH</v>
       </c>
       <c r="B15" t="str">
         <v>Martins Point Competitive</v>
@@ -28235,7 +28234,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="str">
-        <v>Beltone BTE Digital Rely 3 66DW</v>
+        <v>Beltone BTE Digital Rely 2 95DW</v>
       </c>
       <c r="B16" t="str">
         <v>Nations Hearing Competitive</v>
@@ -28243,7 +28242,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="str">
-        <v>Beltone BTE Digital Rely 3 76DW</v>
+        <v>Beltone BTE Digital Rely 3 66DW</v>
       </c>
       <c r="B17" t="str">
         <v>Open House Special</v>
@@ -28251,7 +28250,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="str">
-        <v>Beltone BTE Digital Rely 3 86DWH</v>
+        <v>Beltone BTE Digital Rely 3 76DW</v>
       </c>
       <c r="B18" t="str">
         <v>Tri-Care</v>
@@ -28259,7 +28258,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="str">
-        <v>Beltone BTE Digital Rely 3 95DW</v>
+        <v>Beltone BTE Digital Rely 3 86DWH</v>
       </c>
       <c r="B19" t="str">
         <v>TruHearing Competitive</v>
@@ -28267,7 +28266,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="str">
-        <v>Beltone BTE Digital Rely 4 66DW</v>
+        <v>Beltone BTE Digital Rely 3 95DW</v>
       </c>
       <c r="B20" t="str">
         <v>UHCH Competitive</v>
@@ -28275,7 +28274,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="str">
-        <v>Beltone BTE Digital Rely 4 76DW</v>
+        <v>Beltone BTE Digital Rely 4 66DW</v>
       </c>
       <c r="B21" t="str">
         <v>Veterans Discount</v>
@@ -28283,7 +28282,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="str">
-        <v>Beltone BTE Digital Rely 4 86DWH</v>
+        <v>Beltone BTE Digital Rely 4 76DW</v>
       </c>
       <c r="B22" t="str">
         <v>WellCare Competitive</v>
@@ -28291,52 +28290,52 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="str">
-        <v>Beltone BTE Digital Rely 4 95DW</v>
+        <v>Beltone BTE Digital Rely 4 86DWH</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="str">
-        <v>Beltone CIC Digital Rely 3</v>
+        <v>Beltone BTE Digital Rely 4 95DW</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="str">
-        <v>Beltone CIC Digital Rely 4</v>
+        <v>Beltone CIC Digital Rely 3</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="str">
-        <v>Beltone ITC Digital Rely 2</v>
+        <v>Beltone CIC Digital Rely 4</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="str">
-        <v>Beltone ITC Digital Rely 3</v>
+        <v>Beltone ITC Digital Rely 2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="str">
-        <v>Beltone ITC Digital Rely 4</v>
+        <v>Beltone ITC Digital Rely 3</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="str">
-        <v>Beltone ITE Digital Rely 2</v>
+        <v>Beltone ITC Digital Rely 4</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="str">
-        <v>Beltone ITE Digital Rely 3</v>
+        <v>Beltone ITE Digital Rely 2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="str">
-        <v>Beltone ITE Digital Rely 4</v>
+        <v>Beltone ITE Digital Rely 3</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="str">
-        <v>Beltone RIE Digital Boost Max S 4 95-DWHC</v>
+        <v>Beltone ITE Digital Rely 4</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1213" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42CB9F7B-7005-4F02-8742-7462BB1C99C4}"/>
+  <xr:revisionPtr revIDLastSave="1215" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAFA67FA-E2FB-4AEC-A583-732C8540A694}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -1937,19 +1937,19 @@
     <t>Beltone BTE Digital Boost Max S 9 95-DWHC</t>
   </si>
   <si>
-    <t>Beltone Boost Max S 4 95-DWHC BTE Digital</t>
-  </si>
-  <si>
-    <t>Beltone Boost Max S 17 95-DWHC BTE Digital</t>
-  </si>
-  <si>
-    <t>Beltone Boost Max S 6 95-DWHC BTE Digital</t>
-  </si>
-  <si>
-    <t>Beltone Boost Max S 9 95-DWHC BTE Digital</t>
-  </si>
-  <si>
     <t>Beltone BTE Digital Boost Max S 4 95-DWHC</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 4 95-DWHC Digital BTE</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 17 95-DWHC Digital BTE</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 6 95-DWHC Digital BTE</t>
+  </si>
+  <si>
+    <t>Beltone Boost Max S 9 95-DWHC Digital BTE</t>
   </si>
 </sst>
 </file>
@@ -3491,16 +3491,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Beltone Boost Max S 17 95-DWHC BTE Digital"/>
-        <filter val="Beltone Boost Max S 4 95-DWHC BTE Digital"/>
-        <filter val="Beltone Boost Max S 6 95-DWHC BTE Digital"/>
-        <filter val="Beltone Boost Max S 9 95-DWHC BTE Digital"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V159">
     <sortCondition ref="I2:I159"/>
   </sortState>
@@ -4468,7 +4459,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="12.75" hidden="1">
+    <row r="2" spans="1:31" ht="12.75">
       <c r="A2" s="37" t="s">
         <v>501</v>
       </c>
@@ -4532,7 +4523,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="12.75" hidden="1">
+    <row r="3" spans="1:31" ht="12.75">
       <c r="A3" s="37" t="s">
         <v>500</v>
       </c>
@@ -4595,7 +4586,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="12.75" hidden="1">
+    <row r="4" spans="1:31" ht="12.75">
       <c r="A4" s="37" t="s">
         <v>499</v>
       </c>
@@ -4658,7 +4649,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="12.75" hidden="1">
+    <row r="5" spans="1:31" ht="12.75">
       <c r="A5" s="37" t="s">
         <v>496</v>
       </c>
@@ -4727,7 +4718,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="12.75" hidden="1">
+    <row r="6" spans="1:31" ht="12.75">
       <c r="A6" s="37" t="s">
         <v>498</v>
       </c>
@@ -4797,7 +4788,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="12.75" hidden="1">
+    <row r="7" spans="1:31" ht="12.75">
       <c r="A7" s="37" t="s">
         <v>497</v>
       </c>
@@ -4867,7 +4858,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="12.75" hidden="1">
+    <row r="8" spans="1:31" ht="12.75">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -4936,7 +4927,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="12.75" hidden="1">
+    <row r="9" spans="1:31" ht="12.75">
       <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
@@ -5005,7 +4996,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="12.75" hidden="1">
+    <row r="10" spans="1:31" ht="12.75">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -5074,7 +5065,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="12.75" hidden="1">
+    <row r="11" spans="1:31" ht="12.75">
       <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
@@ -5143,7 +5134,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="12.75" hidden="1">
+    <row r="12" spans="1:31" ht="12.75">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -5212,7 +5203,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="12.75" hidden="1">
+    <row r="13" spans="1:31" ht="12.75">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -5281,7 +5272,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="12.75" hidden="1">
+    <row r="14" spans="1:31" ht="12.75">
       <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
@@ -5348,7 +5339,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="12.75" hidden="1">
+    <row r="15" spans="1:31" ht="12.75">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -5416,7 +5407,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="12.75" hidden="1">
+    <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
@@ -5486,7 +5477,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="12.75" hidden="1">
+    <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="3" t="s">
         <v>406</v>
       </c>
@@ -5555,7 +5546,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="12.75" hidden="1">
+    <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
@@ -5624,7 +5615,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="12.75" hidden="1">
+    <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
@@ -5693,7 +5684,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="12.75" hidden="1">
+    <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -5762,7 +5753,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="12.75" hidden="1">
+    <row r="21" spans="1:31" ht="12.75">
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
@@ -5831,7 +5822,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="12.75" hidden="1">
+    <row r="22" spans="1:31" ht="12.75">
       <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
@@ -5900,7 +5891,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="12.75" hidden="1">
+    <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
@@ -5966,7 +5957,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="12.75" hidden="1">
+    <row r="24" spans="1:31" ht="12.75">
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
@@ -6033,7 +6024,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="12.75" hidden="1">
+    <row r="25" spans="1:31" ht="12.75">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -6101,7 +6092,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="12.75" hidden="1">
+    <row r="26" spans="1:31" ht="12.75">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -6171,7 +6162,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="12.75" hidden="1">
+    <row r="27" spans="1:31" ht="12.75">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -6241,7 +6232,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="12.75" hidden="1">
+    <row r="28" spans="1:31" ht="12.75">
       <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
@@ -6310,7 +6301,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="12.75" hidden="1">
+    <row r="29" spans="1:31" ht="12.75">
       <c r="A29" s="3" t="s">
         <v>19</v>
       </c>
@@ -6379,7 +6370,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="12.75" hidden="1">
+    <row r="30" spans="1:31" ht="12.75">
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
@@ -6448,7 +6439,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="12.75" hidden="1">
+    <row r="31" spans="1:31" ht="12.75">
       <c r="A31" s="3" t="s">
         <v>21</v>
       </c>
@@ -6517,7 +6508,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="12.75" hidden="1">
+    <row r="32" spans="1:31" ht="12.75">
       <c r="A32" s="3" t="s">
         <v>22</v>
       </c>
@@ -6584,7 +6575,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="12.75" hidden="1">
+    <row r="33" spans="1:31" ht="12.75">
       <c r="A33" s="3" t="s">
         <v>23</v>
       </c>
@@ -6651,7 +6642,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="12.75" hidden="1">
+    <row r="34" spans="1:31" ht="12.75">
       <c r="A34" s="3" t="s">
         <v>24</v>
       </c>
@@ -6720,10 +6711,10 @@
     </row>
     <row r="35" spans="1:31" ht="12.75">
       <c r="A35" s="142" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B35" s="142" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C35" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -6784,7 +6775,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="12.75" hidden="1">
+    <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="37" t="s">
         <v>500</v>
       </c>
@@ -6857,7 +6848,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="12.75" hidden="1">
+    <row r="37" spans="1:31" ht="12.75">
       <c r="A37" s="3" t="s">
         <v>413</v>
       </c>
@@ -6929,7 +6920,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="12.75" hidden="1">
+    <row r="38" spans="1:31" ht="12.75">
       <c r="A38" s="3" t="s">
         <v>414</v>
       </c>
@@ -7001,7 +6992,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="12.75" hidden="1">
+    <row r="39" spans="1:31" ht="12.75">
       <c r="A39" s="3" t="s">
         <v>415</v>
       </c>
@@ -7073,7 +7064,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="12.75" hidden="1">
+    <row r="40" spans="1:31" ht="12.75">
       <c r="A40" s="37" t="s">
         <v>496</v>
       </c>
@@ -7145,7 +7136,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="12.75" hidden="1">
+    <row r="41" spans="1:31" ht="12.75">
       <c r="A41" s="37" t="s">
         <v>498</v>
       </c>
@@ -7217,7 +7208,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="12.75" hidden="1">
+    <row r="42" spans="1:31" ht="12.75">
       <c r="A42" s="37" t="s">
         <v>497</v>
       </c>
@@ -7294,7 +7285,7 @@
         <v>621</v>
       </c>
       <c r="B43" s="142" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C43" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7363,7 +7354,7 @@
         <v>622</v>
       </c>
       <c r="B44" s="142" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C44" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7432,7 +7423,7 @@
         <v>623</v>
       </c>
       <c r="B45" s="142" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C45" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -7496,7 +7487,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="12.75" hidden="1">
+    <row r="46" spans="1:31" ht="12.75">
       <c r="A46" s="142" t="s">
         <v>496</v>
       </c>
@@ -7568,7 +7559,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="12.75" hidden="1">
+    <row r="47" spans="1:31" ht="12.75">
       <c r="A47" s="142" t="s">
         <v>498</v>
       </c>
@@ -7640,7 +7631,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="12.75" hidden="1">
+    <row r="48" spans="1:31" ht="12.75">
       <c r="A48" s="142" t="s">
         <v>497</v>
       </c>
@@ -7712,7 +7703,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="12.75" hidden="1">
+    <row r="49" spans="1:32" ht="12.75">
       <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
@@ -7785,7 +7776,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="12.75" hidden="1">
+    <row r="50" spans="1:32" ht="12.75">
       <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
@@ -7858,7 +7849,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="12.75" hidden="1">
+    <row r="51" spans="1:32" ht="12.75">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -7931,7 +7922,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="12.75" hidden="1">
+    <row r="52" spans="1:32" ht="12.75">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -8004,7 +7995,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="12.75" hidden="1">
+    <row r="53" spans="1:32" ht="12.75">
       <c r="A53" s="3" t="s">
         <v>55</v>
       </c>
@@ -8077,7 +8068,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="12.75" hidden="1">
+    <row r="54" spans="1:32" ht="12.75">
       <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
@@ -8150,7 +8141,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="12.75" hidden="1">
+    <row r="55" spans="1:32" ht="12.75">
       <c r="A55" s="37" t="s">
         <v>501</v>
       </c>
@@ -8223,7 +8214,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="12.75" hidden="1">
+    <row r="56" spans="1:32" ht="12.75">
       <c r="A56" s="37" t="s">
         <v>500</v>
       </c>
@@ -8296,7 +8287,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="12.75" hidden="1">
+    <row r="57" spans="1:32" ht="12.75">
       <c r="A57" s="37" t="s">
         <v>499</v>
       </c>
@@ -8369,7 +8360,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:32" ht="12.75" hidden="1">
+    <row r="58" spans="1:32" ht="12.75">
       <c r="A58" s="37" t="s">
         <v>496</v>
       </c>
@@ -8442,7 +8433,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:32" ht="12.75" hidden="1">
+    <row r="59" spans="1:32" ht="12.75">
       <c r="A59" s="37" t="s">
         <v>498</v>
       </c>
@@ -8515,7 +8506,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:32" ht="12.75" hidden="1">
+    <row r="60" spans="1:32" ht="12.75">
       <c r="A60" s="37" t="s">
         <v>497</v>
       </c>
@@ -8588,7 +8579,7 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:32" ht="12.75" hidden="1">
+    <row r="61" spans="1:32" ht="12.75">
       <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
@@ -8661,7 +8652,7 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:32" ht="12.75" hidden="1">
+    <row r="62" spans="1:32" ht="12.75">
       <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
@@ -8733,7 +8724,7 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:32" ht="12.75" hidden="1">
+    <row r="63" spans="1:32" ht="12.75">
       <c r="A63" s="3" t="s">
         <v>29</v>
       </c>
@@ -8805,7 +8796,7 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:32" ht="12.75" hidden="1">
+    <row r="64" spans="1:32" ht="12.75">
       <c r="A64" s="3" t="s">
         <v>30</v>
       </c>
@@ -8878,7 +8869,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="12.75" hidden="1">
+    <row r="65" spans="1:31" ht="12.75">
       <c r="A65" s="3" t="s">
         <v>31</v>
       </c>
@@ -8951,7 +8942,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="12.75" hidden="1">
+    <row r="66" spans="1:31" ht="12.75">
       <c r="A66" s="3" t="s">
         <v>32</v>
       </c>
@@ -9024,7 +9015,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="12.75" hidden="1">
+    <row r="67" spans="1:31" ht="12.75">
       <c r="A67" s="3" t="s">
         <v>38</v>
       </c>
@@ -9095,7 +9086,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="12.75" hidden="1">
+    <row r="68" spans="1:31" ht="12.75">
       <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
@@ -9166,7 +9157,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="12.75" hidden="1">
+    <row r="69" spans="1:31" ht="12.75">
       <c r="A69" s="3" t="s">
         <v>44</v>
       </c>
@@ -9239,7 +9230,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="12.75" hidden="1">
+    <row r="70" spans="1:31" ht="12.75">
       <c r="A70" s="3" t="s">
         <v>406</v>
       </c>
@@ -9312,7 +9303,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="12.75" hidden="1">
+    <row r="71" spans="1:31" ht="12.75">
       <c r="A71" s="3" t="s">
         <v>45</v>
       </c>
@@ -9385,7 +9376,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="12.75" hidden="1">
+    <row r="72" spans="1:31" ht="12.75">
       <c r="A72" s="3" t="s">
         <v>33</v>
       </c>
@@ -9458,7 +9449,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="12.75" hidden="1">
+    <row r="73" spans="1:31" ht="12.75">
       <c r="A73" s="3" t="s">
         <v>34</v>
       </c>
@@ -9531,7 +9522,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="12.75" hidden="1">
+    <row r="74" spans="1:31" ht="12.75">
       <c r="A74" s="3" t="s">
         <v>35</v>
       </c>
@@ -9604,7 +9595,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="12.75" hidden="1">
+    <row r="75" spans="1:31" ht="12.75">
       <c r="A75" s="3" t="s">
         <v>36</v>
       </c>
@@ -9677,7 +9668,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="12.75" hidden="1">
+    <row r="76" spans="1:31" ht="12.75">
       <c r="A76" s="3" t="s">
         <v>37</v>
       </c>
@@ -9748,7 +9739,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="12.75" hidden="1">
+    <row r="77" spans="1:31" ht="12.75">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -9819,7 +9810,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="12.75" hidden="1">
+    <row r="78" spans="1:31" ht="12.75">
       <c r="A78" s="3" t="s">
         <v>41</v>
       </c>
@@ -9890,7 +9881,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="12.75" hidden="1">
+    <row r="79" spans="1:31" ht="12.75">
       <c r="A79" s="3" t="s">
         <v>25</v>
       </c>
@@ -9963,7 +9954,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="12.75" hidden="1">
+    <row r="80" spans="1:31" ht="12.75">
       <c r="A80" s="3" t="s">
         <v>27</v>
       </c>
@@ -10036,7 +10027,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="12.75" hidden="1">
+    <row r="81" spans="1:31" ht="12.75">
       <c r="A81" s="3" t="s">
         <v>15</v>
       </c>
@@ -10109,7 +10100,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="12.75" hidden="1">
+    <row r="82" spans="1:31" ht="12.75">
       <c r="A82" s="3" t="s">
         <v>19</v>
       </c>
@@ -10182,7 +10173,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="12.75" hidden="1">
+    <row r="83" spans="1:31" ht="12.75">
       <c r="A83" s="3" t="s">
         <v>20</v>
       </c>
@@ -10255,7 +10246,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="12.75" hidden="1">
+    <row r="84" spans="1:31" ht="12.75">
       <c r="A84" s="3" t="s">
         <v>21</v>
       </c>
@@ -10328,7 +10319,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="12.75" hidden="1">
+    <row r="85" spans="1:31" ht="12.75">
       <c r="A85" s="3" t="s">
         <v>22</v>
       </c>
@@ -10399,7 +10390,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="12.75" hidden="1">
+    <row r="86" spans="1:31" ht="12.75">
       <c r="A86" s="3" t="s">
         <v>23</v>
       </c>
@@ -10470,7 +10461,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="12.75" hidden="1">
+    <row r="87" spans="1:31" ht="12.75">
       <c r="A87" s="3" t="s">
         <v>24</v>
       </c>
@@ -10541,7 +10532,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="12.75" hidden="1">
+    <row r="88" spans="1:31" ht="12.75">
       <c r="A88" s="3" t="s">
         <v>413</v>
       </c>
@@ -10614,7 +10605,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="12.75" hidden="1">
+    <row r="89" spans="1:31" ht="12.75">
       <c r="A89" s="3" t="s">
         <v>414</v>
       </c>
@@ -10687,7 +10678,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="12.75" hidden="1">
+    <row r="90" spans="1:31" ht="12.75">
       <c r="A90" s="3" t="s">
         <v>415</v>
       </c>
@@ -10765,7 +10756,7 @@
         <v>621</v>
       </c>
       <c r="B91" s="142" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C91" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10832,10 +10823,10 @@
     </row>
     <row r="92" spans="1:31" ht="12.75">
       <c r="A92" s="142" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B92" s="142" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C92" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10899,7 +10890,7 @@
         <v>623</v>
       </c>
       <c r="B93" s="142" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C93" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -10969,7 +10960,7 @@
         <v>622</v>
       </c>
       <c r="B94" s="142" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C94" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -11034,7 +11025,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="12.75" hidden="1">
+    <row r="95" spans="1:31" ht="12.75">
       <c r="A95" s="37" t="s">
         <v>500</v>
       </c>
@@ -11107,7 +11098,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="12.75" hidden="1">
+    <row r="96" spans="1:31" ht="12.75">
       <c r="A96" s="3" t="s">
         <v>413</v>
       </c>
@@ -11179,7 +11170,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="12.75" hidden="1">
+    <row r="97" spans="1:31" ht="12.75">
       <c r="A97" s="3" t="s">
         <v>414</v>
       </c>
@@ -11251,7 +11242,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="12.75" hidden="1">
+    <row r="98" spans="1:31" ht="12.75">
       <c r="A98" s="3" t="s">
         <v>415</v>
       </c>
@@ -11323,7 +11314,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="12.75" hidden="1">
+    <row r="99" spans="1:31" ht="12.75">
       <c r="A99" s="37" t="s">
         <v>500</v>
       </c>
@@ -11395,7 +11386,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="12.75" hidden="1">
+    <row r="100" spans="1:31" ht="12.75">
       <c r="A100" s="3" t="s">
         <v>413</v>
       </c>
@@ -11467,7 +11458,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="12.75" hidden="1">
+    <row r="101" spans="1:31" ht="12.75">
       <c r="A101" s="3" t="s">
         <v>414</v>
       </c>
@@ -11539,7 +11530,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="12.75" hidden="1">
+    <row r="102" spans="1:31" ht="12.75">
       <c r="A102" s="3" t="s">
         <v>415</v>
       </c>
@@ -11612,7 +11603,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="12.75" hidden="1">
+    <row r="103" spans="1:31" ht="12.75">
       <c r="A103" s="37" t="s">
         <v>500</v>
       </c>
@@ -11684,7 +11675,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="12.75" hidden="1">
+    <row r="104" spans="1:31" ht="12.75">
       <c r="A104" s="3" t="s">
         <v>413</v>
       </c>
@@ -11756,7 +11747,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="12.75" hidden="1">
+    <row r="105" spans="1:31" ht="12.75">
       <c r="A105" s="3" t="s">
         <v>414</v>
       </c>
@@ -11828,7 +11819,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="12.75" hidden="1">
+    <row r="106" spans="1:31" ht="12.75">
       <c r="A106" s="3" t="s">
         <v>415</v>
       </c>
@@ -11900,7 +11891,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="12.75" hidden="1">
+    <row r="107" spans="1:31" ht="12.75">
       <c r="A107" s="37" t="s">
         <v>500</v>
       </c>
@@ -11972,7 +11963,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="12.75" hidden="1">
+    <row r="108" spans="1:31" ht="12.75">
       <c r="A108" s="3" t="s">
         <v>413</v>
       </c>
@@ -12044,7 +12035,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="12.75" hidden="1">
+    <row r="109" spans="1:31" ht="12.75">
       <c r="A109" s="3" t="s">
         <v>414</v>
       </c>
@@ -12116,7 +12107,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="12.75" hidden="1">
+    <row r="110" spans="1:31" ht="12.75">
       <c r="A110" s="3" t="s">
         <v>415</v>
       </c>
@@ -12188,7 +12179,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="12.75" hidden="1">
+    <row r="111" spans="1:31" ht="12.75">
       <c r="A111" s="3" t="s">
         <v>51</v>
       </c>
@@ -12261,7 +12252,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="12.75" hidden="1">
+    <row r="112" spans="1:31" ht="12.75">
       <c r="A112" s="3" t="s">
         <v>52</v>
       </c>
@@ -12334,7 +12325,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="12.75" hidden="1">
+    <row r="113" spans="1:31" ht="12.75">
       <c r="A113" s="3" t="s">
         <v>53</v>
       </c>
@@ -12407,7 +12398,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="12.75" hidden="1">
+    <row r="114" spans="1:31" ht="12.75">
       <c r="A114" s="3" t="s">
         <v>54</v>
       </c>
@@ -12480,7 +12471,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="12.75" hidden="1">
+    <row r="115" spans="1:31" ht="12.75">
       <c r="A115" s="3" t="s">
         <v>55</v>
       </c>
@@ -12553,7 +12544,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="12.75" hidden="1">
+    <row r="116" spans="1:31" ht="12.75">
       <c r="A116" s="3" t="s">
         <v>56</v>
       </c>
@@ -12626,7 +12617,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.75" hidden="1">
+    <row r="117" spans="1:31" ht="12.75">
       <c r="A117" s="37" t="s">
         <v>496</v>
       </c>
@@ -12699,7 +12690,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.75" hidden="1">
+    <row r="118" spans="1:31" ht="12.75">
       <c r="A118" s="37" t="s">
         <v>498</v>
       </c>
@@ -12772,7 +12763,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.75" hidden="1">
+    <row r="119" spans="1:31" ht="12.75">
       <c r="A119" s="37" t="s">
         <v>497</v>
       </c>
@@ -12845,7 +12836,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="12.75" hidden="1">
+    <row r="120" spans="1:31" ht="12.75">
       <c r="A120" s="3" t="s">
         <v>413</v>
       </c>
@@ -12918,7 +12909,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="12.75" hidden="1">
+    <row r="121" spans="1:31" ht="12.75">
       <c r="A121" s="3" t="s">
         <v>414</v>
       </c>
@@ -12991,7 +12982,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="12.75" hidden="1">
+    <row r="122" spans="1:31" ht="12.75">
       <c r="A122" s="3" t="s">
         <v>415</v>
       </c>
@@ -13070,7 +13061,7 @@
         <v>621</v>
       </c>
       <c r="B123" s="142" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C123" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13143,7 +13134,7 @@
         <v>622</v>
       </c>
       <c r="B124" s="142" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C124" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13216,7 +13207,7 @@
         <v>623</v>
       </c>
       <c r="B125" s="142" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C125" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -13284,7 +13275,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.75" hidden="1">
+    <row r="126" spans="1:31" ht="12.75">
       <c r="A126" s="37" t="s">
         <v>500</v>
       </c>
@@ -13357,7 +13348,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="12.75" hidden="1">
+    <row r="127" spans="1:31" ht="12.75">
       <c r="A127" s="3" t="s">
         <v>413</v>
       </c>
@@ -13430,7 +13421,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="12.75" hidden="1">
+    <row r="128" spans="1:31" ht="12.75">
       <c r="A128" s="3" t="s">
         <v>414</v>
       </c>
@@ -13503,7 +13494,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="12.75" hidden="1">
+    <row r="129" spans="1:31" ht="12.75">
       <c r="A129" s="3" t="s">
         <v>415</v>
       </c>
@@ -13576,7 +13567,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="12.75" hidden="1">
+    <row r="130" spans="1:31" ht="12.75">
       <c r="A130" s="37" t="s">
         <v>500</v>
       </c>
@@ -13649,7 +13640,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="12.75" hidden="1">
+    <row r="131" spans="1:31" ht="12.75">
       <c r="A131" s="3" t="s">
         <v>413</v>
       </c>
@@ -13722,7 +13713,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="12.75" hidden="1">
+    <row r="132" spans="1:31" ht="12.75">
       <c r="A132" s="3" t="s">
         <v>414</v>
       </c>
@@ -13795,7 +13786,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="12.75" hidden="1">
+    <row r="133" spans="1:31" ht="12.75">
       <c r="A133" s="3" t="s">
         <v>415</v>
       </c>
@@ -13868,7 +13859,7 @@
       <c r="AD133"/>
       <c r="AE133"/>
     </row>
-    <row r="134" spans="1:31" ht="12.75" hidden="1">
+    <row r="134" spans="1:31" ht="12.75">
       <c r="A134" s="37" t="s">
         <v>496</v>
       </c>
@@ -13941,7 +13932,7 @@
       <c r="AD134"/>
       <c r="AE134"/>
     </row>
-    <row r="135" spans="1:31" ht="12.75" hidden="1">
+    <row r="135" spans="1:31" ht="12.75">
       <c r="A135" s="37" t="s">
         <v>498</v>
       </c>
@@ -14014,7 +14005,7 @@
       <c r="AD135"/>
       <c r="AE135"/>
     </row>
-    <row r="136" spans="1:31" ht="12.75" hidden="1">
+    <row r="136" spans="1:31" ht="12.75">
       <c r="A136" s="37" t="s">
         <v>497</v>
       </c>
@@ -14092,7 +14083,7 @@
         <v>621</v>
       </c>
       <c r="B137" s="142" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C137" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14165,7 +14156,7 @@
         <v>622</v>
       </c>
       <c r="B138" s="142" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C138" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14238,7 +14229,7 @@
         <v>623</v>
       </c>
       <c r="B139" s="142" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C139" s="55">
         <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
@@ -14305,7 +14296,7 @@
       <c r="AC139" s="2"/>
       <c r="AD139" s="2"/>
     </row>
-    <row r="140" spans="1:31" ht="12.75" hidden="1">
+    <row r="140" spans="1:31" ht="12.75">
       <c r="A140" s="114" t="s">
         <v>500</v>
       </c>
@@ -14377,7 +14368,7 @@
       <c r="AC140" s="2"/>
       <c r="AD140" s="2"/>
     </row>
-    <row r="141" spans="1:31" ht="12.75" hidden="1">
+    <row r="141" spans="1:31" ht="12.75">
       <c r="A141" s="112" t="s">
         <v>413</v>
       </c>
@@ -14449,7 +14440,7 @@
       <c r="AC141" s="2"/>
       <c r="AD141" s="8"/>
     </row>
-    <row r="142" spans="1:31" ht="12.75" hidden="1">
+    <row r="142" spans="1:31" ht="12.75">
       <c r="A142" s="112" t="s">
         <v>414</v>
       </c>
@@ -14521,7 +14512,7 @@
       <c r="AC142" s="2"/>
       <c r="AD142" s="8"/>
     </row>
-    <row r="143" spans="1:31" ht="12.75" hidden="1">
+    <row r="143" spans="1:31" ht="12.75">
       <c r="A143" s="112" t="s">
         <v>415</v>
       </c>
@@ -14593,7 +14584,7 @@
       <c r="AC143" s="2"/>
       <c r="AD143" s="8"/>
     </row>
-    <row r="144" spans="1:31" ht="12.75" hidden="1">
+    <row r="144" spans="1:31" ht="12.75">
       <c r="A144" s="114" t="s">
         <v>500</v>
       </c>
@@ -14665,7 +14656,7 @@
       <c r="AC144" s="2"/>
       <c r="AD144" s="8"/>
     </row>
-    <row r="145" spans="1:31" ht="12.75" hidden="1">
+    <row r="145" spans="1:31" ht="12.75">
       <c r="A145" s="112" t="s">
         <v>413</v>
       </c>
@@ -14738,7 +14729,7 @@
       <c r="AD145" s="8"/>
       <c r="AE145" s="25"/>
     </row>
-    <row r="146" spans="1:31" ht="12.75" hidden="1">
+    <row r="146" spans="1:31" ht="12.75">
       <c r="A146" s="112" t="s">
         <v>414</v>
       </c>
@@ -14811,7 +14802,7 @@
       <c r="AD146" s="12"/>
       <c r="AE146" s="25"/>
     </row>
-    <row r="147" spans="1:31" ht="12.75" hidden="1">
+    <row r="147" spans="1:31" ht="12.75">
       <c r="A147" s="112" t="s">
         <v>415</v>
       </c>
@@ -14884,7 +14875,7 @@
       <c r="AD147" s="12"/>
       <c r="AE147" s="25"/>
     </row>
-    <row r="148" spans="1:31" ht="12.75" hidden="1">
+    <row r="148" spans="1:31" ht="12.75">
       <c r="A148" s="113" t="s">
         <v>500</v>
       </c>
@@ -14956,7 +14947,7 @@
       <c r="AC148" s="2"/>
       <c r="AD148" s="12"/>
     </row>
-    <row r="149" spans="1:31" ht="12.75" hidden="1">
+    <row r="149" spans="1:31" ht="12.75">
       <c r="A149" s="113" t="s">
         <v>413</v>
       </c>
@@ -15028,7 +15019,7 @@
       <c r="AC149" s="2"/>
       <c r="AD149" s="12"/>
     </row>
-    <row r="150" spans="1:31" ht="12.75" hidden="1">
+    <row r="150" spans="1:31" ht="12.75">
       <c r="A150" s="113" t="s">
         <v>414</v>
       </c>
@@ -15100,7 +15091,7 @@
       <c r="AC150" s="2"/>
       <c r="AD150" s="12"/>
     </row>
-    <row r="151" spans="1:31" ht="12.75" hidden="1">
+    <row r="151" spans="1:31" ht="12.75">
       <c r="A151" s="113" t="s">
         <v>415</v>
       </c>
@@ -15172,7 +15163,7 @@
       <c r="AC151" s="2"/>
       <c r="AD151" s="12"/>
     </row>
-    <row r="152" spans="1:31" ht="12.75" hidden="1">
+    <row r="152" spans="1:31" ht="12.75">
       <c r="A152" s="154" t="s">
         <v>500</v>
       </c>
@@ -15244,7 +15235,7 @@
       <c r="AC152" s="2"/>
       <c r="AD152" s="8"/>
     </row>
-    <row r="153" spans="1:31" ht="12.75" hidden="1">
+    <row r="153" spans="1:31" ht="12.75">
       <c r="A153" s="3" t="s">
         <v>413</v>
       </c>
@@ -15316,7 +15307,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="12.75" hidden="1">
+    <row r="154" spans="1:31" ht="12.75">
       <c r="A154" s="3" t="s">
         <v>414</v>
       </c>
@@ -15388,7 +15379,7 @@
       <c r="AD154"/>
       <c r="AE154"/>
     </row>
-    <row r="155" spans="1:31" ht="12.75" hidden="1">
+    <row r="155" spans="1:31" ht="12.75">
       <c r="A155" s="3" t="s">
         <v>415</v>
       </c>
@@ -15460,7 +15451,7 @@
       <c r="AD155"/>
       <c r="AE155"/>
     </row>
-    <row r="156" spans="1:31" ht="12.75" hidden="1">
+    <row r="156" spans="1:31" ht="12.75">
       <c r="A156" s="37" t="s">
         <v>500</v>
       </c>
@@ -15532,7 +15523,7 @@
       <c r="AD156"/>
       <c r="AE156"/>
     </row>
-    <row r="157" spans="1:31" ht="12.75" hidden="1">
+    <row r="157" spans="1:31" ht="12.75">
       <c r="A157" s="3" t="s">
         <v>413</v>
       </c>
@@ -15604,7 +15595,7 @@
       <c r="AD157"/>
       <c r="AE157"/>
     </row>
-    <row r="158" spans="1:31" ht="12.75" hidden="1">
+    <row r="158" spans="1:31" ht="12.75">
       <c r="A158" s="3" t="s">
         <v>414</v>
       </c>
@@ -15677,7 +15668,7 @@
       <c r="AD158"/>
       <c r="AE158"/>
     </row>
-    <row r="159" spans="1:31" ht="12.75" hidden="1">
+    <row r="159" spans="1:31" ht="12.75">
       <c r="A159" s="3" t="s">
         <v>415</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1215" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAFA67FA-E2FB-4AEC-A583-732C8540A694}"/>
+  <xr:revisionPtr revIDLastSave="1277" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7692134-C93C-4B42-BE6F-6BC8A9C2C3B6}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="accessoryList" sheetId="5" r:id="rId6"/>
     <sheet name="Data Lists" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2839" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2867" uniqueCount="638">
   <si>
     <t>Choose Qty</t>
   </si>
@@ -1950,6 +1950,33 @@
   </si>
   <si>
     <t>Beltone Boost Max S 9 95-DWHC Digital BTE</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital XC 4 61DRWC</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital XF 5 60SDRWC</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital XF 7 60SDRWC</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital XF 9 60SDRWC</t>
+  </si>
+  <si>
+    <t>Beltone XC 4 61DRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone XF 5 60SDRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone XF 7 60SDRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone XF 9 60SDRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>BCBS Blue365 Member</t>
   </si>
 </sst>
 </file>
@@ -2361,7 +2388,7 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2656,6 +2683,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3490,8 +3521,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V159" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V159" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}" name="HearingAids" displayName="HearingAids" ref="A1:V163" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+  <autoFilter ref="A1:V163" xr:uid="{0EDF487B-BC6A-43CC-A5E2-F07346E1A4ED}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V159">
     <sortCondition ref="I2:I159"/>
   </sortState>
@@ -3946,7 +3977,7 @@
         <v>586</v>
       </c>
       <c r="B3" s="171" t="s">
-        <v>496</v>
+        <v>632</v>
       </c>
       <c r="C3" s="172"/>
     </row>
@@ -3972,7 +4003,7 @@
         <v>61</v>
       </c>
       <c r="B7" s="171" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="C7" s="172"/>
     </row>
@@ -4020,14 +4051,14 @@
       </c>
       <c r="B13" s="75" cm="1">
         <f t="array" ref="B13">IF($B$3="","",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!A:A&amp;haList!I:I,haList!D:D))</f>
-        <v>5819</v>
+        <v>5579</v>
       </c>
       <c r="C13" s="74" t="s">
         <v>412</v>
       </c>
       <c r="D13" s="76" cm="1">
         <f t="array" ref="D13">IF($B$5=1,"",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!A:A&amp;haList!I:I,haList!D:D))</f>
-        <v>5819</v>
+        <v>5579</v>
       </c>
       <c r="F13" s="57"/>
     </row>
@@ -4037,14 +4068,14 @@
       </c>
       <c r="B14" s="61" cm="1">
         <f t="array" ref="B14">_xlfn.XLOOKUP($B$3,haList!$A:$A,-haList!$F:$F)</f>
-        <v>-1256.5</v>
+        <v>162.5</v>
       </c>
       <c r="C14" s="74" t="s">
         <v>538</v>
       </c>
       <c r="D14" s="61" cm="1">
         <f t="array" ref="D14">IF(B5=1,"",_xlfn.XLOOKUP($B$3,haList!$A:$A,-haList!$F:$F))</f>
-        <v>-1256.5</v>
+        <v>162.5</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
@@ -4055,14 +4086,14 @@
       </c>
       <c r="B15" s="75">
         <f>B13+B14</f>
-        <v>4562.5</v>
+        <v>5741.5</v>
       </c>
       <c r="C15" s="74" t="s">
         <v>587</v>
       </c>
       <c r="D15" s="77">
         <f>IF(B5=1,"",D13+D14)</f>
-        <v>4562.5</v>
+        <v>5741.5</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
@@ -4073,14 +4104,14 @@
       </c>
       <c r="B16" s="75" cm="1">
         <f t="array" ref="B16">_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,-haList!$J:$J)</f>
-        <v>-750</v>
+        <v>-3405</v>
       </c>
       <c r="C16" s="74" t="s">
         <v>588</v>
       </c>
       <c r="D16" s="75" cm="1">
         <f t="array" ref="D16">IF(B5=1,"",_xlfn.XLOOKUP($B$3&amp;$B$7,haList!$A:$A&amp;haList!$I:$I,-haList!$J:$J))</f>
-        <v>-750</v>
+        <v>-3405</v>
       </c>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
@@ -4091,14 +4122,14 @@
       </c>
       <c r="B17" s="75">
         <f>B15+B16</f>
-        <v>3812.5</v>
+        <v>2336.5</v>
       </c>
       <c r="C17" s="74" t="s">
         <v>589</v>
       </c>
       <c r="D17" s="77">
         <f>IF(B5=1,"",D15+D16)</f>
-        <v>3812.5</v>
+        <v>2336.5</v>
       </c>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
@@ -4127,14 +4158,14 @@
       </c>
       <c r="B19" s="79">
         <f>B17+B18</f>
-        <v>3812.5</v>
+        <v>2336.5</v>
       </c>
       <c r="C19" s="78" t="s">
         <v>591</v>
       </c>
       <c r="D19" s="80">
         <f>IF(B5=1,"",D17+D18)</f>
-        <v>3812.5</v>
+        <v>2336.5</v>
       </c>
       <c r="E19" s="57"/>
       <c r="F19" s="57"/>
@@ -4155,7 +4186,7 @@
       </c>
       <c r="C22" s="82">
         <f>B19</f>
-        <v>3812.5</v>
+        <v>2336.5</v>
       </c>
       <c r="D22" s="81"/>
       <c r="E22" s="57"/>
@@ -4168,7 +4199,7 @@
       </c>
       <c r="C23" s="83">
         <f>IF(B5=2,D19,0)</f>
-        <v>3812.5</v>
+        <v>2336.5</v>
       </c>
       <c r="D23" s="81"/>
       <c r="E23" s="57"/>
@@ -4218,7 +4249,7 @@
       </c>
       <c r="C27" s="82">
         <f>C22+C23+C24+C25+C26</f>
-        <v>7950</v>
+        <v>4998</v>
       </c>
       <c r="D27" s="66"/>
       <c r="E27" s="66"/>
@@ -4246,7 +4277,7 @@
       </c>
       <c r="C29" s="87">
         <f>C27+C28</f>
-        <v>8350</v>
+        <v>5398</v>
       </c>
       <c r="D29" s="86"/>
       <c r="E29" s="86"/>
@@ -4275,7 +4306,7 @@
       </c>
       <c r="C33" s="57">
         <f>C29</f>
-        <v>8350</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1" thickBot="1">
@@ -4291,7 +4322,7 @@
 IF('Price Calculator'!B33='Data Lists'!C6,800,
 IF(AND('Price Calculator'!B33='Data Lists'!C7,C33&lt;5555),C33*10%,
 IF(AND('Price Calculator'!B33='Data Lists'!C7,C33&gt;5555),C33-5000,""))))))</f>
-        <v>3350</v>
+        <v>539.80000000000007</v>
       </c>
       <c r="D34" s="57"/>
       <c r="F34" s="57"/>
@@ -4304,7 +4335,7 @@
       </c>
       <c r="C35" s="60">
         <f>C33-C34</f>
-        <v>5000</v>
+        <v>4858.2</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1"/>
@@ -4352,7 +4383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
-  <dimension ref="A1:AF232"/>
+  <dimension ref="A1:AF234"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="53.85546875" customWidth="1"/>
@@ -15742,17 +15773,76 @@
       <c r="AE159"/>
     </row>
     <row r="160" spans="1:31" ht="12.75">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
-      <c r="I160" s="8"/>
-      <c r="J160" s="8"/>
-      <c r="K160" s="8"/>
-      <c r="M160" s="2"/>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
-      <c r="Q160" s="4"/>
-      <c r="U160" s="2"/>
+      <c r="A160" s="173" t="s">
+        <v>629</v>
+      </c>
+      <c r="B160" s="174" t="s">
+        <v>633</v>
+      </c>
+      <c r="C160" s="55">
+        <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
+        <v>6043</v>
+      </c>
+      <c r="D160" s="143">
+        <v>2909</v>
+      </c>
+      <c r="E160" s="51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F160" s="144">
+        <f>HearingAids[[#This Row],[haMSRP]]-((HearingAids[[#This Row],[ListPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)</f>
+        <v>-112.5</v>
+      </c>
+      <c r="G160" s="38">
+        <f>HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]]</f>
+        <v>3021.5</v>
+      </c>
+      <c r="H160" s="101">
+        <v>6268</v>
+      </c>
+      <c r="I160" s="145" t="s">
+        <v>637</v>
+      </c>
+      <c r="J160" s="144">
+        <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
+        <v>1935</v>
+      </c>
+      <c r="K160" s="175">
+        <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
+        <v>1086.5</v>
+      </c>
+      <c r="L160" s="152">
+        <f>1199*2</f>
+        <v>2398</v>
+      </c>
+      <c r="M160" s="146"/>
+      <c r="N160" s="176">
+        <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
+        <v>1086.5</v>
+      </c>
+      <c r="O160" s="176">
+        <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P160" s="144"/>
+      <c r="Q160" s="15">
+        <v>1</v>
+      </c>
+      <c r="R160" s="157" t="s">
+        <v>9</v>
+      </c>
+      <c r="S160" s="22">
+        <v>225</v>
+      </c>
+      <c r="T160" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="U160" s="2">
+        <v>0</v>
+      </c>
+      <c r="V160" s="161" t="s">
+        <v>11</v>
+      </c>
       <c r="X160" s="2"/>
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
@@ -15762,37 +15852,155 @@
       <c r="AD160" s="2"/>
     </row>
     <row r="161" spans="1:30" ht="12.75">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
-      <c r="C161" s="3"/>
-      <c r="I161" s="8"/>
-      <c r="J161" s="8"/>
-      <c r="K161" s="8"/>
-      <c r="M161" s="2"/>
-      <c r="N161" s="2"/>
-      <c r="O161" s="2"/>
-      <c r="Q161" s="4"/>
-      <c r="U161" s="2"/>
+      <c r="A161" s="173" t="s">
+        <v>630</v>
+      </c>
+      <c r="B161" s="174" t="s">
+        <v>634</v>
+      </c>
+      <c r="C161" s="55">
+        <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
+        <v>7463</v>
+      </c>
+      <c r="D161" s="143">
+        <v>3569</v>
+      </c>
+      <c r="E161" s="51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F161" s="144">
+        <f>HearingAids[[#This Row],[haMSRP]]-((HearingAids[[#This Row],[ListPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)</f>
+        <v>-162.5</v>
+      </c>
+      <c r="G161" s="38">
+        <f>HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]]</f>
+        <v>3731.5</v>
+      </c>
+      <c r="H161" s="101">
+        <v>7788</v>
+      </c>
+      <c r="I161" s="145" t="s">
+        <v>637</v>
+      </c>
+      <c r="J161" s="144">
+        <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
+        <v>2095</v>
+      </c>
+      <c r="K161" s="175">
+        <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
+        <v>1636.5</v>
+      </c>
+      <c r="L161" s="152">
+        <f>1799*2</f>
+        <v>3598</v>
+      </c>
+      <c r="M161" s="146"/>
+      <c r="N161" s="176">
+        <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
+        <v>1636.5</v>
+      </c>
+      <c r="O161" s="176">
+        <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P161" s="144"/>
+      <c r="Q161" s="15">
+        <v>1</v>
+      </c>
+      <c r="R161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S161" s="39">
+        <v>325</v>
+      </c>
+      <c r="T161" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="U161" s="2">
+        <v>0</v>
+      </c>
+      <c r="V161" s="161" t="s">
+        <v>11</v>
+      </c>
       <c r="X161" s="2"/>
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
       <c r="AB161" s="2"/>
       <c r="AC161" s="2"/>
-      <c r="AD161" s="2"/>
+      <c r="AD161" s="8"/>
     </row>
     <row r="162" spans="1:30" ht="12.75">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
-      <c r="C162" s="3"/>
-      <c r="I162" s="8"/>
-      <c r="J162" s="8"/>
-      <c r="K162" s="8"/>
-      <c r="M162" s="2"/>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
-      <c r="Q162" s="4"/>
-      <c r="U162" s="2"/>
+      <c r="A162" s="173" t="s">
+        <v>631</v>
+      </c>
+      <c r="B162" s="174" t="s">
+        <v>635</v>
+      </c>
+      <c r="C162" s="55">
+        <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
+        <v>9323</v>
+      </c>
+      <c r="D162" s="143">
+        <v>4499</v>
+      </c>
+      <c r="E162" s="51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F162" s="144">
+        <f>HearingAids[[#This Row],[haMSRP]]-((HearingAids[[#This Row],[ListPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)</f>
+        <v>-162.5</v>
+      </c>
+      <c r="G162" s="38">
+        <f>HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]]</f>
+        <v>4661.5</v>
+      </c>
+      <c r="H162" s="101">
+        <v>9648</v>
+      </c>
+      <c r="I162" s="145" t="s">
+        <v>637</v>
+      </c>
+      <c r="J162" s="144">
+        <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
+        <v>2575</v>
+      </c>
+      <c r="K162" s="175">
+        <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
+        <v>2086.5</v>
+      </c>
+      <c r="L162" s="152">
+        <f>2249*2</f>
+        <v>4498</v>
+      </c>
+      <c r="M162" s="146"/>
+      <c r="N162" s="176">
+        <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2086.5</v>
+      </c>
+      <c r="O162" s="176">
+        <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P162" s="144"/>
+      <c r="Q162" s="15">
+        <v>1</v>
+      </c>
+      <c r="R162" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S162" s="39">
+        <v>325</v>
+      </c>
+      <c r="T162" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="U162" s="2">
+        <v>0</v>
+      </c>
+      <c r="V162" s="161" t="s">
+        <v>11</v>
+      </c>
       <c r="X162" s="2"/>
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
@@ -15802,24 +16010,83 @@
       <c r="AD162" s="8"/>
     </row>
     <row r="163" spans="1:30" ht="12.75">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="3"/>
-      <c r="I163" s="8"/>
-      <c r="J163" s="8"/>
-      <c r="K163" s="8"/>
-      <c r="M163" s="2"/>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
-      <c r="Q163" s="4"/>
-      <c r="U163" s="2"/>
+      <c r="A163" s="173" t="s">
+        <v>632</v>
+      </c>
+      <c r="B163" s="174" t="s">
+        <v>636</v>
+      </c>
+      <c r="C163" s="55">
+        <f>(HearingAids[[#This Row],[haMSRP]]*2)+HearingAids[[#This Row],[chargerPrice]]</f>
+        <v>11483</v>
+      </c>
+      <c r="D163" s="143">
+        <v>5579</v>
+      </c>
+      <c r="E163" s="51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F163" s="144">
+        <f>HearingAids[[#This Row],[haMSRP]]-((HearingAids[[#This Row],[ListPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)</f>
+        <v>-162.5</v>
+      </c>
+      <c r="G163" s="38">
+        <f>HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]]</f>
+        <v>5741.5</v>
+      </c>
+      <c r="H163" s="101">
+        <v>11808</v>
+      </c>
+      <c r="I163" s="145" t="s">
+        <v>637</v>
+      </c>
+      <c r="J163" s="144">
+        <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
+        <v>3405</v>
+      </c>
+      <c r="K163" s="175">
+        <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
+        <v>2336.5</v>
+      </c>
+      <c r="L163" s="152">
+        <f>2499*2</f>
+        <v>4998</v>
+      </c>
+      <c r="M163" s="146"/>
+      <c r="N163" s="176">
+        <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2336.5</v>
+      </c>
+      <c r="O163" s="176">
+        <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P163" s="144"/>
+      <c r="Q163" s="15">
+        <v>1</v>
+      </c>
+      <c r="R163" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S163" s="39">
+        <v>325</v>
+      </c>
+      <c r="T163" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="U163" s="2">
+        <v>0</v>
+      </c>
+      <c r="V163" s="161" t="s">
+        <v>11</v>
+      </c>
       <c r="X163" s="2"/>
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
       <c r="AB163" s="2"/>
       <c r="AC163" s="2"/>
-      <c r="AD163" s="8"/>
+      <c r="AD163" s="12"/>
     </row>
     <row r="164" spans="1:30" ht="12.75">
       <c r="A164" s="3"/>
@@ -15879,12 +16146,13 @@
       <c r="AA166" s="2"/>
       <c r="AB166" s="2"/>
       <c r="AC166" s="2"/>
-      <c r="AD166" s="12"/>
+      <c r="AD166" s="2"/>
     </row>
     <row r="167" spans="1:30" ht="12.75">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
+      <c r="H167" s="21"/>
       <c r="I167" s="8"/>
       <c r="J167" s="8"/>
       <c r="K167" s="8"/>
@@ -15905,6 +16173,7 @@
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
+      <c r="H168" s="21"/>
       <c r="I168" s="8"/>
       <c r="J168" s="8"/>
       <c r="K168" s="8"/>
@@ -15919,7 +16188,7 @@
       <c r="AA168" s="2"/>
       <c r="AB168" s="2"/>
       <c r="AC168" s="2"/>
-      <c r="AD168" s="2"/>
+      <c r="AD168" s="12"/>
     </row>
     <row r="169" spans="1:30" ht="12.75">
       <c r="A169" s="3"/>
@@ -15979,7 +16248,7 @@
       <c r="AA171" s="2"/>
       <c r="AB171" s="2"/>
       <c r="AC171" s="2"/>
-      <c r="AD171" s="12"/>
+      <c r="AD171" s="2"/>
     </row>
     <row r="172" spans="1:30" ht="12.75">
       <c r="A172" s="3"/>
@@ -16019,7 +16288,7 @@
       <c r="AA173" s="2"/>
       <c r="AB173" s="2"/>
       <c r="AC173" s="2"/>
-      <c r="AD173" s="2"/>
+      <c r="AD173" s="12"/>
     </row>
     <row r="174" spans="1:30" ht="12.75">
       <c r="A174" s="3"/>
@@ -16079,7 +16348,7 @@
       <c r="AA176" s="2"/>
       <c r="AB176" s="2"/>
       <c r="AC176" s="2"/>
-      <c r="AD176" s="12"/>
+      <c r="AD176" s="2"/>
     </row>
     <row r="177" spans="1:30" ht="12.75">
       <c r="A177" s="3"/>
@@ -16119,7 +16388,7 @@
       <c r="AA178" s="2"/>
       <c r="AB178" s="2"/>
       <c r="AC178" s="2"/>
-      <c r="AD178" s="2"/>
+      <c r="AD178" s="8"/>
     </row>
     <row r="179" spans="1:30" ht="12.75">
       <c r="A179" s="3"/>
@@ -16228,7 +16497,7 @@
       <c r="I184" s="8"/>
       <c r="J184" s="8"/>
       <c r="K184" s="8"/>
-      <c r="M184" s="22"/>
+      <c r="M184" s="2"/>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="Q184" s="4"/>
@@ -16248,7 +16517,7 @@
       <c r="I185" s="8"/>
       <c r="J185" s="8"/>
       <c r="K185" s="8"/>
-      <c r="M185" s="31"/>
+      <c r="M185" s="2"/>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="Q185" s="4"/>
@@ -16268,7 +16537,7 @@
       <c r="I186" s="8"/>
       <c r="J186" s="8"/>
       <c r="K186" s="8"/>
-      <c r="M186" s="31"/>
+      <c r="M186" s="22"/>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="Q186" s="4"/>
@@ -16279,7 +16548,7 @@
       <c r="AA186" s="2"/>
       <c r="AB186" s="2"/>
       <c r="AC186" s="2"/>
-      <c r="AD186" s="8"/>
+      <c r="AD186" s="12"/>
     </row>
     <row r="187" spans="1:30" ht="12.75">
       <c r="A187" s="3"/>
@@ -16333,45 +16602,45 @@
       <c r="O189" s="2"/>
       <c r="Q189" s="4"/>
       <c r="U189" s="2"/>
-      <c r="X189" s="2"/>
-      <c r="Y189" s="2"/>
-      <c r="Z189" s="2"/>
-      <c r="AA189" s="2"/>
-      <c r="AB189" s="2"/>
-      <c r="AC189" s="2"/>
-      <c r="AD189" s="12"/>
+      <c r="X189" s="22"/>
+      <c r="Y189" s="22"/>
+      <c r="Z189" s="22"/>
+      <c r="AA189" s="22"/>
+      <c r="AB189" s="22"/>
+      <c r="AD189" s="25"/>
     </row>
     <row r="190" spans="1:30" ht="12.75">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
-      <c r="I190" s="22"/>
-      <c r="J190" s="22"/>
-      <c r="K190" s="22"/>
+      <c r="I190" s="8"/>
+      <c r="J190" s="8"/>
+      <c r="K190" s="8"/>
       <c r="M190" s="31"/>
-      <c r="N190" s="22"/>
-      <c r="O190" s="22"/>
+      <c r="N190" s="2"/>
+      <c r="O190" s="2"/>
       <c r="Q190" s="4"/>
-      <c r="U190" s="22"/>
-      <c r="X190" s="22"/>
-      <c r="Y190" s="22"/>
-      <c r="Z190" s="22"/>
-      <c r="AA190" s="22"/>
-      <c r="AB190" s="22"/>
-      <c r="AD190" s="25"/>
+      <c r="U190" s="2"/>
+      <c r="X190" s="8"/>
+      <c r="Y190" s="31"/>
+      <c r="Z190" s="31"/>
+      <c r="AA190" s="31"/>
+      <c r="AB190" s="31"/>
+      <c r="AC190" s="31"/>
+      <c r="AD190" s="31"/>
     </row>
     <row r="191" spans="1:30" ht="12.75">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
-      <c r="C191" s="29"/>
-      <c r="I191" s="31"/>
-      <c r="J191" s="31"/>
-      <c r="K191" s="31"/>
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8"/>
+      <c r="K191" s="8"/>
       <c r="M191" s="31"/>
-      <c r="N191" s="31"/>
-      <c r="O191" s="31"/>
-      <c r="Q191" s="30"/>
-      <c r="U191" s="31"/>
+      <c r="N191" s="2"/>
+      <c r="O191" s="2"/>
+      <c r="Q191" s="4"/>
+      <c r="U191" s="2"/>
       <c r="X191" s="8"/>
       <c r="Y191" s="31"/>
       <c r="Z191" s="31"/>
@@ -16381,17 +16650,17 @@
       <c r="AD191" s="31"/>
     </row>
     <row r="192" spans="1:30" ht="12.75">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
-      <c r="C192" s="29"/>
-      <c r="I192" s="31"/>
-      <c r="J192" s="31"/>
-      <c r="K192" s="31"/>
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="I192" s="22"/>
+      <c r="J192" s="22"/>
+      <c r="K192" s="22"/>
       <c r="M192" s="31"/>
-      <c r="N192" s="31"/>
-      <c r="O192" s="31"/>
-      <c r="Q192" s="30"/>
-      <c r="U192" s="31"/>
+      <c r="N192" s="22"/>
+      <c r="O192" s="22"/>
+      <c r="Q192" s="4"/>
+      <c r="U192" s="22"/>
       <c r="X192" s="8"/>
       <c r="Y192" s="31"/>
       <c r="Z192" s="31"/>
@@ -17087,6 +17356,7 @@
       <c r="I227" s="31"/>
       <c r="J227" s="31"/>
       <c r="K227" s="31"/>
+      <c r="M227" s="31"/>
       <c r="N227" s="31"/>
       <c r="O227" s="31"/>
       <c r="Q227" s="30"/>
@@ -17106,6 +17376,7 @@
       <c r="I228" s="31"/>
       <c r="J228" s="31"/>
       <c r="K228" s="31"/>
+      <c r="M228" s="31"/>
       <c r="N228" s="31"/>
       <c r="O228" s="31"/>
       <c r="Q228" s="30"/>
@@ -17186,13 +17457,30 @@
       <c r="O232" s="31"/>
       <c r="Q232" s="30"/>
       <c r="U232" s="31"/>
-      <c r="X232" s="8"/>
-      <c r="Y232" s="31"/>
-      <c r="Z232" s="31"/>
-      <c r="AA232" s="31"/>
-      <c r="AB232" s="31"/>
-      <c r="AC232" s="31"/>
-      <c r="AD232" s="31"/>
+    </row>
+    <row r="233" spans="1:30" ht="12.75">
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
+      <c r="C233" s="29"/>
+      <c r="I233" s="31"/>
+      <c r="J233" s="31"/>
+      <c r="K233" s="31"/>
+      <c r="N233" s="31"/>
+      <c r="O233" s="31"/>
+      <c r="Q233" s="30"/>
+      <c r="U233" s="31"/>
+    </row>
+    <row r="234" spans="1:30" ht="12.75">
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
+      <c r="C234" s="29"/>
+      <c r="I234" s="31"/>
+      <c r="J234" s="31"/>
+      <c r="K234" s="31"/>
+      <c r="N234" s="31"/>
+      <c r="O234" s="31"/>
+      <c r="Q234" s="30"/>
+      <c r="U234" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -28079,7 +28367,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B02B6F-B860-41DC-9D50-B3B43A9E1932}">
-  <dimension ref="A2:E48"/>
+  <dimension ref="A2:E52"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
@@ -28104,11 +28392,11 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="str" cm="1">
-        <f t="array" ref="A3:A48">_xlfn.UNIQUE(_xlfn._xlws.SORT((HearingAids[haModel])))</f>
+        <f t="array" ref="A3:A52">_xlfn.UNIQUE(_xlfn._xlws.SORT((HearingAids[haModel])))</f>
         <v>Beltone BTE Digital Boost Max S 17 95-DWHC</v>
       </c>
       <c r="B3" t="str" cm="1">
-        <f t="array" ref="B3:B22">_xlfn.UNIQUE(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(HearingAids[Discount Type 2], HearingAids[Discount Type 2]&lt;&gt;"")))</f>
+        <f t="array" ref="B3:B23">_xlfn.UNIQUE(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(HearingAids[Discount Type 2], HearingAids[Discount Type 2]&lt;&gt;"")))</f>
         <v>&lt;none&gt;</v>
       </c>
       <c r="C3" t="s">
@@ -28131,7 +28419,7 @@
         <v>Beltone BTE Digital Boost Max S 6 95-DWHC</v>
       </c>
       <c r="B5" t="str">
-        <v>Early Lease Upgrade</v>
+        <v>BCBS Blue365 Member</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -28142,7 +28430,7 @@
         <v>Beltone BTE Digital Boost Max S 9 95-DWHC</v>
       </c>
       <c r="B6" t="str">
-        <v>Envision 17 Special</v>
+        <v>Early Lease Upgrade</v>
       </c>
       <c r="C6" t="s">
         <v>596</v>
@@ -28153,7 +28441,7 @@
         <v>Beltone BTE Digital Boost Ultra 17 86DWHT</v>
       </c>
       <c r="B7" t="str">
-        <v>Envision 6 Special</v>
+        <v>Envision 17 Special</v>
       </c>
       <c r="C7" t="s">
         <v>65</v>
@@ -28164,7 +28452,7 @@
         <v>Beltone BTE Digital Boost Ultra 17 95DWT</v>
       </c>
       <c r="B8" t="str">
-        <v>Envision 9 Special</v>
+        <v>Envision 6 Special</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -28172,7 +28460,7 @@
         <v>Beltone BTE Digital Boost Ultra 6 86DWHT</v>
       </c>
       <c r="B9" t="str">
-        <v>Fast Funding</v>
+        <v>Envision 9 Special</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -28180,7 +28468,7 @@
         <v>Beltone BTE Digital Boost Ultra 6 95DWT</v>
       </c>
       <c r="B10" t="str">
-        <v>GHB Competitive</v>
+        <v>Fast Funding</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -28188,7 +28476,7 @@
         <v>Beltone BTE Digital Boost Ultra 9 86DWHT</v>
       </c>
       <c r="B11" t="str">
-        <v>HCS Competitive</v>
+        <v>GHB Competitive</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -28196,7 +28484,7 @@
         <v>Beltone BTE Digital Boost Ultra 9 95DWT</v>
       </c>
       <c r="B12" t="str">
-        <v>HearUSA Competitive</v>
+        <v>HCS Competitive</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -28204,7 +28492,7 @@
         <v>Beltone BTE Digital Rely 2 66DW</v>
       </c>
       <c r="B13" t="str">
-        <v>Humana</v>
+        <v>HearUSA Competitive</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -28212,7 +28500,7 @@
         <v>Beltone BTE Digital Rely 2 76DW</v>
       </c>
       <c r="B14" t="str">
-        <v>Marketing Offer</v>
+        <v>Humana</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -28220,7 +28508,7 @@
         <v>Beltone BTE Digital Rely 2 86DWH</v>
       </c>
       <c r="B15" t="str">
-        <v>Martins Point Competitive</v>
+        <v>Marketing Offer</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -28228,7 +28516,7 @@
         <v>Beltone BTE Digital Rely 2 95DW</v>
       </c>
       <c r="B16" t="str">
-        <v>Nations Hearing Competitive</v>
+        <v>Martins Point Competitive</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -28236,7 +28524,7 @@
         <v>Beltone BTE Digital Rely 3 66DW</v>
       </c>
       <c r="B17" t="str">
-        <v>Open House Special</v>
+        <v>Nations Hearing Competitive</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -28244,7 +28532,7 @@
         <v>Beltone BTE Digital Rely 3 76DW</v>
       </c>
       <c r="B18" t="str">
-        <v>Tri-Care</v>
+        <v>Open House Special</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -28252,7 +28540,7 @@
         <v>Beltone BTE Digital Rely 3 86DWH</v>
       </c>
       <c r="B19" t="str">
-        <v>TruHearing Competitive</v>
+        <v>Tri-Care</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -28260,7 +28548,7 @@
         <v>Beltone BTE Digital Rely 3 95DW</v>
       </c>
       <c r="B20" t="str">
-        <v>UHCH Competitive</v>
+        <v>TruHearing Competitive</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -28268,7 +28556,7 @@
         <v>Beltone BTE Digital Rely 4 66DW</v>
       </c>
       <c r="B21" t="str">
-        <v>Veterans Discount</v>
+        <v>UHCH Competitive</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -28276,13 +28564,16 @@
         <v>Beltone BTE Digital Rely 4 76DW</v>
       </c>
       <c r="B22" t="str">
-        <v>WellCare Competitive</v>
+        <v>Veterans Discount</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="str">
         <v>Beltone BTE Digital Rely 4 86DWH</v>
       </c>
+      <c r="B23" t="str">
+        <v>WellCare Competitive</v>
+      </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="str">
@@ -28407,6 +28698,26 @@
     <row r="48" spans="1:1">
       <c r="A48" t="str">
         <v>Beltone RIE Digital Serene 9 62SDRWC</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="str">
+        <v>Beltone RIE Digital XC 4 61DRWC</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="str">
+        <v>Beltone RIE Digital XF 5 60SDRWC</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="str">
+        <v>Beltone RIE Digital XF 7 60SDRWC</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="str">
+        <v>Beltone RIE Digital XF 9 60SDRWC</v>
       </c>
     </row>
   </sheetData>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -21,7 +21,7 @@
     <sheet name="accessoryList" sheetId="5" r:id="rId6"/>
     <sheet name="Data Lists" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/npacheco_beltonene_com/Documents/Pricing Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1277" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7692134-C93C-4B42-BE6F-6BC8A9C2C3B6}"/>
+  <xr:revisionPtr revIDLastSave="1278" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65BC2999-9C93-460F-9BB6-5B3636016658}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -2388,7 +2388,7 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2683,10 +2683,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4388,13 +4384,13 @@
   <cols>
     <col min="1" max="1" width="53.85546875" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="23" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -15773,10 +15769,10 @@
       <c r="AE159"/>
     </row>
     <row r="160" spans="1:31" ht="12.75">
-      <c r="A160" s="173" t="s">
+      <c r="A160" s="142" t="s">
         <v>629</v>
       </c>
-      <c r="B160" s="174" t="s">
+      <c r="B160" s="142" t="s">
         <v>633</v>
       </c>
       <c r="C160" s="55">
@@ -15807,7 +15803,7 @@
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
         <v>1935</v>
       </c>
-      <c r="K160" s="175">
+      <c r="K160" s="144">
         <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
         <v>1086.5</v>
       </c>
@@ -15816,11 +15812,11 @@
         <v>2398</v>
       </c>
       <c r="M160" s="146"/>
-      <c r="N160" s="176">
+      <c r="N160" s="146">
         <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
         <v>1086.5</v>
       </c>
-      <c r="O160" s="176">
+      <c r="O160" s="146">
         <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
@@ -15852,10 +15848,10 @@
       <c r="AD160" s="2"/>
     </row>
     <row r="161" spans="1:30" ht="12.75">
-      <c r="A161" s="173" t="s">
+      <c r="A161" s="142" t="s">
         <v>630</v>
       </c>
-      <c r="B161" s="174" t="s">
+      <c r="B161" s="142" t="s">
         <v>634</v>
       </c>
       <c r="C161" s="55">
@@ -15886,7 +15882,7 @@
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
         <v>2095</v>
       </c>
-      <c r="K161" s="175">
+      <c r="K161" s="144">
         <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
         <v>1636.5</v>
       </c>
@@ -15895,11 +15891,11 @@
         <v>3598</v>
       </c>
       <c r="M161" s="146"/>
-      <c r="N161" s="176">
+      <c r="N161" s="146">
         <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
         <v>1636.5</v>
       </c>
-      <c r="O161" s="176">
+      <c r="O161" s="146">
         <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
@@ -15931,10 +15927,10 @@
       <c r="AD161" s="8"/>
     </row>
     <row r="162" spans="1:30" ht="12.75">
-      <c r="A162" s="173" t="s">
+      <c r="A162" s="142" t="s">
         <v>631</v>
       </c>
-      <c r="B162" s="174" t="s">
+      <c r="B162" s="142" t="s">
         <v>635</v>
       </c>
       <c r="C162" s="55">
@@ -15965,7 +15961,7 @@
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
         <v>2575</v>
       </c>
-      <c r="K162" s="175">
+      <c r="K162" s="144">
         <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
         <v>2086.5</v>
       </c>
@@ -15974,11 +15970,11 @@
         <v>4498</v>
       </c>
       <c r="M162" s="146"/>
-      <c r="N162" s="176">
+      <c r="N162" s="146">
         <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
         <v>2086.5</v>
       </c>
-      <c r="O162" s="176">
+      <c r="O162" s="146">
         <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>
@@ -16010,10 +16006,10 @@
       <c r="AD162" s="8"/>
     </row>
     <row r="163" spans="1:30" ht="12.75">
-      <c r="A163" s="173" t="s">
+      <c r="A163" s="142" t="s">
         <v>632</v>
       </c>
-      <c r="B163" s="174" t="s">
+      <c r="B163" s="142" t="s">
         <v>636</v>
       </c>
       <c r="C163" s="55">
@@ -16044,7 +16040,7 @@
         <f>(HearingAids[[#This Row],[haMSRP]]-HearingAids[[#This Row],[Discount Amount 1]])-(HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2</f>
         <v>3405</v>
       </c>
-      <c r="K163" s="175">
+      <c r="K163" s="144">
         <f>HearingAids[[#This Row],[HAListPrice]]-HearingAids[[#This Row],[Discount Amount 2]]</f>
         <v>2336.5</v>
       </c>
@@ -16053,11 +16049,11 @@
         <v>4998</v>
       </c>
       <c r="M163" s="146"/>
-      <c r="N163" s="176">
+      <c r="N163" s="146">
         <f>((HearingAids[[#This Row],[haNetPriceBinural]]-HearingAids[[#This Row],[chargerPrice]])/2)-HearingAids[[#This Row],[haNetPriceBinural2]]</f>
         <v>2336.5</v>
       </c>
-      <c r="O163" s="176">
+      <c r="O163" s="146">
         <f>HearingAids[[#This Row],[haNetPrice]]-HearingAids[[#This Row],[Discount Amount 3]]</f>
         <v>0</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1300" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F43D29E-A91E-4A1A-A8D1-E67A92FF98BB}"/>
+  <xr:revisionPtr revIDLastSave="1304" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA140AE7-784E-4339-9236-1B5F3EBD627D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="639">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -1978,6 +1978,9 @@
   </si>
   <si>
     <t>AllWell Lease Upgrade</t>
+  </si>
+  <si>
+    <t>VIP Event</t>
   </si>
 </sst>
 </file>
@@ -2317,7 +2320,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2502,6 +2505,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2513,14 +2524,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2528,6 +2538,268 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="60">
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3079,268 +3351,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3355,98 +3365,92 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V163" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="A1:V163" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="Open House Special"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V164" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+  <autoFilter ref="A1:V164" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V150">
     <sortCondition ref="A1:A163"/>
   </sortState>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A759776D-F1C7-439A-A017-B16601DE8834}" name="haModel" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{DB2EB2AC-0D9E-4335-9000-DEA2CFAF79BE}" name="haDescription" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{A8AFAABA-873B-479C-A0A1-068DA38EFBB1}" name="BiNuralMSRP w/Charger" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{A759776D-F1C7-439A-A017-B16601DE8834}" name="haModel" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{DB2EB2AC-0D9E-4335-9000-DEA2CFAF79BE}" name="haDescription" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{A8AFAABA-873B-479C-A0A1-068DA38EFBB1}" name="BiNuralMSRP w/Charger" dataDxfId="55">
       <calculatedColumnFormula>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4320CF9C-2A9B-4102-AF79-01876AA8A2EF}" name="haMSRP" dataDxfId="18" dataCellStyle="Comma"/>
-    <tableColumn id="17" xr3:uid="{4C421CF5-5A00-4BAB-9342-FFFA22CE1848}" name="Discount Type 1" dataDxfId="17" dataCellStyle="Comma"/>
-    <tableColumn id="18" xr3:uid="{8DC0A1BB-67C5-4FA7-9D6C-1F3492CDCE35}" name="Discount Amount 1" dataDxfId="16" dataCellStyle="Comma">
+    <tableColumn id="3" xr3:uid="{4320CF9C-2A9B-4102-AF79-01876AA8A2EF}" name="haMSRP" dataDxfId="54" dataCellStyle="Comma"/>
+    <tableColumn id="17" xr3:uid="{4C421CF5-5A00-4BAB-9342-FFFA22CE1848}" name="Discount Type 1" dataDxfId="53" dataCellStyle="Comma"/>
+    <tableColumn id="18" xr3:uid="{8DC0A1BB-67C5-4FA7-9D6C-1F3492CDCE35}" name="Discount Amount 1" dataDxfId="52" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3C382293-5620-4D91-9805-F4C06BA1B79D}" name="HAListPrice" dataDxfId="15" dataCellStyle="Comma">
+    <tableColumn id="14" xr3:uid="{3C382293-5620-4D91-9805-F4C06BA1B79D}" name="HAListPrice" dataDxfId="51" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9BCEF15A-97C4-45E4-AD6E-381196FF2F4C}" name="ListPriceBinural" dataDxfId="14" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{39D3FD35-3ACA-4445-A872-4D74E2EF38DC}" name="Discount Type 2" dataDxfId="13" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{00DDF5BF-EC07-4D8E-95CD-80770F4B2F7B}" name="Discount Amount 2" dataDxfId="12" dataCellStyle="Comma">
+    <tableColumn id="8" xr3:uid="{9BCEF15A-97C4-45E4-AD6E-381196FF2F4C}" name="ListPriceBinural" dataDxfId="50" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{39D3FD35-3ACA-4445-A872-4D74E2EF38DC}" name="Discount Type 2" dataDxfId="49" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{00DDF5BF-EC07-4D8E-95CD-80770F4B2F7B}" name="Discount Amount 2" dataDxfId="48" dataCellStyle="Comma">
       <calculatedColumnFormula>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A092CA1D-CDF6-4BEE-9660-5E274D9BBCB7}" name="haNetPrice" dataDxfId="11" dataCellStyle="Comma">
+    <tableColumn id="7" xr3:uid="{A092CA1D-CDF6-4BEE-9660-5E274D9BBCB7}" name="haNetPrice" dataDxfId="47" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{A444CAEB-7549-4620-A20C-551B5BE7881A}" name="haNetPriceBinural" dataDxfId="10" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{863CE0AE-0F5F-4D32-A9DC-1629115B0F70}" name="Discount Type 3" dataDxfId="9" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{A9C4A9DC-EFB5-4D09-8ADA-EFC229107602}" name="Discount Amount 3" dataDxfId="8" dataCellStyle="Comma">
+    <tableColumn id="20" xr3:uid="{A444CAEB-7549-4620-A20C-551B5BE7881A}" name="haNetPriceBinural" dataDxfId="46" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{863CE0AE-0F5F-4D32-A9DC-1629115B0F70}" name="Discount Type 3" dataDxfId="45" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{A9C4A9DC-EFB5-4D09-8ADA-EFC229107602}" name="Discount Amount 3" dataDxfId="44" dataCellStyle="Comma">
       <calculatedColumnFormula>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{7CBDD182-D316-4241-BE01-D84B5F3CE9AD}" name="haNetPrice2" dataDxfId="7" dataCellStyle="Comma">
+    <tableColumn id="22" xr3:uid="{7CBDD182-D316-4241-BE01-D84B5F3CE9AD}" name="haNetPrice2" dataDxfId="43" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{25381E46-1821-4592-B7AE-7DCCB3D5FF9F}" name="haNetPriceBinural2" dataDxfId="6" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{0C52264D-EACD-4040-AD20-A870B977D0E1}" name="paFittingFee" dataDxfId="5" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{6B597A7B-6B6C-463B-B14D-B782009871B6}" name="chargerType" dataDxfId="4" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{E5E93448-BE27-43BD-8173-C3E29A57EB56}" name="chargerPrice" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{F65D1D5F-35EF-4BFA-A7D0-F4C8368206E1}" name="haReceiverType" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{E15C872A-F3DF-4E26-9A56-6C33CBF526D3}" name="haReceiverPrice" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{2FF24650-9052-4D7C-908B-99CBF45A3D62}" name="haReceiverDiscountDescription" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="16" xr3:uid="{25381E46-1821-4592-B7AE-7DCCB3D5FF9F}" name="haNetPriceBinural2" dataDxfId="42" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{0C52264D-EACD-4040-AD20-A870B977D0E1}" name="paFittingFee" dataDxfId="41" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{6B597A7B-6B6C-463B-B14D-B782009871B6}" name="chargerType" dataDxfId="40" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{E5E93448-BE27-43BD-8173-C3E29A57EB56}" name="chargerPrice" dataDxfId="39" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{F65D1D5F-35EF-4BFA-A7D0-F4C8368206E1}" name="haReceiverType" dataDxfId="38" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{E15C872A-F3DF-4E26-9A56-6C33CBF526D3}" name="haReceiverPrice" dataDxfId="37" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{2FF24650-9052-4D7C-908B-99CBF45A3D62}" name="haReceiverDiscountDescription" dataDxfId="36" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="35">
   <autoFilter ref="A1:I260" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H286">
     <sortCondition ref="H1:H286"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="57">
+    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="33">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="56"/>
-    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23">
   <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H74">
     <sortCondition ref="H1:H74"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{FDC3E4DD-A231-46DD-8097-7C0DC18260BD}" name="barcodeName"/>
-    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="46">
+    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="22">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{D0382781-2AC8-4DE6-BF59-9B38B78B1184}" name="remoteModel"/>
     <tableColumn id="4" xr3:uid="{9B080694-7BEA-4586-AA70-DDEC1D67D699}" name="remoteType"/>
     <tableColumn id="7" xr3:uid="{CCB41D66-8697-4FAF-A74F-5F54F6CCA4F8}" name="remoteListAmount"/>
-    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="20">
       <calculatedColumnFormula>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{435AFC97-0382-475D-9332-93EDAB756C8B}" name="remoteDiscountDescription"/>
@@ -3456,37 +3460,37 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9E35851D-E21C-4957-852B-C619133CF977}" name="Table4" displayName="Table4" ref="A1:H3" totalsRowShown="0" headerRowDxfId="43" dataDxfId="41" headerRowBorderDxfId="42" tableBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9E35851D-E21C-4957-852B-C619133CF977}" name="Table4" displayName="Table4" ref="A1:H3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16">
   <autoFilter ref="A1:H3" xr:uid="{9E35851D-E21C-4957-852B-C619133CF977}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{9C5C5DE5-EA97-4EF1-8892-EBFCAC4443EA}" name="barcodeName" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{3987A654-3331-4022-95F5-BEF488FDFD5D}" name="barcode" dataDxfId="38">
+    <tableColumn id="1" xr3:uid="{9C5C5DE5-EA97-4EF1-8892-EBFCAC4443EA}" name="barcodeName" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{3987A654-3331-4022-95F5-BEF488FDFD5D}" name="barcode" dataDxfId="14">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B575D7DB-8A17-44F2-812F-84D8DF10D3DD}" name="serviceDescription" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{1E8BF5D4-6F7F-4C9F-B1C6-A5382AB6523A}" name="serviceDiscountDescription" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{A104B7ED-7164-4645-80F4-4FB3B815FA1C}" name="serviceListAmount" dataDxfId="35" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{FA21F863-CA81-4450-AB48-77E6CBCB2D99}" name="serviceDiscountAmount" dataDxfId="34" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{0C0AAA86-C611-4A7B-8F6A-7547563ECBBB}" name="serviceAmount" dataDxfId="33" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{BA455156-79BF-4EC7-BA14-3484B2B4810B}" name="paFittingFee" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{B575D7DB-8A17-44F2-812F-84D8DF10D3DD}" name="serviceDescription" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{1E8BF5D4-6F7F-4C9F-B1C6-A5382AB6523A}" name="serviceDiscountDescription" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{A104B7ED-7164-4645-80F4-4FB3B815FA1C}" name="serviceListAmount" dataDxfId="11" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{FA21F863-CA81-4450-AB48-77E6CBCB2D99}" name="serviceDiscountAmount" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{0C0AAA86-C611-4A7B-8F6A-7547563ECBBB}" name="serviceAmount" dataDxfId="9" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{BA455156-79BF-4EC7-BA14-3484B2B4810B}" name="paFittingFee" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{06EED7A3-D2B4-46BC-8F41-FB11FC20F42F}" name="Table5" displayName="Table5" ref="A1:G3" totalsRowShown="0" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{06EED7A3-D2B4-46BC-8F41-FB11FC20F42F}" name="Table5" displayName="Table5" ref="A1:G3" totalsRowShown="0" dataDxfId="7">
   <autoFilter ref="A1:G3" xr:uid="{06EED7A3-D2B4-46BC-8F41-FB11FC20F42F}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA5C7967-7D68-4146-84DE-1135A119CC3D}" name="barcodeName" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{C49A42F5-93EA-4670-959A-42455600C7C8}" name="barcode" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{EA5C7967-7D68-4146-84DE-1135A119CC3D}" name="barcodeName" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{C49A42F5-93EA-4670-959A-42455600C7C8}" name="barcode" dataDxfId="5">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2609A236-2D4A-49A0-BD07-CC9B0426F536}" name="accessoryDescription" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{9F5155AE-6C5F-4BA4-AD9F-DAE0C8053CCF}" name="accessoryDiscountDescription" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{CE967C46-B3C7-4797-BD2D-C5D197F6260B}" name="accessoryListAmount" dataDxfId="26" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{CAA4A522-ACE9-4EE8-A795-EFB2F9D3E99B}" name="accessoryDiscountAmount" dataDxfId="25" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{C6197BEF-5482-4860-814F-46EEEB1E034B}" name="accessoryAmount" dataDxfId="24" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{2609A236-2D4A-49A0-BD07-CC9B0426F536}" name="accessoryDescription" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{9F5155AE-6C5F-4BA4-AD9F-DAE0C8053CCF}" name="accessoryDiscountDescription" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{CE967C46-B3C7-4797-BD2D-C5D197F6260B}" name="accessoryListAmount" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{CAA4A522-ACE9-4EE8-A795-EFB2F9D3E99B}" name="accessoryDiscountAmount" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{C6197BEF-5482-4860-814F-46EEEB1E034B}" name="accessoryAmount" dataDxfId="0" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3790,18 +3794,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7B380E-1396-4B6E-A468-8A3D9AA81345}">
   <dimension ref="A2:I36"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="36.09765625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="28" customWidth="1"/>
-    <col min="4" max="5" width="19.296875" style="28" customWidth="1"/>
-    <col min="6" max="6" width="38.296875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.09765625" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="9.09765625" style="28"/>
+    <col min="4" max="5" width="19.28515625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="13" thickBot="1">
+    <row r="2" spans="1:8" ht="13.5" thickBot="1">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
@@ -3811,21 +3815,21 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
     </row>
-    <row r="3" spans="1:8" ht="13" thickBot="1">
+    <row r="3" spans="1:8" ht="13.5" thickBot="1">
       <c r="A3" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="101"/>
+      <c r="C3" s="107"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="1:8" ht="13" thickBot="1">
+    <row r="4" spans="1:8" ht="13.5" thickBot="1">
       <c r="A4" s="62"/>
       <c r="B4" s="44"/>
       <c r="C4" s="44"/>
@@ -3835,14 +3839,14 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
     </row>
-    <row r="5" spans="1:8" ht="13" thickBot="1">
+    <row r="5" spans="1:8" ht="13.5" thickBot="1">
       <c r="A5" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="100">
+      <c r="B5" s="106">
         <v>2</v>
       </c>
-      <c r="C5" s="101"/>
+      <c r="C5" s="107"/>
       <c r="D5" s="44"/>
       <c r="E5" s="44"/>
       <c r="F5" s="44"/>
@@ -3859,14 +3863,14 @@
       <c r="G6" s="29"/>
       <c r="H6" s="30"/>
     </row>
-    <row r="7" spans="1:8" ht="13" thickBot="1">
+    <row r="7" spans="1:8" ht="13.5" thickBot="1">
       <c r="A7" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="101"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="44"/>
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
@@ -3895,7 +3899,7 @@
       <c r="G10" s="63"/>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="1:8" ht="13" thickBot="1">
+    <row r="11" spans="1:8" ht="13.5" thickBot="1">
       <c r="A11" s="64"/>
       <c r="B11" s="64"/>
       <c r="C11" s="64"/>
@@ -3905,7 +3909,7 @@
       <c r="G11" s="63"/>
       <c r="H11" s="44"/>
     </row>
-    <row r="12" spans="1:8" ht="13">
+    <row r="12" spans="1:8">
       <c r="A12" s="31" t="s">
         <v>6</v>
       </c>
@@ -4225,9 +4229,9 @@
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="99"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99"/>
+      <c r="A30" s="105"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="26"/>
@@ -4358,35 +4362,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
   <dimension ref="A1:AF234"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="53.8984375" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="28.59765625" customWidth="1"/>
-    <col min="4" max="4" width="12.8984375" customWidth="1"/>
-    <col min="5" max="5" width="20.09765625" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="20.296875" customWidth="1"/>
-    <col min="9" max="9" width="25.69921875" customWidth="1"/>
-    <col min="10" max="10" width="23.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="24.09765625" customWidth="1"/>
-    <col min="16" max="16" width="23.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="24.140625" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" style="42" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="38" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.09765625" customWidth="1"/>
-    <col min="25" max="25" width="16.8984375" customWidth="1"/>
-    <col min="26" max="26" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="9.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.8984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.140625" customWidth="1"/>
+    <col min="25" max="25" width="16.85546875" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="9.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -4464,7 +4468,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="12.5" hidden="1">
+    <row r="2" spans="1:31" ht="12.75">
       <c r="A2" s="44" t="s">
         <v>130</v>
       </c>
@@ -4534,7 +4538,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="12.5" hidden="1">
+    <row r="3" spans="1:31" ht="12.75">
       <c r="A3" s="44" t="s">
         <v>130</v>
       </c>
@@ -4603,7 +4607,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="12.5" hidden="1">
+    <row r="4" spans="1:31" ht="12.75">
       <c r="A4" s="44" t="s">
         <v>130</v>
       </c>
@@ -4675,7 +4679,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="12.5">
+    <row r="5" spans="1:31" ht="12.75">
       <c r="A5" s="44" t="s">
         <v>130</v>
       </c>
@@ -4747,7 +4751,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="12.5" hidden="1">
+    <row r="6" spans="1:31" ht="12.75">
       <c r="A6" s="44" t="s">
         <v>120</v>
       </c>
@@ -4814,7 +4818,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="12.5" hidden="1">
+    <row r="7" spans="1:31" ht="12.75">
       <c r="A7" s="44" t="s">
         <v>120</v>
       </c>
@@ -4878,7 +4882,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="12.5" hidden="1">
+    <row r="8" spans="1:31" ht="12.75">
       <c r="A8" s="44" t="s">
         <v>61</v>
       </c>
@@ -4947,7 +4951,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="12.5" hidden="1">
+    <row r="9" spans="1:31" ht="12.75">
       <c r="A9" s="44" t="s">
         <v>64</v>
       </c>
@@ -5016,7 +5020,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="12.5" hidden="1">
+    <row r="10" spans="1:31" ht="12.75">
       <c r="A10" s="44" t="s">
         <v>66</v>
       </c>
@@ -5085,7 +5089,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="12.5" hidden="1">
+    <row r="11" spans="1:31" ht="12.75">
       <c r="A11" s="44" t="s">
         <v>70</v>
       </c>
@@ -5154,7 +5158,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="12.5" hidden="1">
+    <row r="12" spans="1:31" ht="12.75">
       <c r="A12" s="44" t="s">
         <v>72</v>
       </c>
@@ -5223,7 +5227,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="12.5" hidden="1">
+    <row r="13" spans="1:31" ht="12.75">
       <c r="A13" s="44" t="s">
         <v>75</v>
       </c>
@@ -5292,7 +5296,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="12.5" hidden="1">
+    <row r="14" spans="1:31" ht="12.75">
       <c r="A14" s="44" t="s">
         <v>77</v>
       </c>
@@ -5359,7 +5363,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="12.5" hidden="1">
+    <row r="15" spans="1:31" ht="12.75">
       <c r="A15" s="44" t="s">
         <v>80</v>
       </c>
@@ -5427,7 +5431,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="12.5" hidden="1">
+    <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="44" t="s">
         <v>82</v>
       </c>
@@ -5497,7 +5501,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="12.5" hidden="1">
+    <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="44" t="s">
         <v>84</v>
       </c>
@@ -5566,7 +5570,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="12.5" hidden="1">
+    <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="44" t="s">
         <v>86</v>
       </c>
@@ -5635,7 +5639,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="12.5" hidden="1">
+    <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="44" t="s">
         <v>88</v>
       </c>
@@ -5704,7 +5708,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="12.5" hidden="1">
+    <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="44" t="s">
         <v>90</v>
       </c>
@@ -5773,7 +5777,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="12.5" hidden="1">
+    <row r="21" spans="1:31" ht="12.75">
       <c r="A21" s="44" t="s">
         <v>92</v>
       </c>
@@ -5842,7 +5846,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="12.5" hidden="1">
+    <row r="22" spans="1:31" ht="12.75">
       <c r="A22" s="44" t="s">
         <v>94</v>
       </c>
@@ -5911,7 +5915,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="12.5" hidden="1">
+    <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="44" t="s">
         <v>96</v>
       </c>
@@ -5977,7 +5981,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="12.5" hidden="1">
+    <row r="24" spans="1:31" ht="12.75">
       <c r="A24" s="44" t="s">
         <v>98</v>
       </c>
@@ -6044,7 +6048,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="12.5" hidden="1">
+    <row r="25" spans="1:31" ht="12.75">
       <c r="A25" s="44" t="s">
         <v>100</v>
       </c>
@@ -6112,7 +6116,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="12.5" hidden="1">
+    <row r="26" spans="1:31" ht="12.75">
       <c r="A26" s="44" t="s">
         <v>102</v>
       </c>
@@ -6182,7 +6186,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="12.5" hidden="1">
+    <row r="27" spans="1:31" ht="12.75">
       <c r="A27" s="44" t="s">
         <v>104</v>
       </c>
@@ -6252,7 +6256,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="12.5" hidden="1">
+    <row r="28" spans="1:31" ht="12.75">
       <c r="A28" s="44" t="s">
         <v>106</v>
       </c>
@@ -6321,7 +6325,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="12.5" hidden="1">
+    <row r="29" spans="1:31" ht="12.75">
       <c r="A29" s="44" t="s">
         <v>108</v>
       </c>
@@ -6390,7 +6394,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="12.5" hidden="1">
+    <row r="30" spans="1:31" ht="12.75">
       <c r="A30" s="44" t="s">
         <v>110</v>
       </c>
@@ -6459,7 +6463,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="12.5" hidden="1">
+    <row r="31" spans="1:31" ht="12.75">
       <c r="A31" s="44" t="s">
         <v>112</v>
       </c>
@@ -6528,7 +6532,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="12.5" hidden="1">
+    <row r="32" spans="1:31" ht="12.75">
       <c r="A32" s="44" t="s">
         <v>114</v>
       </c>
@@ -6595,7 +6599,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="12.5" hidden="1">
+    <row r="33" spans="1:31" ht="12.75">
       <c r="A33" s="44" t="s">
         <v>116</v>
       </c>
@@ -6662,7 +6666,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="12.5" hidden="1">
+    <row r="34" spans="1:31" ht="12.75">
       <c r="A34" s="44" t="s">
         <v>118</v>
       </c>
@@ -6729,7 +6733,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="12.5" hidden="1">
+    <row r="35" spans="1:31" ht="12.75">
       <c r="A35" s="44" t="s">
         <v>132</v>
       </c>
@@ -6798,7 +6802,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="12.5" hidden="1">
+    <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="44" t="s">
         <v>132</v>
       </c>
@@ -6868,7 +6872,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="12.5" hidden="1">
+    <row r="37" spans="1:31" ht="12.75">
       <c r="A37" s="44" t="s">
         <v>123</v>
       </c>
@@ -6940,7 +6944,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="12.5" hidden="1">
+    <row r="38" spans="1:31" ht="12.75">
       <c r="A38" s="44" t="s">
         <v>125</v>
       </c>
@@ -7012,7 +7016,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="12.5" hidden="1">
+    <row r="39" spans="1:31" ht="12.75">
       <c r="A39" s="44" t="s">
         <v>127</v>
       </c>
@@ -7084,7 +7088,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="12.5" hidden="1">
+    <row r="40" spans="1:31" ht="12.75">
       <c r="A40" s="44" t="s">
         <v>132</v>
       </c>
@@ -7156,7 +7160,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="12.5">
+    <row r="41" spans="1:31" ht="12.75">
       <c r="A41" s="44" t="s">
         <v>132</v>
       </c>
@@ -7228,7 +7232,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="12.5" hidden="1">
+    <row r="42" spans="1:31" ht="12.75">
       <c r="A42" s="44" t="s">
         <v>134</v>
       </c>
@@ -7297,7 +7301,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="12.5" hidden="1">
+    <row r="43" spans="1:31" ht="12.75">
       <c r="A43" s="44" t="s">
         <v>134</v>
       </c>
@@ -7366,7 +7370,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="12.5" hidden="1">
+    <row r="44" spans="1:31" ht="12.75">
       <c r="A44" s="44" t="s">
         <v>134</v>
       </c>
@@ -7438,7 +7442,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="12.5">
+    <row r="45" spans="1:31" ht="12.75">
       <c r="A45" s="44" t="s">
         <v>134</v>
       </c>
@@ -7510,7 +7514,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="12.5" hidden="1">
+    <row r="46" spans="1:31" ht="12.75">
       <c r="A46" s="44" t="s">
         <v>43</v>
       </c>
@@ -7573,7 +7577,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="12.5" hidden="1">
+    <row r="47" spans="1:31" ht="12.75">
       <c r="A47" s="44" t="s">
         <v>43</v>
       </c>
@@ -7645,7 +7649,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="12.5" hidden="1">
+    <row r="48" spans="1:31" ht="12.75">
       <c r="A48" s="44" t="s">
         <v>47</v>
       </c>
@@ -7708,7 +7712,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="12.5" hidden="1">
+    <row r="49" spans="1:32" ht="12.75">
       <c r="A49" s="44" t="s">
         <v>139</v>
       </c>
@@ -7781,7 +7785,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="12.5" hidden="1">
+    <row r="50" spans="1:32" ht="12.75">
       <c r="A50" s="44" t="s">
         <v>142</v>
       </c>
@@ -7854,7 +7858,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="12.5" hidden="1">
+    <row r="51" spans="1:32" ht="12.75">
       <c r="A51" s="44" t="s">
         <v>144</v>
       </c>
@@ -7927,7 +7931,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="12.5" hidden="1">
+    <row r="52" spans="1:32" ht="12.75">
       <c r="A52" s="44" t="s">
         <v>146</v>
       </c>
@@ -8000,7 +8004,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="12.5" hidden="1">
+    <row r="53" spans="1:32" ht="12.75">
       <c r="A53" s="44" t="s">
         <v>148</v>
       </c>
@@ -8073,7 +8077,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="12.5" hidden="1">
+    <row r="54" spans="1:32" ht="12.75">
       <c r="A54" s="44" t="s">
         <v>150</v>
       </c>
@@ -8146,7 +8150,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="12.5" hidden="1">
+    <row r="55" spans="1:32" ht="12.75">
       <c r="A55" s="44" t="s">
         <v>47</v>
       </c>
@@ -8219,7 +8223,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="12.5" hidden="1">
+    <row r="56" spans="1:32" ht="12.75">
       <c r="A56" s="44" t="s">
         <v>47</v>
       </c>
@@ -8292,7 +8296,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="12.5" hidden="1">
+    <row r="57" spans="1:32" ht="12.75">
       <c r="A57" s="44" t="s">
         <v>47</v>
       </c>
@@ -8365,7 +8369,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:32" ht="12.5" hidden="1">
+    <row r="58" spans="1:32" ht="12.75">
       <c r="A58" s="44" t="s">
         <v>47</v>
       </c>
@@ -8438,7 +8442,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:32" ht="12.5" hidden="1">
+    <row r="59" spans="1:32" ht="12.75">
       <c r="A59" s="44" t="s">
         <v>47</v>
       </c>
@@ -8511,7 +8515,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:32" ht="12.5" hidden="1">
+    <row r="60" spans="1:32" ht="12.75">
       <c r="A60" s="44" t="s">
         <v>47</v>
       </c>
@@ -8584,7 +8588,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="12.5" hidden="1">
+    <row r="61" spans="1:32" ht="12.75">
       <c r="A61" s="44" t="s">
         <v>61</v>
       </c>
@@ -8657,7 +8661,7 @@
       <c r="AE61" s="16"/>
       <c r="AF61" s="16"/>
     </row>
-    <row r="62" spans="1:32" ht="12.5" hidden="1">
+    <row r="62" spans="1:32" ht="12.75">
       <c r="A62" s="44" t="s">
         <v>64</v>
       </c>
@@ -8729,7 +8733,7 @@
       <c r="AE62" s="16"/>
       <c r="AF62" s="16"/>
     </row>
-    <row r="63" spans="1:32" ht="12.5" hidden="1">
+    <row r="63" spans="1:32" ht="12.75">
       <c r="A63" s="44" t="s">
         <v>66</v>
       </c>
@@ -8801,7 +8805,7 @@
       <c r="AE63" s="16"/>
       <c r="AF63" s="16"/>
     </row>
-    <row r="64" spans="1:32" ht="12.5" hidden="1">
+    <row r="64" spans="1:32" ht="12.75">
       <c r="A64" s="44" t="s">
         <v>70</v>
       </c>
@@ -8874,7 +8878,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="12.5" hidden="1">
+    <row r="65" spans="1:31" ht="12.75">
       <c r="A65" s="44" t="s">
         <v>72</v>
       </c>
@@ -8947,7 +8951,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="12.5" hidden="1">
+    <row r="66" spans="1:31" ht="12.75">
       <c r="A66" s="44" t="s">
         <v>75</v>
       </c>
@@ -9020,7 +9024,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="12.5" hidden="1">
+    <row r="67" spans="1:31" ht="12.75">
       <c r="A67" s="44" t="s">
         <v>77</v>
       </c>
@@ -9091,7 +9095,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="12.5" hidden="1">
+    <row r="68" spans="1:31" ht="12.75">
       <c r="A68" s="44" t="s">
         <v>80</v>
       </c>
@@ -9162,7 +9166,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="12.5" hidden="1">
+    <row r="69" spans="1:31" ht="12.75">
       <c r="A69" s="44" t="s">
         <v>82</v>
       </c>
@@ -9235,7 +9239,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="12.5" hidden="1">
+    <row r="70" spans="1:31" ht="12.75">
       <c r="A70" s="44" t="s">
         <v>84</v>
       </c>
@@ -9308,7 +9312,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="12.5" hidden="1">
+    <row r="71" spans="1:31" ht="12.75">
       <c r="A71" s="44" t="s">
         <v>86</v>
       </c>
@@ -9381,7 +9385,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="12.5" hidden="1">
+    <row r="72" spans="1:31" ht="12.75">
       <c r="A72" s="44" t="s">
         <v>88</v>
       </c>
@@ -9454,7 +9458,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="12.5" hidden="1">
+    <row r="73" spans="1:31" ht="12.75">
       <c r="A73" s="44" t="s">
         <v>90</v>
       </c>
@@ -9527,7 +9531,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="12.5" hidden="1">
+    <row r="74" spans="1:31" ht="12.75">
       <c r="A74" s="44" t="s">
         <v>92</v>
       </c>
@@ -9600,7 +9604,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="12.5" hidden="1">
+    <row r="75" spans="1:31" ht="12.75">
       <c r="A75" s="44" t="s">
         <v>94</v>
       </c>
@@ -9673,7 +9677,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="12.5" hidden="1">
+    <row r="76" spans="1:31" ht="12.75">
       <c r="A76" s="44" t="s">
         <v>96</v>
       </c>
@@ -9744,7 +9748,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="12.5" hidden="1">
+    <row r="77" spans="1:31" ht="12.75">
       <c r="A77" s="44" t="s">
         <v>98</v>
       </c>
@@ -9815,7 +9819,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="12.5" hidden="1">
+    <row r="78" spans="1:31" ht="12.75">
       <c r="A78" s="44" t="s">
         <v>100</v>
       </c>
@@ -9886,7 +9890,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="12.5" hidden="1">
+    <row r="79" spans="1:31" ht="12.75">
       <c r="A79" s="44" t="s">
         <v>102</v>
       </c>
@@ -9959,7 +9963,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="12.5" hidden="1">
+    <row r="80" spans="1:31" ht="12.75">
       <c r="A80" s="44" t="s">
         <v>104</v>
       </c>
@@ -10032,7 +10036,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="12.5" hidden="1">
+    <row r="81" spans="1:31" ht="12.75">
       <c r="A81" s="44" t="s">
         <v>106</v>
       </c>
@@ -10105,7 +10109,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="12.5" hidden="1">
+    <row r="82" spans="1:31" ht="12.75">
       <c r="A82" s="44" t="s">
         <v>108</v>
       </c>
@@ -10178,7 +10182,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="12.5" hidden="1">
+    <row r="83" spans="1:31" ht="12.75">
       <c r="A83" s="44" t="s">
         <v>110</v>
       </c>
@@ -10251,7 +10255,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="12.5" hidden="1">
+    <row r="84" spans="1:31" ht="12.75">
       <c r="A84" s="44" t="s">
         <v>112</v>
       </c>
@@ -10324,7 +10328,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="12.5" hidden="1">
+    <row r="85" spans="1:31" ht="12.75">
       <c r="A85" s="44" t="s">
         <v>114</v>
       </c>
@@ -10395,7 +10399,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="12.5" hidden="1">
+    <row r="86" spans="1:31" ht="12.75">
       <c r="A86" s="44" t="s">
         <v>116</v>
       </c>
@@ -10466,7 +10470,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="12.5" hidden="1">
+    <row r="87" spans="1:31" ht="12.75">
       <c r="A87" s="44" t="s">
         <v>118</v>
       </c>
@@ -10537,7 +10541,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="12.5" hidden="1">
+    <row r="88" spans="1:31" ht="12.75">
       <c r="A88" s="44" t="s">
         <v>123</v>
       </c>
@@ -10610,7 +10614,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="12.5" hidden="1">
+    <row r="89" spans="1:31" ht="12.75">
       <c r="A89" s="44" t="s">
         <v>125</v>
       </c>
@@ -10683,7 +10687,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="12.5" hidden="1">
+    <row r="90" spans="1:31" ht="12.75">
       <c r="A90" s="44" t="s">
         <v>127</v>
       </c>
@@ -10756,7 +10760,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="12.5" hidden="1">
+    <row r="91" spans="1:31" ht="12.75">
       <c r="A91" s="44" t="s">
         <v>47</v>
       </c>
@@ -10829,7 +10833,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="12.5" hidden="1">
+    <row r="92" spans="1:31" ht="12.75">
       <c r="A92" s="44" t="s">
         <v>47</v>
       </c>
@@ -10902,7 +10906,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="12.5" hidden="1">
+    <row r="93" spans="1:31" ht="12.75">
       <c r="A93" s="44" t="s">
         <v>47</v>
       </c>
@@ -10947,7 +10951,7 @@
       <c r="M93" s="48"/>
       <c r="N93" s="48"/>
       <c r="O93" s="48"/>
-      <c r="P93" s="102"/>
+      <c r="P93" s="99"/>
       <c r="Q93" s="49">
         <v>1</v>
       </c>
@@ -10975,7 +10979,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="12.5" hidden="1">
+    <row r="94" spans="1:31" ht="12.75">
       <c r="A94" s="44" t="s">
         <v>47</v>
       </c>
@@ -11020,23 +11024,23 @@
       <c r="M94" s="48"/>
       <c r="N94" s="48"/>
       <c r="O94" s="48"/>
-      <c r="P94" s="102"/>
-      <c r="Q94" s="103">
+      <c r="P94" s="99"/>
+      <c r="Q94" s="100">
         <v>1</v>
       </c>
-      <c r="R94" s="104" t="s">
+      <c r="R94" s="101" t="s">
         <v>49</v>
       </c>
       <c r="S94" s="79">
         <v>225</v>
       </c>
-      <c r="T94" s="105" t="s">
+      <c r="T94" s="102" t="s">
         <v>63</v>
       </c>
       <c r="U94" s="21">
         <v>0</v>
       </c>
-      <c r="V94" s="106" t="s">
+      <c r="V94" s="103" t="s">
         <v>56</v>
       </c>
       <c r="W94" s="4"/>
@@ -11048,7 +11052,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="12.5" hidden="1">
+    <row r="95" spans="1:31" ht="12.75">
       <c r="A95" s="44" t="s">
         <v>47</v>
       </c>
@@ -11121,7 +11125,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="12.5" hidden="1">
+    <row r="96" spans="1:31" ht="12.75">
       <c r="A96" s="44" t="s">
         <v>123</v>
       </c>
@@ -11193,7 +11197,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="12.5" hidden="1">
+    <row r="97" spans="1:31" ht="12.75">
       <c r="A97" s="44" t="s">
         <v>125</v>
       </c>
@@ -11265,7 +11269,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="12.5" hidden="1">
+    <row r="98" spans="1:31" ht="12.75">
       <c r="A98" s="44" t="s">
         <v>127</v>
       </c>
@@ -11337,7 +11341,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="12.5" hidden="1">
+    <row r="99" spans="1:31" ht="12.75">
       <c r="A99" s="44" t="s">
         <v>47</v>
       </c>
@@ -11382,7 +11386,7 @@
       <c r="M99" s="48"/>
       <c r="N99" s="48"/>
       <c r="O99" s="48"/>
-      <c r="P99" s="102"/>
+      <c r="P99" s="99"/>
       <c r="Q99" s="49">
         <v>1</v>
       </c>
@@ -11409,7 +11413,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="12.5" hidden="1">
+    <row r="100" spans="1:31" ht="12.75">
       <c r="A100" s="44" t="s">
         <v>123</v>
       </c>
@@ -11481,7 +11485,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="12.5" hidden="1">
+    <row r="101" spans="1:31" ht="12.75">
       <c r="A101" s="44" t="s">
         <v>125</v>
       </c>
@@ -11553,7 +11557,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="12.5" hidden="1">
+    <row r="102" spans="1:31" ht="12.75">
       <c r="A102" s="44" t="s">
         <v>127</v>
       </c>
@@ -11626,7 +11630,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="12.5" hidden="1">
+    <row r="103" spans="1:31" ht="12.75">
       <c r="A103" s="44" t="s">
         <v>47</v>
       </c>
@@ -11698,7 +11702,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="12.5" hidden="1">
+    <row r="104" spans="1:31" ht="12.75">
       <c r="A104" s="44" t="s">
         <v>123</v>
       </c>
@@ -11770,7 +11774,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="12.5" hidden="1">
+    <row r="105" spans="1:31" ht="12.75">
       <c r="A105" s="44" t="s">
         <v>125</v>
       </c>
@@ -11842,7 +11846,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="12.5" hidden="1">
+    <row r="106" spans="1:31" ht="12.75">
       <c r="A106" s="44" t="s">
         <v>127</v>
       </c>
@@ -11914,7 +11918,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="12.5" hidden="1">
+    <row r="107" spans="1:31" ht="12.75">
       <c r="A107" s="44" t="s">
         <v>53</v>
       </c>
@@ -11983,7 +11987,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="12.5" hidden="1">
+    <row r="108" spans="1:31" ht="12.75">
       <c r="A108" s="44" t="s">
         <v>123</v>
       </c>
@@ -12055,7 +12059,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="12.5" hidden="1">
+    <row r="109" spans="1:31" ht="12.75">
       <c r="A109" s="44" t="s">
         <v>125</v>
       </c>
@@ -12127,7 +12131,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="12.5" hidden="1">
+    <row r="110" spans="1:31" ht="12.75">
       <c r="A110" s="44" t="s">
         <v>127</v>
       </c>
@@ -12199,7 +12203,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="12.5" hidden="1">
+    <row r="111" spans="1:31" ht="12.75">
       <c r="A111" s="44" t="s">
         <v>139</v>
       </c>
@@ -12272,7 +12276,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="12.5" hidden="1">
+    <row r="112" spans="1:31" ht="12.75">
       <c r="A112" s="44" t="s">
         <v>142</v>
       </c>
@@ -12345,7 +12349,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="12.5" hidden="1">
+    <row r="113" spans="1:31" ht="12.75">
       <c r="A113" s="44" t="s">
         <v>144</v>
       </c>
@@ -12418,7 +12422,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="12.5" hidden="1">
+    <row r="114" spans="1:31" ht="12.75">
       <c r="A114" s="44" t="s">
         <v>146</v>
       </c>
@@ -12491,7 +12495,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="12.5" hidden="1">
+    <row r="115" spans="1:31" ht="12.75">
       <c r="A115" s="44" t="s">
         <v>148</v>
       </c>
@@ -12564,7 +12568,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="12.5" hidden="1">
+    <row r="116" spans="1:31" ht="12.75">
       <c r="A116" s="44" t="s">
         <v>150</v>
       </c>
@@ -12637,7 +12641,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.5" hidden="1">
+    <row r="117" spans="1:31" ht="12.75">
       <c r="A117" s="44" t="s">
         <v>53</v>
       </c>
@@ -12709,7 +12713,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.5" hidden="1">
+    <row r="118" spans="1:31" ht="12.75">
       <c r="A118" s="44" t="s">
         <v>53</v>
       </c>
@@ -12781,7 +12785,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.5" hidden="1">
+    <row r="119" spans="1:31" ht="12.75">
       <c r="A119" s="44" t="s">
         <v>53</v>
       </c>
@@ -12853,7 +12857,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="12.5" hidden="1">
+    <row r="120" spans="1:31" ht="12.75">
       <c r="A120" s="44" t="s">
         <v>123</v>
       </c>
@@ -12926,7 +12930,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="12.5" hidden="1">
+    <row r="121" spans="1:31" ht="12.75">
       <c r="A121" s="44" t="s">
         <v>125</v>
       </c>
@@ -12999,7 +13003,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="12.5" hidden="1">
+    <row r="122" spans="1:31" ht="12.75">
       <c r="A122" s="44" t="s">
         <v>127</v>
       </c>
@@ -13073,7 +13077,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="12.5" hidden="1">
+    <row r="123" spans="1:31" ht="12.75">
       <c r="A123" s="44" t="s">
         <v>53</v>
       </c>
@@ -13147,7 +13151,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="12.5">
+    <row r="124" spans="1:31" ht="12.75">
       <c r="A124" s="44" t="s">
         <v>53</v>
       </c>
@@ -13220,7 +13224,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="12.5" hidden="1">
+    <row r="125" spans="1:31" ht="12.75">
       <c r="A125" s="44" t="s">
         <v>50</v>
       </c>
@@ -13292,7 +13296,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.5" hidden="1">
+    <row r="126" spans="1:31" ht="12.75">
       <c r="A126" s="44" t="s">
         <v>50</v>
       </c>
@@ -13365,7 +13369,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="12.5" hidden="1">
+    <row r="127" spans="1:31" ht="12.75">
       <c r="A127" s="44" t="s">
         <v>123</v>
       </c>
@@ -13438,7 +13442,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="12.5" hidden="1">
+    <row r="128" spans="1:31" ht="12.75">
       <c r="A128" s="44" t="s">
         <v>125</v>
       </c>
@@ -13511,7 +13515,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="12.5" hidden="1">
+    <row r="129" spans="1:31" ht="12.75">
       <c r="A129" s="44" t="s">
         <v>127</v>
       </c>
@@ -13584,7 +13588,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="12.5" hidden="1">
+    <row r="130" spans="1:31" ht="12.75">
       <c r="A130" s="44" t="s">
         <v>57</v>
       </c>
@@ -13654,7 +13658,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="12.5" hidden="1">
+    <row r="131" spans="1:31" ht="12.75">
       <c r="A131" s="44" t="s">
         <v>123</v>
       </c>
@@ -13727,7 +13731,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="12.5" hidden="1">
+    <row r="132" spans="1:31" ht="12.75">
       <c r="A132" s="44" t="s">
         <v>125</v>
       </c>
@@ -13800,7 +13804,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="12.5" hidden="1">
+    <row r="133" spans="1:31" ht="12.75">
       <c r="A133" s="44" t="s">
         <v>127</v>
       </c>
@@ -13873,7 +13877,7 @@
       <c r="AD133"/>
       <c r="AE133"/>
     </row>
-    <row r="134" spans="1:31" ht="12.5" hidden="1">
+    <row r="134" spans="1:31" ht="12.75">
       <c r="A134" s="44" t="s">
         <v>57</v>
       </c>
@@ -13946,7 +13950,7 @@
       <c r="AD134"/>
       <c r="AE134"/>
     </row>
-    <row r="135" spans="1:31" ht="12.5" hidden="1">
+    <row r="135" spans="1:31" ht="12.75">
       <c r="A135" s="44" t="s">
         <v>57</v>
       </c>
@@ -14019,7 +14023,7 @@
       <c r="AD135"/>
       <c r="AE135"/>
     </row>
-    <row r="136" spans="1:31" ht="12.5" hidden="1">
+    <row r="136" spans="1:31" ht="12.75">
       <c r="A136" s="44" t="s">
         <v>57</v>
       </c>
@@ -14092,7 +14096,7 @@
       <c r="AD136"/>
       <c r="AE136"/>
     </row>
-    <row r="137" spans="1:31" ht="12.5" hidden="1">
+    <row r="137" spans="1:31" ht="12.75">
       <c r="A137" s="44" t="s">
         <v>57</v>
       </c>
@@ -14166,7 +14170,7 @@
       <c r="AD137"/>
       <c r="AE137"/>
     </row>
-    <row r="138" spans="1:31" ht="12.5">
+    <row r="138" spans="1:31" ht="12.75">
       <c r="A138" s="44" t="s">
         <v>57</v>
       </c>
@@ -14239,7 +14243,7 @@
       <c r="AD138"/>
       <c r="AE138"/>
     </row>
-    <row r="139" spans="1:31" ht="12.5" hidden="1">
+    <row r="139" spans="1:31" ht="12.75">
       <c r="A139" s="87" t="s">
         <v>59</v>
       </c>
@@ -14308,7 +14312,7 @@
       <c r="AC139" s="48"/>
       <c r="AD139" s="48"/>
     </row>
-    <row r="140" spans="1:31" ht="12.5" hidden="1">
+    <row r="140" spans="1:31" ht="12.75">
       <c r="A140" s="87" t="s">
         <v>59</v>
       </c>
@@ -14380,7 +14384,7 @@
       <c r="AC140" s="48"/>
       <c r="AD140" s="48"/>
     </row>
-    <row r="141" spans="1:31" ht="12.5" hidden="1">
+    <row r="141" spans="1:31" ht="12.75">
       <c r="A141" s="87" t="s">
         <v>123</v>
       </c>
@@ -14452,7 +14456,7 @@
       <c r="AC141" s="48"/>
       <c r="AD141" s="46"/>
     </row>
-    <row r="142" spans="1:31" ht="12.5" hidden="1">
+    <row r="142" spans="1:31" ht="12.75">
       <c r="A142" s="87" t="s">
         <v>125</v>
       </c>
@@ -14524,7 +14528,7 @@
       <c r="AC142" s="48"/>
       <c r="AD142" s="46"/>
     </row>
-    <row r="143" spans="1:31" ht="12.5" hidden="1">
+    <row r="143" spans="1:31" ht="12.75">
       <c r="A143" s="87" t="s">
         <v>127</v>
       </c>
@@ -14596,7 +14600,7 @@
       <c r="AC143" s="48"/>
       <c r="AD143" s="46"/>
     </row>
-    <row r="144" spans="1:31" ht="12.5" hidden="1">
+    <row r="144" spans="1:31" ht="12.75">
       <c r="A144" s="87" t="s">
         <v>59</v>
       </c>
@@ -14668,7 +14672,7 @@
       <c r="AC144" s="48"/>
       <c r="AD144" s="46"/>
     </row>
-    <row r="145" spans="1:31" ht="12.5" hidden="1">
+    <row r="145" spans="1:31" ht="12.75">
       <c r="A145" s="87" t="s">
         <v>123</v>
       </c>
@@ -14741,7 +14745,7 @@
       <c r="AD145" s="46"/>
       <c r="AE145" s="16"/>
     </row>
-    <row r="146" spans="1:31" ht="12.5" hidden="1">
+    <row r="146" spans="1:31" ht="12.75">
       <c r="A146" s="87" t="s">
         <v>125</v>
       </c>
@@ -14814,7 +14818,7 @@
       <c r="AD146" s="7"/>
       <c r="AE146" s="16"/>
     </row>
-    <row r="147" spans="1:31" ht="12.5" hidden="1">
+    <row r="147" spans="1:31" ht="12.75">
       <c r="A147" s="87" t="s">
         <v>127</v>
       </c>
@@ -14887,7 +14891,7 @@
       <c r="AD147" s="7"/>
       <c r="AE147" s="16"/>
     </row>
-    <row r="148" spans="1:31" ht="12.5" hidden="1">
+    <row r="148" spans="1:31" ht="12.75">
       <c r="A148" s="87" t="s">
         <v>59</v>
       </c>
@@ -14959,7 +14963,7 @@
       <c r="AC148" s="48"/>
       <c r="AD148" s="7"/>
     </row>
-    <row r="149" spans="1:31" ht="12.5" hidden="1">
+    <row r="149" spans="1:31" ht="12.75">
       <c r="A149" s="87" t="s">
         <v>123</v>
       </c>
@@ -15031,7 +15035,7 @@
       <c r="AC149" s="48"/>
       <c r="AD149" s="7"/>
     </row>
-    <row r="150" spans="1:31" ht="12.5" hidden="1">
+    <row r="150" spans="1:31" ht="12.75">
       <c r="A150" s="87" t="s">
         <v>125</v>
       </c>
@@ -15103,7 +15107,7 @@
       <c r="AC150" s="48"/>
       <c r="AD150" s="7"/>
     </row>
-    <row r="151" spans="1:31" ht="12.5" hidden="1">
+    <row r="151" spans="1:31" ht="12.75">
       <c r="A151" s="87" t="s">
         <v>127</v>
       </c>
@@ -15175,7 +15179,7 @@
       <c r="AC151" s="48"/>
       <c r="AD151" s="7"/>
     </row>
-    <row r="152" spans="1:31" ht="12.5" hidden="1">
+    <row r="152" spans="1:31" ht="12.75">
       <c r="A152" s="93" t="s">
         <v>59</v>
       </c>
@@ -15237,7 +15241,7 @@
       <c r="U152" s="98">
         <v>0</v>
       </c>
-      <c r="V152" s="107" t="s">
+      <c r="V152" s="104" t="s">
         <v>56</v>
       </c>
       <c r="X152" s="48"/>
@@ -15248,7 +15252,7 @@
       <c r="AC152" s="48"/>
       <c r="AD152" s="46"/>
     </row>
-    <row r="153" spans="1:31" ht="12.5" hidden="1">
+    <row r="153" spans="1:31" ht="12.75">
       <c r="A153" s="44" t="s">
         <v>123</v>
       </c>
@@ -15320,7 +15324,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="12.5" hidden="1">
+    <row r="154" spans="1:31" ht="12.75">
       <c r="A154" s="44" t="s">
         <v>125</v>
       </c>
@@ -15392,7 +15396,7 @@
       <c r="AD154"/>
       <c r="AE154"/>
     </row>
-    <row r="155" spans="1:31" ht="12.5" hidden="1">
+    <row r="155" spans="1:31" ht="12.75">
       <c r="A155" s="44" t="s">
         <v>127</v>
       </c>
@@ -15464,7 +15468,7 @@
       <c r="AD155"/>
       <c r="AE155"/>
     </row>
-    <row r="156" spans="1:31" ht="12.5">
+    <row r="156" spans="1:31" ht="12.75">
       <c r="A156" s="44" t="s">
         <v>59</v>
       </c>
@@ -15536,7 +15540,7 @@
       <c r="AD156"/>
       <c r="AE156"/>
     </row>
-    <row r="157" spans="1:31" ht="12.5" hidden="1">
+    <row r="157" spans="1:31" ht="12.75">
       <c r="A157" s="44" t="s">
         <v>123</v>
       </c>
@@ -15608,7 +15612,7 @@
       <c r="AD157"/>
       <c r="AE157"/>
     </row>
-    <row r="158" spans="1:31" ht="12.5" hidden="1">
+    <row r="158" spans="1:31" ht="12.75">
       <c r="A158" s="44" t="s">
         <v>125</v>
       </c>
@@ -15681,7 +15685,7 @@
       <c r="AD158"/>
       <c r="AE158"/>
     </row>
-    <row r="159" spans="1:31" ht="12.5" hidden="1">
+    <row r="159" spans="1:31" ht="12.75">
       <c r="A159" s="44" t="s">
         <v>127</v>
       </c>
@@ -15754,7 +15758,7 @@
       <c r="AD159"/>
       <c r="AE159"/>
     </row>
-    <row r="160" spans="1:31" ht="12.5" hidden="1">
+    <row r="160" spans="1:31" ht="12.75">
       <c r="A160" s="44" t="s">
         <v>165</v>
       </c>
@@ -15833,7 +15837,7 @@
       <c r="AC160" s="48"/>
       <c r="AD160" s="48"/>
     </row>
-    <row r="161" spans="1:30" ht="12.5" hidden="1">
+    <row r="161" spans="1:30" ht="12.75">
       <c r="A161" s="44" t="s">
         <v>167</v>
       </c>
@@ -15912,7 +15916,7 @@
       <c r="AC161" s="48"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="12.5" hidden="1">
+    <row r="162" spans="1:30" ht="12.75">
       <c r="A162" s="44" t="s">
         <v>169</v>
       </c>
@@ -15991,7 +15995,7 @@
       <c r="AC162" s="48"/>
       <c r="AD162" s="46"/>
     </row>
-    <row r="163" spans="1:30" ht="12.5" hidden="1">
+    <row r="163" spans="1:30" ht="12.75">
       <c r="A163" s="44" t="s">
         <v>1</v>
       </c>
@@ -16070,18 +16074,76 @@
       <c r="AC163" s="48"/>
       <c r="AD163" s="7"/>
     </row>
-    <row r="164" spans="1:30" ht="12.5">
-      <c r="A164" s="44"/>
-      <c r="B164" s="44"/>
-      <c r="C164" s="44"/>
-      <c r="I164" s="46"/>
-      <c r="J164" s="46"/>
-      <c r="K164" s="46"/>
-      <c r="M164" s="48"/>
-      <c r="N164" s="48"/>
-      <c r="O164" s="48"/>
-      <c r="Q164" s="61"/>
-      <c r="U164" s="48"/>
+    <row r="164" spans="1:30" ht="12.75">
+      <c r="A164" s="108" t="s">
+        <v>53</v>
+      </c>
+      <c r="B164" s="109" t="s">
+        <v>54</v>
+      </c>
+      <c r="C164" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>11963</v>
+      </c>
+      <c r="D164" s="46">
+        <v>5819</v>
+      </c>
+      <c r="E164" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>1256.5</v>
+      </c>
+      <c r="G164" s="110">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4562.5</v>
+      </c>
+      <c r="H164" s="40">
+        <v>9450</v>
+      </c>
+      <c r="I164" s="47" t="s">
+        <v>638</v>
+      </c>
+      <c r="J164" s="48">
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>443.5</v>
+      </c>
+      <c r="K164" s="111">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4119</v>
+      </c>
+      <c r="L164" s="55">
+        <v>8563</v>
+      </c>
+      <c r="M164" s="47"/>
+      <c r="N164" s="111">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>4119</v>
+      </c>
+      <c r="O164" s="112">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P164" s="46"/>
+      <c r="Q164" s="85">
+        <v>1</v>
+      </c>
+      <c r="R164" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="S164" s="49">
+        <v>325</v>
+      </c>
+      <c r="T164" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="U164" s="50">
+        <v>0</v>
+      </c>
+      <c r="V164" s="50" t="s">
+        <v>56</v>
+      </c>
       <c r="X164" s="48"/>
       <c r="Y164" s="48"/>
       <c r="Z164" s="48"/>
@@ -16090,7 +16152,7 @@
       <c r="AC164" s="48"/>
       <c r="AD164" s="7"/>
     </row>
-    <row r="165" spans="1:30" ht="12.5">
+    <row r="165" spans="1:30" ht="12.75">
       <c r="A165" s="44"/>
       <c r="B165" s="44"/>
       <c r="C165" s="44"/>
@@ -16110,7 +16172,7 @@
       <c r="AC165" s="48"/>
       <c r="AD165" s="7"/>
     </row>
-    <row r="166" spans="1:30" ht="12.5">
+    <row r="166" spans="1:30" ht="12.75">
       <c r="A166" s="44"/>
       <c r="B166" s="44"/>
       <c r="C166" s="44"/>
@@ -16130,7 +16192,7 @@
       <c r="AC166" s="48"/>
       <c r="AD166" s="48"/>
     </row>
-    <row r="167" spans="1:30" ht="12.5">
+    <row r="167" spans="1:30" ht="12.75">
       <c r="A167" s="44"/>
       <c r="B167" s="44"/>
       <c r="C167" s="44"/>
@@ -16151,7 +16213,7 @@
       <c r="AC167" s="48"/>
       <c r="AD167" s="48"/>
     </row>
-    <row r="168" spans="1:30" ht="12.5">
+    <row r="168" spans="1:30" ht="12.75">
       <c r="A168" s="44"/>
       <c r="B168" s="44"/>
       <c r="C168" s="44"/>
@@ -16172,7 +16234,7 @@
       <c r="AC168" s="48"/>
       <c r="AD168" s="7"/>
     </row>
-    <row r="169" spans="1:30" ht="12.5">
+    <row r="169" spans="1:30" ht="12.75">
       <c r="A169" s="44"/>
       <c r="B169" s="44"/>
       <c r="C169" s="44"/>
@@ -16192,7 +16254,7 @@
       <c r="AC169" s="48"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="12.5">
+    <row r="170" spans="1:30" ht="12.75">
       <c r="A170" s="44"/>
       <c r="B170" s="44"/>
       <c r="C170" s="44"/>
@@ -16212,7 +16274,7 @@
       <c r="AC170" s="48"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="12.5">
+    <row r="171" spans="1:30" ht="12.75">
       <c r="A171" s="44"/>
       <c r="B171" s="44"/>
       <c r="C171" s="44"/>
@@ -16232,7 +16294,7 @@
       <c r="AC171" s="48"/>
       <c r="AD171" s="48"/>
     </row>
-    <row r="172" spans="1:30" ht="12.5">
+    <row r="172" spans="1:30" ht="12.75">
       <c r="A172" s="44"/>
       <c r="B172" s="44"/>
       <c r="C172" s="44"/>
@@ -16252,7 +16314,7 @@
       <c r="AC172" s="48"/>
       <c r="AD172" s="48"/>
     </row>
-    <row r="173" spans="1:30" ht="12.5">
+    <row r="173" spans="1:30" ht="12.75">
       <c r="A173" s="44"/>
       <c r="B173" s="44"/>
       <c r="C173" s="44"/>
@@ -16272,7 +16334,7 @@
       <c r="AC173" s="48"/>
       <c r="AD173" s="7"/>
     </row>
-    <row r="174" spans="1:30" ht="12.5">
+    <row r="174" spans="1:30" ht="12.75">
       <c r="A174" s="44"/>
       <c r="B174" s="44"/>
       <c r="C174" s="44"/>
@@ -16292,7 +16354,7 @@
       <c r="AC174" s="48"/>
       <c r="AD174" s="7"/>
     </row>
-    <row r="175" spans="1:30" ht="12.5">
+    <row r="175" spans="1:30" ht="12.75">
       <c r="A175" s="44"/>
       <c r="B175" s="44"/>
       <c r="C175" s="44"/>
@@ -16312,7 +16374,7 @@
       <c r="AC175" s="48"/>
       <c r="AD175" s="7"/>
     </row>
-    <row r="176" spans="1:30" ht="12.5">
+    <row r="176" spans="1:30" ht="12.75">
       <c r="A176" s="44"/>
       <c r="B176" s="44"/>
       <c r="C176" s="44"/>
@@ -16332,7 +16394,7 @@
       <c r="AC176" s="48"/>
       <c r="AD176" s="48"/>
     </row>
-    <row r="177" spans="1:30" ht="12.5">
+    <row r="177" spans="1:30" ht="12.75">
       <c r="A177" s="44"/>
       <c r="B177" s="44"/>
       <c r="C177" s="44"/>
@@ -16352,7 +16414,7 @@
       <c r="AC177" s="48"/>
       <c r="AD177" s="48"/>
     </row>
-    <row r="178" spans="1:30" ht="12.5">
+    <row r="178" spans="1:30" ht="12.75">
       <c r="A178" s="44"/>
       <c r="B178" s="44"/>
       <c r="C178" s="44"/>
@@ -16372,7 +16434,7 @@
       <c r="AC178" s="48"/>
       <c r="AD178" s="46"/>
     </row>
-    <row r="179" spans="1:30" ht="12.5">
+    <row r="179" spans="1:30" ht="12.75">
       <c r="A179" s="44"/>
       <c r="B179" s="44"/>
       <c r="C179" s="44"/>
@@ -16392,7 +16454,7 @@
       <c r="AC179" s="48"/>
       <c r="AD179" s="46"/>
     </row>
-    <row r="180" spans="1:30" ht="12.5">
+    <row r="180" spans="1:30" ht="12.75">
       <c r="A180" s="44"/>
       <c r="B180" s="44"/>
       <c r="C180" s="44"/>
@@ -16412,7 +16474,7 @@
       <c r="AC180" s="48"/>
       <c r="AD180" s="46"/>
     </row>
-    <row r="181" spans="1:30" ht="12.5">
+    <row r="181" spans="1:30" ht="12.75">
       <c r="A181" s="44"/>
       <c r="B181" s="44"/>
       <c r="C181" s="44"/>
@@ -16432,7 +16494,7 @@
       <c r="AC181" s="48"/>
       <c r="AD181" s="46"/>
     </row>
-    <row r="182" spans="1:30" ht="12.5">
+    <row r="182" spans="1:30" ht="12.75">
       <c r="A182" s="44"/>
       <c r="B182" s="44"/>
       <c r="C182" s="44"/>
@@ -16452,7 +16514,7 @@
       <c r="AC182" s="48"/>
       <c r="AD182" s="46"/>
     </row>
-    <row r="183" spans="1:30" ht="12.5">
+    <row r="183" spans="1:30" ht="12.75">
       <c r="A183" s="44"/>
       <c r="B183" s="44"/>
       <c r="C183" s="44"/>
@@ -16472,7 +16534,7 @@
       <c r="AC183" s="48"/>
       <c r="AD183" s="46"/>
     </row>
-    <row r="184" spans="1:30" ht="12.5">
+    <row r="184" spans="1:30" ht="12.75">
       <c r="A184" s="44"/>
       <c r="B184" s="44"/>
       <c r="C184" s="44"/>
@@ -16492,7 +16554,7 @@
       <c r="AC184" s="48"/>
       <c r="AD184" s="46"/>
     </row>
-    <row r="185" spans="1:30" ht="12.5">
+    <row r="185" spans="1:30" ht="12.75">
       <c r="A185" s="44"/>
       <c r="B185" s="44"/>
       <c r="C185" s="44"/>
@@ -16512,7 +16574,7 @@
       <c r="AC185" s="48"/>
       <c r="AD185" s="46"/>
     </row>
-    <row r="186" spans="1:30" ht="12.5">
+    <row r="186" spans="1:30" ht="12.75">
       <c r="A186" s="44"/>
       <c r="B186" s="44"/>
       <c r="C186" s="44"/>
@@ -16532,7 +16594,7 @@
       <c r="AC186" s="48"/>
       <c r="AD186" s="7"/>
     </row>
-    <row r="187" spans="1:30" ht="12.5">
+    <row r="187" spans="1:30" ht="12.75">
       <c r="A187" s="44"/>
       <c r="B187" s="44"/>
       <c r="C187" s="44"/>
@@ -16552,7 +16614,7 @@
       <c r="AC187" s="48"/>
       <c r="AD187" s="7"/>
     </row>
-    <row r="188" spans="1:30" ht="12.5">
+    <row r="188" spans="1:30" ht="12.75">
       <c r="A188" s="44"/>
       <c r="B188" s="44"/>
       <c r="C188" s="44"/>
@@ -16572,7 +16634,7 @@
       <c r="AC188" s="48"/>
       <c r="AD188" s="7"/>
     </row>
-    <row r="189" spans="1:30" ht="12.5">
+    <row r="189" spans="1:30" ht="12.75">
       <c r="A189" s="44"/>
       <c r="B189" s="44"/>
       <c r="C189" s="44"/>
@@ -16591,7 +16653,7 @@
       <c r="AB189" s="79"/>
       <c r="AD189" s="16"/>
     </row>
-    <row r="190" spans="1:30" ht="12.5">
+    <row r="190" spans="1:30" ht="12.75">
       <c r="A190" s="44"/>
       <c r="B190" s="44"/>
       <c r="C190" s="44"/>
@@ -16611,7 +16673,7 @@
       <c r="AC190" s="46"/>
       <c r="AD190" s="46"/>
     </row>
-    <row r="191" spans="1:30" ht="12.5">
+    <row r="191" spans="1:30" ht="12.75">
       <c r="A191" s="44"/>
       <c r="B191" s="44"/>
       <c r="C191" s="44"/>
@@ -16631,7 +16693,7 @@
       <c r="AC191" s="46"/>
       <c r="AD191" s="46"/>
     </row>
-    <row r="192" spans="1:30" ht="12.5">
+    <row r="192" spans="1:30" ht="12.75">
       <c r="A192" s="44"/>
       <c r="B192" s="44"/>
       <c r="C192" s="44"/>
@@ -16651,7 +16713,7 @@
       <c r="AC192" s="46"/>
       <c r="AD192" s="46"/>
     </row>
-    <row r="193" spans="1:30" ht="12.5">
+    <row r="193" spans="1:30" ht="12.75">
       <c r="A193" s="44"/>
       <c r="B193" s="44"/>
       <c r="C193" s="44"/>
@@ -16671,7 +16733,7 @@
       <c r="AC193" s="46"/>
       <c r="AD193" s="46"/>
     </row>
-    <row r="194" spans="1:30" ht="12.5">
+    <row r="194" spans="1:30" ht="12.75">
       <c r="A194" s="44"/>
       <c r="B194" s="44"/>
       <c r="C194" s="44"/>
@@ -16691,7 +16753,7 @@
       <c r="AC194" s="46"/>
       <c r="AD194" s="46"/>
     </row>
-    <row r="195" spans="1:30" ht="12.5">
+    <row r="195" spans="1:30" ht="12.75">
       <c r="A195" s="44"/>
       <c r="B195" s="44"/>
       <c r="C195" s="44"/>
@@ -16711,7 +16773,7 @@
       <c r="AC195" s="46"/>
       <c r="AD195" s="46"/>
     </row>
-    <row r="196" spans="1:30" ht="12.5">
+    <row r="196" spans="1:30" ht="12.75">
       <c r="A196" s="44"/>
       <c r="B196" s="44"/>
       <c r="C196" s="44"/>
@@ -16731,7 +16793,7 @@
       <c r="AC196" s="46"/>
       <c r="AD196" s="46"/>
     </row>
-    <row r="197" spans="1:30" ht="12.5">
+    <row r="197" spans="1:30" ht="12.75">
       <c r="A197" s="44"/>
       <c r="B197" s="44"/>
       <c r="C197" s="44"/>
@@ -16751,7 +16813,7 @@
       <c r="AC197" s="46"/>
       <c r="AD197" s="46"/>
     </row>
-    <row r="198" spans="1:30" ht="12.5">
+    <row r="198" spans="1:30" ht="12.75">
       <c r="A198" s="44"/>
       <c r="B198" s="44"/>
       <c r="C198" s="44"/>
@@ -16771,7 +16833,7 @@
       <c r="AC198" s="46"/>
       <c r="AD198" s="46"/>
     </row>
-    <row r="199" spans="1:30" ht="12.5">
+    <row r="199" spans="1:30" ht="12.75">
       <c r="A199" s="44"/>
       <c r="B199" s="44"/>
       <c r="C199" s="44"/>
@@ -16791,7 +16853,7 @@
       <c r="AC199" s="46"/>
       <c r="AD199" s="46"/>
     </row>
-    <row r="200" spans="1:30" ht="12.5">
+    <row r="200" spans="1:30" ht="12.75">
       <c r="A200" s="44"/>
       <c r="B200" s="44"/>
       <c r="C200" s="44"/>
@@ -16811,7 +16873,7 @@
       <c r="AC200" s="46"/>
       <c r="AD200" s="46"/>
     </row>
-    <row r="201" spans="1:30" ht="12.5">
+    <row r="201" spans="1:30" ht="12.75">
       <c r="A201" s="44"/>
       <c r="B201" s="44"/>
       <c r="C201" s="44"/>
@@ -16831,7 +16893,7 @@
       <c r="AC201" s="46"/>
       <c r="AD201" s="46"/>
     </row>
-    <row r="202" spans="1:30" ht="12.5">
+    <row r="202" spans="1:30" ht="12.75">
       <c r="A202" s="44"/>
       <c r="B202" s="44"/>
       <c r="C202" s="44"/>
@@ -16851,7 +16913,7 @@
       <c r="AC202" s="46"/>
       <c r="AD202" s="46"/>
     </row>
-    <row r="203" spans="1:30" ht="12.5">
+    <row r="203" spans="1:30" ht="12.75">
       <c r="A203" s="44"/>
       <c r="B203" s="44"/>
       <c r="C203" s="44"/>
@@ -16871,7 +16933,7 @@
       <c r="AC203" s="46"/>
       <c r="AD203" s="46"/>
     </row>
-    <row r="204" spans="1:30" ht="12.5">
+    <row r="204" spans="1:30" ht="12.75">
       <c r="A204" s="44"/>
       <c r="B204" s="44"/>
       <c r="C204" s="44"/>
@@ -16891,7 +16953,7 @@
       <c r="AC204" s="46"/>
       <c r="AD204" s="46"/>
     </row>
-    <row r="205" spans="1:30" ht="12.5">
+    <row r="205" spans="1:30" ht="12.75">
       <c r="A205" s="44"/>
       <c r="B205" s="44"/>
       <c r="C205" s="44"/>
@@ -16911,7 +16973,7 @@
       <c r="AC205" s="46"/>
       <c r="AD205" s="46"/>
     </row>
-    <row r="206" spans="1:30" ht="12.5">
+    <row r="206" spans="1:30" ht="12.75">
       <c r="A206" s="44"/>
       <c r="B206" s="44"/>
       <c r="C206" s="44"/>
@@ -16931,7 +16993,7 @@
       <c r="AC206" s="46"/>
       <c r="AD206" s="46"/>
     </row>
-    <row r="207" spans="1:30" ht="12.5">
+    <row r="207" spans="1:30" ht="12.75">
       <c r="A207" s="44"/>
       <c r="B207" s="44"/>
       <c r="C207" s="44"/>
@@ -16951,7 +17013,7 @@
       <c r="AC207" s="46"/>
       <c r="AD207" s="46"/>
     </row>
-    <row r="208" spans="1:30" ht="12.5">
+    <row r="208" spans="1:30" ht="12.75">
       <c r="A208" s="44"/>
       <c r="B208" s="44"/>
       <c r="C208" s="44"/>
@@ -16971,7 +17033,7 @@
       <c r="AC208" s="46"/>
       <c r="AD208" s="46"/>
     </row>
-    <row r="209" spans="1:30" ht="12.5">
+    <row r="209" spans="1:30" ht="12.75">
       <c r="A209" s="44"/>
       <c r="B209" s="44"/>
       <c r="C209" s="44"/>
@@ -16991,7 +17053,7 @@
       <c r="AC209" s="46"/>
       <c r="AD209" s="46"/>
     </row>
-    <row r="210" spans="1:30" ht="12.5">
+    <row r="210" spans="1:30" ht="12.75">
       <c r="A210" s="44"/>
       <c r="B210" s="44"/>
       <c r="C210" s="44"/>
@@ -17011,7 +17073,7 @@
       <c r="AC210" s="46"/>
       <c r="AD210" s="46"/>
     </row>
-    <row r="211" spans="1:30" ht="12.5">
+    <row r="211" spans="1:30" ht="12.75">
       <c r="A211" s="44"/>
       <c r="B211" s="44"/>
       <c r="C211" s="44"/>
@@ -17031,7 +17093,7 @@
       <c r="AC211" s="46"/>
       <c r="AD211" s="46"/>
     </row>
-    <row r="212" spans="1:30" ht="12.5">
+    <row r="212" spans="1:30" ht="12.75">
       <c r="A212" s="44"/>
       <c r="B212" s="44"/>
       <c r="C212" s="44"/>
@@ -17051,7 +17113,7 @@
       <c r="AC212" s="46"/>
       <c r="AD212" s="46"/>
     </row>
-    <row r="213" spans="1:30" ht="12.5">
+    <row r="213" spans="1:30" ht="12.75">
       <c r="A213" s="44"/>
       <c r="B213" s="44"/>
       <c r="C213" s="44"/>
@@ -17071,7 +17133,7 @@
       <c r="AC213" s="46"/>
       <c r="AD213" s="46"/>
     </row>
-    <row r="214" spans="1:30" ht="12.5">
+    <row r="214" spans="1:30" ht="12.75">
       <c r="A214" s="44"/>
       <c r="B214" s="44"/>
       <c r="C214" s="44"/>
@@ -17091,7 +17153,7 @@
       <c r="AC214" s="46"/>
       <c r="AD214" s="46"/>
     </row>
-    <row r="215" spans="1:30" ht="12.5">
+    <row r="215" spans="1:30" ht="12.75">
       <c r="A215" s="44"/>
       <c r="B215" s="44"/>
       <c r="C215" s="44"/>
@@ -17111,7 +17173,7 @@
       <c r="AC215" s="46"/>
       <c r="AD215" s="46"/>
     </row>
-    <row r="216" spans="1:30" ht="12.5">
+    <row r="216" spans="1:30" ht="12.75">
       <c r="A216" s="44"/>
       <c r="B216" s="44"/>
       <c r="C216" s="44"/>
@@ -17131,7 +17193,7 @@
       <c r="AC216" s="46"/>
       <c r="AD216" s="46"/>
     </row>
-    <row r="217" spans="1:30" ht="12.5">
+    <row r="217" spans="1:30" ht="12.75">
       <c r="A217" s="44"/>
       <c r="B217" s="44"/>
       <c r="C217" s="44"/>
@@ -17151,7 +17213,7 @@
       <c r="AC217" s="46"/>
       <c r="AD217" s="46"/>
     </row>
-    <row r="218" spans="1:30" ht="12.5">
+    <row r="218" spans="1:30" ht="12.75">
       <c r="A218" s="44"/>
       <c r="B218" s="44"/>
       <c r="C218" s="44"/>
@@ -17171,7 +17233,7 @@
       <c r="AC218" s="46"/>
       <c r="AD218" s="46"/>
     </row>
-    <row r="219" spans="1:30" ht="12.5">
+    <row r="219" spans="1:30" ht="12.75">
       <c r="A219" s="44"/>
       <c r="B219" s="44"/>
       <c r="C219" s="44"/>
@@ -17191,7 +17253,7 @@
       <c r="AC219" s="46"/>
       <c r="AD219" s="46"/>
     </row>
-    <row r="220" spans="1:30" ht="12.5">
+    <row r="220" spans="1:30" ht="12.75">
       <c r="A220" s="44"/>
       <c r="B220" s="44"/>
       <c r="C220" s="44"/>
@@ -17211,7 +17273,7 @@
       <c r="AC220" s="46"/>
       <c r="AD220" s="46"/>
     </row>
-    <row r="221" spans="1:30" ht="12.5">
+    <row r="221" spans="1:30" ht="12.75">
       <c r="A221" s="44"/>
       <c r="B221" s="44"/>
       <c r="C221" s="44"/>
@@ -17231,7 +17293,7 @@
       <c r="AC221" s="46"/>
       <c r="AD221" s="46"/>
     </row>
-    <row r="222" spans="1:30" ht="12.5">
+    <row r="222" spans="1:30" ht="12.75">
       <c r="A222" s="44"/>
       <c r="B222" s="44"/>
       <c r="C222" s="44"/>
@@ -17251,7 +17313,7 @@
       <c r="AC222" s="46"/>
       <c r="AD222" s="46"/>
     </row>
-    <row r="223" spans="1:30" ht="12.5">
+    <row r="223" spans="1:30" ht="12.75">
       <c r="A223" s="44"/>
       <c r="B223" s="44"/>
       <c r="C223" s="44"/>
@@ -17271,7 +17333,7 @@
       <c r="AC223" s="46"/>
       <c r="AD223" s="46"/>
     </row>
-    <row r="224" spans="1:30" ht="12.5">
+    <row r="224" spans="1:30" ht="12.75">
       <c r="A224" s="44"/>
       <c r="B224" s="44"/>
       <c r="C224" s="44"/>
@@ -17291,7 +17353,7 @@
       <c r="AC224" s="46"/>
       <c r="AD224" s="46"/>
     </row>
-    <row r="225" spans="1:30" ht="12.5">
+    <row r="225" spans="1:30" ht="12.75">
       <c r="A225" s="44"/>
       <c r="B225" s="44"/>
       <c r="C225" s="44"/>
@@ -17311,7 +17373,7 @@
       <c r="AC225" s="46"/>
       <c r="AD225" s="46"/>
     </row>
-    <row r="226" spans="1:30" ht="12.5">
+    <row r="226" spans="1:30" ht="12.75">
       <c r="A226" s="44"/>
       <c r="B226" s="44"/>
       <c r="C226" s="44"/>
@@ -17331,7 +17393,7 @@
       <c r="AC226" s="46"/>
       <c r="AD226" s="46"/>
     </row>
-    <row r="227" spans="1:30" ht="12.5">
+    <row r="227" spans="1:30" ht="12.75">
       <c r="A227" s="44"/>
       <c r="B227" s="44"/>
       <c r="C227" s="44"/>
@@ -17351,7 +17413,7 @@
       <c r="AC227" s="46"/>
       <c r="AD227" s="46"/>
     </row>
-    <row r="228" spans="1:30" ht="12.5">
+    <row r="228" spans="1:30" ht="12.75">
       <c r="A228" s="44"/>
       <c r="B228" s="44"/>
       <c r="C228" s="44"/>
@@ -17371,7 +17433,7 @@
       <c r="AC228" s="46"/>
       <c r="AD228" s="46"/>
     </row>
-    <row r="229" spans="1:30" ht="12.5">
+    <row r="229" spans="1:30" ht="12.75">
       <c r="A229" s="44"/>
       <c r="B229" s="44"/>
       <c r="C229" s="44"/>
@@ -17390,7 +17452,7 @@
       <c r="AC229" s="46"/>
       <c r="AD229" s="46"/>
     </row>
-    <row r="230" spans="1:30" ht="12.5">
+    <row r="230" spans="1:30" ht="12.75">
       <c r="A230" s="44"/>
       <c r="B230" s="44"/>
       <c r="C230" s="44"/>
@@ -17409,7 +17471,7 @@
       <c r="AC230" s="46"/>
       <c r="AD230" s="46"/>
     </row>
-    <row r="231" spans="1:30" ht="12.5">
+    <row r="231" spans="1:30" ht="12.75">
       <c r="A231" s="44"/>
       <c r="B231" s="44"/>
       <c r="C231" s="44"/>
@@ -17428,7 +17490,7 @@
       <c r="AC231" s="46"/>
       <c r="AD231" s="46"/>
     </row>
-    <row r="232" spans="1:30" ht="12.5">
+    <row r="232" spans="1:30" ht="12.75">
       <c r="A232" s="44"/>
       <c r="B232" s="44"/>
       <c r="C232" s="44"/>
@@ -17440,7 +17502,7 @@
       <c r="Q232" s="61"/>
       <c r="U232" s="46"/>
     </row>
-    <row r="233" spans="1:30" ht="12.5">
+    <row r="233" spans="1:30" ht="12.75">
       <c r="A233" s="44"/>
       <c r="B233" s="44"/>
       <c r="C233" s="44"/>
@@ -17452,7 +17514,7 @@
       <c r="Q233" s="61"/>
       <c r="U233" s="46"/>
     </row>
-    <row r="234" spans="1:30" ht="12.5">
+    <row r="234" spans="1:30" ht="12.75">
       <c r="A234" s="44"/>
       <c r="B234" s="44"/>
       <c r="C234" s="44"/>
@@ -17479,15 +17541,15 @@
   <dimension ref="A1:I286"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.69921875" customWidth="1"/>
-    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.69921875" customWidth="1"/>
-    <col min="7" max="7" width="23.8984375" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.296875" customWidth="1"/>
-    <col min="10" max="10" width="26.296875" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
@@ -17519,7 +17581,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="11.5">
+    <row r="2" spans="1:9" ht="12">
       <c r="A2" s="11" t="s">
         <v>181</v>
       </c>
@@ -25561,13 +25623,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2051AA2F-ED82-497D-A0D7-BA51300AC6DC}">
   <dimension ref="A1:J92"/>
-  <sheetFormatPr defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="19.296875" customWidth="1"/>
-    <col min="6" max="7" width="23.296875" customWidth="1"/>
-    <col min="8" max="8" width="26.09765625" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="7" width="23.28515625" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28155,15 +28217,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197CD5C8-84EF-4E52-92C3-639A9DF2089C}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="25.59765625" customWidth="1"/>
-    <col min="6" max="6" width="25.3984375" customWidth="1"/>
-    <col min="7" max="7" width="22.59765625" customWidth="1"/>
-    <col min="8" max="8" width="12.8984375" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28258,13 +28320,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD50CF4B-F9EC-407F-8C73-9C597C45A3D8}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="24.69921875" customWidth="1"/>
-    <col min="6" max="6" width="21.69921875" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -28350,13 +28412,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B02B6F-B860-41DC-9D50-B3B43A9E1932}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="36.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5">
@@ -28378,7 +28440,7 @@
         <v>#REF!</v>
       </c>
       <c r="B3" t="e" cm="1">
-        <f t="array" ref="B3">_xlfn.UNIQUE(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(#REF!, #REF!&lt;&gt;"")))</f>
+        <f t="array" ref="B3">_xlfn.UNIQUE(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(#REF!,#REF!&lt;&gt; "")))</f>
         <v>#REF!</v>
       </c>
       <c r="C3" t="s">

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1304" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA140AE7-784E-4339-9236-1B5F3EBD627D}"/>
+  <xr:revisionPtr revIDLastSave="1321" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCAE9152-BEC5-456B-98D4-9A585A710564}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -2320,7 +2320,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2523,13 +2523,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3366,7 +3359,15 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V164" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V164" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
+  <autoFilter ref="A1:V164" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="&lt;none&gt;"/>
+        <filter val="Open House Special"/>
+        <filter val="VIP Event"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V150">
     <sortCondition ref="A1:A163"/>
   </sortState>
@@ -4468,7 +4469,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="12.75">
+    <row r="2" spans="1:31" ht="12.75" hidden="1">
       <c r="A2" s="44" t="s">
         <v>130</v>
       </c>
@@ -4538,7 +4539,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="12.75">
+    <row r="3" spans="1:31" ht="12.75" hidden="1">
       <c r="A3" s="44" t="s">
         <v>130</v>
       </c>
@@ -4607,7 +4608,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="12.75">
+    <row r="4" spans="1:31" ht="12.75" hidden="1">
       <c r="A4" s="44" t="s">
         <v>130</v>
       </c>
@@ -4818,7 +4819,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="12.75">
+    <row r="7" spans="1:31" ht="12.75" hidden="1">
       <c r="A7" s="44" t="s">
         <v>120</v>
       </c>
@@ -6733,7 +6734,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="12.75">
+    <row r="35" spans="1:31" ht="12.75" hidden="1">
       <c r="A35" s="44" t="s">
         <v>132</v>
       </c>
@@ -6802,7 +6803,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="12.75">
+    <row r="36" spans="1:31" ht="12.75" hidden="1">
       <c r="A36" s="44" t="s">
         <v>132</v>
       </c>
@@ -6872,7 +6873,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="12.75">
+    <row r="37" spans="1:31" ht="12.75" hidden="1">
       <c r="A37" s="44" t="s">
         <v>123</v>
       </c>
@@ -6944,7 +6945,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="12.75">
+    <row r="38" spans="1:31" ht="12.75" hidden="1">
       <c r="A38" s="44" t="s">
         <v>125</v>
       </c>
@@ -7016,7 +7017,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="12.75">
+    <row r="39" spans="1:31" ht="12.75" hidden="1">
       <c r="A39" s="44" t="s">
         <v>127</v>
       </c>
@@ -7088,7 +7089,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="12.75">
+    <row r="40" spans="1:31" ht="12.75" hidden="1">
       <c r="A40" s="44" t="s">
         <v>132</v>
       </c>
@@ -7232,7 +7233,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="12.75">
+    <row r="42" spans="1:31" ht="12.75" hidden="1">
       <c r="A42" s="44" t="s">
         <v>134</v>
       </c>
@@ -7301,7 +7302,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="12.75">
+    <row r="43" spans="1:31" ht="12.75" hidden="1">
       <c r="A43" s="44" t="s">
         <v>134</v>
       </c>
@@ -7370,7 +7371,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="12.75">
+    <row r="44" spans="1:31" ht="12.75" hidden="1">
       <c r="A44" s="44" t="s">
         <v>134</v>
       </c>
@@ -7577,7 +7578,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="12.75">
+    <row r="47" spans="1:31" ht="12.75" hidden="1">
       <c r="A47" s="44" t="s">
         <v>43</v>
       </c>
@@ -7712,7 +7713,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="12.75">
+    <row r="49" spans="1:32" ht="12.75" hidden="1">
       <c r="A49" s="44" t="s">
         <v>139</v>
       </c>
@@ -7785,7 +7786,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="12.75">
+    <row r="50" spans="1:32" ht="12.75" hidden="1">
       <c r="A50" s="44" t="s">
         <v>142</v>
       </c>
@@ -7858,7 +7859,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="12.75">
+    <row r="51" spans="1:32" ht="12.75" hidden="1">
       <c r="A51" s="44" t="s">
         <v>144</v>
       </c>
@@ -7931,7 +7932,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="12.75">
+    <row r="52" spans="1:32" ht="12.75" hidden="1">
       <c r="A52" s="44" t="s">
         <v>146</v>
       </c>
@@ -8004,7 +8005,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="12.75">
+    <row r="53" spans="1:32" ht="12.75" hidden="1">
       <c r="A53" s="44" t="s">
         <v>148</v>
       </c>
@@ -8077,7 +8078,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="12.75">
+    <row r="54" spans="1:32" ht="12.75" hidden="1">
       <c r="A54" s="44" t="s">
         <v>150</v>
       </c>
@@ -8150,7 +8151,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="12.75">
+    <row r="55" spans="1:32" ht="12.75" hidden="1">
       <c r="A55" s="44" t="s">
         <v>47</v>
       </c>
@@ -8223,7 +8224,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="12.75">
+    <row r="56" spans="1:32" ht="12.75" hidden="1">
       <c r="A56" s="44" t="s">
         <v>47</v>
       </c>
@@ -8296,7 +8297,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="12.75">
+    <row r="57" spans="1:32" ht="12.75" hidden="1">
       <c r="A57" s="44" t="s">
         <v>47</v>
       </c>
@@ -8369,7 +8370,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:32" ht="12.75">
+    <row r="58" spans="1:32" ht="12.75" hidden="1">
       <c r="A58" s="44" t="s">
         <v>47</v>
       </c>
@@ -8442,7 +8443,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:32" ht="12.75">
+    <row r="59" spans="1:32" ht="12.75" hidden="1">
       <c r="A59" s="44" t="s">
         <v>47</v>
       </c>
@@ -8515,7 +8516,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:32" ht="12.75">
+    <row r="60" spans="1:32" ht="12.75" hidden="1">
       <c r="A60" s="44" t="s">
         <v>47</v>
       </c>
@@ -8588,7 +8589,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="12.75">
+    <row r="61" spans="1:32" ht="12.75" hidden="1">
       <c r="A61" s="44" t="s">
         <v>61</v>
       </c>
@@ -8661,7 +8662,7 @@
       <c r="AE61" s="16"/>
       <c r="AF61" s="16"/>
     </row>
-    <row r="62" spans="1:32" ht="12.75">
+    <row r="62" spans="1:32" ht="12.75" hidden="1">
       <c r="A62" s="44" t="s">
         <v>64</v>
       </c>
@@ -8733,7 +8734,7 @@
       <c r="AE62" s="16"/>
       <c r="AF62" s="16"/>
     </row>
-    <row r="63" spans="1:32" ht="12.75">
+    <row r="63" spans="1:32" ht="12.75" hidden="1">
       <c r="A63" s="44" t="s">
         <v>66</v>
       </c>
@@ -8805,7 +8806,7 @@
       <c r="AE63" s="16"/>
       <c r="AF63" s="16"/>
     </row>
-    <row r="64" spans="1:32" ht="12.75">
+    <row r="64" spans="1:32" ht="12.75" hidden="1">
       <c r="A64" s="44" t="s">
         <v>70</v>
       </c>
@@ -8878,7 +8879,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="12.75">
+    <row r="65" spans="1:31" ht="12.75" hidden="1">
       <c r="A65" s="44" t="s">
         <v>72</v>
       </c>
@@ -8951,7 +8952,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="12.75">
+    <row r="66" spans="1:31" ht="12.75" hidden="1">
       <c r="A66" s="44" t="s">
         <v>75</v>
       </c>
@@ -9024,7 +9025,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="12.75">
+    <row r="67" spans="1:31" ht="12.75" hidden="1">
       <c r="A67" s="44" t="s">
         <v>77</v>
       </c>
@@ -9095,7 +9096,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="12.75">
+    <row r="68" spans="1:31" ht="12.75" hidden="1">
       <c r="A68" s="44" t="s">
         <v>80</v>
       </c>
@@ -9166,7 +9167,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="12.75">
+    <row r="69" spans="1:31" ht="12.75" hidden="1">
       <c r="A69" s="44" t="s">
         <v>82</v>
       </c>
@@ -9239,7 +9240,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="12.75">
+    <row r="70" spans="1:31" ht="12.75" hidden="1">
       <c r="A70" s="44" t="s">
         <v>84</v>
       </c>
@@ -9312,7 +9313,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="12.75">
+    <row r="71" spans="1:31" ht="12.75" hidden="1">
       <c r="A71" s="44" t="s">
         <v>86</v>
       </c>
@@ -9385,7 +9386,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="12.75">
+    <row r="72" spans="1:31" ht="12.75" hidden="1">
       <c r="A72" s="44" t="s">
         <v>88</v>
       </c>
@@ -9458,7 +9459,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="12.75">
+    <row r="73" spans="1:31" ht="12.75" hidden="1">
       <c r="A73" s="44" t="s">
         <v>90</v>
       </c>
@@ -9531,7 +9532,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="12.75">
+    <row r="74" spans="1:31" ht="12.75" hidden="1">
       <c r="A74" s="44" t="s">
         <v>92</v>
       </c>
@@ -9604,7 +9605,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="12.75">
+    <row r="75" spans="1:31" ht="12.75" hidden="1">
       <c r="A75" s="44" t="s">
         <v>94</v>
       </c>
@@ -9677,7 +9678,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="12.75">
+    <row r="76" spans="1:31" ht="12.75" hidden="1">
       <c r="A76" s="44" t="s">
         <v>96</v>
       </c>
@@ -9748,7 +9749,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="12.75">
+    <row r="77" spans="1:31" ht="12.75" hidden="1">
       <c r="A77" s="44" t="s">
         <v>98</v>
       </c>
@@ -9819,7 +9820,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="12.75">
+    <row r="78" spans="1:31" ht="12.75" hidden="1">
       <c r="A78" s="44" t="s">
         <v>100</v>
       </c>
@@ -9890,7 +9891,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="12.75">
+    <row r="79" spans="1:31" ht="12.75" hidden="1">
       <c r="A79" s="44" t="s">
         <v>102</v>
       </c>
@@ -9963,7 +9964,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="12.75">
+    <row r="80" spans="1:31" ht="12.75" hidden="1">
       <c r="A80" s="44" t="s">
         <v>104</v>
       </c>
@@ -10036,7 +10037,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="12.75">
+    <row r="81" spans="1:31" ht="12.75" hidden="1">
       <c r="A81" s="44" t="s">
         <v>106</v>
       </c>
@@ -10109,7 +10110,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="12.75">
+    <row r="82" spans="1:31" ht="12.75" hidden="1">
       <c r="A82" s="44" t="s">
         <v>108</v>
       </c>
@@ -10182,7 +10183,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="12.75">
+    <row r="83" spans="1:31" ht="12.75" hidden="1">
       <c r="A83" s="44" t="s">
         <v>110</v>
       </c>
@@ -10255,7 +10256,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="12.75">
+    <row r="84" spans="1:31" ht="12.75" hidden="1">
       <c r="A84" s="44" t="s">
         <v>112</v>
       </c>
@@ -10328,7 +10329,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="12.75">
+    <row r="85" spans="1:31" ht="12.75" hidden="1">
       <c r="A85" s="44" t="s">
         <v>114</v>
       </c>
@@ -10399,7 +10400,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="12.75">
+    <row r="86" spans="1:31" ht="12.75" hidden="1">
       <c r="A86" s="44" t="s">
         <v>116</v>
       </c>
@@ -10470,7 +10471,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="12.75">
+    <row r="87" spans="1:31" ht="12.75" hidden="1">
       <c r="A87" s="44" t="s">
         <v>118</v>
       </c>
@@ -10541,7 +10542,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="12.75">
+    <row r="88" spans="1:31" ht="12.75" hidden="1">
       <c r="A88" s="44" t="s">
         <v>123</v>
       </c>
@@ -10614,7 +10615,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="12.75">
+    <row r="89" spans="1:31" ht="12.75" hidden="1">
       <c r="A89" s="44" t="s">
         <v>125</v>
       </c>
@@ -10687,7 +10688,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="12.75">
+    <row r="90" spans="1:31" ht="12.75" hidden="1">
       <c r="A90" s="44" t="s">
         <v>127</v>
       </c>
@@ -10760,7 +10761,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="12.75">
+    <row r="91" spans="1:31" ht="12.75" hidden="1">
       <c r="A91" s="44" t="s">
         <v>47</v>
       </c>
@@ -10833,7 +10834,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="12.75">
+    <row r="92" spans="1:31" ht="12.75" hidden="1">
       <c r="A92" s="44" t="s">
         <v>47</v>
       </c>
@@ -10906,7 +10907,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="12.75">
+    <row r="93" spans="1:31" ht="12.75" hidden="1">
       <c r="A93" s="44" t="s">
         <v>47</v>
       </c>
@@ -10979,7 +10980,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="12.75">
+    <row r="94" spans="1:31" ht="12.75" hidden="1">
       <c r="A94" s="44" t="s">
         <v>47</v>
       </c>
@@ -11052,7 +11053,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="12.75">
+    <row r="95" spans="1:31" ht="12.75" hidden="1">
       <c r="A95" s="44" t="s">
         <v>47</v>
       </c>
@@ -11125,7 +11126,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="12.75">
+    <row r="96" spans="1:31" ht="12.75" hidden="1">
       <c r="A96" s="44" t="s">
         <v>123</v>
       </c>
@@ -11197,7 +11198,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="12.75">
+    <row r="97" spans="1:31" ht="12.75" hidden="1">
       <c r="A97" s="44" t="s">
         <v>125</v>
       </c>
@@ -11269,7 +11270,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="12.75">
+    <row r="98" spans="1:31" ht="12.75" hidden="1">
       <c r="A98" s="44" t="s">
         <v>127</v>
       </c>
@@ -11341,7 +11342,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="12.75">
+    <row r="99" spans="1:31" ht="12.75" hidden="1">
       <c r="A99" s="44" t="s">
         <v>47</v>
       </c>
@@ -11413,7 +11414,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="12.75">
+    <row r="100" spans="1:31" ht="12.75" hidden="1">
       <c r="A100" s="44" t="s">
         <v>123</v>
       </c>
@@ -11485,7 +11486,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="12.75">
+    <row r="101" spans="1:31" ht="12.75" hidden="1">
       <c r="A101" s="44" t="s">
         <v>125</v>
       </c>
@@ -11557,7 +11558,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="12.75">
+    <row r="102" spans="1:31" ht="12.75" hidden="1">
       <c r="A102" s="44" t="s">
         <v>127</v>
       </c>
@@ -11630,7 +11631,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="12.75">
+    <row r="103" spans="1:31" ht="12.75" hidden="1">
       <c r="A103" s="44" t="s">
         <v>47</v>
       </c>
@@ -11702,7 +11703,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="12.75">
+    <row r="104" spans="1:31" ht="12.75" hidden="1">
       <c r="A104" s="44" t="s">
         <v>123</v>
       </c>
@@ -11774,7 +11775,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="12.75">
+    <row r="105" spans="1:31" ht="12.75" hidden="1">
       <c r="A105" s="44" t="s">
         <v>125</v>
       </c>
@@ -11846,7 +11847,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="12.75">
+    <row r="106" spans="1:31" ht="12.75" hidden="1">
       <c r="A106" s="44" t="s">
         <v>127</v>
       </c>
@@ -11987,7 +11988,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="12.75">
+    <row r="108" spans="1:31" ht="12.75" hidden="1">
       <c r="A108" s="44" t="s">
         <v>123</v>
       </c>
@@ -12059,7 +12060,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="12.75">
+    <row r="109" spans="1:31" ht="12.75" hidden="1">
       <c r="A109" s="44" t="s">
         <v>125</v>
       </c>
@@ -12131,7 +12132,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="12.75">
+    <row r="110" spans="1:31" ht="12.75" hidden="1">
       <c r="A110" s="44" t="s">
         <v>127</v>
       </c>
@@ -12203,7 +12204,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="12.75">
+    <row r="111" spans="1:31" ht="12.75" hidden="1">
       <c r="A111" s="44" t="s">
         <v>139</v>
       </c>
@@ -12276,7 +12277,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="12.75">
+    <row r="112" spans="1:31" ht="12.75" hidden="1">
       <c r="A112" s="44" t="s">
         <v>142</v>
       </c>
@@ -12349,7 +12350,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="12.75">
+    <row r="113" spans="1:31" ht="12.75" hidden="1">
       <c r="A113" s="44" t="s">
         <v>144</v>
       </c>
@@ -12422,7 +12423,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="12.75">
+    <row r="114" spans="1:31" ht="12.75" hidden="1">
       <c r="A114" s="44" t="s">
         <v>146</v>
       </c>
@@ -12495,7 +12496,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="12.75">
+    <row r="115" spans="1:31" ht="12.75" hidden="1">
       <c r="A115" s="44" t="s">
         <v>148</v>
       </c>
@@ -12568,7 +12569,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="12.75">
+    <row r="116" spans="1:31" ht="12.75" hidden="1">
       <c r="A116" s="44" t="s">
         <v>150</v>
       </c>
@@ -12641,7 +12642,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.75">
+    <row r="117" spans="1:31" ht="12.75" hidden="1">
       <c r="A117" s="44" t="s">
         <v>53</v>
       </c>
@@ -12713,7 +12714,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.75">
+    <row r="118" spans="1:31" ht="12.75" hidden="1">
       <c r="A118" s="44" t="s">
         <v>53</v>
       </c>
@@ -12785,7 +12786,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.75">
+    <row r="119" spans="1:31" ht="12.75" hidden="1">
       <c r="A119" s="44" t="s">
         <v>53</v>
       </c>
@@ -12857,7 +12858,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="12.75">
+    <row r="120" spans="1:31" ht="12.75" hidden="1">
       <c r="A120" s="44" t="s">
         <v>123</v>
       </c>
@@ -12930,7 +12931,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="12.75">
+    <row r="121" spans="1:31" ht="12.75" hidden="1">
       <c r="A121" s="44" t="s">
         <v>125</v>
       </c>
@@ -13003,7 +13004,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="12.75">
+    <row r="122" spans="1:31" ht="12.75" hidden="1">
       <c r="A122" s="44" t="s">
         <v>127</v>
       </c>
@@ -13077,7 +13078,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="12.75">
+    <row r="123" spans="1:31" ht="12.75" hidden="1">
       <c r="A123" s="44" t="s">
         <v>53</v>
       </c>
@@ -13296,7 +13297,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.75">
+    <row r="126" spans="1:31" ht="12.75" hidden="1">
       <c r="A126" s="44" t="s">
         <v>50</v>
       </c>
@@ -13369,7 +13370,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="12.75">
+    <row r="127" spans="1:31" ht="12.75" hidden="1">
       <c r="A127" s="44" t="s">
         <v>123</v>
       </c>
@@ -13442,7 +13443,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="12.75">
+    <row r="128" spans="1:31" ht="12.75" hidden="1">
       <c r="A128" s="44" t="s">
         <v>125</v>
       </c>
@@ -13515,7 +13516,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="12.75">
+    <row r="129" spans="1:31" ht="12.75" hidden="1">
       <c r="A129" s="44" t="s">
         <v>127</v>
       </c>
@@ -13658,7 +13659,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="12.75">
+    <row r="131" spans="1:31" ht="12.75" hidden="1">
       <c r="A131" s="44" t="s">
         <v>123</v>
       </c>
@@ -13731,7 +13732,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="12.75">
+    <row r="132" spans="1:31" ht="12.75" hidden="1">
       <c r="A132" s="44" t="s">
         <v>125</v>
       </c>
@@ -13804,7 +13805,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="12.75">
+    <row r="133" spans="1:31" ht="12.75" hidden="1">
       <c r="A133" s="44" t="s">
         <v>127</v>
       </c>
@@ -13877,7 +13878,7 @@
       <c r="AD133"/>
       <c r="AE133"/>
     </row>
-    <row r="134" spans="1:31" ht="12.75">
+    <row r="134" spans="1:31" ht="12.75" hidden="1">
       <c r="A134" s="44" t="s">
         <v>57</v>
       </c>
@@ -13950,7 +13951,7 @@
       <c r="AD134"/>
       <c r="AE134"/>
     </row>
-    <row r="135" spans="1:31" ht="12.75">
+    <row r="135" spans="1:31" ht="12.75" hidden="1">
       <c r="A135" s="44" t="s">
         <v>57</v>
       </c>
@@ -14023,7 +14024,7 @@
       <c r="AD135"/>
       <c r="AE135"/>
     </row>
-    <row r="136" spans="1:31" ht="12.75">
+    <row r="136" spans="1:31" ht="12.75" hidden="1">
       <c r="A136" s="44" t="s">
         <v>57</v>
       </c>
@@ -14096,7 +14097,7 @@
       <c r="AD136"/>
       <c r="AE136"/>
     </row>
-    <row r="137" spans="1:31" ht="12.75">
+    <row r="137" spans="1:31" ht="12.75" hidden="1">
       <c r="A137" s="44" t="s">
         <v>57</v>
       </c>
@@ -14312,7 +14313,7 @@
       <c r="AC139" s="48"/>
       <c r="AD139" s="48"/>
     </row>
-    <row r="140" spans="1:31" ht="12.75">
+    <row r="140" spans="1:31" ht="12.75" hidden="1">
       <c r="A140" s="87" t="s">
         <v>59</v>
       </c>
@@ -14384,7 +14385,7 @@
       <c r="AC140" s="48"/>
       <c r="AD140" s="48"/>
     </row>
-    <row r="141" spans="1:31" ht="12.75">
+    <row r="141" spans="1:31" ht="12.75" hidden="1">
       <c r="A141" s="87" t="s">
         <v>123</v>
       </c>
@@ -14456,7 +14457,7 @@
       <c r="AC141" s="48"/>
       <c r="AD141" s="46"/>
     </row>
-    <row r="142" spans="1:31" ht="12.75">
+    <row r="142" spans="1:31" ht="12.75" hidden="1">
       <c r="A142" s="87" t="s">
         <v>125</v>
       </c>
@@ -14528,7 +14529,7 @@
       <c r="AC142" s="48"/>
       <c r="AD142" s="46"/>
     </row>
-    <row r="143" spans="1:31" ht="12.75">
+    <row r="143" spans="1:31" ht="12.75" hidden="1">
       <c r="A143" s="87" t="s">
         <v>127</v>
       </c>
@@ -14600,7 +14601,7 @@
       <c r="AC143" s="48"/>
       <c r="AD143" s="46"/>
     </row>
-    <row r="144" spans="1:31" ht="12.75">
+    <row r="144" spans="1:31" ht="12.75" hidden="1">
       <c r="A144" s="87" t="s">
         <v>59</v>
       </c>
@@ -14672,7 +14673,7 @@
       <c r="AC144" s="48"/>
       <c r="AD144" s="46"/>
     </row>
-    <row r="145" spans="1:31" ht="12.75">
+    <row r="145" spans="1:31" ht="12.75" hidden="1">
       <c r="A145" s="87" t="s">
         <v>123</v>
       </c>
@@ -14745,7 +14746,7 @@
       <c r="AD145" s="46"/>
       <c r="AE145" s="16"/>
     </row>
-    <row r="146" spans="1:31" ht="12.75">
+    <row r="146" spans="1:31" ht="12.75" hidden="1">
       <c r="A146" s="87" t="s">
         <v>125</v>
       </c>
@@ -14818,7 +14819,7 @@
       <c r="AD146" s="7"/>
       <c r="AE146" s="16"/>
     </row>
-    <row r="147" spans="1:31" ht="12.75">
+    <row r="147" spans="1:31" ht="12.75" hidden="1">
       <c r="A147" s="87" t="s">
         <v>127</v>
       </c>
@@ -14891,7 +14892,7 @@
       <c r="AD147" s="7"/>
       <c r="AE147" s="16"/>
     </row>
-    <row r="148" spans="1:31" ht="12.75">
+    <row r="148" spans="1:31" ht="12.75" hidden="1">
       <c r="A148" s="87" t="s">
         <v>59</v>
       </c>
@@ -14963,7 +14964,7 @@
       <c r="AC148" s="48"/>
       <c r="AD148" s="7"/>
     </row>
-    <row r="149" spans="1:31" ht="12.75">
+    <row r="149" spans="1:31" ht="12.75" hidden="1">
       <c r="A149" s="87" t="s">
         <v>123</v>
       </c>
@@ -15035,7 +15036,7 @@
       <c r="AC149" s="48"/>
       <c r="AD149" s="7"/>
     </row>
-    <row r="150" spans="1:31" ht="12.75">
+    <row r="150" spans="1:31" ht="12.75" hidden="1">
       <c r="A150" s="87" t="s">
         <v>125</v>
       </c>
@@ -15107,7 +15108,7 @@
       <c r="AC150" s="48"/>
       <c r="AD150" s="7"/>
     </row>
-    <row r="151" spans="1:31" ht="12.75">
+    <row r="151" spans="1:31" ht="12.75" hidden="1">
       <c r="A151" s="87" t="s">
         <v>127</v>
       </c>
@@ -15179,7 +15180,7 @@
       <c r="AC151" s="48"/>
       <c r="AD151" s="7"/>
     </row>
-    <row r="152" spans="1:31" ht="12.75">
+    <row r="152" spans="1:31" ht="12.75" hidden="1">
       <c r="A152" s="93" t="s">
         <v>59</v>
       </c>
@@ -15252,7 +15253,7 @@
       <c r="AC152" s="48"/>
       <c r="AD152" s="46"/>
     </row>
-    <row r="153" spans="1:31" ht="12.75">
+    <row r="153" spans="1:31" ht="12.75" hidden="1">
       <c r="A153" s="44" t="s">
         <v>123</v>
       </c>
@@ -15324,7 +15325,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="12.75">
+    <row r="154" spans="1:31" ht="12.75" hidden="1">
       <c r="A154" s="44" t="s">
         <v>125</v>
       </c>
@@ -15396,7 +15397,7 @@
       <c r="AD154"/>
       <c r="AE154"/>
     </row>
-    <row r="155" spans="1:31" ht="12.75">
+    <row r="155" spans="1:31" ht="12.75" hidden="1">
       <c r="A155" s="44" t="s">
         <v>127</v>
       </c>
@@ -15540,7 +15541,7 @@
       <c r="AD156"/>
       <c r="AE156"/>
     </row>
-    <row r="157" spans="1:31" ht="12.75">
+    <row r="157" spans="1:31" ht="12.75" hidden="1">
       <c r="A157" s="44" t="s">
         <v>123</v>
       </c>
@@ -15612,7 +15613,7 @@
       <c r="AD157"/>
       <c r="AE157"/>
     </row>
-    <row r="158" spans="1:31" ht="12.75">
+    <row r="158" spans="1:31" ht="12.75" hidden="1">
       <c r="A158" s="44" t="s">
         <v>125</v>
       </c>
@@ -15685,7 +15686,7 @@
       <c r="AD158"/>
       <c r="AE158"/>
     </row>
-    <row r="159" spans="1:31" ht="12.75">
+    <row r="159" spans="1:31" ht="12.75" hidden="1">
       <c r="A159" s="44" t="s">
         <v>127</v>
       </c>
@@ -15758,7 +15759,7 @@
       <c r="AD159"/>
       <c r="AE159"/>
     </row>
-    <row r="160" spans="1:31" ht="12.75">
+    <row r="160" spans="1:31" ht="12.75" hidden="1">
       <c r="A160" s="44" t="s">
         <v>165</v>
       </c>
@@ -15837,7 +15838,7 @@
       <c r="AC160" s="48"/>
       <c r="AD160" s="48"/>
     </row>
-    <row r="161" spans="1:30" ht="12.75">
+    <row r="161" spans="1:30" ht="12.75" hidden="1">
       <c r="A161" s="44" t="s">
         <v>167</v>
       </c>
@@ -15916,7 +15917,7 @@
       <c r="AC161" s="48"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="12.75">
+    <row r="162" spans="1:30" ht="12.75" hidden="1">
       <c r="A162" s="44" t="s">
         <v>169</v>
       </c>
@@ -15995,7 +15996,7 @@
       <c r="AC162" s="48"/>
       <c r="AD162" s="46"/>
     </row>
-    <row r="163" spans="1:30" ht="12.75">
+    <row r="163" spans="1:30" ht="12.75" hidden="1">
       <c r="A163" s="44" t="s">
         <v>1</v>
       </c>
@@ -16075,10 +16076,10 @@
       <c r="AD163" s="7"/>
     </row>
     <row r="164" spans="1:30" ht="12.75">
-      <c r="A164" s="108" t="s">
+      <c r="A164" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="B164" s="109" t="s">
+      <c r="B164" s="44" t="s">
         <v>54</v>
       </c>
       <c r="C164" s="45">
@@ -16089,56 +16090,47 @@
         <v>5819</v>
       </c>
       <c r="E164" s="46" t="s">
-        <v>10</v>
+        <v>638</v>
       </c>
       <c r="F164" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
-      </c>
-      <c r="G164" s="110">
+        <v>1200</v>
+      </c>
+      <c r="G164" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H164" s="40">
-        <v>9450</v>
-      </c>
-      <c r="I164" s="47" t="s">
-        <v>638</v>
+        <v>4619</v>
+      </c>
+      <c r="H164" s="52">
+        <v>9563</v>
+      </c>
+      <c r="I164" s="61" t="s">
+        <v>45</v>
       </c>
       <c r="J164" s="48">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>443.5</v>
-      </c>
-      <c r="K164" s="111">
+        <v>0</v>
+      </c>
+      <c r="K164" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4119</v>
-      </c>
-      <c r="L164" s="55">
-        <v>8563</v>
-      </c>
-      <c r="M164" s="47"/>
-      <c r="N164" s="111">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>4119</v>
-      </c>
-      <c r="O164" s="112">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
-      <c r="P164" s="46"/>
-      <c r="Q164" s="85">
+        <v>4619</v>
+      </c>
+      <c r="L164" s="52"/>
+      <c r="M164" s="48"/>
+      <c r="N164" s="48"/>
+      <c r="O164" s="48"/>
+      <c r="P164" s="48"/>
+      <c r="Q164" s="49">
         <v>1</v>
       </c>
-      <c r="R164" s="85" t="s">
+      <c r="R164" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="S164" s="49">
+      <c r="S164" s="48">
         <v>325</v>
       </c>
       <c r="T164" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="U164" s="50">
+      <c r="U164" s="51">
         <v>0</v>
       </c>
       <c r="V164" s="50" t="s">

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1321" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCAE9152-BEC5-456B-98D4-9A585A710564}"/>
+  <xr:revisionPtr revIDLastSave="1322" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F743767-36AC-4912-9160-ED55DF399200}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="638">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -1978,9 +1978,6 @@
   </si>
   <si>
     <t>AllWell Lease Upgrade</t>
-  </si>
-  <si>
-    <t>VIP Event</t>
   </si>
 </sst>
 </file>
@@ -3358,8 +3355,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V164" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V164" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V163" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+  <autoFilter ref="A1:V163" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
     <filterColumn colId="8">
       <filters>
         <filter val="&lt;none&gt;"/>
@@ -4362,7 +4359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
-  <dimension ref="A1:AF234"/>
+  <dimension ref="A1:AF233"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="53.85546875" customWidth="1"/>
@@ -16076,66 +16073,17 @@
       <c r="AD163" s="7"/>
     </row>
     <row r="164" spans="1:30" ht="12.75">
-      <c r="A164" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B164" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="C164" s="45">
-        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D164" s="46">
-        <v>5819</v>
-      </c>
-      <c r="E164" s="46" t="s">
-        <v>638</v>
-      </c>
-      <c r="F164" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1200</v>
-      </c>
-      <c r="G164" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4619</v>
-      </c>
-      <c r="H164" s="52">
-        <v>9563</v>
-      </c>
-      <c r="I164" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="J164" s="48">
-        <v>0</v>
-      </c>
-      <c r="K164" s="48">
-        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4619</v>
-      </c>
-      <c r="L164" s="52"/>
+      <c r="A164" s="44"/>
+      <c r="B164" s="44"/>
+      <c r="C164" s="44"/>
+      <c r="I164" s="46"/>
+      <c r="J164" s="46"/>
+      <c r="K164" s="46"/>
       <c r="M164" s="48"/>
       <c r="N164" s="48"/>
       <c r="O164" s="48"/>
-      <c r="P164" s="48"/>
-      <c r="Q164" s="49">
-        <v>1</v>
-      </c>
-      <c r="R164" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="S164" s="48">
-        <v>325</v>
-      </c>
-      <c r="T164" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="U164" s="51">
-        <v>0</v>
-      </c>
-      <c r="V164" s="50" t="s">
-        <v>56</v>
-      </c>
+      <c r="Q164" s="61"/>
+      <c r="U164" s="48"/>
       <c r="X164" s="48"/>
       <c r="Y164" s="48"/>
       <c r="Z164" s="48"/>
@@ -16162,12 +16110,13 @@
       <c r="AA165" s="48"/>
       <c r="AB165" s="48"/>
       <c r="AC165" s="48"/>
-      <c r="AD165" s="7"/>
+      <c r="AD165" s="48"/>
     </row>
     <row r="166" spans="1:30" ht="12.75">
       <c r="A166" s="44"/>
       <c r="B166" s="44"/>
       <c r="C166" s="44"/>
+      <c r="H166" s="15"/>
       <c r="I166" s="46"/>
       <c r="J166" s="46"/>
       <c r="K166" s="46"/>
@@ -16203,13 +16152,12 @@
       <c r="AA167" s="48"/>
       <c r="AB167" s="48"/>
       <c r="AC167" s="48"/>
-      <c r="AD167" s="48"/>
+      <c r="AD167" s="7"/>
     </row>
     <row r="168" spans="1:30" ht="12.75">
       <c r="A168" s="44"/>
       <c r="B168" s="44"/>
       <c r="C168" s="44"/>
-      <c r="H168" s="15"/>
       <c r="I168" s="46"/>
       <c r="J168" s="46"/>
       <c r="K168" s="46"/>
@@ -16264,7 +16212,7 @@
       <c r="AA170" s="48"/>
       <c r="AB170" s="48"/>
       <c r="AC170" s="48"/>
-      <c r="AD170" s="7"/>
+      <c r="AD170" s="48"/>
     </row>
     <row r="171" spans="1:30" ht="12.75">
       <c r="A171" s="44"/>
@@ -16304,7 +16252,7 @@
       <c r="AA172" s="48"/>
       <c r="AB172" s="48"/>
       <c r="AC172" s="48"/>
-      <c r="AD172" s="48"/>
+      <c r="AD172" s="7"/>
     </row>
     <row r="173" spans="1:30" ht="12.75">
       <c r="A173" s="44"/>
@@ -16364,7 +16312,7 @@
       <c r="AA175" s="48"/>
       <c r="AB175" s="48"/>
       <c r="AC175" s="48"/>
-      <c r="AD175" s="7"/>
+      <c r="AD175" s="48"/>
     </row>
     <row r="176" spans="1:30" ht="12.75">
       <c r="A176" s="44"/>
@@ -16404,7 +16352,7 @@
       <c r="AA177" s="48"/>
       <c r="AB177" s="48"/>
       <c r="AC177" s="48"/>
-      <c r="AD177" s="48"/>
+      <c r="AD177" s="46"/>
     </row>
     <row r="178" spans="1:30" ht="12.75">
       <c r="A178" s="44"/>
@@ -16553,7 +16501,7 @@
       <c r="I185" s="46"/>
       <c r="J185" s="46"/>
       <c r="K185" s="46"/>
-      <c r="M185" s="48"/>
+      <c r="M185" s="79"/>
       <c r="N185" s="48"/>
       <c r="O185" s="48"/>
       <c r="Q185" s="61"/>
@@ -16564,7 +16512,7 @@
       <c r="AA185" s="48"/>
       <c r="AB185" s="48"/>
       <c r="AC185" s="48"/>
-      <c r="AD185" s="46"/>
+      <c r="AD185" s="7"/>
     </row>
     <row r="186" spans="1:30" ht="12.75">
       <c r="A186" s="44"/>
@@ -16573,7 +16521,7 @@
       <c r="I186" s="46"/>
       <c r="J186" s="46"/>
       <c r="K186" s="46"/>
-      <c r="M186" s="79"/>
+      <c r="M186" s="46"/>
       <c r="N186" s="48"/>
       <c r="O186" s="48"/>
       <c r="Q186" s="61"/>
@@ -16618,13 +16566,12 @@
       <c r="O188" s="48"/>
       <c r="Q188" s="61"/>
       <c r="U188" s="48"/>
-      <c r="X188" s="48"/>
-      <c r="Y188" s="48"/>
-      <c r="Z188" s="48"/>
-      <c r="AA188" s="48"/>
-      <c r="AB188" s="48"/>
-      <c r="AC188" s="48"/>
-      <c r="AD188" s="7"/>
+      <c r="X188" s="79"/>
+      <c r="Y188" s="79"/>
+      <c r="Z188" s="79"/>
+      <c r="AA188" s="79"/>
+      <c r="AB188" s="79"/>
+      <c r="AD188" s="16"/>
     </row>
     <row r="189" spans="1:30" ht="12.75">
       <c r="A189" s="44"/>
@@ -16638,12 +16585,13 @@
       <c r="O189" s="48"/>
       <c r="Q189" s="61"/>
       <c r="U189" s="48"/>
-      <c r="X189" s="79"/>
-      <c r="Y189" s="79"/>
-      <c r="Z189" s="79"/>
-      <c r="AA189" s="79"/>
-      <c r="AB189" s="79"/>
-      <c r="AD189" s="16"/>
+      <c r="X189" s="46"/>
+      <c r="Y189" s="46"/>
+      <c r="Z189" s="46"/>
+      <c r="AA189" s="46"/>
+      <c r="AB189" s="46"/>
+      <c r="AC189" s="46"/>
+      <c r="AD189" s="46"/>
     </row>
     <row r="190" spans="1:30" ht="12.75">
       <c r="A190" s="44"/>
@@ -16669,14 +16617,14 @@
       <c r="A191" s="44"/>
       <c r="B191" s="44"/>
       <c r="C191" s="44"/>
-      <c r="I191" s="46"/>
-      <c r="J191" s="46"/>
-      <c r="K191" s="46"/>
+      <c r="I191" s="79"/>
+      <c r="J191" s="79"/>
+      <c r="K191" s="79"/>
       <c r="M191" s="46"/>
-      <c r="N191" s="48"/>
-      <c r="O191" s="48"/>
+      <c r="N191" s="79"/>
+      <c r="O191" s="79"/>
       <c r="Q191" s="61"/>
-      <c r="U191" s="48"/>
+      <c r="U191" s="79"/>
       <c r="X191" s="46"/>
       <c r="Y191" s="46"/>
       <c r="Z191" s="46"/>
@@ -16689,14 +16637,14 @@
       <c r="A192" s="44"/>
       <c r="B192" s="44"/>
       <c r="C192" s="44"/>
-      <c r="I192" s="79"/>
-      <c r="J192" s="79"/>
-      <c r="K192" s="79"/>
+      <c r="I192" s="46"/>
+      <c r="J192" s="46"/>
+      <c r="K192" s="46"/>
       <c r="M192" s="46"/>
-      <c r="N192" s="79"/>
-      <c r="O192" s="79"/>
+      <c r="N192" s="46"/>
+      <c r="O192" s="46"/>
       <c r="Q192" s="61"/>
-      <c r="U192" s="79"/>
+      <c r="U192" s="46"/>
       <c r="X192" s="46"/>
       <c r="Y192" s="46"/>
       <c r="Z192" s="46"/>
@@ -17412,7 +17360,6 @@
       <c r="I228" s="46"/>
       <c r="J228" s="46"/>
       <c r="K228" s="46"/>
-      <c r="M228" s="46"/>
       <c r="N228" s="46"/>
       <c r="O228" s="46"/>
       <c r="Q228" s="61"/>
@@ -17474,13 +17421,6 @@
       <c r="O231" s="46"/>
       <c r="Q231" s="61"/>
       <c r="U231" s="46"/>
-      <c r="X231" s="46"/>
-      <c r="Y231" s="46"/>
-      <c r="Z231" s="46"/>
-      <c r="AA231" s="46"/>
-      <c r="AB231" s="46"/>
-      <c r="AC231" s="46"/>
-      <c r="AD231" s="46"/>
     </row>
     <row r="232" spans="1:30" ht="12.75">
       <c r="A232" s="44"/>
@@ -17505,18 +17445,6 @@
       <c r="O233" s="46"/>
       <c r="Q233" s="61"/>
       <c r="U233" s="46"/>
-    </row>
-    <row r="234" spans="1:30" ht="12.75">
-      <c r="A234" s="44"/>
-      <c r="B234" s="44"/>
-      <c r="C234" s="44"/>
-      <c r="I234" s="46"/>
-      <c r="J234" s="46"/>
-      <c r="K234" s="46"/>
-      <c r="N234" s="46"/>
-      <c r="O234" s="46"/>
-      <c r="Q234" s="61"/>
-      <c r="U234" s="46"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1322" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F743767-36AC-4912-9160-ED55DF399200}"/>
+  <xr:revisionPtr revIDLastSave="1336" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{872EDEEE-FA94-4002-8DD2-83D605F5B0F1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="649">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -1978,6 +1978,39 @@
   </si>
   <si>
     <t>AllWell Lease Upgrade</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital Illuminate 17 62S-DRWC</t>
+  </si>
+  <si>
+    <t>Beltone Illuminate 17 62S-DRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Illuminate 17 Special</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital Illuminate 4 62S-DRWC</t>
+  </si>
+  <si>
+    <t>Beltone Illuminate 4 62S-DRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital Illuminate 6 62S-DRWC</t>
+  </si>
+  <si>
+    <t>Beltone Illuminate 6 62S-DRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Illuminate 6 Special</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital Illuminate 9 62S-DRWC</t>
+  </si>
+  <si>
+    <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Illuminate 9 Special</t>
   </si>
 </sst>
 </file>
@@ -2069,7 +2102,7 @@
       <charset val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2098,6 +2131,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -2317,7 +2356,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2520,6 +2559,34 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3355,13 +3422,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V163" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V163" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V183" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+  <autoFilter ref="A1:V183" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+    <filterColumn colId="0">
       <filters>
-        <filter val="&lt;none&gt;"/>
-        <filter val="Open House Special"/>
-        <filter val="VIP Event"/>
+        <filter val="Beltone RIE Digital Envision 17 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Envision 4 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Envision 6 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Envision 9 62S-DRWC"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4677,7 +4745,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="12.75">
+    <row r="5" spans="1:31" ht="12.75" hidden="1">
       <c r="A5" s="44" t="s">
         <v>130</v>
       </c>
@@ -4749,7 +4817,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="12.75">
+    <row r="6" spans="1:31" ht="12.75" hidden="1">
       <c r="A6" s="44" t="s">
         <v>120</v>
       </c>
@@ -4880,7 +4948,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="12.75">
+    <row r="8" spans="1:31" ht="12.75" hidden="1">
       <c r="A8" s="44" t="s">
         <v>61</v>
       </c>
@@ -4949,7 +5017,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="12.75">
+    <row r="9" spans="1:31" ht="12.75" hidden="1">
       <c r="A9" s="44" t="s">
         <v>64</v>
       </c>
@@ -5018,7 +5086,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="12.75">
+    <row r="10" spans="1:31" ht="12.75" hidden="1">
       <c r="A10" s="44" t="s">
         <v>66</v>
       </c>
@@ -5087,7 +5155,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="12.75">
+    <row r="11" spans="1:31" ht="12.75" hidden="1">
       <c r="A11" s="44" t="s">
         <v>70</v>
       </c>
@@ -5156,7 +5224,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="12.75">
+    <row r="12" spans="1:31" ht="12.75" hidden="1">
       <c r="A12" s="44" t="s">
         <v>72</v>
       </c>
@@ -5225,7 +5293,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="12.75">
+    <row r="13" spans="1:31" ht="12.75" hidden="1">
       <c r="A13" s="44" t="s">
         <v>75</v>
       </c>
@@ -5294,7 +5362,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="12.75">
+    <row r="14" spans="1:31" ht="12.75" hidden="1">
       <c r="A14" s="44" t="s">
         <v>77</v>
       </c>
@@ -5361,7 +5429,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="12.75">
+    <row r="15" spans="1:31" ht="12.75" hidden="1">
       <c r="A15" s="44" t="s">
         <v>80</v>
       </c>
@@ -5429,7 +5497,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="12.75">
+    <row r="16" spans="1:31" ht="12.75" hidden="1">
       <c r="A16" s="44" t="s">
         <v>82</v>
       </c>
@@ -5499,7 +5567,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="12.75">
+    <row r="17" spans="1:31" ht="12.75" hidden="1">
       <c r="A17" s="44" t="s">
         <v>84</v>
       </c>
@@ -5568,7 +5636,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="12.75">
+    <row r="18" spans="1:31" ht="12.75" hidden="1">
       <c r="A18" s="44" t="s">
         <v>86</v>
       </c>
@@ -5637,7 +5705,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="12.75">
+    <row r="19" spans="1:31" ht="12.75" hidden="1">
       <c r="A19" s="44" t="s">
         <v>88</v>
       </c>
@@ -5706,7 +5774,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="12.75">
+    <row r="20" spans="1:31" ht="12.75" hidden="1">
       <c r="A20" s="44" t="s">
         <v>90</v>
       </c>
@@ -5775,7 +5843,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="12.75">
+    <row r="21" spans="1:31" ht="12.75" hidden="1">
       <c r="A21" s="44" t="s">
         <v>92</v>
       </c>
@@ -5844,7 +5912,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="12.75">
+    <row r="22" spans="1:31" ht="12.75" hidden="1">
       <c r="A22" s="44" t="s">
         <v>94</v>
       </c>
@@ -5913,7 +5981,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="12.75">
+    <row r="23" spans="1:31" ht="12.75" hidden="1">
       <c r="A23" s="44" t="s">
         <v>96</v>
       </c>
@@ -5979,7 +6047,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="12.75">
+    <row r="24" spans="1:31" ht="12.75" hidden="1">
       <c r="A24" s="44" t="s">
         <v>98</v>
       </c>
@@ -6046,7 +6114,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="12.75">
+    <row r="25" spans="1:31" ht="12.75" hidden="1">
       <c r="A25" s="44" t="s">
         <v>100</v>
       </c>
@@ -6114,7 +6182,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="12.75">
+    <row r="26" spans="1:31" ht="12.75" hidden="1">
       <c r="A26" s="44" t="s">
         <v>102</v>
       </c>
@@ -6184,7 +6252,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="12.75">
+    <row r="27" spans="1:31" ht="12.75" hidden="1">
       <c r="A27" s="44" t="s">
         <v>104</v>
       </c>
@@ -6254,7 +6322,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="12.75">
+    <row r="28" spans="1:31" ht="12.75" hidden="1">
       <c r="A28" s="44" t="s">
         <v>106</v>
       </c>
@@ -6323,7 +6391,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="12.75">
+    <row r="29" spans="1:31" ht="12.75" hidden="1">
       <c r="A29" s="44" t="s">
         <v>108</v>
       </c>
@@ -6392,7 +6460,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="12.75">
+    <row r="30" spans="1:31" ht="12.75" hidden="1">
       <c r="A30" s="44" t="s">
         <v>110</v>
       </c>
@@ -6461,7 +6529,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="12.75">
+    <row r="31" spans="1:31" ht="12.75" hidden="1">
       <c r="A31" s="44" t="s">
         <v>112</v>
       </c>
@@ -6530,7 +6598,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="12.75">
+    <row r="32" spans="1:31" ht="12.75" hidden="1">
       <c r="A32" s="44" t="s">
         <v>114</v>
       </c>
@@ -6597,7 +6665,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="12.75">
+    <row r="33" spans="1:31" ht="12.75" hidden="1">
       <c r="A33" s="44" t="s">
         <v>116</v>
       </c>
@@ -6664,7 +6732,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="12.75">
+    <row r="34" spans="1:31" ht="12.75" hidden="1">
       <c r="A34" s="44" t="s">
         <v>118</v>
       </c>
@@ -7158,7 +7226,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="12.75">
+    <row r="41" spans="1:31" ht="12.75" hidden="1">
       <c r="A41" s="44" t="s">
         <v>132</v>
       </c>
@@ -7440,7 +7508,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="12.75">
+    <row r="45" spans="1:31" ht="12.75" hidden="1">
       <c r="A45" s="44" t="s">
         <v>134</v>
       </c>
@@ -7512,7 +7580,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="12.75">
+    <row r="46" spans="1:31" ht="12.75" hidden="1">
       <c r="A46" s="44" t="s">
         <v>43</v>
       </c>
@@ -7647,7 +7715,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="12.75">
+    <row r="48" spans="1:31" ht="12.75" hidden="1">
       <c r="A48" s="44" t="s">
         <v>47</v>
       </c>
@@ -12639,7 +12707,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.75" hidden="1">
+    <row r="117" spans="1:31" ht="12.75">
       <c r="A117" s="44" t="s">
         <v>53</v>
       </c>
@@ -12711,7 +12779,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.75" hidden="1">
+    <row r="118" spans="1:31" ht="12.75">
       <c r="A118" s="44" t="s">
         <v>53</v>
       </c>
@@ -12783,7 +12851,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.75" hidden="1">
+    <row r="119" spans="1:31" ht="12.75">
       <c r="A119" s="44" t="s">
         <v>53</v>
       </c>
@@ -13075,7 +13143,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="12.75" hidden="1">
+    <row r="123" spans="1:31" ht="12.75">
       <c r="A123" s="44" t="s">
         <v>53</v>
       </c>
@@ -13294,7 +13362,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.75" hidden="1">
+    <row r="126" spans="1:31" ht="12.75">
       <c r="A126" s="44" t="s">
         <v>50</v>
       </c>
@@ -13875,7 +13943,7 @@
       <c r="AD133"/>
       <c r="AE133"/>
     </row>
-    <row r="134" spans="1:31" ht="12.75" hidden="1">
+    <row r="134" spans="1:31" ht="12.75">
       <c r="A134" s="44" t="s">
         <v>57</v>
       </c>
@@ -13948,7 +14016,7 @@
       <c r="AD134"/>
       <c r="AE134"/>
     </row>
-    <row r="135" spans="1:31" ht="12.75" hidden="1">
+    <row r="135" spans="1:31" ht="12.75">
       <c r="A135" s="44" t="s">
         <v>57</v>
       </c>
@@ -14021,7 +14089,7 @@
       <c r="AD135"/>
       <c r="AE135"/>
     </row>
-    <row r="136" spans="1:31" ht="12.75" hidden="1">
+    <row r="136" spans="1:31" ht="12.75">
       <c r="A136" s="44" t="s">
         <v>57</v>
       </c>
@@ -14094,7 +14162,7 @@
       <c r="AD136"/>
       <c r="AE136"/>
     </row>
-    <row r="137" spans="1:31" ht="12.75" hidden="1">
+    <row r="137" spans="1:31" ht="12.75">
       <c r="A137" s="44" t="s">
         <v>57</v>
       </c>
@@ -14310,7 +14378,7 @@
       <c r="AC139" s="48"/>
       <c r="AD139" s="48"/>
     </row>
-    <row r="140" spans="1:31" ht="12.75" hidden="1">
+    <row r="140" spans="1:31" ht="12.75">
       <c r="A140" s="87" t="s">
         <v>59</v>
       </c>
@@ -14598,7 +14666,7 @@
       <c r="AC143" s="48"/>
       <c r="AD143" s="46"/>
     </row>
-    <row r="144" spans="1:31" ht="12.75" hidden="1">
+    <row r="144" spans="1:31" ht="12.75">
       <c r="A144" s="87" t="s">
         <v>59</v>
       </c>
@@ -14889,7 +14957,7 @@
       <c r="AD147" s="7"/>
       <c r="AE147" s="16"/>
     </row>
-    <row r="148" spans="1:31" ht="12.75" hidden="1">
+    <row r="148" spans="1:31" ht="12.75">
       <c r="A148" s="87" t="s">
         <v>59</v>
       </c>
@@ -15177,7 +15245,7 @@
       <c r="AC151" s="48"/>
       <c r="AD151" s="7"/>
     </row>
-    <row r="152" spans="1:31" ht="12.75" hidden="1">
+    <row r="152" spans="1:31" ht="12.75">
       <c r="A152" s="93" t="s">
         <v>59</v>
       </c>
@@ -16073,17 +16141,67 @@
       <c r="AD163" s="7"/>
     </row>
     <row r="164" spans="1:30" ht="12.75">
-      <c r="A164" s="44"/>
-      <c r="B164" s="44"/>
-      <c r="C164" s="44"/>
-      <c r="I164" s="46"/>
-      <c r="J164" s="46"/>
-      <c r="K164" s="46"/>
-      <c r="M164" s="48"/>
-      <c r="N164" s="48"/>
-      <c r="O164" s="48"/>
-      <c r="Q164" s="61"/>
-      <c r="U164" s="48"/>
+      <c r="A164" s="110" t="s">
+        <v>638</v>
+      </c>
+      <c r="B164" s="111" t="s">
+        <v>639</v>
+      </c>
+      <c r="C164" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D164" s="88"/>
+      <c r="E164" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G164" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H164" s="108"/>
+      <c r="I164" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="J164" s="88">
+        <v>0</v>
+      </c>
+      <c r="K164" s="113">
+        <v>4562.5</v>
+      </c>
+      <c r="L164" s="109"/>
+      <c r="M164" s="88"/>
+      <c r="N164" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O164" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4725</v>
+      </c>
+      <c r="P164" s="88"/>
+      <c r="Q164" s="89">
+        <v>1</v>
+      </c>
+      <c r="R164" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S164" s="89">
+        <v>325</v>
+      </c>
+      <c r="T164" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U164" s="90">
+        <v>0</v>
+      </c>
+      <c r="V164" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X164" s="48"/>
       <c r="Y164" s="48"/>
       <c r="Z164" s="48"/>
@@ -16093,17 +16211,67 @@
       <c r="AD164" s="7"/>
     </row>
     <row r="165" spans="1:30" ht="12.75">
-      <c r="A165" s="44"/>
-      <c r="B165" s="44"/>
-      <c r="C165" s="44"/>
-      <c r="I165" s="46"/>
-      <c r="J165" s="46"/>
-      <c r="K165" s="46"/>
-      <c r="M165" s="48"/>
-      <c r="N165" s="48"/>
-      <c r="O165" s="48"/>
-      <c r="Q165" s="61"/>
-      <c r="U165" s="48"/>
+      <c r="A165" s="110" t="s">
+        <v>638</v>
+      </c>
+      <c r="B165" s="112" t="s">
+        <v>639</v>
+      </c>
+      <c r="C165" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D165" s="88"/>
+      <c r="E165" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G165" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H165" s="108"/>
+      <c r="I165" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="J165" s="88">
+        <v>0</v>
+      </c>
+      <c r="K165" s="113">
+        <v>4562.5</v>
+      </c>
+      <c r="L165" s="109"/>
+      <c r="M165" s="88"/>
+      <c r="N165" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O165" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4725</v>
+      </c>
+      <c r="P165" s="88"/>
+      <c r="Q165" s="89">
+        <v>1</v>
+      </c>
+      <c r="R165" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S165" s="89">
+        <v>325</v>
+      </c>
+      <c r="T165" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U165" s="90">
+        <v>0</v>
+      </c>
+      <c r="V165" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X165" s="48"/>
       <c r="Y165" s="48"/>
       <c r="Z165" s="48"/>
@@ -16113,18 +16281,67 @@
       <c r="AD165" s="48"/>
     </row>
     <row r="166" spans="1:30" ht="12.75">
-      <c r="A166" s="44"/>
-      <c r="B166" s="44"/>
-      <c r="C166" s="44"/>
-      <c r="H166" s="15"/>
-      <c r="I166" s="46"/>
-      <c r="J166" s="46"/>
-      <c r="K166" s="46"/>
-      <c r="M166" s="48"/>
-      <c r="N166" s="48"/>
-      <c r="O166" s="48"/>
-      <c r="Q166" s="61"/>
-      <c r="U166" s="48"/>
+      <c r="A166" s="110" t="s">
+        <v>638</v>
+      </c>
+      <c r="B166" s="111" t="s">
+        <v>639</v>
+      </c>
+      <c r="C166" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D166" s="88"/>
+      <c r="E166" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F166" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G166" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H166" s="108"/>
+      <c r="I166" s="86" t="s">
+        <v>640</v>
+      </c>
+      <c r="J166" s="88">
+        <v>750</v>
+      </c>
+      <c r="K166" s="113">
+        <v>3812.5</v>
+      </c>
+      <c r="L166" s="109"/>
+      <c r="M166" s="88"/>
+      <c r="N166" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O166" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3975</v>
+      </c>
+      <c r="P166" s="88"/>
+      <c r="Q166" s="89">
+        <v>1</v>
+      </c>
+      <c r="R166" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S166" s="89">
+        <v>325</v>
+      </c>
+      <c r="T166" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U166" s="90">
+        <v>0</v>
+      </c>
+      <c r="V166" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X166" s="48"/>
       <c r="Y166" s="48"/>
       <c r="Z166" s="48"/>
@@ -16134,18 +16351,67 @@
       <c r="AD166" s="48"/>
     </row>
     <row r="167" spans="1:30" ht="12.75">
-      <c r="A167" s="44"/>
-      <c r="B167" s="44"/>
-      <c r="C167" s="44"/>
-      <c r="H167" s="15"/>
-      <c r="I167" s="46"/>
-      <c r="J167" s="46"/>
-      <c r="K167" s="46"/>
-      <c r="M167" s="48"/>
-      <c r="N167" s="48"/>
-      <c r="O167" s="48"/>
-      <c r="Q167" s="61"/>
-      <c r="U167" s="48"/>
+      <c r="A167" s="110" t="s">
+        <v>638</v>
+      </c>
+      <c r="B167" s="112" t="s">
+        <v>639</v>
+      </c>
+      <c r="C167" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D167" s="88"/>
+      <c r="E167" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F167" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G167" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H167" s="108"/>
+      <c r="I167" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="J167" s="88">
+        <v>0</v>
+      </c>
+      <c r="K167" s="113">
+        <v>4562.5</v>
+      </c>
+      <c r="L167" s="109"/>
+      <c r="M167" s="88"/>
+      <c r="N167" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O167" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4725</v>
+      </c>
+      <c r="P167" s="88"/>
+      <c r="Q167" s="89">
+        <v>1</v>
+      </c>
+      <c r="R167" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S167" s="89">
+        <v>325</v>
+      </c>
+      <c r="T167" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U167" s="90">
+        <v>0</v>
+      </c>
+      <c r="V167" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X167" s="48"/>
       <c r="Y167" s="48"/>
       <c r="Z167" s="48"/>
@@ -16155,17 +16421,67 @@
       <c r="AD167" s="7"/>
     </row>
     <row r="168" spans="1:30" ht="12.75">
-      <c r="A168" s="44"/>
-      <c r="B168" s="44"/>
-      <c r="C168" s="44"/>
-      <c r="I168" s="46"/>
-      <c r="J168" s="46"/>
-      <c r="K168" s="46"/>
-      <c r="M168" s="48"/>
-      <c r="N168" s="48"/>
-      <c r="O168" s="48"/>
-      <c r="Q168" s="61"/>
-      <c r="U168" s="48"/>
+      <c r="A168" s="110" t="s">
+        <v>638</v>
+      </c>
+      <c r="B168" s="111" t="s">
+        <v>639</v>
+      </c>
+      <c r="C168" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D168" s="88"/>
+      <c r="E168" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F168" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G168" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H168" s="108"/>
+      <c r="I168" s="86" t="s">
+        <v>156</v>
+      </c>
+      <c r="J168" s="88">
+        <v>500</v>
+      </c>
+      <c r="K168" s="113">
+        <v>4062.5</v>
+      </c>
+      <c r="L168" s="109"/>
+      <c r="M168" s="88"/>
+      <c r="N168" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O168" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4225</v>
+      </c>
+      <c r="P168" s="88"/>
+      <c r="Q168" s="89">
+        <v>1</v>
+      </c>
+      <c r="R168" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S168" s="89">
+        <v>325</v>
+      </c>
+      <c r="T168" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U168" s="90">
+        <v>0</v>
+      </c>
+      <c r="V168" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X168" s="48"/>
       <c r="Y168" s="48"/>
       <c r="Z168" s="48"/>
@@ -16175,17 +16491,67 @@
       <c r="AD168" s="7"/>
     </row>
     <row r="169" spans="1:30" ht="12.75">
-      <c r="A169" s="44"/>
-      <c r="B169" s="44"/>
-      <c r="C169" s="44"/>
-      <c r="I169" s="46"/>
-      <c r="J169" s="46"/>
-      <c r="K169" s="46"/>
-      <c r="M169" s="48"/>
-      <c r="N169" s="48"/>
-      <c r="O169" s="48"/>
-      <c r="Q169" s="61"/>
-      <c r="U169" s="48"/>
+      <c r="A169" s="110" t="s">
+        <v>638</v>
+      </c>
+      <c r="B169" s="112" t="s">
+        <v>639</v>
+      </c>
+      <c r="C169" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D169" s="88"/>
+      <c r="E169" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F169" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G169" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H169" s="108"/>
+      <c r="I169" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="J169" s="88">
+        <v>925</v>
+      </c>
+      <c r="K169" s="113">
+        <v>3637.5</v>
+      </c>
+      <c r="L169" s="109"/>
+      <c r="M169" s="86"/>
+      <c r="N169" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O169" s="114">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3800</v>
+      </c>
+      <c r="P169" s="88"/>
+      <c r="Q169" s="89">
+        <v>1</v>
+      </c>
+      <c r="R169" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S169" s="89">
+        <v>325</v>
+      </c>
+      <c r="T169" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U169" s="90">
+        <v>0</v>
+      </c>
+      <c r="V169" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X169" s="48"/>
       <c r="Y169" s="48"/>
       <c r="Z169" s="48"/>
@@ -16195,17 +16561,67 @@
       <c r="AD169" s="7"/>
     </row>
     <row r="170" spans="1:30" ht="12.75">
-      <c r="A170" s="44"/>
-      <c r="B170" s="44"/>
-      <c r="C170" s="44"/>
-      <c r="I170" s="46"/>
-      <c r="J170" s="46"/>
-      <c r="K170" s="46"/>
-      <c r="M170" s="48"/>
-      <c r="N170" s="48"/>
-      <c r="O170" s="48"/>
-      <c r="Q170" s="61"/>
-      <c r="U170" s="48"/>
+      <c r="A170" s="110" t="s">
+        <v>641</v>
+      </c>
+      <c r="B170" s="111" t="s">
+        <v>642</v>
+      </c>
+      <c r="C170" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D170" s="88"/>
+      <c r="E170" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F170" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G170" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H170" s="108"/>
+      <c r="I170" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="J170" s="88">
+        <v>0</v>
+      </c>
+      <c r="K170" s="113">
+        <v>2362.5</v>
+      </c>
+      <c r="L170" s="109"/>
+      <c r="M170" s="88"/>
+      <c r="N170" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O170" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2525</v>
+      </c>
+      <c r="P170" s="88"/>
+      <c r="Q170" s="89">
+        <v>1</v>
+      </c>
+      <c r="R170" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S170" s="89">
+        <v>325</v>
+      </c>
+      <c r="T170" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U170" s="90">
+        <v>0</v>
+      </c>
+      <c r="V170" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X170" s="48"/>
       <c r="Y170" s="48"/>
       <c r="Z170" s="48"/>
@@ -16215,17 +16631,67 @@
       <c r="AD170" s="48"/>
     </row>
     <row r="171" spans="1:30" ht="12.75">
-      <c r="A171" s="44"/>
-      <c r="B171" s="44"/>
-      <c r="C171" s="44"/>
-      <c r="I171" s="46"/>
-      <c r="J171" s="46"/>
-      <c r="K171" s="46"/>
-      <c r="M171" s="48"/>
-      <c r="N171" s="48"/>
-      <c r="O171" s="48"/>
-      <c r="Q171" s="61"/>
-      <c r="U171" s="48"/>
+      <c r="A171" s="110" t="s">
+        <v>641</v>
+      </c>
+      <c r="B171" s="112" t="s">
+        <v>642</v>
+      </c>
+      <c r="C171" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D171" s="88"/>
+      <c r="E171" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G171" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H171" s="108"/>
+      <c r="I171" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="J171" s="88">
+        <v>0</v>
+      </c>
+      <c r="K171" s="113">
+        <v>2362.5</v>
+      </c>
+      <c r="L171" s="109"/>
+      <c r="M171" s="88"/>
+      <c r="N171" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O171" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2525</v>
+      </c>
+      <c r="P171" s="88"/>
+      <c r="Q171" s="89">
+        <v>1</v>
+      </c>
+      <c r="R171" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S171" s="89">
+        <v>325</v>
+      </c>
+      <c r="T171" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U171" s="90">
+        <v>0</v>
+      </c>
+      <c r="V171" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X171" s="48"/>
       <c r="Y171" s="48"/>
       <c r="Z171" s="48"/>
@@ -16235,17 +16701,67 @@
       <c r="AD171" s="48"/>
     </row>
     <row r="172" spans="1:30" ht="12.75">
-      <c r="A172" s="44"/>
-      <c r="B172" s="44"/>
-      <c r="C172" s="44"/>
-      <c r="I172" s="46"/>
-      <c r="J172" s="46"/>
-      <c r="K172" s="46"/>
-      <c r="M172" s="48"/>
-      <c r="N172" s="48"/>
-      <c r="O172" s="48"/>
-      <c r="Q172" s="61"/>
-      <c r="U172" s="48"/>
+      <c r="A172" s="110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B172" s="111" t="s">
+        <v>644</v>
+      </c>
+      <c r="C172" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D172" s="88"/>
+      <c r="E172" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G172" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H172" s="108"/>
+      <c r="I172" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="J172" s="88">
+        <v>0</v>
+      </c>
+      <c r="K172" s="113">
+        <v>3362.5</v>
+      </c>
+      <c r="L172" s="109"/>
+      <c r="M172" s="88"/>
+      <c r="N172" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O172" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3525</v>
+      </c>
+      <c r="P172" s="88"/>
+      <c r="Q172" s="89">
+        <v>1</v>
+      </c>
+      <c r="R172" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S172" s="89">
+        <v>325</v>
+      </c>
+      <c r="T172" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U172" s="90">
+        <v>0</v>
+      </c>
+      <c r="V172" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X172" s="48"/>
       <c r="Y172" s="48"/>
       <c r="Z172" s="48"/>
@@ -16255,17 +16771,67 @@
       <c r="AD172" s="7"/>
     </row>
     <row r="173" spans="1:30" ht="12.75">
-      <c r="A173" s="44"/>
-      <c r="B173" s="44"/>
-      <c r="C173" s="44"/>
-      <c r="I173" s="46"/>
-      <c r="J173" s="46"/>
-      <c r="K173" s="46"/>
-      <c r="M173" s="48"/>
-      <c r="N173" s="48"/>
-      <c r="O173" s="48"/>
-      <c r="Q173" s="61"/>
-      <c r="U173" s="48"/>
+      <c r="A173" s="110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B173" s="112" t="s">
+        <v>644</v>
+      </c>
+      <c r="C173" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D173" s="88"/>
+      <c r="E173" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G173" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H173" s="108"/>
+      <c r="I173" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="J173" s="88">
+        <v>0</v>
+      </c>
+      <c r="K173" s="113">
+        <v>3362.5</v>
+      </c>
+      <c r="L173" s="109"/>
+      <c r="M173" s="88"/>
+      <c r="N173" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O173" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3525</v>
+      </c>
+      <c r="P173" s="88"/>
+      <c r="Q173" s="89">
+        <v>1</v>
+      </c>
+      <c r="R173" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S173" s="89">
+        <v>325</v>
+      </c>
+      <c r="T173" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U173" s="90">
+        <v>0</v>
+      </c>
+      <c r="V173" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X173" s="48"/>
       <c r="Y173" s="48"/>
       <c r="Z173" s="48"/>
@@ -16275,17 +16841,67 @@
       <c r="AD173" s="7"/>
     </row>
     <row r="174" spans="1:30" ht="12.75">
-      <c r="A174" s="44"/>
-      <c r="B174" s="44"/>
-      <c r="C174" s="44"/>
-      <c r="I174" s="46"/>
-      <c r="J174" s="46"/>
-      <c r="K174" s="46"/>
-      <c r="M174" s="48"/>
-      <c r="N174" s="48"/>
-      <c r="O174" s="48"/>
-      <c r="Q174" s="61"/>
-      <c r="U174" s="48"/>
+      <c r="A174" s="110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B174" s="111" t="s">
+        <v>644</v>
+      </c>
+      <c r="C174" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D174" s="88"/>
+      <c r="E174" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F174" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G174" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H174" s="108"/>
+      <c r="I174" s="86" t="s">
+        <v>645</v>
+      </c>
+      <c r="J174" s="88">
+        <v>700</v>
+      </c>
+      <c r="K174" s="113">
+        <v>2662.5</v>
+      </c>
+      <c r="L174" s="109"/>
+      <c r="M174" s="88"/>
+      <c r="N174" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O174" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2825</v>
+      </c>
+      <c r="P174" s="88"/>
+      <c r="Q174" s="89">
+        <v>1</v>
+      </c>
+      <c r="R174" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S174" s="89">
+        <v>325</v>
+      </c>
+      <c r="T174" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U174" s="90">
+        <v>0</v>
+      </c>
+      <c r="V174" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X174" s="48"/>
       <c r="Y174" s="48"/>
       <c r="Z174" s="48"/>
@@ -16295,17 +16911,67 @@
       <c r="AD174" s="7"/>
     </row>
     <row r="175" spans="1:30" ht="12.75">
-      <c r="A175" s="44"/>
-      <c r="B175" s="44"/>
-      <c r="C175" s="44"/>
-      <c r="I175" s="46"/>
-      <c r="J175" s="46"/>
-      <c r="K175" s="46"/>
-      <c r="M175" s="48"/>
-      <c r="N175" s="48"/>
-      <c r="O175" s="48"/>
-      <c r="Q175" s="61"/>
-      <c r="U175" s="48"/>
+      <c r="A175" s="110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B175" s="112" t="s">
+        <v>644</v>
+      </c>
+      <c r="C175" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D175" s="88"/>
+      <c r="E175" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G175" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H175" s="108"/>
+      <c r="I175" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="J175" s="88">
+        <v>0</v>
+      </c>
+      <c r="K175" s="113">
+        <v>3362.5</v>
+      </c>
+      <c r="L175" s="109"/>
+      <c r="M175" s="88"/>
+      <c r="N175" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O175" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3525</v>
+      </c>
+      <c r="P175" s="88"/>
+      <c r="Q175" s="89">
+        <v>1</v>
+      </c>
+      <c r="R175" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S175" s="89">
+        <v>325</v>
+      </c>
+      <c r="T175" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U175" s="90">
+        <v>0</v>
+      </c>
+      <c r="V175" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X175" s="48"/>
       <c r="Y175" s="48"/>
       <c r="Z175" s="48"/>
@@ -16315,17 +16981,67 @@
       <c r="AD175" s="48"/>
     </row>
     <row r="176" spans="1:30" ht="12.75">
-      <c r="A176" s="44"/>
-      <c r="B176" s="44"/>
-      <c r="C176" s="44"/>
-      <c r="I176" s="46"/>
-      <c r="J176" s="46"/>
-      <c r="K176" s="46"/>
-      <c r="M176" s="48"/>
-      <c r="N176" s="48"/>
-      <c r="O176" s="48"/>
-      <c r="Q176" s="61"/>
-      <c r="U176" s="48"/>
+      <c r="A176" s="110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B176" s="111" t="s">
+        <v>644</v>
+      </c>
+      <c r="C176" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D176" s="88"/>
+      <c r="E176" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G176" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H176" s="108"/>
+      <c r="I176" s="86" t="s">
+        <v>156</v>
+      </c>
+      <c r="J176" s="88">
+        <v>500</v>
+      </c>
+      <c r="K176" s="113">
+        <v>2862.5</v>
+      </c>
+      <c r="L176" s="109"/>
+      <c r="M176" s="88"/>
+      <c r="N176" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O176" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3025</v>
+      </c>
+      <c r="P176" s="88"/>
+      <c r="Q176" s="89">
+        <v>1</v>
+      </c>
+      <c r="R176" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S176" s="89">
+        <v>325</v>
+      </c>
+      <c r="T176" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U176" s="90">
+        <v>0</v>
+      </c>
+      <c r="V176" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X176" s="48"/>
       <c r="Y176" s="48"/>
       <c r="Z176" s="48"/>
@@ -16335,17 +17051,67 @@
       <c r="AD176" s="48"/>
     </row>
     <row r="177" spans="1:30" ht="12.75">
-      <c r="A177" s="44"/>
-      <c r="B177" s="44"/>
-      <c r="C177" s="44"/>
-      <c r="I177" s="46"/>
-      <c r="J177" s="46"/>
-      <c r="K177" s="46"/>
-      <c r="M177" s="48"/>
-      <c r="N177" s="48"/>
-      <c r="O177" s="48"/>
-      <c r="Q177" s="61"/>
-      <c r="U177" s="48"/>
+      <c r="A177" s="110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B177" s="112" t="s">
+        <v>644</v>
+      </c>
+      <c r="C177" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D177" s="88"/>
+      <c r="E177" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G177" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H177" s="108"/>
+      <c r="I177" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="J177" s="88">
+        <v>625</v>
+      </c>
+      <c r="K177" s="113">
+        <v>2737.5</v>
+      </c>
+      <c r="L177" s="109"/>
+      <c r="M177" s="86"/>
+      <c r="N177" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O177" s="114">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2900</v>
+      </c>
+      <c r="P177" s="88"/>
+      <c r="Q177" s="89">
+        <v>1</v>
+      </c>
+      <c r="R177" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S177" s="89">
+        <v>325</v>
+      </c>
+      <c r="T177" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U177" s="90">
+        <v>0</v>
+      </c>
+      <c r="V177" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X177" s="48"/>
       <c r="Y177" s="48"/>
       <c r="Z177" s="48"/>
@@ -16355,17 +17121,67 @@
       <c r="AD177" s="46"/>
     </row>
     <row r="178" spans="1:30" ht="12.75">
-      <c r="A178" s="44"/>
-      <c r="B178" s="44"/>
-      <c r="C178" s="44"/>
-      <c r="I178" s="46"/>
-      <c r="J178" s="46"/>
-      <c r="K178" s="46"/>
-      <c r="M178" s="48"/>
-      <c r="N178" s="48"/>
-      <c r="O178" s="48"/>
-      <c r="Q178" s="61"/>
-      <c r="U178" s="48"/>
+      <c r="A178" s="110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B178" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="C178" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D178" s="88"/>
+      <c r="E178" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F178" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G178" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H178" s="108"/>
+      <c r="I178" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="J178" s="88">
+        <v>0</v>
+      </c>
+      <c r="K178" s="113">
+        <v>4012.5</v>
+      </c>
+      <c r="L178" s="109"/>
+      <c r="M178" s="88"/>
+      <c r="N178" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O178" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4175</v>
+      </c>
+      <c r="P178" s="88"/>
+      <c r="Q178" s="89">
+        <v>1</v>
+      </c>
+      <c r="R178" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S178" s="89">
+        <v>325</v>
+      </c>
+      <c r="T178" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U178" s="90">
+        <v>0</v>
+      </c>
+      <c r="V178" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X178" s="48"/>
       <c r="Y178" s="48"/>
       <c r="Z178" s="48"/>
@@ -16375,17 +17191,67 @@
       <c r="AD178" s="46"/>
     </row>
     <row r="179" spans="1:30" ht="12.75">
-      <c r="A179" s="44"/>
-      <c r="B179" s="44"/>
-      <c r="C179" s="44"/>
-      <c r="I179" s="46"/>
-      <c r="J179" s="46"/>
-      <c r="K179" s="46"/>
-      <c r="M179" s="48"/>
-      <c r="N179" s="48"/>
-      <c r="O179" s="48"/>
-      <c r="Q179" s="61"/>
-      <c r="U179" s="48"/>
+      <c r="A179" s="110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B179" s="112" t="s">
+        <v>647</v>
+      </c>
+      <c r="C179" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D179" s="88"/>
+      <c r="E179" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G179" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H179" s="108"/>
+      <c r="I179" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="J179" s="88">
+        <v>0</v>
+      </c>
+      <c r="K179" s="113">
+        <v>4012.5</v>
+      </c>
+      <c r="L179" s="109"/>
+      <c r="M179" s="88"/>
+      <c r="N179" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O179" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4175</v>
+      </c>
+      <c r="P179" s="88"/>
+      <c r="Q179" s="89">
+        <v>1</v>
+      </c>
+      <c r="R179" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S179" s="89">
+        <v>325</v>
+      </c>
+      <c r="T179" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U179" s="90">
+        <v>0</v>
+      </c>
+      <c r="V179" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X179" s="48"/>
       <c r="Y179" s="48"/>
       <c r="Z179" s="48"/>
@@ -16395,17 +17261,67 @@
       <c r="AD179" s="46"/>
     </row>
     <row r="180" spans="1:30" ht="12.75">
-      <c r="A180" s="44"/>
-      <c r="B180" s="44"/>
-      <c r="C180" s="44"/>
-      <c r="I180" s="46"/>
-      <c r="J180" s="46"/>
-      <c r="K180" s="46"/>
-      <c r="M180" s="48"/>
-      <c r="N180" s="48"/>
-      <c r="O180" s="48"/>
-      <c r="Q180" s="61"/>
-      <c r="U180" s="48"/>
+      <c r="A180" s="110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B180" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="C180" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D180" s="88"/>
+      <c r="E180" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G180" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H180" s="108"/>
+      <c r="I180" s="86" t="s">
+        <v>648</v>
+      </c>
+      <c r="J180" s="88">
+        <v>700</v>
+      </c>
+      <c r="K180" s="113">
+        <v>3312.5</v>
+      </c>
+      <c r="L180" s="109"/>
+      <c r="M180" s="88"/>
+      <c r="N180" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O180" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3475</v>
+      </c>
+      <c r="P180" s="88"/>
+      <c r="Q180" s="89">
+        <v>1</v>
+      </c>
+      <c r="R180" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S180" s="89">
+        <v>325</v>
+      </c>
+      <c r="T180" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U180" s="90">
+        <v>0</v>
+      </c>
+      <c r="V180" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X180" s="48"/>
       <c r="Y180" s="48"/>
       <c r="Z180" s="48"/>
@@ -16415,17 +17331,67 @@
       <c r="AD180" s="46"/>
     </row>
     <row r="181" spans="1:30" ht="12.75">
-      <c r="A181" s="44"/>
-      <c r="B181" s="44"/>
-      <c r="C181" s="44"/>
-      <c r="I181" s="46"/>
-      <c r="J181" s="46"/>
-      <c r="K181" s="46"/>
-      <c r="M181" s="48"/>
-      <c r="N181" s="48"/>
-      <c r="O181" s="48"/>
-      <c r="Q181" s="61"/>
-      <c r="U181" s="48"/>
+      <c r="A181" s="110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B181" s="112" t="s">
+        <v>647</v>
+      </c>
+      <c r="C181" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D181" s="88"/>
+      <c r="E181" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F181" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G181" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H181" s="108"/>
+      <c r="I181" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="J181" s="88">
+        <v>0</v>
+      </c>
+      <c r="K181" s="113">
+        <v>4012.5</v>
+      </c>
+      <c r="L181" s="109"/>
+      <c r="M181" s="88"/>
+      <c r="N181" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O181" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>4175</v>
+      </c>
+      <c r="P181" s="88"/>
+      <c r="Q181" s="89">
+        <v>1</v>
+      </c>
+      <c r="R181" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S181" s="89">
+        <v>325</v>
+      </c>
+      <c r="T181" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U181" s="90">
+        <v>0</v>
+      </c>
+      <c r="V181" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X181" s="48"/>
       <c r="Y181" s="48"/>
       <c r="Z181" s="48"/>
@@ -16435,17 +17401,67 @@
       <c r="AD181" s="46"/>
     </row>
     <row r="182" spans="1:30" ht="12.75">
-      <c r="A182" s="44"/>
-      <c r="B182" s="44"/>
-      <c r="C182" s="44"/>
-      <c r="I182" s="46"/>
-      <c r="J182" s="46"/>
-      <c r="K182" s="46"/>
-      <c r="M182" s="48"/>
-      <c r="N182" s="48"/>
-      <c r="O182" s="48"/>
-      <c r="Q182" s="61"/>
-      <c r="U182" s="48"/>
+      <c r="A182" s="110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B182" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="C182" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D182" s="88"/>
+      <c r="E182" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F182" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G182" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H182" s="108"/>
+      <c r="I182" s="86" t="s">
+        <v>156</v>
+      </c>
+      <c r="J182" s="88">
+        <v>500</v>
+      </c>
+      <c r="K182" s="113">
+        <v>3512.5</v>
+      </c>
+      <c r="L182" s="109"/>
+      <c r="M182" s="88"/>
+      <c r="N182" s="113">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O182" s="113">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3675</v>
+      </c>
+      <c r="P182" s="88"/>
+      <c r="Q182" s="89">
+        <v>1</v>
+      </c>
+      <c r="R182" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="S182" s="89">
+        <v>325</v>
+      </c>
+      <c r="T182" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="U182" s="90">
+        <v>0</v>
+      </c>
+      <c r="V182" s="91" t="s">
+        <v>56</v>
+      </c>
       <c r="X182" s="48"/>
       <c r="Y182" s="48"/>
       <c r="Z182" s="48"/>
@@ -16455,17 +17471,67 @@
       <c r="AD182" s="46"/>
     </row>
     <row r="183" spans="1:30" ht="12.75">
-      <c r="A183" s="44"/>
-      <c r="B183" s="44"/>
-      <c r="C183" s="44"/>
-      <c r="I183" s="46"/>
-      <c r="J183" s="46"/>
-      <c r="K183" s="46"/>
-      <c r="M183" s="48"/>
-      <c r="N183" s="48"/>
-      <c r="O183" s="48"/>
-      <c r="Q183" s="61"/>
-      <c r="U183" s="48"/>
+      <c r="A183" s="115" t="s">
+        <v>646</v>
+      </c>
+      <c r="B183" s="116" t="s">
+        <v>647</v>
+      </c>
+      <c r="C183" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>325</v>
+      </c>
+      <c r="D183" s="94"/>
+      <c r="E183" s="94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F183" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>162.5</v>
+      </c>
+      <c r="G183" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="H183" s="118"/>
+      <c r="I183" s="119" t="s">
+        <v>159</v>
+      </c>
+      <c r="J183" s="94">
+        <v>875</v>
+      </c>
+      <c r="K183" s="117">
+        <v>3137.5</v>
+      </c>
+      <c r="L183" s="120"/>
+      <c r="M183" s="119"/>
+      <c r="N183" s="117">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>-162.5</v>
+      </c>
+      <c r="O183" s="121">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>3300</v>
+      </c>
+      <c r="P183" s="94"/>
+      <c r="Q183" s="96">
+        <v>1</v>
+      </c>
+      <c r="R183" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="S183" s="96">
+        <v>325</v>
+      </c>
+      <c r="T183" s="98" t="s">
+        <v>55</v>
+      </c>
+      <c r="U183" s="98">
+        <v>0</v>
+      </c>
+      <c r="V183" s="104" t="s">
+        <v>56</v>
+      </c>
       <c r="X183" s="48"/>
       <c r="Y183" s="48"/>
       <c r="Z183" s="48"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1336" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{872EDEEE-FA94-4002-8DD2-83D605F5B0F1}"/>
+  <xr:revisionPtr revIDLastSave="1430" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F65ED290-5D98-49B7-B332-A25358C2B5C7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3191" uniqueCount="652">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -1986,9 +1986,6 @@
     <t>Beltone Illuminate 17 62S-DRWC Digital RIE</t>
   </si>
   <si>
-    <t>Illuminate 17 Special</t>
-  </si>
-  <si>
     <t>Beltone RIE Digital Illuminate 4 62S-DRWC</t>
   </si>
   <si>
@@ -2001,16 +1998,28 @@
     <t>Beltone Illuminate 6 62S-DRWC Digital RIE</t>
   </si>
   <si>
-    <t>Illuminate 6 Special</t>
-  </si>
-  <si>
     <t>Beltone RIE Digital Illuminate 9 62S-DRWC</t>
   </si>
   <si>
     <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
   </si>
   <si>
-    <t>Illuminate 9 Special</t>
+    <t>Beltone RIE Digital Envision 17 62SDRWC</t>
+  </si>
+  <si>
+    <t>Beltone Envision 17 62SDRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital Envision 6 62SDRWC</t>
+  </si>
+  <si>
+    <t>Beltone Envision 6 62SDRWC Digital RIE</t>
+  </si>
+  <si>
+    <t>Beltone RIE Digital Envision 9 62SDRWC</t>
+  </si>
+  <si>
+    <t>Beltone Envision 9 62SDRWC Digital RIE</t>
   </si>
 </sst>
 </file>
@@ -2356,7 +2365,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2516,10 +2525,6 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2560,10 +2565,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2573,12 +2585,12 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2588,6 +2600,19 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2595,62 +2620,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="60">
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2662,200 +2631,18 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="4"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="4"/>
-        <color theme="1"/>
-        <name val="IDAutomationHC39M Free Version"/>
-        <family val="1"/>
-        <charset val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3061,30 +2848,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -3408,6 +3171,268 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="4"/>
+        <color theme="1"/>
+        <name val="IDAutomationHC39M Free Version"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3422,101 +3447,98 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V183" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V183" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V209" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="A1:V209" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Beltone RIE Digital Envision 17 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Envision 4 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Envision 6 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Envision 9 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Commence 3 62-DRWC"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V150">
-    <sortCondition ref="A1:A163"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A107:V209">
+    <sortCondition ref="A1:A209"/>
   </sortState>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{A759776D-F1C7-439A-A017-B16601DE8834}" name="haModel" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{DB2EB2AC-0D9E-4335-9000-DEA2CFAF79BE}" name="haDescription" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{A8AFAABA-873B-479C-A0A1-068DA38EFBB1}" name="BiNuralMSRP w/Charger" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{A759776D-F1C7-439A-A017-B16601DE8834}" name="haModel" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{DB2EB2AC-0D9E-4335-9000-DEA2CFAF79BE}" name="haDescription" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{A8AFAABA-873B-479C-A0A1-068DA38EFBB1}" name="BiNuralMSRP w/Charger" dataDxfId="19">
       <calculatedColumnFormula>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4320CF9C-2A9B-4102-AF79-01876AA8A2EF}" name="haMSRP" dataDxfId="54" dataCellStyle="Comma"/>
-    <tableColumn id="17" xr3:uid="{4C421CF5-5A00-4BAB-9342-FFFA22CE1848}" name="Discount Type 1" dataDxfId="53" dataCellStyle="Comma"/>
-    <tableColumn id="18" xr3:uid="{8DC0A1BB-67C5-4FA7-9D6C-1F3492CDCE35}" name="Discount Amount 1" dataDxfId="52" dataCellStyle="Comma">
+    <tableColumn id="3" xr3:uid="{4320CF9C-2A9B-4102-AF79-01876AA8A2EF}" name="haMSRP" dataDxfId="18" dataCellStyle="Comma"/>
+    <tableColumn id="17" xr3:uid="{4C421CF5-5A00-4BAB-9342-FFFA22CE1848}" name="Discount Type 1" dataDxfId="17" dataCellStyle="Comma"/>
+    <tableColumn id="18" xr3:uid="{8DC0A1BB-67C5-4FA7-9D6C-1F3492CDCE35}" name="Discount Amount 1" dataDxfId="16" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3C382293-5620-4D91-9805-F4C06BA1B79D}" name="HAListPrice" dataDxfId="51" dataCellStyle="Comma">
+    <tableColumn id="14" xr3:uid="{3C382293-5620-4D91-9805-F4C06BA1B79D}" name="HAListPrice" dataDxfId="15" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9BCEF15A-97C4-45E4-AD6E-381196FF2F4C}" name="ListPriceBinural" dataDxfId="50" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{39D3FD35-3ACA-4445-A872-4D74E2EF38DC}" name="Discount Type 2" dataDxfId="49" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{00DDF5BF-EC07-4D8E-95CD-80770F4B2F7B}" name="Discount Amount 2" dataDxfId="48" dataCellStyle="Comma">
+    <tableColumn id="8" xr3:uid="{9BCEF15A-97C4-45E4-AD6E-381196FF2F4C}" name="ListPriceBinural" dataDxfId="14" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{39D3FD35-3ACA-4445-A872-4D74E2EF38DC}" name="Discount Type 2" dataDxfId="13" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{00DDF5BF-EC07-4D8E-95CD-80770F4B2F7B}" name="Discount Amount 2" dataDxfId="12" dataCellStyle="Comma">
       <calculatedColumnFormula>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A092CA1D-CDF6-4BEE-9660-5E274D9BBCB7}" name="haNetPrice" dataDxfId="47" dataCellStyle="Comma">
+    <tableColumn id="7" xr3:uid="{A092CA1D-CDF6-4BEE-9660-5E274D9BBCB7}" name="haNetPrice" dataDxfId="11" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{A444CAEB-7549-4620-A20C-551B5BE7881A}" name="haNetPriceBinural" dataDxfId="46" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{863CE0AE-0F5F-4D32-A9DC-1629115B0F70}" name="Discount Type 3" dataDxfId="45" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{A9C4A9DC-EFB5-4D09-8ADA-EFC229107602}" name="Discount Amount 3" dataDxfId="44" dataCellStyle="Comma">
+    <tableColumn id="20" xr3:uid="{A444CAEB-7549-4620-A20C-551B5BE7881A}" name="haNetPriceBinural" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{863CE0AE-0F5F-4D32-A9DC-1629115B0F70}" name="Discount Type 3" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{A9C4A9DC-EFB5-4D09-8ADA-EFC229107602}" name="Discount Amount 3" dataDxfId="9" dataCellStyle="Comma">
       <calculatedColumnFormula>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{7CBDD182-D316-4241-BE01-D84B5F3CE9AD}" name="haNetPrice2" dataDxfId="43" dataCellStyle="Comma">
+    <tableColumn id="22" xr3:uid="{7CBDD182-D316-4241-BE01-D84B5F3CE9AD}" name="haNetPrice2" dataDxfId="8" dataCellStyle="Comma">
       <calculatedColumnFormula>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{25381E46-1821-4592-B7AE-7DCCB3D5FF9F}" name="haNetPriceBinural2" dataDxfId="42" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{0C52264D-EACD-4040-AD20-A870B977D0E1}" name="paFittingFee" dataDxfId="41" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{6B597A7B-6B6C-463B-B14D-B782009871B6}" name="chargerType" dataDxfId="40" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{E5E93448-BE27-43BD-8173-C3E29A57EB56}" name="chargerPrice" dataDxfId="39" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{F65D1D5F-35EF-4BFA-A7D0-F4C8368206E1}" name="haReceiverType" dataDxfId="38" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{E15C872A-F3DF-4E26-9A56-6C33CBF526D3}" name="haReceiverPrice" dataDxfId="37" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{2FF24650-9052-4D7C-908B-99CBF45A3D62}" name="haReceiverDiscountDescription" dataDxfId="36" dataCellStyle="Comma"/>
+    <tableColumn id="16" xr3:uid="{25381E46-1821-4592-B7AE-7DCCB3D5FF9F}" name="haNetPriceBinural2" dataDxfId="7" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{0C52264D-EACD-4040-AD20-A870B977D0E1}" name="paFittingFee" dataDxfId="6" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{6B597A7B-6B6C-463B-B14D-B782009871B6}" name="chargerType" dataDxfId="5" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{E5E93448-BE27-43BD-8173-C3E29A57EB56}" name="chargerPrice" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{F65D1D5F-35EF-4BFA-A7D0-F4C8368206E1}" name="haReceiverType" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{E15C872A-F3DF-4E26-9A56-6C33CBF526D3}" name="haReceiverPrice" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{2FF24650-9052-4D7C-908B-99CBF45A3D62}" name="haReceiverDiscountDescription" dataDxfId="1" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}" name="Table3" displayName="Table3" ref="A1:I260" totalsRowShown="0" dataDxfId="59">
   <autoFilter ref="A1:I260" xr:uid="{B234EB53-350B-4CA0-BBF8-223B5DD3393E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H286">
     <sortCondition ref="H1:H286"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="33">
+    <tableColumn id="3" xr3:uid="{01E33E76-D2E8-4BA1-8B76-7728D954699A}" name="barcodeName" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{AFD2CC34-308A-452C-88C9-7ABCC4C3CBAE}" name="barcode" dataDxfId="57">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="32"/>
-    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{B8801611-8566-463A-835D-35713DE2FBEA}" name="receiverType" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{AD24FFA9-E8B9-4018-8A06-B4494014DBB8}" name="receiverRightDescription2" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{2C8BFB26-ADC9-49BF-859D-B9B1DD563DA3}" name="receiverLeftDescription" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{DF46FFD8-CF92-4CF1-A0FF-3A3AA14FB6A7}" name="receiverListAmount" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{F789C631-ACE4-4877-A193-CFB176AB4CAA}" name="receiverDiscountAmount" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{F07C2478-D3D3-4691-BC4C-7E1A65A10250}" name="receiverDiscountDescription" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{F77E97F1-5006-4D72-B46E-440B6D66854F}" name="receiverPrice" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}" name="Table2" displayName="Table2" ref="A1:H92" totalsRowShown="0" headerRowDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47">
   <autoFilter ref="A1:H92" xr:uid="{DF14951C-F3AB-4A56-8D68-8FEECEDF206A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H74">
     <sortCondition ref="H1:H74"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{FDC3E4DD-A231-46DD-8097-7C0DC18260BD}" name="barcodeName"/>
-    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{AFC95F79-8083-447B-A914-1EBAAA27B722}" name="barcode" dataDxfId="46">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{D0382781-2AC8-4DE6-BF59-9B38B78B1184}" name="remoteModel"/>
     <tableColumn id="4" xr3:uid="{9B080694-7BEA-4586-AA70-DDEC1D67D699}" name="remoteType"/>
     <tableColumn id="7" xr3:uid="{CCB41D66-8697-4FAF-A74F-5F54F6CCA4F8}" name="remoteListAmount"/>
-    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="20">
+    <tableColumn id="5" xr3:uid="{1CE35D6A-9428-4732-9735-D4D6A26B1AB4}" name="remoteDiscountAmount" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{D7583571-F6BF-4E66-B4FE-1F6C0658D1E4}" name="remoteAmount" dataDxfId="44">
       <calculatedColumnFormula>Table2[[#This Row],[remoteListAmount]]-Table2[[#This Row],[remoteDiscountAmount]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{435AFC97-0382-475D-9332-93EDAB756C8B}" name="remoteDiscountDescription"/>
@@ -3526,37 +3548,37 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9E35851D-E21C-4957-852B-C619133CF977}" name="Table4" displayName="Table4" ref="A1:H3" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9E35851D-E21C-4957-852B-C619133CF977}" name="Table4" displayName="Table4" ref="A1:H3" totalsRowShown="0" headerRowDxfId="43" dataDxfId="41" headerRowBorderDxfId="42" tableBorderDxfId="40">
   <autoFilter ref="A1:H3" xr:uid="{9E35851D-E21C-4957-852B-C619133CF977}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{9C5C5DE5-EA97-4EF1-8892-EBFCAC4443EA}" name="barcodeName" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{3987A654-3331-4022-95F5-BEF488FDFD5D}" name="barcode" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{9C5C5DE5-EA97-4EF1-8892-EBFCAC4443EA}" name="barcodeName" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{3987A654-3331-4022-95F5-BEF488FDFD5D}" name="barcode" dataDxfId="38">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B575D7DB-8A17-44F2-812F-84D8DF10D3DD}" name="serviceDescription" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{1E8BF5D4-6F7F-4C9F-B1C6-A5382AB6523A}" name="serviceDiscountDescription" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{A104B7ED-7164-4645-80F4-4FB3B815FA1C}" name="serviceListAmount" dataDxfId="11" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{FA21F863-CA81-4450-AB48-77E6CBCB2D99}" name="serviceDiscountAmount" dataDxfId="10" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{0C0AAA86-C611-4A7B-8F6A-7547563ECBBB}" name="serviceAmount" dataDxfId="9" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{BA455156-79BF-4EC7-BA14-3484B2B4810B}" name="paFittingFee" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B575D7DB-8A17-44F2-812F-84D8DF10D3DD}" name="serviceDescription" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{1E8BF5D4-6F7F-4C9F-B1C6-A5382AB6523A}" name="serviceDiscountDescription" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{A104B7ED-7164-4645-80F4-4FB3B815FA1C}" name="serviceListAmount" dataDxfId="35" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{FA21F863-CA81-4450-AB48-77E6CBCB2D99}" name="serviceDiscountAmount" dataDxfId="34" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{0C0AAA86-C611-4A7B-8F6A-7547563ECBBB}" name="serviceAmount" dataDxfId="33" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{BA455156-79BF-4EC7-BA14-3484B2B4810B}" name="paFittingFee" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{06EED7A3-D2B4-46BC-8F41-FB11FC20F42F}" name="Table5" displayName="Table5" ref="A1:G3" totalsRowShown="0" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{06EED7A3-D2B4-46BC-8F41-FB11FC20F42F}" name="Table5" displayName="Table5" ref="A1:G3" totalsRowShown="0" dataDxfId="31">
   <autoFilter ref="A1:G3" xr:uid="{06EED7A3-D2B4-46BC-8F41-FB11FC20F42F}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA5C7967-7D68-4146-84DE-1135A119CC3D}" name="barcodeName" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{C49A42F5-93EA-4670-959A-42455600C7C8}" name="barcode" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{EA5C7967-7D68-4146-84DE-1135A119CC3D}" name="barcodeName" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{C49A42F5-93EA-4670-959A-42455600C7C8}" name="barcode" dataDxfId="29">
       <calculatedColumnFormula>"("&amp;A2&amp;")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2609A236-2D4A-49A0-BD07-CC9B0426F536}" name="accessoryDescription" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{9F5155AE-6C5F-4BA4-AD9F-DAE0C8053CCF}" name="accessoryDiscountDescription" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{CE967C46-B3C7-4797-BD2D-C5D197F6260B}" name="accessoryListAmount" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{CAA4A522-ACE9-4EE8-A795-EFB2F9D3E99B}" name="accessoryDiscountAmount" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{C6197BEF-5482-4860-814F-46EEEB1E034B}" name="accessoryAmount" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{2609A236-2D4A-49A0-BD07-CC9B0426F536}" name="accessoryDescription" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{9F5155AE-6C5F-4BA4-AD9F-DAE0C8053CCF}" name="accessoryDiscountDescription" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{CE967C46-B3C7-4797-BD2D-C5D197F6260B}" name="accessoryListAmount" dataDxfId="26" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{CAA4A522-ACE9-4EE8-A795-EFB2F9D3E99B}" name="accessoryDiscountAmount" dataDxfId="25" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{C6197BEF-5482-4860-814F-46EEEB1E034B}" name="accessoryAmount" dataDxfId="24" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3885,10 +3907,10 @@
       <c r="A3" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="107"/>
+      <c r="C3" s="105"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
@@ -3909,10 +3931,10 @@
       <c r="A5" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="104">
         <v>2</v>
       </c>
-      <c r="C5" s="107"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="44"/>
       <c r="E5" s="44"/>
       <c r="F5" s="44"/>
@@ -3933,10 +3955,10 @@
       <c r="A7" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="106" t="s">
+      <c r="B7" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="107"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="44"/>
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
@@ -4295,9 +4317,9 @@
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="105"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="105"/>
+      <c r="A30" s="103"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="103"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="26"/>
@@ -4427,7 +4449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8E355-D10F-45CB-8710-0B743D2C5CA5}">
-  <dimension ref="A1:AF233"/>
+  <dimension ref="A1:AF223"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="53.85546875" customWidth="1"/>
@@ -7715,7 +7737,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="12.75" hidden="1">
+    <row r="48" spans="1:31" ht="12.75">
       <c r="A48" s="44" t="s">
         <v>47</v>
       </c>
@@ -7753,7 +7775,9 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1637.5</v>
       </c>
-      <c r="L48" s="52"/>
+      <c r="L48" s="52">
+        <v>3490</v>
+      </c>
       <c r="M48" s="48"/>
       <c r="N48" s="48"/>
       <c r="O48" s="48"/>
@@ -8216,7 +8240,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="12.75" hidden="1">
+    <row r="55" spans="1:32" ht="12.75">
       <c r="A55" s="44" t="s">
         <v>47</v>
       </c>
@@ -8289,7 +8313,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="12.75" hidden="1">
+    <row r="56" spans="1:32" ht="12.75">
       <c r="A56" s="44" t="s">
         <v>47</v>
       </c>
@@ -8362,7 +8386,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="12.75" hidden="1">
+    <row r="57" spans="1:32" ht="12.75">
       <c r="A57" s="44" t="s">
         <v>47</v>
       </c>
@@ -8435,7 +8459,7 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="1:32" ht="12.75" hidden="1">
+    <row r="58" spans="1:32" ht="12.75">
       <c r="A58" s="44" t="s">
         <v>47</v>
       </c>
@@ -8508,7 +8532,7 @@
       <c r="AD58"/>
       <c r="AE58"/>
     </row>
-    <row r="59" spans="1:32" ht="12.75" hidden="1">
+    <row r="59" spans="1:32" ht="12.75">
       <c r="A59" s="44" t="s">
         <v>47</v>
       </c>
@@ -8581,7 +8605,7 @@
       <c r="AD59"/>
       <c r="AE59"/>
     </row>
-    <row r="60" spans="1:32" ht="12.75" hidden="1">
+    <row r="60" spans="1:32" ht="12.75">
       <c r="A60" s="44" t="s">
         <v>47</v>
       </c>
@@ -10826,7 +10850,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="12.75" hidden="1">
+    <row r="91" spans="1:31" ht="12.75">
       <c r="A91" s="44" t="s">
         <v>47</v>
       </c>
@@ -10899,7 +10923,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="12.75" hidden="1">
+    <row r="92" spans="1:31" ht="12.75">
       <c r="A92" s="44" t="s">
         <v>47</v>
       </c>
@@ -10972,7 +10996,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="12.75" hidden="1">
+    <row r="93" spans="1:31" ht="12.75">
       <c r="A93" s="44" t="s">
         <v>47</v>
       </c>
@@ -11017,7 +11041,7 @@
       <c r="M93" s="48"/>
       <c r="N93" s="48"/>
       <c r="O93" s="48"/>
-      <c r="P93" s="99"/>
+      <c r="P93" s="97"/>
       <c r="Q93" s="49">
         <v>1</v>
       </c>
@@ -11045,7 +11069,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="12.75" hidden="1">
+    <row r="94" spans="1:31" ht="12.75">
       <c r="A94" s="44" t="s">
         <v>47</v>
       </c>
@@ -11090,23 +11114,23 @@
       <c r="M94" s="48"/>
       <c r="N94" s="48"/>
       <c r="O94" s="48"/>
-      <c r="P94" s="99"/>
-      <c r="Q94" s="100">
+      <c r="P94" s="97"/>
+      <c r="Q94" s="98">
         <v>1</v>
       </c>
-      <c r="R94" s="101" t="s">
+      <c r="R94" s="99" t="s">
         <v>49</v>
       </c>
       <c r="S94" s="79">
         <v>225</v>
       </c>
-      <c r="T94" s="102" t="s">
+      <c r="T94" s="100" t="s">
         <v>63</v>
       </c>
       <c r="U94" s="21">
         <v>0</v>
       </c>
-      <c r="V94" s="103" t="s">
+      <c r="V94" s="101" t="s">
         <v>56</v>
       </c>
       <c r="W94" s="4"/>
@@ -11118,7 +11142,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="12.75" hidden="1">
+    <row r="95" spans="1:31" ht="12.75">
       <c r="A95" s="44" t="s">
         <v>47</v>
       </c>
@@ -11407,7 +11431,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="12.75" hidden="1">
+    <row r="99" spans="1:31" ht="12.75">
       <c r="A99" s="44" t="s">
         <v>47</v>
       </c>
@@ -11452,7 +11476,7 @@
       <c r="M99" s="48"/>
       <c r="N99" s="48"/>
       <c r="O99" s="48"/>
-      <c r="P99" s="99"/>
+      <c r="P99" s="97"/>
       <c r="Q99" s="49">
         <v>1</v>
       </c>
@@ -11696,7 +11720,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="12.75" hidden="1">
+    <row r="103" spans="1:31" ht="12.75">
       <c r="A103" s="44" t="s">
         <v>47</v>
       </c>
@@ -11984,65 +12008,73 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="12.75">
-      <c r="A107" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B107" s="44" t="s">
-        <v>54</v>
+    <row r="107" spans="1:31" ht="12.75" hidden="1">
+      <c r="A107" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B107" s="127" t="s">
+        <v>647</v>
       </c>
       <c r="C107" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D107" s="46">
+      <c r="D107" s="48">
         <v>5819</v>
       </c>
-      <c r="E107" s="46" t="s">
+      <c r="E107" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F107" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1256.5</v>
       </c>
-      <c r="G107" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+      <c r="G107" s="125">
         <v>4562.5</v>
       </c>
       <c r="H107" s="52">
         <v>9450</v>
       </c>
-      <c r="I107" s="61" t="s">
-        <v>45</v>
+      <c r="I107" s="83" t="s">
+        <v>122</v>
       </c>
       <c r="J107" s="48">
-        <v>0</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1380</v>
       </c>
       <c r="K107" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="L107" s="52"/>
+        <v>3182.5</v>
+      </c>
+      <c r="L107" s="52">
+        <v>6690</v>
+      </c>
       <c r="M107" s="48"/>
-      <c r="N107" s="48"/>
-      <c r="O107" s="48"/>
+      <c r="N107" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O107" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P107" s="48"/>
       <c r="Q107" s="49">
         <v>1</v>
       </c>
-      <c r="R107" s="48" t="s">
+      <c r="R107" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S107" s="48">
+      <c r="S107" s="49">
         <v>325</v>
       </c>
-      <c r="T107" s="50" t="s">
+      <c r="T107" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U107" s="51">
         <v>0</v>
       </c>
-      <c r="V107" s="50" t="s">
+      <c r="V107" s="51" t="s">
         <v>56</v>
       </c>
       <c r="Y107" s="16"/>
@@ -12707,68 +12739,73 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.75">
-      <c r="A117" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B117" s="44" t="s">
-        <v>54</v>
+    <row r="117" spans="1:31" ht="12.75" hidden="1">
+      <c r="A117" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B117" s="128" t="s">
+        <v>647</v>
       </c>
       <c r="C117" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D117" s="46">
+      <c r="D117" s="48">
         <v>5819</v>
       </c>
-      <c r="E117" s="46" t="s">
+      <c r="E117" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F117" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1256.5</v>
       </c>
-      <c r="G117" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+      <c r="G117" s="125">
         <v>4562.5</v>
       </c>
       <c r="H117" s="52">
         <v>9450</v>
       </c>
-      <c r="I117" s="61" t="s">
-        <v>129</v>
+      <c r="I117" s="83" t="s">
+        <v>152</v>
       </c>
       <c r="J117" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="K117" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4562.5</v>
+        <v>3182.5</v>
       </c>
       <c r="L117" s="52">
-        <v>9450</v>
+        <v>6690</v>
       </c>
       <c r="M117" s="48"/>
-      <c r="N117" s="48"/>
-      <c r="O117" s="48"/>
+      <c r="N117" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O117" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P117" s="48"/>
       <c r="Q117" s="49">
         <v>1</v>
       </c>
-      <c r="R117" s="48" t="s">
+      <c r="R117" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S117" s="48">
+      <c r="S117" s="49">
         <v>325</v>
       </c>
-      <c r="T117" s="6" t="s">
+      <c r="T117" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="U117" s="48">
-        <v>0</v>
-      </c>
-      <c r="V117" s="57" t="s">
+      <c r="U117" s="51">
+        <v>0</v>
+      </c>
+      <c r="V117" s="51" t="s">
         <v>56</v>
       </c>
       <c r="Y117" s="16"/>
@@ -12779,51 +12816,56 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.75">
-      <c r="A118" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B118" s="44" t="s">
-        <v>54</v>
+    <row r="118" spans="1:31" ht="12.75" hidden="1">
+      <c r="A118" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B118" s="127" t="s">
+        <v>647</v>
       </c>
       <c r="C118" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D118" s="46">
+      <c r="D118" s="48">
         <v>5819</v>
       </c>
-      <c r="E118" s="46" t="s">
+      <c r="E118" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F118" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1256.5</v>
       </c>
-      <c r="G118" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+      <c r="G118" s="125">
         <v>4562.5</v>
       </c>
-      <c r="H118" s="40">
+      <c r="H118" s="52">
         <v>9450</v>
       </c>
-      <c r="I118" s="47" t="s">
-        <v>136</v>
+      <c r="I118" s="83" t="s">
+        <v>153</v>
       </c>
       <c r="J118" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>750</v>
+        <v>1380</v>
       </c>
       <c r="K118" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3812.5</v>
-      </c>
-      <c r="L118" s="55">
-        <v>7950</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L118" s="52">
+        <v>6690</v>
       </c>
       <c r="M118" s="48"/>
-      <c r="N118" s="48"/>
-      <c r="O118" s="48"/>
+      <c r="N118" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O118" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P118" s="48"/>
       <c r="Q118" s="49">
         <v>1</v>
@@ -12831,16 +12873,16 @@
       <c r="R118" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S118" s="79">
+      <c r="S118" s="49">
         <v>325</v>
       </c>
-      <c r="T118" s="50" t="s">
+      <c r="T118" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U118" s="51">
         <v>0</v>
       </c>
-      <c r="V118" s="50" t="s">
+      <c r="V118" s="51" t="s">
         <v>56</v>
       </c>
       <c r="Y118" s="16"/>
@@ -12851,68 +12893,73 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.75">
-      <c r="A119" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B119" s="44" t="s">
-        <v>54</v>
+    <row r="119" spans="1:31" ht="12.75" hidden="1">
+      <c r="A119" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B119" s="127" t="s">
+        <v>647</v>
       </c>
       <c r="C119" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D119" s="46">
+      <c r="D119" s="48">
         <v>5819</v>
       </c>
-      <c r="E119" s="46" t="s">
+      <c r="E119" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F119" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1256.5</v>
       </c>
-      <c r="G119" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+      <c r="G119" s="125">
         <v>4562.5</v>
       </c>
       <c r="H119" s="52">
         <v>9450</v>
       </c>
-      <c r="I119" s="61" t="s">
-        <v>141</v>
+      <c r="I119" s="83" t="s">
+        <v>154</v>
       </c>
       <c r="J119" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="K119" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4562.5</v>
+        <v>3182.5</v>
       </c>
       <c r="L119" s="52">
-        <v>9450</v>
+        <v>6690</v>
       </c>
       <c r="M119" s="48"/>
-      <c r="N119" s="48"/>
-      <c r="O119" s="48"/>
+      <c r="N119" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O119" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P119" s="48"/>
       <c r="Q119" s="49">
         <v>1</v>
       </c>
-      <c r="R119" s="48" t="s">
+      <c r="R119" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S119" s="48">
+      <c r="S119" s="49">
         <v>325</v>
       </c>
-      <c r="T119" s="50" t="s">
+      <c r="T119" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U119" s="51">
         <v>0</v>
       </c>
-      <c r="V119" s="50" t="s">
+      <c r="V119" s="51" t="s">
         <v>56</v>
       </c>
       <c r="Y119" s="16"/>
@@ -13143,69 +13190,73 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="12.75">
-      <c r="A123" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B123" s="44" t="s">
-        <v>54</v>
+    <row r="123" spans="1:31" ht="12.75" hidden="1">
+      <c r="A123" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B123" s="128" t="s">
+        <v>647</v>
       </c>
       <c r="C123" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D123" s="46">
+      <c r="D123" s="48">
         <v>5819</v>
       </c>
-      <c r="E123" s="46" t="s">
+      <c r="E123" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F123" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1256.5</v>
       </c>
-      <c r="G123" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+      <c r="G123" s="125">
         <v>4562.5</v>
       </c>
       <c r="H123" s="52">
         <v>9450</v>
       </c>
-      <c r="I123" s="61" t="s">
-        <v>156</v>
+      <c r="I123" s="83" t="s">
+        <v>157</v>
       </c>
       <c r="J123" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>500</v>
+        <v>1380</v>
       </c>
       <c r="K123" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4062.5</v>
+        <v>3182.5</v>
       </c>
       <c r="L123" s="52">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>8450</v>
+        <v>6690</v>
       </c>
       <c r="M123" s="48"/>
-      <c r="N123" s="48"/>
-      <c r="O123" s="48"/>
+      <c r="N123" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O123" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P123" s="48"/>
       <c r="Q123" s="49">
         <v>1</v>
       </c>
-      <c r="R123" s="48" t="s">
+      <c r="R123" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S123" s="48">
+      <c r="S123" s="49">
         <v>325</v>
       </c>
-      <c r="T123" s="50" t="s">
+      <c r="T123" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U123" s="51">
         <v>0</v>
       </c>
-      <c r="V123" s="50" t="s">
+      <c r="V123" s="51" t="s">
         <v>56</v>
       </c>
       <c r="W123" s="48"/>
@@ -13217,68 +13268,73 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="12.75">
-      <c r="A124" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B124" s="44" t="s">
-        <v>54</v>
+    <row r="124" spans="1:31" ht="12.75" hidden="1">
+      <c r="A124" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B124" s="127" t="s">
+        <v>647</v>
       </c>
       <c r="C124" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D124" s="46">
+      <c r="D124" s="48">
         <v>5819</v>
       </c>
-      <c r="E124" s="46" t="s">
+      <c r="E124" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F124" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
         <v>1256.5</v>
       </c>
-      <c r="G124" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+      <c r="G124" s="125">
         <v>4562.5</v>
       </c>
       <c r="H124" s="52">
         <v>9450</v>
       </c>
-      <c r="I124" s="61" t="s">
-        <v>159</v>
+      <c r="I124" s="83" t="s">
+        <v>158</v>
       </c>
       <c r="J124" s="48">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>925</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1380</v>
       </c>
       <c r="K124" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3637.5</v>
+        <v>3182.5</v>
       </c>
       <c r="L124" s="52">
-        <v>7600</v>
-      </c>
-      <c r="M124" s="61"/>
-      <c r="N124" s="48"/>
-      <c r="O124" s="84"/>
-      <c r="P124" s="46"/>
-      <c r="Q124" s="85">
+        <v>6690</v>
+      </c>
+      <c r="M124" s="48"/>
+      <c r="N124" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O124" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P124" s="48"/>
+      <c r="Q124" s="49">
         <v>1</v>
       </c>
-      <c r="R124" s="46" t="s">
+      <c r="R124" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S124" s="48">
+      <c r="S124" s="49">
         <v>325</v>
       </c>
-      <c r="T124" s="82" t="s">
+      <c r="T124" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="U124" s="16">
-        <v>0</v>
-      </c>
-      <c r="V124" s="58" t="s">
+      <c r="U124" s="51">
+        <v>0</v>
+      </c>
+      <c r="V124" s="51" t="s">
         <v>56</v>
       </c>
       <c r="W124" s="48"/>
@@ -13290,67 +13346,73 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="12.75">
-      <c r="A125" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B125" s="44" t="s">
-        <v>51</v>
+    <row r="125" spans="1:31" ht="12.75" hidden="1">
+      <c r="A125" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B125" s="128" t="s">
+        <v>647</v>
       </c>
       <c r="C125" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>6383</v>
-      </c>
-      <c r="D125" s="46">
-        <v>3029</v>
-      </c>
-      <c r="E125" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D125" s="48">
+        <v>5819</v>
+      </c>
+      <c r="E125" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
-      </c>
-      <c r="G125" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>2362.5</v>
+        <v>1256.5</v>
+      </c>
+      <c r="G125" s="125">
+        <v>4562.5</v>
       </c>
       <c r="H125" s="52">
-        <v>5050</v>
-      </c>
-      <c r="I125" s="61" t="s">
-        <v>45</v>
+        <v>9450</v>
+      </c>
+      <c r="I125" s="83" t="s">
+        <v>161</v>
       </c>
       <c r="J125" s="48">
-        <v>0</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1380</v>
       </c>
       <c r="K125" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2362.5</v>
+        <v>3182.5</v>
       </c>
       <c r="L125" s="52">
-        <v>5050</v>
+        <v>6690</v>
       </c>
       <c r="M125" s="48"/>
-      <c r="N125" s="48"/>
-      <c r="O125" s="48"/>
+      <c r="N125" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O125" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P125" s="48"/>
       <c r="Q125" s="49">
         <v>1</v>
       </c>
-      <c r="R125" s="81" t="s">
+      <c r="R125" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S125" s="79">
+      <c r="S125" s="49">
         <v>325</v>
       </c>
-      <c r="T125" s="50" t="s">
+      <c r="T125" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U125" s="51">
         <v>0</v>
       </c>
-      <c r="V125" s="50" t="s">
+      <c r="V125" s="51" t="s">
         <v>56</v>
       </c>
       <c r="W125" s="4"/>
@@ -13362,68 +13424,73 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.75">
-      <c r="A126" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B126" s="44" t="s">
-        <v>51</v>
+    <row r="126" spans="1:31" ht="12.75" hidden="1">
+      <c r="A126" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B126" s="127" t="s">
+        <v>647</v>
       </c>
       <c r="C126" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>6383</v>
-      </c>
-      <c r="D126" s="46">
-        <v>3029</v>
-      </c>
-      <c r="E126" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D126" s="48">
+        <v>5819</v>
+      </c>
+      <c r="E126" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F126" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
-      </c>
-      <c r="G126" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>2362.5</v>
+        <v>1256.5</v>
+      </c>
+      <c r="G126" s="125">
+        <v>4562.5</v>
       </c>
       <c r="H126" s="52">
-        <v>5050</v>
-      </c>
-      <c r="I126" s="61" t="s">
-        <v>141</v>
+        <v>9450</v>
+      </c>
+      <c r="I126" s="83" t="s">
+        <v>162</v>
       </c>
       <c r="J126" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="K126" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2362.5</v>
+        <v>3182.5</v>
       </c>
       <c r="L126" s="52">
-        <v>5050</v>
+        <v>6690</v>
       </c>
       <c r="M126" s="48"/>
-      <c r="N126" s="48"/>
-      <c r="O126" s="48"/>
+      <c r="N126" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O126" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P126" s="48"/>
       <c r="Q126" s="49">
         <v>1</v>
       </c>
-      <c r="R126" s="78" t="s">
+      <c r="R126" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S126" s="48">
+      <c r="S126" s="49">
         <v>325</v>
       </c>
-      <c r="T126" s="50" t="s">
+      <c r="T126" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U126" s="51">
         <v>0</v>
       </c>
-      <c r="V126" s="50" t="s">
+      <c r="V126" s="51" t="s">
         <v>56</v>
       </c>
       <c r="W126" s="4"/>
@@ -13654,65 +13721,73 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="12.75">
-      <c r="A130" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B130" s="44" t="s">
-        <v>58</v>
+    <row r="130" spans="1:31" ht="12.75" hidden="1">
+      <c r="A130" s="126" t="s">
+        <v>646</v>
+      </c>
+      <c r="B130" s="128" t="s">
+        <v>647</v>
       </c>
       <c r="C130" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D130" s="46">
-        <v>3689</v>
-      </c>
-      <c r="E130" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D130" s="48">
+        <v>5819</v>
+      </c>
+      <c r="E130" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F130" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
-      </c>
-      <c r="G130" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
+        <v>1256.5</v>
+      </c>
+      <c r="G130" s="125">
+        <v>4562.5</v>
       </c>
       <c r="H130" s="52">
-        <v>7050</v>
-      </c>
-      <c r="I130" s="61" t="s">
-        <v>45</v>
+        <v>9450</v>
+      </c>
+      <c r="I130" s="83" t="s">
+        <v>164</v>
       </c>
       <c r="J130" s="48">
-        <v>0</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1380</v>
       </c>
       <c r="K130" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="L130" s="52"/>
+        <v>3182.5</v>
+      </c>
+      <c r="L130" s="52">
+        <v>6690</v>
+      </c>
       <c r="M130" s="48"/>
-      <c r="N130" s="48"/>
-      <c r="O130" s="48"/>
+      <c r="N130" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>3182.5</v>
+      </c>
+      <c r="O130" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P130" s="48"/>
       <c r="Q130" s="49">
         <v>1</v>
       </c>
-      <c r="R130" s="48" t="s">
+      <c r="R130" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S130" s="48">
+      <c r="S130" s="49">
         <v>325</v>
       </c>
-      <c r="T130" s="50" t="s">
+      <c r="T130" s="51" t="s">
         <v>55</v>
       </c>
       <c r="U130" s="51">
         <v>0</v>
       </c>
-      <c r="V130" s="50" t="s">
+      <c r="V130" s="51" t="s">
         <v>56</v>
       </c>
       <c r="W130" s="4"/>
@@ -13943,48 +14018,45 @@
       <c r="AD133"/>
       <c r="AE133"/>
     </row>
-    <row r="134" spans="1:31" ht="12.75">
+    <row r="134" spans="1:31" ht="12.75" hidden="1">
       <c r="A134" s="44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B134" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C134" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
+        <v>11963</v>
       </c>
       <c r="D134" s="46">
-        <v>3689</v>
+        <v>5819</v>
       </c>
       <c r="E134" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F134" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G134" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
+        <v>4562.5</v>
       </c>
       <c r="H134" s="52">
-        <v>7050</v>
+        <v>9450</v>
       </c>
       <c r="I134" s="61" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="J134" s="48">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>0</v>
       </c>
       <c r="K134" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="L134" s="52">
-        <v>7050</v>
-      </c>
+        <v>4562.5</v>
+      </c>
+      <c r="L134" s="52"/>
       <c r="M134" s="48"/>
       <c r="N134" s="48"/>
       <c r="O134" s="48"/>
@@ -13998,13 +14070,13 @@
       <c r="S134" s="48">
         <v>325</v>
       </c>
-      <c r="T134" s="6" t="s">
+      <c r="T134" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="U134" s="48">
-        <v>0</v>
-      </c>
-      <c r="V134" s="57" t="s">
+      <c r="U134" s="51">
+        <v>0</v>
+      </c>
+      <c r="V134" s="50" t="s">
         <v>56</v>
       </c>
       <c r="W134" s="4"/>
@@ -14016,47 +14088,47 @@
       <c r="AD134"/>
       <c r="AE134"/>
     </row>
-    <row r="135" spans="1:31" ht="12.75">
+    <row r="135" spans="1:31" ht="12.75" hidden="1">
       <c r="A135" s="44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B135" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C135" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
+        <v>11963</v>
       </c>
       <c r="D135" s="46">
-        <v>3689</v>
+        <v>5819</v>
       </c>
       <c r="E135" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F135" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G135" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H135" s="40">
-        <v>7050</v>
-      </c>
-      <c r="I135" s="47" t="s">
-        <v>137</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H135" s="52">
+        <v>9450</v>
+      </c>
+      <c r="I135" s="61" t="s">
+        <v>129</v>
       </c>
       <c r="J135" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="K135" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2662.5</v>
-      </c>
-      <c r="L135" s="55">
-        <v>5650</v>
+        <v>4562.5</v>
+      </c>
+      <c r="L135" s="52">
+        <v>9450</v>
       </c>
       <c r="M135" s="48"/>
       <c r="N135" s="48"/>
@@ -14065,19 +14137,19 @@
       <c r="Q135" s="49">
         <v>1</v>
       </c>
-      <c r="R135" s="49" t="s">
+      <c r="R135" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="S135" s="79">
+      <c r="S135" s="48">
         <v>325</v>
       </c>
-      <c r="T135" s="50" t="s">
+      <c r="T135" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="U135" s="51">
-        <v>0</v>
-      </c>
-      <c r="V135" s="50" t="s">
+      <c r="U135" s="48">
+        <v>0</v>
+      </c>
+      <c r="V135" s="57" t="s">
         <v>56</v>
       </c>
       <c r="W135" s="4"/>
@@ -14089,47 +14161,47 @@
       <c r="AD135"/>
       <c r="AE135"/>
     </row>
-    <row r="136" spans="1:31" ht="12.75">
+    <row r="136" spans="1:31" ht="12.75" hidden="1">
       <c r="A136" s="44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B136" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C136" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
+        <v>11963</v>
       </c>
       <c r="D136" s="46">
-        <v>3689</v>
+        <v>5819</v>
       </c>
       <c r="E136" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F136" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G136" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H136" s="52">
-        <v>7050</v>
-      </c>
-      <c r="I136" s="61" t="s">
-        <v>141</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H136" s="40">
+        <v>9450</v>
+      </c>
+      <c r="I136" s="47" t="s">
+        <v>136</v>
       </c>
       <c r="J136" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="K136" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="L136" s="52">
-        <v>7050</v>
+        <v>3812.5</v>
+      </c>
+      <c r="L136" s="55">
+        <v>7950</v>
       </c>
       <c r="M136" s="48"/>
       <c r="N136" s="48"/>
@@ -14138,10 +14210,10 @@
       <c r="Q136" s="49">
         <v>1</v>
       </c>
-      <c r="R136" s="48" t="s">
+      <c r="R136" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S136" s="48">
+      <c r="S136" s="79">
         <v>325</v>
       </c>
       <c r="T136" s="50" t="s">
@@ -14162,50 +14234,49 @@
       <c r="AD136"/>
       <c r="AE136"/>
     </row>
-    <row r="137" spans="1:31" ht="12.75">
+    <row r="137" spans="1:31" ht="12.75" hidden="1">
       <c r="A137" s="44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B137" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C137" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
+        <v>11963</v>
       </c>
       <c r="D137" s="46">
-        <v>3689</v>
+        <v>5819</v>
       </c>
       <c r="E137" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F137" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G137" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
+        <v>4562.5</v>
       </c>
       <c r="H137" s="52">
-        <v>7050</v>
+        <v>9450</v>
       </c>
       <c r="I137" s="61" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="J137" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K137" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2862.5</v>
+        <v>4562.5</v>
       </c>
       <c r="L137" s="52">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>6050</v>
-      </c>
-      <c r="M137" s="88"/>
+        <v>9450</v>
+      </c>
+      <c r="M137" s="86"/>
       <c r="N137" s="48"/>
       <c r="O137" s="48"/>
       <c r="P137" s="48"/>
@@ -14236,68 +14307,69 @@
       <c r="AD137"/>
       <c r="AE137"/>
     </row>
-    <row r="138" spans="1:31" ht="12.75">
+    <row r="138" spans="1:31" ht="12.75" hidden="1">
       <c r="A138" s="44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B138" s="44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C138" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
+        <v>11963</v>
       </c>
       <c r="D138" s="46">
-        <v>3689</v>
+        <v>5819</v>
       </c>
       <c r="E138" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F138" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G138" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
+        <v>4562.5</v>
       </c>
       <c r="H138" s="52">
-        <v>7050</v>
+        <v>9450</v>
       </c>
       <c r="I138" s="61" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J138" s="48">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>625</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>500</v>
       </c>
       <c r="K138" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2737.5</v>
+        <v>4062.5</v>
       </c>
       <c r="L138" s="52">
-        <v>5800</v>
-      </c>
-      <c r="M138" s="92"/>
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>8450</v>
+      </c>
+      <c r="M138" s="86"/>
       <c r="N138" s="48"/>
-      <c r="O138" s="84"/>
-      <c r="P138" s="46"/>
-      <c r="Q138" s="85">
+      <c r="O138" s="48"/>
+      <c r="P138" s="48"/>
+      <c r="Q138" s="49">
         <v>1</v>
       </c>
-      <c r="R138" s="46" t="s">
+      <c r="R138" s="48" t="s">
         <v>52</v>
       </c>
       <c r="S138" s="48">
         <v>325</v>
       </c>
-      <c r="T138" s="82" t="s">
+      <c r="T138" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="U138" s="16">
-        <v>0</v>
-      </c>
-      <c r="V138" s="58" t="s">
+      <c r="U138" s="51">
+        <v>0</v>
+      </c>
+      <c r="V138" s="50" t="s">
         <v>56</v>
       </c>
       <c r="W138" s="4"/>
@@ -14309,65 +14381,68 @@
       <c r="AD138"/>
       <c r="AE138"/>
     </row>
-    <row r="139" spans="1:31" ht="12.75">
-      <c r="A139" s="87" t="s">
-        <v>59</v>
+    <row r="139" spans="1:31" ht="12.75" hidden="1">
+      <c r="A139" s="85" t="s">
+        <v>53</v>
       </c>
       <c r="B139" s="44" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C139" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
-      </c>
-      <c r="D139" s="88">
-        <v>4679</v>
-      </c>
-      <c r="E139" s="88" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D139" s="86">
+        <v>5819</v>
+      </c>
+      <c r="E139" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F139" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G139" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
+        <v>4562.5</v>
       </c>
       <c r="H139" s="52">
-        <v>8350</v>
-      </c>
-      <c r="I139" s="92" t="s">
-        <v>45</v>
+        <v>9450</v>
+      </c>
+      <c r="I139" s="90" t="s">
+        <v>159</v>
       </c>
       <c r="J139" s="48">
-        <v>0</v>
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>925</v>
       </c>
       <c r="K139" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="L139" s="52"/>
-      <c r="M139" s="88"/>
+        <v>3637.5</v>
+      </c>
+      <c r="L139" s="52">
+        <v>7600</v>
+      </c>
+      <c r="M139" s="90"/>
       <c r="N139" s="48"/>
-      <c r="O139" s="88"/>
-      <c r="P139" s="88"/>
-      <c r="Q139" s="89">
+      <c r="O139" s="111"/>
+      <c r="P139" s="86"/>
+      <c r="Q139" s="87">
         <v>1</v>
       </c>
-      <c r="R139" s="88" t="s">
+      <c r="R139" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S139" s="48">
         <v>325</v>
       </c>
-      <c r="T139" s="90" t="s">
+      <c r="T139" s="110" t="s">
         <v>55</v>
       </c>
-      <c r="U139" s="90">
-        <v>0</v>
-      </c>
-      <c r="V139" s="91" t="s">
+      <c r="U139" s="20">
+        <v>0</v>
+      </c>
+      <c r="V139" s="108" t="s">
         <v>56</v>
       </c>
       <c r="X139" s="48"/>
@@ -14378,21 +14453,21 @@
       <c r="AC139" s="48"/>
       <c r="AD139" s="48"/>
     </row>
-    <row r="140" spans="1:31" ht="12.75">
-      <c r="A140" s="87" t="s">
-        <v>59</v>
+    <row r="140" spans="1:31" ht="12.75" hidden="1">
+      <c r="A140" s="85" t="s">
+        <v>50</v>
       </c>
       <c r="B140" s="44" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C140" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
-      </c>
-      <c r="D140" s="88">
-        <v>4679</v>
-      </c>
-      <c r="E140" s="88" t="s">
+        <v>6383</v>
+      </c>
+      <c r="D140" s="86">
+        <v>3029</v>
+      </c>
+      <c r="E140" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F140" s="46">
@@ -14401,45 +14476,44 @@
       </c>
       <c r="G140" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
+        <v>2362.5</v>
       </c>
       <c r="H140" s="52">
-        <v>8350</v>
-      </c>
-      <c r="I140" s="92" t="s">
-        <v>129</v>
+        <v>5050</v>
+      </c>
+      <c r="I140" s="90" t="s">
+        <v>45</v>
       </c>
       <c r="J140" s="48">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>0</v>
       </c>
       <c r="K140" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4012.5</v>
+        <v>2362.5</v>
       </c>
       <c r="L140" s="52">
-        <v>8350</v>
-      </c>
-      <c r="M140" s="88"/>
+        <v>5050</v>
+      </c>
+      <c r="M140" s="86"/>
       <c r="N140" s="48"/>
-      <c r="O140" s="88"/>
-      <c r="P140" s="88"/>
-      <c r="Q140" s="89">
+      <c r="O140" s="86"/>
+      <c r="P140" s="86"/>
+      <c r="Q140" s="87">
         <v>1</v>
       </c>
-      <c r="R140" s="88" t="s">
+      <c r="R140" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="S140" s="48">
+      <c r="S140" s="79">
         <v>325</v>
       </c>
-      <c r="T140" s="43" t="s">
+      <c r="T140" s="88" t="s">
         <v>55</v>
       </c>
       <c r="U140" s="88">
         <v>0</v>
       </c>
-      <c r="V140" s="59" t="s">
+      <c r="V140" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X140" s="48"/>
@@ -14451,7 +14525,7 @@
       <c r="AD140" s="48"/>
     </row>
     <row r="141" spans="1:31" ht="12.75" hidden="1">
-      <c r="A141" s="87" t="s">
+      <c r="A141" s="85" t="s">
         <v>123</v>
       </c>
       <c r="B141" s="44" t="s">
@@ -14461,10 +14535,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D141" s="88">
+      <c r="D141" s="86">
         <v>5819</v>
       </c>
-      <c r="E141" s="88" t="s">
+      <c r="E141" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F141" s="46">
@@ -14478,7 +14552,7 @@
       <c r="H141" s="52">
         <v>9450</v>
       </c>
-      <c r="I141" s="92" t="s">
+      <c r="I141" s="90" t="s">
         <v>160</v>
       </c>
       <c r="J141" s="48">
@@ -14492,14 +14566,14 @@
       <c r="L141" s="52">
         <v>6690</v>
       </c>
-      <c r="M141" s="88"/>
+      <c r="M141" s="86"/>
       <c r="N141" s="48"/>
-      <c r="O141" s="88"/>
-      <c r="P141" s="88"/>
-      <c r="Q141" s="89">
+      <c r="O141" s="86"/>
+      <c r="P141" s="86"/>
+      <c r="Q141" s="87">
         <v>1</v>
       </c>
-      <c r="R141" s="88" t="s">
+      <c r="R141" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S141" s="48">
@@ -14508,7 +14582,7 @@
       <c r="T141" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="U141" s="88">
+      <c r="U141" s="86">
         <v>0</v>
       </c>
       <c r="V141" s="59" t="s">
@@ -14523,7 +14597,7 @@
       <c r="AD141" s="46"/>
     </row>
     <row r="142" spans="1:31" ht="12.75" hidden="1">
-      <c r="A142" s="87" t="s">
+      <c r="A142" s="85" t="s">
         <v>125</v>
       </c>
       <c r="B142" s="44" t="s">
@@ -14533,10 +14607,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D142" s="88">
+      <c r="D142" s="86">
         <v>3689</v>
       </c>
-      <c r="E142" s="88" t="s">
+      <c r="E142" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F142" s="46">
@@ -14550,7 +14624,7 @@
       <c r="H142" s="52">
         <v>7050</v>
       </c>
-      <c r="I142" s="92" t="s">
+      <c r="I142" s="90" t="s">
         <v>160</v>
       </c>
       <c r="J142" s="48">
@@ -14564,14 +14638,14 @@
       <c r="L142" s="52">
         <v>4890</v>
       </c>
-      <c r="M142" s="88"/>
+      <c r="M142" s="86"/>
       <c r="N142" s="48"/>
-      <c r="O142" s="88"/>
-      <c r="P142" s="88"/>
-      <c r="Q142" s="89">
+      <c r="O142" s="86"/>
+      <c r="P142" s="86"/>
+      <c r="Q142" s="87">
         <v>1</v>
       </c>
-      <c r="R142" s="88" t="s">
+      <c r="R142" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S142" s="48">
@@ -14580,7 +14654,7 @@
       <c r="T142" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="U142" s="88">
+      <c r="U142" s="86">
         <v>0</v>
       </c>
       <c r="V142" s="59" t="s">
@@ -14595,7 +14669,7 @@
       <c r="AD142" s="46"/>
     </row>
     <row r="143" spans="1:31" ht="12.75" hidden="1">
-      <c r="A143" s="87" t="s">
+      <c r="A143" s="85" t="s">
         <v>127</v>
       </c>
       <c r="B143" s="44" t="s">
@@ -14605,10 +14679,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D143" s="88">
+      <c r="D143" s="86">
         <v>4679</v>
       </c>
-      <c r="E143" s="88" t="s">
+      <c r="E143" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F143" s="46">
@@ -14622,7 +14696,7 @@
       <c r="H143" s="52">
         <v>7350</v>
       </c>
-      <c r="I143" s="92" t="s">
+      <c r="I143" s="90" t="s">
         <v>160</v>
       </c>
       <c r="J143" s="48">
@@ -14636,14 +14710,14 @@
       <c r="L143" s="52">
         <v>5690</v>
       </c>
-      <c r="M143" s="88"/>
+      <c r="M143" s="86"/>
       <c r="N143" s="48"/>
-      <c r="O143" s="88"/>
-      <c r="P143" s="88"/>
-      <c r="Q143" s="89">
+      <c r="O143" s="86"/>
+      <c r="P143" s="86"/>
+      <c r="Q143" s="87">
         <v>1</v>
       </c>
-      <c r="R143" s="88" t="s">
+      <c r="R143" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S143" s="48">
@@ -14652,7 +14726,7 @@
       <c r="T143" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="U143" s="88">
+      <c r="U143" s="86">
         <v>0</v>
       </c>
       <c r="V143" s="59" t="s">
@@ -14666,21 +14740,21 @@
       <c r="AC143" s="48"/>
       <c r="AD143" s="46"/>
     </row>
-    <row r="144" spans="1:31" ht="12.75">
-      <c r="A144" s="87" t="s">
-        <v>59</v>
+    <row r="144" spans="1:31" ht="12.75" hidden="1">
+      <c r="A144" s="85" t="s">
+        <v>50</v>
       </c>
       <c r="B144" s="44" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C144" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
-      </c>
-      <c r="D144" s="88">
-        <v>4679</v>
-      </c>
-      <c r="E144" s="88" t="s">
+        <v>6383</v>
+      </c>
+      <c r="D144" s="86">
+        <v>3029</v>
+      </c>
+      <c r="E144" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F144" s="46">
@@ -14689,45 +14763,45 @@
       </c>
       <c r="G144" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H144" s="40">
-        <v>8350</v>
-      </c>
-      <c r="I144" s="86" t="s">
-        <v>138</v>
+        <v>2362.5</v>
+      </c>
+      <c r="H144" s="52">
+        <v>5050</v>
+      </c>
+      <c r="I144" s="90" t="s">
+        <v>141</v>
       </c>
       <c r="J144" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="K144" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3312.5</v>
-      </c>
-      <c r="L144" s="55">
-        <v>6950</v>
-      </c>
-      <c r="M144" s="88"/>
+        <v>2362.5</v>
+      </c>
+      <c r="L144" s="52">
+        <v>5050</v>
+      </c>
+      <c r="M144" s="86"/>
       <c r="N144" s="48"/>
-      <c r="O144" s="88"/>
-      <c r="P144" s="88"/>
-      <c r="Q144" s="89">
+      <c r="O144" s="86"/>
+      <c r="P144" s="86"/>
+      <c r="Q144" s="87">
         <v>1</v>
       </c>
-      <c r="R144" s="89" t="s">
+      <c r="R144" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="S144" s="79">
+      <c r="S144" s="48">
         <v>325</v>
       </c>
-      <c r="T144" s="90" t="s">
+      <c r="T144" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U144" s="90">
-        <v>0</v>
-      </c>
-      <c r="V144" s="91" t="s">
+      <c r="U144" s="88">
+        <v>0</v>
+      </c>
+      <c r="V144" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X144" s="48"/>
@@ -14739,7 +14813,7 @@
       <c r="AD144" s="46"/>
     </row>
     <row r="145" spans="1:31" ht="12.75" hidden="1">
-      <c r="A145" s="87" t="s">
+      <c r="A145" s="85" t="s">
         <v>123</v>
       </c>
       <c r="B145" s="44" t="s">
@@ -14749,10 +14823,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D145" s="88">
+      <c r="D145" s="86">
         <v>5819</v>
       </c>
-      <c r="E145" s="88" t="s">
+      <c r="E145" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F145" s="46">
@@ -14766,7 +14840,7 @@
       <c r="H145" s="52">
         <v>9450</v>
       </c>
-      <c r="I145" s="92" t="s">
+      <c r="I145" s="90" t="s">
         <v>161</v>
       </c>
       <c r="J145" s="48">
@@ -14780,14 +14854,14 @@
       <c r="L145" s="52">
         <v>6690</v>
       </c>
-      <c r="M145" s="88"/>
+      <c r="M145" s="86"/>
       <c r="N145" s="48"/>
-      <c r="O145" s="88"/>
-      <c r="P145" s="88"/>
-      <c r="Q145" s="89">
+      <c r="O145" s="86"/>
+      <c r="P145" s="86"/>
+      <c r="Q145" s="87">
         <v>1</v>
       </c>
-      <c r="R145" s="88" t="s">
+      <c r="R145" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S145" s="48">
@@ -14796,7 +14870,7 @@
       <c r="T145" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="U145" s="88">
+      <c r="U145" s="86">
         <v>0</v>
       </c>
       <c r="V145" s="59" t="s">
@@ -14812,7 +14886,7 @@
       <c r="AE145" s="16"/>
     </row>
     <row r="146" spans="1:31" ht="12.75" hidden="1">
-      <c r="A146" s="87" t="s">
+      <c r="A146" s="85" t="s">
         <v>125</v>
       </c>
       <c r="B146" s="44" t="s">
@@ -14822,10 +14896,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D146" s="88">
+      <c r="D146" s="86">
         <v>3689</v>
       </c>
-      <c r="E146" s="88" t="s">
+      <c r="E146" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F146" s="46">
@@ -14839,7 +14913,7 @@
       <c r="H146" s="52">
         <v>7050</v>
       </c>
-      <c r="I146" s="92" t="s">
+      <c r="I146" s="90" t="s">
         <v>161</v>
       </c>
       <c r="J146" s="48">
@@ -14853,14 +14927,14 @@
       <c r="L146" s="52">
         <v>4890</v>
       </c>
-      <c r="M146" s="88"/>
+      <c r="M146" s="86"/>
       <c r="N146" s="48"/>
-      <c r="O146" s="88"/>
-      <c r="P146" s="88"/>
-      <c r="Q146" s="89">
+      <c r="O146" s="86"/>
+      <c r="P146" s="86"/>
+      <c r="Q146" s="87">
         <v>1</v>
       </c>
-      <c r="R146" s="88" t="s">
+      <c r="R146" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S146" s="48">
@@ -14869,7 +14943,7 @@
       <c r="T146" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="U146" s="88">
+      <c r="U146" s="86">
         <v>0</v>
       </c>
       <c r="V146" s="59" t="s">
@@ -14885,7 +14959,7 @@
       <c r="AE146" s="16"/>
     </row>
     <row r="147" spans="1:31" ht="12.75" hidden="1">
-      <c r="A147" s="87" t="s">
+      <c r="A147" s="85" t="s">
         <v>127</v>
       </c>
       <c r="B147" s="44" t="s">
@@ -14895,10 +14969,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D147" s="88">
+      <c r="D147" s="86">
         <v>4679</v>
       </c>
-      <c r="E147" s="88" t="s">
+      <c r="E147" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F147" s="46">
@@ -14912,7 +14986,7 @@
       <c r="H147" s="52">
         <v>8350</v>
       </c>
-      <c r="I147" s="92" t="s">
+      <c r="I147" s="90" t="s">
         <v>161</v>
       </c>
       <c r="J147" s="48">
@@ -14926,14 +15000,14 @@
       <c r="L147" s="52">
         <v>5690</v>
       </c>
-      <c r="M147" s="88"/>
+      <c r="M147" s="86"/>
       <c r="N147" s="48"/>
-      <c r="O147" s="88"/>
-      <c r="P147" s="88"/>
-      <c r="Q147" s="89">
+      <c r="O147" s="86"/>
+      <c r="P147" s="86"/>
+      <c r="Q147" s="87">
         <v>1</v>
       </c>
-      <c r="R147" s="88" t="s">
+      <c r="R147" s="86" t="s">
         <v>52</v>
       </c>
       <c r="S147" s="48">
@@ -14942,7 +15016,7 @@
       <c r="T147" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="U147" s="88">
+      <c r="U147" s="86">
         <v>0</v>
       </c>
       <c r="V147" s="59" t="s">
@@ -14957,68 +15031,73 @@
       <c r="AD147" s="7"/>
       <c r="AE147" s="16"/>
     </row>
-    <row r="148" spans="1:31" ht="12.75">
-      <c r="A148" s="87" t="s">
-        <v>59</v>
-      </c>
-      <c r="B148" s="44" t="s">
-        <v>60</v>
+    <row r="148" spans="1:31" ht="12.75" hidden="1">
+      <c r="A148" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B148" s="128" t="s">
+        <v>649</v>
       </c>
       <c r="C148" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
-      </c>
-      <c r="D148" s="88">
-        <v>4679</v>
-      </c>
-      <c r="E148" s="88" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D148" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E148" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F148" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
-      </c>
-      <c r="G148" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
+        <v>326.5</v>
+      </c>
+      <c r="G148" s="125">
+        <v>3362.5</v>
       </c>
       <c r="H148" s="52">
-        <v>8350</v>
-      </c>
-      <c r="I148" s="92" t="s">
-        <v>141</v>
+        <v>7050</v>
+      </c>
+      <c r="I148" s="84" t="s">
+        <v>122</v>
       </c>
       <c r="J148" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="K148" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4012.5</v>
+        <v>2332.5</v>
       </c>
       <c r="L148" s="52">
-        <v>8350</v>
-      </c>
-      <c r="M148" s="88"/>
-      <c r="N148" s="48"/>
-      <c r="O148" s="88"/>
-      <c r="P148" s="88"/>
-      <c r="Q148" s="89">
+        <v>4990</v>
+      </c>
+      <c r="M148" s="86"/>
+      <c r="N148" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O148" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P148" s="86"/>
+      <c r="Q148" s="87">
         <v>1</v>
       </c>
-      <c r="R148" s="88" t="s">
+      <c r="R148" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S148" s="48">
+      <c r="S148" s="49">
         <v>325</v>
       </c>
-      <c r="T148" s="90" t="s">
+      <c r="T148" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U148" s="90">
-        <v>0</v>
-      </c>
-      <c r="V148" s="91" t="s">
+      <c r="U148" s="88">
+        <v>0</v>
+      </c>
+      <c r="V148" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X148" s="48"/>
@@ -15030,7 +15109,7 @@
       <c r="AD148" s="7"/>
     </row>
     <row r="149" spans="1:31" ht="12.75" hidden="1">
-      <c r="A149" s="87" t="s">
+      <c r="A149" s="85" t="s">
         <v>123</v>
       </c>
       <c r="B149" s="44" t="s">
@@ -15040,10 +15119,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D149" s="88">
+      <c r="D149" s="86">
         <v>5819</v>
       </c>
-      <c r="E149" s="88" t="s">
+      <c r="E149" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F149" s="46">
@@ -15057,7 +15136,7 @@
       <c r="H149" s="40">
         <v>9450</v>
       </c>
-      <c r="I149" s="86" t="s">
+      <c r="I149" s="84" t="s">
         <v>162</v>
       </c>
       <c r="J149" s="48">
@@ -15071,26 +15150,26 @@
       <c r="L149" s="55">
         <v>6690</v>
       </c>
-      <c r="M149" s="88"/>
+      <c r="M149" s="86"/>
       <c r="N149" s="48"/>
-      <c r="O149" s="88"/>
-      <c r="P149" s="88"/>
-      <c r="Q149" s="89">
+      <c r="O149" s="86"/>
+      <c r="P149" s="86"/>
+      <c r="Q149" s="87">
         <v>1</v>
       </c>
-      <c r="R149" s="89" t="s">
+      <c r="R149" s="87" t="s">
         <v>52</v>
       </c>
       <c r="S149" s="48">
         <v>325</v>
       </c>
-      <c r="T149" s="90" t="s">
+      <c r="T149" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U149" s="90">
-        <v>0</v>
-      </c>
-      <c r="V149" s="91" t="s">
+      <c r="U149" s="88">
+        <v>0</v>
+      </c>
+      <c r="V149" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X149" s="48"/>
@@ -15102,7 +15181,7 @@
       <c r="AD149" s="7"/>
     </row>
     <row r="150" spans="1:31" ht="12.75" hidden="1">
-      <c r="A150" s="87" t="s">
+      <c r="A150" s="85" t="s">
         <v>125</v>
       </c>
       <c r="B150" s="44" t="s">
@@ -15112,10 +15191,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D150" s="88">
+      <c r="D150" s="86">
         <v>3689</v>
       </c>
-      <c r="E150" s="88" t="s">
+      <c r="E150" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F150" s="46">
@@ -15129,7 +15208,7 @@
       <c r="H150" s="40">
         <v>7050</v>
       </c>
-      <c r="I150" s="86" t="s">
+      <c r="I150" s="84" t="s">
         <v>162</v>
       </c>
       <c r="J150" s="48">
@@ -15143,26 +15222,26 @@
       <c r="L150" s="55">
         <v>4890</v>
       </c>
-      <c r="M150" s="88"/>
+      <c r="M150" s="86"/>
       <c r="N150" s="48"/>
-      <c r="O150" s="88"/>
-      <c r="P150" s="88"/>
-      <c r="Q150" s="89">
+      <c r="O150" s="86"/>
+      <c r="P150" s="86"/>
+      <c r="Q150" s="87">
         <v>1</v>
       </c>
-      <c r="R150" s="89" t="s">
+      <c r="R150" s="87" t="s">
         <v>52</v>
       </c>
       <c r="S150" s="48">
         <v>325</v>
       </c>
-      <c r="T150" s="90" t="s">
+      <c r="T150" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U150" s="90">
-        <v>0</v>
-      </c>
-      <c r="V150" s="91" t="s">
+      <c r="U150" s="88">
+        <v>0</v>
+      </c>
+      <c r="V150" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X150" s="48"/>
@@ -15174,7 +15253,7 @@
       <c r="AD150" s="7"/>
     </row>
     <row r="151" spans="1:31" ht="12.75" hidden="1">
-      <c r="A151" s="87" t="s">
+      <c r="A151" s="85" t="s">
         <v>127</v>
       </c>
       <c r="B151" s="44" t="s">
@@ -15184,10 +15263,10 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D151" s="88">
+      <c r="D151" s="86">
         <v>4679</v>
       </c>
-      <c r="E151" s="88" t="s">
+      <c r="E151" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F151" s="46">
@@ -15201,7 +15280,7 @@
       <c r="H151" s="40">
         <v>8350</v>
       </c>
-      <c r="I151" s="86" t="s">
+      <c r="I151" s="84" t="s">
         <v>162</v>
       </c>
       <c r="J151" s="48">
@@ -15215,26 +15294,26 @@
       <c r="L151" s="55">
         <v>5690</v>
       </c>
-      <c r="M151" s="88"/>
+      <c r="M151" s="86"/>
       <c r="N151" s="48"/>
-      <c r="O151" s="88"/>
-      <c r="P151" s="88"/>
-      <c r="Q151" s="89">
+      <c r="O151" s="86"/>
+      <c r="P151" s="86"/>
+      <c r="Q151" s="87">
         <v>1</v>
       </c>
-      <c r="R151" s="89" t="s">
+      <c r="R151" s="87" t="s">
         <v>52</v>
       </c>
       <c r="S151" s="48">
         <v>325</v>
       </c>
-      <c r="T151" s="90" t="s">
+      <c r="T151" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U151" s="90">
-        <v>0</v>
-      </c>
-      <c r="V151" s="91" t="s">
+      <c r="U151" s="88">
+        <v>0</v>
+      </c>
+      <c r="V151" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X151" s="48"/>
@@ -15245,69 +15324,73 @@
       <c r="AC151" s="48"/>
       <c r="AD151" s="7"/>
     </row>
-    <row r="152" spans="1:31" ht="12.75">
-      <c r="A152" s="93" t="s">
-        <v>59</v>
-      </c>
-      <c r="B152" s="44" t="s">
-        <v>60</v>
+    <row r="152" spans="1:31" ht="12.75" hidden="1">
+      <c r="A152" s="119" t="s">
+        <v>648</v>
+      </c>
+      <c r="B152" s="127" t="s">
+        <v>649</v>
       </c>
       <c r="C152" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
-      </c>
-      <c r="D152" s="94">
-        <v>4679</v>
-      </c>
-      <c r="E152" s="94" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D152" s="92">
+        <v>3689</v>
+      </c>
+      <c r="E152" s="92" t="s">
         <v>10</v>
       </c>
       <c r="F152" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
-      </c>
-      <c r="G152" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
+        <v>326.5</v>
+      </c>
+      <c r="G152" s="125">
+        <v>3362.5</v>
       </c>
       <c r="H152" s="52">
-        <v>8350</v>
-      </c>
-      <c r="I152" s="95" t="s">
-        <v>156</v>
+        <v>7050</v>
+      </c>
+      <c r="I152" s="122" t="s">
+        <v>152</v>
       </c>
       <c r="J152" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>500</v>
+        <v>1030</v>
       </c>
       <c r="K152" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3512.5</v>
+        <v>2332.5</v>
       </c>
       <c r="L152" s="52">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>7350</v>
-      </c>
-      <c r="M152" s="94"/>
-      <c r="N152" s="94"/>
-      <c r="O152" s="94"/>
-      <c r="P152" s="94"/>
-      <c r="Q152" s="96">
+        <v>4990</v>
+      </c>
+      <c r="M152" s="92"/>
+      <c r="N152" s="121">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O152" s="121">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P152" s="92"/>
+      <c r="Q152" s="94">
         <v>1</v>
       </c>
       <c r="R152" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="S152" s="48">
+      <c r="S152" s="49">
         <v>325</v>
       </c>
-      <c r="T152" s="98" t="s">
+      <c r="T152" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="U152" s="98">
-        <v>0</v>
-      </c>
-      <c r="V152" s="104" t="s">
+      <c r="U152" s="96">
+        <v>0</v>
+      </c>
+      <c r="V152" s="102" t="s">
         <v>56</v>
       </c>
       <c r="X152" s="48"/>
@@ -15534,68 +15617,73 @@
       <c r="AD155"/>
       <c r="AE155"/>
     </row>
-    <row r="156" spans="1:31" ht="12.75">
-      <c r="A156" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B156" s="44" t="s">
-        <v>60</v>
+    <row r="156" spans="1:31" ht="12.75" hidden="1">
+      <c r="A156" s="126" t="s">
+        <v>648</v>
+      </c>
+      <c r="B156" s="128" t="s">
+        <v>649</v>
       </c>
       <c r="C156" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
-      </c>
-      <c r="D156" s="46">
-        <v>4679</v>
-      </c>
-      <c r="E156" s="46" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D156" s="48">
+        <v>3689</v>
+      </c>
+      <c r="E156" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F156" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
-      </c>
-      <c r="G156" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
+        <v>326.5</v>
+      </c>
+      <c r="G156" s="125">
+        <v>3362.5</v>
       </c>
       <c r="H156" s="52">
-        <v>8350</v>
-      </c>
-      <c r="I156" s="61" t="s">
-        <v>159</v>
+        <v>7050</v>
+      </c>
+      <c r="I156" s="83" t="s">
+        <v>153</v>
       </c>
       <c r="J156" s="48">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>875</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
       </c>
       <c r="K156" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3137.5</v>
+        <v>2332.5</v>
       </c>
       <c r="L156" s="52">
-        <v>6600</v>
-      </c>
-      <c r="M156" s="61"/>
-      <c r="N156" s="48"/>
-      <c r="O156" s="84"/>
-      <c r="P156" s="46"/>
-      <c r="Q156" s="85">
+        <v>4990</v>
+      </c>
+      <c r="M156" s="48"/>
+      <c r="N156" s="125">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O156" s="125">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P156" s="48"/>
+      <c r="Q156" s="49">
         <v>1</v>
       </c>
-      <c r="R156" s="46" t="s">
+      <c r="R156" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="S156" s="48">
+      <c r="S156" s="49">
         <v>325</v>
       </c>
-      <c r="T156" s="82" t="s">
+      <c r="T156" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="U156" s="16">
-        <v>0</v>
-      </c>
-      <c r="V156" s="58" t="s">
+      <c r="U156" s="51">
+        <v>0</v>
+      </c>
+      <c r="V156" s="51" t="s">
         <v>56</v>
       </c>
       <c r="Y156" s="16"/>
@@ -15770,21 +15858,19 @@
       </c>
       <c r="F159" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>4841.5</v>
       </c>
       <c r="G159" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H159" s="52">
-        <v>8350</v>
-      </c>
+        <v>-162.5</v>
+      </c>
+      <c r="H159" s="52"/>
       <c r="I159" s="61" t="s">
         <v>164</v>
       </c>
       <c r="J159" s="48">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1330</v>
+        <v>-2845</v>
       </c>
       <c r="K159" s="48">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
@@ -15849,7 +15935,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3021.5</v>
       </c>
-      <c r="H160" s="39">
+      <c r="H160" s="52">
         <v>6268</v>
       </c>
       <c r="I160" s="47" t="s">
@@ -15880,7 +15966,7 @@
       <c r="Q160" s="49">
         <v>1</v>
       </c>
-      <c r="R160" s="97" t="s">
+      <c r="R160" s="95" t="s">
         <v>49</v>
       </c>
       <c r="S160" s="79">
@@ -15928,7 +16014,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3731.5</v>
       </c>
-      <c r="H161" s="39">
+      <c r="H161" s="52">
         <v>7788</v>
       </c>
       <c r="I161" s="47" t="s">
@@ -16007,7 +16093,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4661.5</v>
       </c>
-      <c r="H162" s="39">
+      <c r="H162" s="52">
         <v>9648</v>
       </c>
       <c r="I162" s="47" t="s">
@@ -16086,7 +16172,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>5741.5</v>
       </c>
-      <c r="H163" s="39">
+      <c r="H163" s="52">
         <v>11808</v>
       </c>
       <c r="I163" s="47" t="s">
@@ -16140,66 +16226,71 @@
       <c r="AC163" s="48"/>
       <c r="AD163" s="7"/>
     </row>
-    <row r="164" spans="1:30" ht="12.75">
-      <c r="A164" s="110" t="s">
+    <row r="164" spans="1:30" ht="12.75" hidden="1">
+      <c r="A164" s="113" t="s">
         <v>638</v>
       </c>
-      <c r="B164" s="111" t="s">
+      <c r="B164" s="114" t="s">
         <v>639</v>
       </c>
       <c r="C164" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D164" s="88"/>
-      <c r="E164" s="88" t="s">
+      <c r="D164" s="86"/>
+      <c r="E164" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F164" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-4662.5</v>
       </c>
       <c r="G164" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H164" s="108"/>
-      <c r="I164" s="86" t="s">
+        <v>4662.5</v>
+      </c>
+      <c r="H164" s="52">
+        <v>9650</v>
+      </c>
+      <c r="I164" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="J164" s="88">
-        <v>0</v>
-      </c>
-      <c r="K164" s="113">
+      <c r="J164" s="86">
+        <v>0</v>
+      </c>
+      <c r="K164" s="116">
         <v>4562.5</v>
       </c>
-      <c r="L164" s="109"/>
-      <c r="M164" s="88"/>
-      <c r="N164" s="113">
+      <c r="L164" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>9650</v>
+      </c>
+      <c r="M164" s="86"/>
+      <c r="N164" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O164" s="113">
+        <v>4662.5</v>
+      </c>
+      <c r="O164" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4725</v>
-      </c>
-      <c r="P164" s="88"/>
-      <c r="Q164" s="89">
+        <v>-100</v>
+      </c>
+      <c r="P164" s="86"/>
+      <c r="Q164" s="87">
         <v>1</v>
       </c>
-      <c r="R164" s="89" t="s">
+      <c r="R164" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S164" s="89">
+      <c r="S164" s="87">
         <v>325</v>
       </c>
-      <c r="T164" s="90" t="s">
+      <c r="T164" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U164" s="90">
-        <v>0</v>
-      </c>
-      <c r="V164" s="91" t="s">
+      <c r="U164" s="88">
+        <v>0</v>
+      </c>
+      <c r="V164" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X164" s="48"/>
@@ -16210,66 +16301,71 @@
       <c r="AC164" s="48"/>
       <c r="AD164" s="7"/>
     </row>
-    <row r="165" spans="1:30" ht="12.75">
-      <c r="A165" s="110" t="s">
+    <row r="165" spans="1:30" ht="12.75" hidden="1">
+      <c r="A165" s="113" t="s">
         <v>638</v>
       </c>
-      <c r="B165" s="112" t="s">
+      <c r="B165" s="114" t="s">
         <v>639</v>
       </c>
       <c r="C165" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D165" s="88"/>
-      <c r="E165" s="88" t="s">
+      <c r="D165" s="86"/>
+      <c r="E165" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F165" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-4662.5</v>
       </c>
       <c r="G165" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H165" s="108"/>
-      <c r="I165" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J165" s="88">
-        <v>0</v>
-      </c>
-      <c r="K165" s="113">
-        <v>4562.5</v>
-      </c>
-      <c r="L165" s="109"/>
-      <c r="M165" s="88"/>
-      <c r="N165" s="113">
+        <v>4662.5</v>
+      </c>
+      <c r="H165" s="52">
+        <v>9650</v>
+      </c>
+      <c r="I165" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="J165" s="86">
+        <v>500</v>
+      </c>
+      <c r="K165" s="116">
+        <v>4062.5</v>
+      </c>
+      <c r="L165" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>8650</v>
+      </c>
+      <c r="M165" s="86"/>
+      <c r="N165" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O165" s="113">
+        <v>4162.5</v>
+      </c>
+      <c r="O165" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4725</v>
-      </c>
-      <c r="P165" s="88"/>
-      <c r="Q165" s="89">
+        <v>-100</v>
+      </c>
+      <c r="P165" s="86"/>
+      <c r="Q165" s="87">
         <v>1</v>
       </c>
-      <c r="R165" s="89" t="s">
+      <c r="R165" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S165" s="89">
+      <c r="S165" s="87">
         <v>325</v>
       </c>
-      <c r="T165" s="90" t="s">
+      <c r="T165" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U165" s="90">
-        <v>0</v>
-      </c>
-      <c r="V165" s="91" t="s">
+      <c r="U165" s="88">
+        <v>0</v>
+      </c>
+      <c r="V165" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X165" s="48"/>
@@ -16278,68 +16374,70 @@
       <c r="AA165" s="48"/>
       <c r="AB165" s="48"/>
       <c r="AC165" s="48"/>
-      <c r="AD165" s="48"/>
-    </row>
-    <row r="166" spans="1:30" ht="12.75">
-      <c r="A166" s="110" t="s">
+      <c r="AD165" s="7"/>
+    </row>
+    <row r="166" spans="1:30" ht="12.75" hidden="1">
+      <c r="A166" s="113" t="s">
         <v>638</v>
       </c>
-      <c r="B166" s="111" t="s">
+      <c r="B166" s="115" t="s">
         <v>639</v>
       </c>
       <c r="C166" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D166" s="88"/>
-      <c r="E166" s="88" t="s">
+      <c r="D166" s="86"/>
+      <c r="E166" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F166" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-4662.5</v>
       </c>
       <c r="G166" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H166" s="108"/>
-      <c r="I166" s="86" t="s">
-        <v>640</v>
-      </c>
-      <c r="J166" s="88">
-        <v>750</v>
-      </c>
-      <c r="K166" s="113">
-        <v>3812.5</v>
+        <v>4662.5</v>
+      </c>
+      <c r="H166" s="52">
+        <v>9650</v>
+      </c>
+      <c r="I166" s="84" t="s">
+        <v>159</v>
+      </c>
+      <c r="J166" s="86">
+        <v>925</v>
+      </c>
+      <c r="K166" s="116">
+        <v>3637.5</v>
       </c>
       <c r="L166" s="109"/>
-      <c r="M166" s="88"/>
-      <c r="N166" s="113">
+      <c r="M166" s="84"/>
+      <c r="N166" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>-162.5</v>
       </c>
-      <c r="O166" s="113">
+      <c r="O166" s="117">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3975</v>
-      </c>
-      <c r="P166" s="88"/>
-      <c r="Q166" s="89">
+        <v>3800</v>
+      </c>
+      <c r="P166" s="86"/>
+      <c r="Q166" s="87">
         <v>1</v>
       </c>
-      <c r="R166" s="89" t="s">
+      <c r="R166" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S166" s="89">
+      <c r="S166" s="87">
         <v>325</v>
       </c>
-      <c r="T166" s="90" t="s">
+      <c r="T166" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U166" s="90">
-        <v>0</v>
-      </c>
-      <c r="V166" s="91" t="s">
+      <c r="U166" s="88">
+        <v>0</v>
+      </c>
+      <c r="V166" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X166" s="48"/>
@@ -16348,68 +16446,73 @@
       <c r="AA166" s="48"/>
       <c r="AB166" s="48"/>
       <c r="AC166" s="48"/>
-      <c r="AD166" s="48"/>
-    </row>
-    <row r="167" spans="1:30" ht="12.75">
-      <c r="A167" s="110" t="s">
-        <v>638</v>
-      </c>
-      <c r="B167" s="112" t="s">
-        <v>639</v>
+      <c r="AD166" s="7"/>
+    </row>
+    <row r="167" spans="1:30" ht="12.75" hidden="1">
+      <c r="A167" s="113" t="s">
+        <v>640</v>
+      </c>
+      <c r="B167" s="114" t="s">
+        <v>641</v>
       </c>
       <c r="C167" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D167" s="88"/>
-      <c r="E167" s="88" t="s">
+      <c r="D167" s="86"/>
+      <c r="E167" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F167" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-2512.5</v>
       </c>
       <c r="G167" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H167" s="108"/>
-      <c r="I167" s="86" t="s">
-        <v>141</v>
-      </c>
-      <c r="J167" s="88">
-        <v>0</v>
-      </c>
-      <c r="K167" s="113">
-        <v>4562.5</v>
-      </c>
-      <c r="L167" s="109"/>
-      <c r="M167" s="88"/>
-      <c r="N167" s="113">
+        <v>2512.5</v>
+      </c>
+      <c r="H167" s="52">
+        <v>5350</v>
+      </c>
+      <c r="I167" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="J167" s="86">
+        <v>0</v>
+      </c>
+      <c r="K167" s="116">
+        <v>2362.5</v>
+      </c>
+      <c r="L167" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>5350</v>
+      </c>
+      <c r="M167" s="86"/>
+      <c r="N167" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O167" s="113">
+        <v>2512.5</v>
+      </c>
+      <c r="O167" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4725</v>
-      </c>
-      <c r="P167" s="88"/>
-      <c r="Q167" s="89">
+        <v>-150</v>
+      </c>
+      <c r="P167" s="86"/>
+      <c r="Q167" s="87">
         <v>1</v>
       </c>
-      <c r="R167" s="89" t="s">
+      <c r="R167" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S167" s="89">
+      <c r="S167" s="87">
         <v>325</v>
       </c>
-      <c r="T167" s="90" t="s">
+      <c r="T167" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U167" s="90">
-        <v>0</v>
-      </c>
-      <c r="V167" s="91" t="s">
+      <c r="U167" s="88">
+        <v>0</v>
+      </c>
+      <c r="V167" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X167" s="48"/>
@@ -16418,68 +16521,73 @@
       <c r="AA167" s="48"/>
       <c r="AB167" s="48"/>
       <c r="AC167" s="48"/>
-      <c r="AD167" s="7"/>
-    </row>
-    <row r="168" spans="1:30" ht="12.75">
-      <c r="A168" s="110" t="s">
-        <v>638</v>
-      </c>
-      <c r="B168" s="111" t="s">
-        <v>639</v>
+      <c r="AD167" s="48"/>
+    </row>
+    <row r="168" spans="1:30" ht="12.75" hidden="1">
+      <c r="A168" s="113" t="s">
+        <v>642</v>
+      </c>
+      <c r="B168" s="114" t="s">
+        <v>643</v>
       </c>
       <c r="C168" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D168" s="88"/>
-      <c r="E168" s="88" t="s">
+      <c r="D168" s="86"/>
+      <c r="E168" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F168" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-3562.5</v>
       </c>
       <c r="G168" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H168" s="108"/>
-      <c r="I168" s="86" t="s">
-        <v>156</v>
-      </c>
-      <c r="J168" s="88">
-        <v>500</v>
-      </c>
-      <c r="K168" s="113">
-        <v>4062.5</v>
-      </c>
-      <c r="L168" s="109"/>
-      <c r="M168" s="88"/>
-      <c r="N168" s="113">
+        <v>3562.5</v>
+      </c>
+      <c r="H168" s="52">
+        <v>7450</v>
+      </c>
+      <c r="I168" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="J168" s="86">
+        <v>0</v>
+      </c>
+      <c r="K168" s="116">
+        <v>3362.5</v>
+      </c>
+      <c r="L168" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>7450</v>
+      </c>
+      <c r="M168" s="86"/>
+      <c r="N168" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O168" s="113">
+        <v>3562.5</v>
+      </c>
+      <c r="O168" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4225</v>
-      </c>
-      <c r="P168" s="88"/>
-      <c r="Q168" s="89">
+        <v>-200</v>
+      </c>
+      <c r="P168" s="86"/>
+      <c r="Q168" s="87">
         <v>1</v>
       </c>
-      <c r="R168" s="89" t="s">
+      <c r="R168" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S168" s="89">
+      <c r="S168" s="87">
         <v>325</v>
       </c>
-      <c r="T168" s="90" t="s">
+      <c r="T168" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U168" s="90">
-        <v>0</v>
-      </c>
-      <c r="V168" s="91" t="s">
+      <c r="U168" s="88">
+        <v>0</v>
+      </c>
+      <c r="V168" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X168" s="48"/>
@@ -16490,66 +16598,71 @@
       <c r="AC168" s="48"/>
       <c r="AD168" s="7"/>
     </row>
-    <row r="169" spans="1:30" ht="12.75">
-      <c r="A169" s="110" t="s">
-        <v>638</v>
-      </c>
-      <c r="B169" s="112" t="s">
-        <v>639</v>
+    <row r="169" spans="1:30" ht="12.75" hidden="1">
+      <c r="A169" s="113" t="s">
+        <v>642</v>
+      </c>
+      <c r="B169" s="114" t="s">
+        <v>643</v>
       </c>
       <c r="C169" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D169" s="88"/>
-      <c r="E169" s="88" t="s">
+      <c r="D169" s="86"/>
+      <c r="E169" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F169" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-3562.5</v>
       </c>
       <c r="G169" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H169" s="108"/>
-      <c r="I169" s="86" t="s">
-        <v>159</v>
-      </c>
-      <c r="J169" s="88">
-        <v>925</v>
-      </c>
-      <c r="K169" s="113">
-        <v>3637.5</v>
-      </c>
-      <c r="L169" s="109"/>
+        <v>3562.5</v>
+      </c>
+      <c r="H169" s="52">
+        <v>7450</v>
+      </c>
+      <c r="I169" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="J169" s="86">
+        <v>500</v>
+      </c>
+      <c r="K169" s="116">
+        <v>2862.5</v>
+      </c>
+      <c r="L169" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>6450</v>
+      </c>
       <c r="M169" s="86"/>
-      <c r="N169" s="113">
+      <c r="N169" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O169" s="114">
+        <v>3062.5</v>
+      </c>
+      <c r="O169" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3800</v>
-      </c>
-      <c r="P169" s="88"/>
-      <c r="Q169" s="89">
+        <v>-200</v>
+      </c>
+      <c r="P169" s="86"/>
+      <c r="Q169" s="87">
         <v>1</v>
       </c>
-      <c r="R169" s="89" t="s">
+      <c r="R169" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S169" s="89">
+      <c r="S169" s="87">
         <v>325</v>
       </c>
-      <c r="T169" s="90" t="s">
+      <c r="T169" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U169" s="90">
-        <v>0</v>
-      </c>
-      <c r="V169" s="91" t="s">
+      <c r="U169" s="88">
+        <v>0</v>
+      </c>
+      <c r="V169" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X169" s="48"/>
@@ -16558,68 +16671,70 @@
       <c r="AA169" s="48"/>
       <c r="AB169" s="48"/>
       <c r="AC169" s="48"/>
-      <c r="AD169" s="7"/>
-    </row>
-    <row r="170" spans="1:30" ht="12.75">
-      <c r="A170" s="110" t="s">
-        <v>641</v>
-      </c>
-      <c r="B170" s="111" t="s">
+      <c r="AD169" s="48"/>
+    </row>
+    <row r="170" spans="1:30" ht="12.75" hidden="1">
+      <c r="A170" s="113" t="s">
         <v>642</v>
+      </c>
+      <c r="B170" s="115" t="s">
+        <v>643</v>
       </c>
       <c r="C170" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D170" s="88"/>
-      <c r="E170" s="88" t="s">
+      <c r="D170" s="86"/>
+      <c r="E170" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F170" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-3562.5</v>
       </c>
       <c r="G170" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H170" s="108"/>
-      <c r="I170" s="86" t="s">
-        <v>45</v>
-      </c>
-      <c r="J170" s="88">
-        <v>0</v>
-      </c>
-      <c r="K170" s="113">
-        <v>2362.5</v>
+        <v>3562.5</v>
+      </c>
+      <c r="H170" s="52">
+        <v>7450</v>
+      </c>
+      <c r="I170" s="84" t="s">
+        <v>159</v>
+      </c>
+      <c r="J170" s="86">
+        <v>625</v>
+      </c>
+      <c r="K170" s="116">
+        <v>2737.5</v>
       </c>
       <c r="L170" s="109"/>
-      <c r="M170" s="88"/>
-      <c r="N170" s="113">
+      <c r="M170" s="84"/>
+      <c r="N170" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>-162.5</v>
       </c>
-      <c r="O170" s="113">
+      <c r="O170" s="117">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2525</v>
-      </c>
-      <c r="P170" s="88"/>
-      <c r="Q170" s="89">
+        <v>2900</v>
+      </c>
+      <c r="P170" s="86"/>
+      <c r="Q170" s="87">
         <v>1</v>
       </c>
-      <c r="R170" s="89" t="s">
+      <c r="R170" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S170" s="89">
+      <c r="S170" s="87">
         <v>325</v>
       </c>
-      <c r="T170" s="90" t="s">
+      <c r="T170" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U170" s="90">
-        <v>0</v>
-      </c>
-      <c r="V170" s="91" t="s">
+      <c r="U170" s="88">
+        <v>0</v>
+      </c>
+      <c r="V170" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X170" s="48"/>
@@ -16628,68 +16743,73 @@
       <c r="AA170" s="48"/>
       <c r="AB170" s="48"/>
       <c r="AC170" s="48"/>
-      <c r="AD170" s="48"/>
-    </row>
-    <row r="171" spans="1:30" ht="12.75">
-      <c r="A171" s="110" t="s">
-        <v>641</v>
-      </c>
-      <c r="B171" s="112" t="s">
-        <v>642</v>
+      <c r="AD170" s="46"/>
+    </row>
+    <row r="171" spans="1:30" ht="12.75" hidden="1">
+      <c r="A171" s="113" t="s">
+        <v>644</v>
+      </c>
+      <c r="B171" s="114" t="s">
+        <v>645</v>
       </c>
       <c r="C171" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D171" s="88"/>
-      <c r="E171" s="88" t="s">
+      <c r="D171" s="86"/>
+      <c r="E171" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F171" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-4112.5</v>
       </c>
       <c r="G171" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H171" s="108"/>
-      <c r="I171" s="86" t="s">
-        <v>141</v>
-      </c>
-      <c r="J171" s="88">
-        <v>0</v>
-      </c>
-      <c r="K171" s="113">
-        <v>2362.5</v>
-      </c>
-      <c r="L171" s="109"/>
-      <c r="M171" s="88"/>
-      <c r="N171" s="113">
+        <v>4112.5</v>
+      </c>
+      <c r="H171" s="52">
+        <v>8550</v>
+      </c>
+      <c r="I171" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="J171" s="86">
+        <v>0</v>
+      </c>
+      <c r="K171" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="L171" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>8550</v>
+      </c>
+      <c r="M171" s="86"/>
+      <c r="N171" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O171" s="113">
+        <v>4112.5</v>
+      </c>
+      <c r="O171" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2525</v>
-      </c>
-      <c r="P171" s="88"/>
-      <c r="Q171" s="89">
+        <v>-100</v>
+      </c>
+      <c r="P171" s="86"/>
+      <c r="Q171" s="87">
         <v>1</v>
       </c>
-      <c r="R171" s="89" t="s">
+      <c r="R171" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S171" s="89">
+      <c r="S171" s="87">
         <v>325</v>
       </c>
-      <c r="T171" s="90" t="s">
+      <c r="T171" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U171" s="90">
-        <v>0</v>
-      </c>
-      <c r="V171" s="91" t="s">
+      <c r="U171" s="88">
+        <v>0</v>
+      </c>
+      <c r="V171" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X171" s="48"/>
@@ -16698,68 +16818,73 @@
       <c r="AA171" s="48"/>
       <c r="AB171" s="48"/>
       <c r="AC171" s="48"/>
-      <c r="AD171" s="48"/>
-    </row>
-    <row r="172" spans="1:30" ht="12.75">
-      <c r="A172" s="110" t="s">
-        <v>643</v>
-      </c>
-      <c r="B172" s="111" t="s">
+      <c r="AD171" s="46"/>
+    </row>
+    <row r="172" spans="1:30" ht="12.75" hidden="1">
+      <c r="A172" s="113" t="s">
         <v>644</v>
+      </c>
+      <c r="B172" s="114" t="s">
+        <v>645</v>
       </c>
       <c r="C172" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D172" s="88"/>
-      <c r="E172" s="88" t="s">
+      <c r="D172" s="86"/>
+      <c r="E172" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F172" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-4112.5</v>
       </c>
       <c r="G172" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H172" s="108"/>
-      <c r="I172" s="86" t="s">
-        <v>45</v>
-      </c>
-      <c r="J172" s="88">
-        <v>0</v>
-      </c>
-      <c r="K172" s="113">
-        <v>3362.5</v>
-      </c>
-      <c r="L172" s="109"/>
-      <c r="M172" s="88"/>
-      <c r="N172" s="113">
+        <v>4112.5</v>
+      </c>
+      <c r="H172" s="52">
+        <v>8550</v>
+      </c>
+      <c r="I172" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="J172" s="86">
+        <v>500</v>
+      </c>
+      <c r="K172" s="116">
+        <v>3512.5</v>
+      </c>
+      <c r="L172" s="109">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>7550</v>
+      </c>
+      <c r="M172" s="86"/>
+      <c r="N172" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O172" s="113">
+        <v>3612.5</v>
+      </c>
+      <c r="O172" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3525</v>
-      </c>
-      <c r="P172" s="88"/>
-      <c r="Q172" s="89">
+        <v>-100</v>
+      </c>
+      <c r="P172" s="86"/>
+      <c r="Q172" s="87">
         <v>1</v>
       </c>
-      <c r="R172" s="89" t="s">
+      <c r="R172" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S172" s="89">
+      <c r="S172" s="87">
         <v>325</v>
       </c>
-      <c r="T172" s="90" t="s">
+      <c r="T172" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U172" s="90">
-        <v>0</v>
-      </c>
-      <c r="V172" s="91" t="s">
+      <c r="U172" s="88">
+        <v>0</v>
+      </c>
+      <c r="V172" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X172" s="48"/>
@@ -16768,68 +16893,70 @@
       <c r="AA172" s="48"/>
       <c r="AB172" s="48"/>
       <c r="AC172" s="48"/>
-      <c r="AD172" s="7"/>
-    </row>
-    <row r="173" spans="1:30" ht="12.75">
-      <c r="A173" s="110" t="s">
-        <v>643</v>
-      </c>
-      <c r="B173" s="112" t="s">
+      <c r="AD172" s="46"/>
+    </row>
+    <row r="173" spans="1:30" ht="12.75" hidden="1">
+      <c r="A173" s="119" t="s">
         <v>644</v>
+      </c>
+      <c r="B173" s="120" t="s">
+        <v>645</v>
       </c>
       <c r="C173" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>325</v>
       </c>
-      <c r="D173" s="88"/>
-      <c r="E173" s="88" t="s">
+      <c r="D173" s="92"/>
+      <c r="E173" s="92" t="s">
         <v>10</v>
       </c>
       <c r="F173" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
+        <v>-4112.5</v>
       </c>
       <c r="G173" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H173" s="108"/>
-      <c r="I173" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J173" s="88">
-        <v>0</v>
-      </c>
-      <c r="K173" s="113">
-        <v>3362.5</v>
-      </c>
-      <c r="L173" s="109"/>
-      <c r="M173" s="88"/>
-      <c r="N173" s="113">
+        <v>4112.5</v>
+      </c>
+      <c r="H173" s="52">
+        <v>8550</v>
+      </c>
+      <c r="I173" s="122" t="s">
+        <v>159</v>
+      </c>
+      <c r="J173" s="92">
+        <v>875</v>
+      </c>
+      <c r="K173" s="121">
+        <v>3137.5</v>
+      </c>
+      <c r="L173" s="123"/>
+      <c r="M173" s="122"/>
+      <c r="N173" s="121">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
         <v>-162.5</v>
       </c>
-      <c r="O173" s="113">
+      <c r="O173" s="124">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3525</v>
-      </c>
-      <c r="P173" s="88"/>
-      <c r="Q173" s="89">
+        <v>3300</v>
+      </c>
+      <c r="P173" s="92"/>
+      <c r="Q173" s="94">
         <v>1</v>
       </c>
-      <c r="R173" s="89" t="s">
+      <c r="R173" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="S173" s="89">
+      <c r="S173" s="94">
         <v>325</v>
       </c>
-      <c r="T173" s="90" t="s">
+      <c r="T173" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="U173" s="90">
-        <v>0</v>
-      </c>
-      <c r="V173" s="91" t="s">
+      <c r="U173" s="96">
+        <v>0</v>
+      </c>
+      <c r="V173" s="102" t="s">
         <v>56</v>
       </c>
       <c r="X173" s="48"/>
@@ -16838,68 +16965,75 @@
       <c r="AA173" s="48"/>
       <c r="AB173" s="48"/>
       <c r="AC173" s="48"/>
-      <c r="AD173" s="7"/>
-    </row>
-    <row r="174" spans="1:30" ht="12.75">
-      <c r="A174" s="110" t="s">
-        <v>643</v>
-      </c>
-      <c r="B174" s="111" t="s">
-        <v>644</v>
+      <c r="AD173" s="46"/>
+    </row>
+    <row r="174" spans="1:30" ht="12.75" hidden="1">
+      <c r="A174" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B174" s="115" t="s">
+        <v>649</v>
       </c>
       <c r="C174" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D174" s="88"/>
-      <c r="E174" s="88" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D174" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E174" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F174" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G174" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H174" s="108"/>
-      <c r="I174" s="86" t="s">
-        <v>645</v>
-      </c>
-      <c r="J174" s="88">
-        <v>700</v>
-      </c>
-      <c r="K174" s="113">
-        <v>2662.5</v>
-      </c>
-      <c r="L174" s="109"/>
-      <c r="M174" s="88"/>
-      <c r="N174" s="113">
+        <v>326.5</v>
+      </c>
+      <c r="G174" s="116">
+        <v>3362.5</v>
+      </c>
+      <c r="H174" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I174" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="J174" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
+      </c>
+      <c r="K174" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="L174" s="52">
+        <v>4990</v>
+      </c>
+      <c r="M174" s="86"/>
+      <c r="N174" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O174" s="113">
+        <v>2332.5</v>
+      </c>
+      <c r="O174" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2825</v>
-      </c>
-      <c r="P174" s="88"/>
-      <c r="Q174" s="89">
+        <v>0</v>
+      </c>
+      <c r="P174" s="86"/>
+      <c r="Q174" s="87">
         <v>1</v>
       </c>
-      <c r="R174" s="89" t="s">
+      <c r="R174" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S174" s="89">
+      <c r="S174" s="87">
         <v>325</v>
       </c>
-      <c r="T174" s="90" t="s">
+      <c r="T174" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U174" s="90">
-        <v>0</v>
-      </c>
-      <c r="V174" s="91" t="s">
+      <c r="U174" s="88">
+        <v>0</v>
+      </c>
+      <c r="V174" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X174" s="48"/>
@@ -16908,68 +17042,75 @@
       <c r="AA174" s="48"/>
       <c r="AB174" s="48"/>
       <c r="AC174" s="48"/>
-      <c r="AD174" s="7"/>
-    </row>
-    <row r="175" spans="1:30" ht="12.75">
-      <c r="A175" s="110" t="s">
-        <v>643</v>
-      </c>
-      <c r="B175" s="112" t="s">
-        <v>644</v>
+      <c r="AD174" s="46"/>
+    </row>
+    <row r="175" spans="1:30" ht="12.75" hidden="1">
+      <c r="A175" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B175" s="114" t="s">
+        <v>649</v>
       </c>
       <c r="C175" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D175" s="88"/>
-      <c r="E175" s="88" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D175" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E175" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F175" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G175" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H175" s="108"/>
-      <c r="I175" s="86" t="s">
-        <v>141</v>
-      </c>
-      <c r="J175" s="88">
-        <v>0</v>
-      </c>
-      <c r="K175" s="113">
+        <v>326.5</v>
+      </c>
+      <c r="G175" s="116">
         <v>3362.5</v>
       </c>
-      <c r="L175" s="109"/>
-      <c r="M175" s="88"/>
-      <c r="N175" s="113">
+      <c r="H175" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I175" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="J175" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
+      </c>
+      <c r="K175" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="L175" s="52">
+        <v>4990</v>
+      </c>
+      <c r="M175" s="86"/>
+      <c r="N175" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O175" s="113">
+        <v>2332.5</v>
+      </c>
+      <c r="O175" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3525</v>
-      </c>
-      <c r="P175" s="88"/>
-      <c r="Q175" s="89">
+        <v>0</v>
+      </c>
+      <c r="P175" s="86"/>
+      <c r="Q175" s="87">
         <v>1</v>
       </c>
-      <c r="R175" s="89" t="s">
+      <c r="R175" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S175" s="89">
+      <c r="S175" s="87">
         <v>325</v>
       </c>
-      <c r="T175" s="90" t="s">
+      <c r="T175" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U175" s="90">
-        <v>0</v>
-      </c>
-      <c r="V175" s="91" t="s">
+      <c r="U175" s="88">
+        <v>0</v>
+      </c>
+      <c r="V175" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X175" s="48"/>
@@ -16978,68 +17119,75 @@
       <c r="AA175" s="48"/>
       <c r="AB175" s="48"/>
       <c r="AC175" s="48"/>
-      <c r="AD175" s="48"/>
-    </row>
-    <row r="176" spans="1:30" ht="12.75">
-      <c r="A176" s="110" t="s">
-        <v>643</v>
-      </c>
-      <c r="B176" s="111" t="s">
-        <v>644</v>
+      <c r="AD175" s="7"/>
+    </row>
+    <row r="176" spans="1:30" ht="12.75" hidden="1">
+      <c r="A176" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B176" s="115" t="s">
+        <v>649</v>
       </c>
       <c r="C176" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D176" s="88"/>
-      <c r="E176" s="88" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D176" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E176" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F176" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G176" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H176" s="108"/>
-      <c r="I176" s="86" t="s">
-        <v>156</v>
-      </c>
-      <c r="J176" s="88">
-        <v>500</v>
-      </c>
-      <c r="K176" s="113">
-        <v>2862.5</v>
-      </c>
-      <c r="L176" s="109"/>
-      <c r="M176" s="88"/>
-      <c r="N176" s="113">
+        <v>326.5</v>
+      </c>
+      <c r="G176" s="116">
+        <v>3362.5</v>
+      </c>
+      <c r="H176" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I176" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="J176" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
+      </c>
+      <c r="K176" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="L176" s="52">
+        <v>4990</v>
+      </c>
+      <c r="M176" s="86"/>
+      <c r="N176" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O176" s="113">
+        <v>2332.5</v>
+      </c>
+      <c r="O176" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3025</v>
-      </c>
-      <c r="P176" s="88"/>
-      <c r="Q176" s="89">
+        <v>0</v>
+      </c>
+      <c r="P176" s="86"/>
+      <c r="Q176" s="87">
         <v>1</v>
       </c>
-      <c r="R176" s="89" t="s">
+      <c r="R176" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="S176" s="89">
+      <c r="S176" s="87">
         <v>325</v>
       </c>
-      <c r="T176" s="90" t="s">
+      <c r="T176" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U176" s="90">
-        <v>0</v>
-      </c>
-      <c r="V176" s="91" t="s">
+      <c r="U176" s="88">
+        <v>0</v>
+      </c>
+      <c r="V176" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X176" s="48"/>
@@ -17048,68 +17196,75 @@
       <c r="AA176" s="48"/>
       <c r="AB176" s="48"/>
       <c r="AC176" s="48"/>
-      <c r="AD176" s="48"/>
+      <c r="AD176" s="7"/>
     </row>
     <row r="177" spans="1:30" ht="12.75">
-      <c r="A177" s="110" t="s">
-        <v>643</v>
-      </c>
-      <c r="B177" s="112" t="s">
-        <v>644</v>
+      <c r="A177" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B177" s="115" t="s">
+        <v>48</v>
       </c>
       <c r="C177" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D177" s="88"/>
-      <c r="E177" s="88" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D177" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E177" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F177" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G177" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H177" s="108"/>
-      <c r="I177" s="86" t="s">
-        <v>159</v>
-      </c>
-      <c r="J177" s="88">
-        <v>625</v>
-      </c>
-      <c r="K177" s="113">
-        <v>2737.5</v>
-      </c>
-      <c r="L177" s="109"/>
+        <v>701.5</v>
+      </c>
+      <c r="G177" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H177" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I177" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="J177" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K177" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L177" s="52">
+        <v>3500</v>
+      </c>
       <c r="M177" s="86"/>
-      <c r="N177" s="113">
+      <c r="N177" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O177" s="114">
+        <v>1637.5</v>
+      </c>
+      <c r="O177" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2900</v>
-      </c>
-      <c r="P177" s="88"/>
-      <c r="Q177" s="89">
+        <v>0</v>
+      </c>
+      <c r="P177" s="86"/>
+      <c r="Q177" s="87">
         <v>1</v>
       </c>
-      <c r="R177" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="S177" s="89">
-        <v>325</v>
-      </c>
-      <c r="T177" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="U177" s="90">
-        <v>0</v>
-      </c>
-      <c r="V177" s="91" t="s">
+      <c r="R177" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S177" s="87">
+        <v>225</v>
+      </c>
+      <c r="T177" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U177" s="88">
+        <v>0</v>
+      </c>
+      <c r="V177" s="89" t="s">
         <v>56</v>
       </c>
       <c r="X177" s="48"/>
@@ -17118,539 +17273,910 @@
       <c r="AA177" s="48"/>
       <c r="AB177" s="48"/>
       <c r="AC177" s="48"/>
-      <c r="AD177" s="46"/>
+      <c r="AD177" s="7"/>
     </row>
     <row r="178" spans="1:30" ht="12.75">
-      <c r="A178" s="110" t="s">
-        <v>646</v>
-      </c>
-      <c r="B178" s="111" t="s">
-        <v>647</v>
+      <c r="A178" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B178" s="114" t="s">
+        <v>48</v>
       </c>
       <c r="C178" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D178" s="88"/>
-      <c r="E178" s="88" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D178" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E178" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F178" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G178" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H178" s="108"/>
-      <c r="I178" s="86" t="s">
-        <v>45</v>
-      </c>
-      <c r="J178" s="88">
-        <v>0</v>
-      </c>
-      <c r="K178" s="113">
-        <v>4012.5</v>
-      </c>
-      <c r="L178" s="109"/>
-      <c r="M178" s="88"/>
-      <c r="N178" s="113">
+        <v>701.5</v>
+      </c>
+      <c r="G178" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H178" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I178" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="J178" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K178" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L178" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M178" s="86"/>
+      <c r="N178" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O178" s="113">
+        <v>1637.5</v>
+      </c>
+      <c r="O178" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4175</v>
-      </c>
-      <c r="P178" s="88"/>
-      <c r="Q178" s="89">
+        <v>0</v>
+      </c>
+      <c r="P178" s="86"/>
+      <c r="Q178" s="87">
         <v>1</v>
       </c>
-      <c r="R178" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="S178" s="89">
-        <v>325</v>
-      </c>
-      <c r="T178" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="U178" s="90">
-        <v>0</v>
-      </c>
-      <c r="V178" s="91" t="s">
+      <c r="R178" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S178" s="87">
+        <v>225</v>
+      </c>
+      <c r="T178" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U178" s="88">
+        <v>0</v>
+      </c>
+      <c r="V178" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="X178" s="48"/>
-      <c r="Y178" s="48"/>
-      <c r="Z178" s="48"/>
-      <c r="AA178" s="48"/>
-      <c r="AB178" s="48"/>
-      <c r="AC178" s="48"/>
-      <c r="AD178" s="46"/>
+      <c r="X178" s="79"/>
+      <c r="Y178" s="79"/>
+      <c r="Z178" s="79"/>
+      <c r="AA178" s="79"/>
+      <c r="AB178" s="79"/>
+      <c r="AD178" s="16"/>
     </row>
     <row r="179" spans="1:30" ht="12.75">
-      <c r="A179" s="110" t="s">
-        <v>646</v>
-      </c>
-      <c r="B179" s="112" t="s">
-        <v>647</v>
+      <c r="A179" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B179" s="115" t="s">
+        <v>48</v>
       </c>
       <c r="C179" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D179" s="88"/>
-      <c r="E179" s="88" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D179" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E179" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F179" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G179" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H179" s="108"/>
-      <c r="I179" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="J179" s="88">
-        <v>0</v>
-      </c>
-      <c r="K179" s="113">
-        <v>4012.5</v>
-      </c>
-      <c r="L179" s="109"/>
-      <c r="M179" s="88"/>
-      <c r="N179" s="113">
+        <v>701.5</v>
+      </c>
+      <c r="G179" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H179" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I179" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="J179" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K179" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L179" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M179" s="86"/>
+      <c r="N179" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O179" s="113">
+        <v>1637.5</v>
+      </c>
+      <c r="O179" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4175</v>
-      </c>
-      <c r="P179" s="88"/>
-      <c r="Q179" s="89">
+        <v>0</v>
+      </c>
+      <c r="P179" s="86"/>
+      <c r="Q179" s="87">
         <v>1</v>
       </c>
-      <c r="R179" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="S179" s="89">
-        <v>325</v>
-      </c>
-      <c r="T179" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="U179" s="90">
-        <v>0</v>
-      </c>
-      <c r="V179" s="91" t="s">
+      <c r="R179" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S179" s="87">
+        <v>225</v>
+      </c>
+      <c r="T179" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U179" s="88">
+        <v>0</v>
+      </c>
+      <c r="V179" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="X179" s="48"/>
-      <c r="Y179" s="48"/>
-      <c r="Z179" s="48"/>
-      <c r="AA179" s="48"/>
-      <c r="AB179" s="48"/>
-      <c r="AC179" s="48"/>
+      <c r="X179" s="46"/>
+      <c r="Y179" s="46"/>
+      <c r="Z179" s="46"/>
+      <c r="AA179" s="46"/>
+      <c r="AB179" s="46"/>
+      <c r="AC179" s="46"/>
       <c r="AD179" s="46"/>
     </row>
     <row r="180" spans="1:30" ht="12.75">
-      <c r="A180" s="110" t="s">
-        <v>646</v>
-      </c>
-      <c r="B180" s="111" t="s">
-        <v>647</v>
+      <c r="A180" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B180" s="114" t="s">
+        <v>48</v>
       </c>
       <c r="C180" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D180" s="88"/>
-      <c r="E180" s="88" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D180" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E180" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F180" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G180" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H180" s="108"/>
-      <c r="I180" s="86" t="s">
-        <v>648</v>
-      </c>
-      <c r="J180" s="88">
-        <v>700</v>
-      </c>
-      <c r="K180" s="113">
-        <v>3312.5</v>
-      </c>
-      <c r="L180" s="109"/>
-      <c r="M180" s="88"/>
-      <c r="N180" s="113">
+        <v>701.5</v>
+      </c>
+      <c r="G180" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H180" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I180" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="J180" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K180" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L180" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M180" s="86"/>
+      <c r="N180" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O180" s="113">
+        <v>1637.5</v>
+      </c>
+      <c r="O180" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3475</v>
-      </c>
-      <c r="P180" s="88"/>
-      <c r="Q180" s="89">
+        <v>0</v>
+      </c>
+      <c r="P180" s="86"/>
+      <c r="Q180" s="87">
         <v>1</v>
       </c>
-      <c r="R180" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="S180" s="89">
-        <v>325</v>
-      </c>
-      <c r="T180" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="U180" s="90">
-        <v>0</v>
-      </c>
-      <c r="V180" s="91" t="s">
+      <c r="R180" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S180" s="87">
+        <v>225</v>
+      </c>
+      <c r="T180" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U180" s="88">
+        <v>0</v>
+      </c>
+      <c r="V180" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="X180" s="48"/>
-      <c r="Y180" s="48"/>
-      <c r="Z180" s="48"/>
-      <c r="AA180" s="48"/>
-      <c r="AB180" s="48"/>
-      <c r="AC180" s="48"/>
+      <c r="X180" s="46"/>
+      <c r="Y180" s="46"/>
+      <c r="Z180" s="46"/>
+      <c r="AA180" s="46"/>
+      <c r="AB180" s="46"/>
+      <c r="AC180" s="46"/>
       <c r="AD180" s="46"/>
     </row>
     <row r="181" spans="1:30" ht="12.75">
-      <c r="A181" s="110" t="s">
-        <v>646</v>
-      </c>
-      <c r="B181" s="112" t="s">
-        <v>647</v>
+      <c r="A181" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B181" s="115" t="s">
+        <v>48</v>
       </c>
       <c r="C181" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D181" s="88"/>
-      <c r="E181" s="88" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D181" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E181" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F181" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G181" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H181" s="108"/>
-      <c r="I181" s="86" t="s">
-        <v>141</v>
-      </c>
-      <c r="J181" s="88">
-        <v>0</v>
-      </c>
-      <c r="K181" s="113">
-        <v>4012.5</v>
-      </c>
-      <c r="L181" s="109"/>
-      <c r="M181" s="88"/>
-      <c r="N181" s="113">
+        <v>701.5</v>
+      </c>
+      <c r="G181" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H181" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I181" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="J181" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K181" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L181" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M181" s="86"/>
+      <c r="N181" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O181" s="113">
+        <v>1637.5</v>
+      </c>
+      <c r="O181" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>4175</v>
-      </c>
-      <c r="P181" s="88"/>
-      <c r="Q181" s="89">
+        <v>0</v>
+      </c>
+      <c r="P181" s="86"/>
+      <c r="Q181" s="87">
         <v>1</v>
       </c>
-      <c r="R181" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="S181" s="89">
-        <v>325</v>
-      </c>
-      <c r="T181" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="U181" s="90">
-        <v>0</v>
-      </c>
-      <c r="V181" s="91" t="s">
+      <c r="R181" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S181" s="87">
+        <v>225</v>
+      </c>
+      <c r="T181" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U181" s="88">
+        <v>0</v>
+      </c>
+      <c r="V181" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="X181" s="48"/>
-      <c r="Y181" s="48"/>
-      <c r="Z181" s="48"/>
-      <c r="AA181" s="48"/>
-      <c r="AB181" s="48"/>
-      <c r="AC181" s="48"/>
+      <c r="X181" s="46"/>
+      <c r="Y181" s="46"/>
+      <c r="Z181" s="46"/>
+      <c r="AA181" s="46"/>
+      <c r="AB181" s="46"/>
+      <c r="AC181" s="46"/>
       <c r="AD181" s="46"/>
     </row>
     <row r="182" spans="1:30" ht="12.75">
-      <c r="A182" s="110" t="s">
-        <v>646</v>
-      </c>
-      <c r="B182" s="111" t="s">
-        <v>647</v>
+      <c r="A182" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B182" s="114" t="s">
+        <v>48</v>
       </c>
       <c r="C182" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D182" s="88"/>
-      <c r="E182" s="88" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D182" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E182" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F182" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G182" s="46">
-        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H182" s="108"/>
-      <c r="I182" s="86" t="s">
-        <v>156</v>
-      </c>
-      <c r="J182" s="88">
-        <v>500</v>
-      </c>
-      <c r="K182" s="113">
-        <v>3512.5</v>
-      </c>
-      <c r="L182" s="109"/>
-      <c r="M182" s="88"/>
-      <c r="N182" s="113">
+        <v>701.5</v>
+      </c>
+      <c r="G182" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H182" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I182" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="J182" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K182" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L182" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M182" s="86"/>
+      <c r="N182" s="116">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O182" s="113">
+        <v>1637.5</v>
+      </c>
+      <c r="O182" s="116">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3675</v>
-      </c>
-      <c r="P182" s="88"/>
-      <c r="Q182" s="89">
+        <v>0</v>
+      </c>
+      <c r="P182" s="86"/>
+      <c r="Q182" s="87">
         <v>1</v>
       </c>
-      <c r="R182" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="S182" s="89">
-        <v>325</v>
-      </c>
-      <c r="T182" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="U182" s="90">
-        <v>0</v>
-      </c>
-      <c r="V182" s="91" t="s">
+      <c r="R182" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S182" s="87">
+        <v>225</v>
+      </c>
+      <c r="T182" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U182" s="88">
+        <v>0</v>
+      </c>
+      <c r="V182" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="X182" s="48"/>
-      <c r="Y182" s="48"/>
-      <c r="Z182" s="48"/>
-      <c r="AA182" s="48"/>
-      <c r="AB182" s="48"/>
-      <c r="AC182" s="48"/>
+      <c r="X182" s="46"/>
+      <c r="Y182" s="46"/>
+      <c r="Z182" s="46"/>
+      <c r="AA182" s="46"/>
+      <c r="AB182" s="46"/>
+      <c r="AC182" s="46"/>
       <c r="AD182" s="46"/>
     </row>
     <row r="183" spans="1:30" ht="12.75">
-      <c r="A183" s="115" t="s">
-        <v>646</v>
-      </c>
-      <c r="B183" s="116" t="s">
-        <v>647</v>
+      <c r="A183" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B183" s="115" t="s">
+        <v>48</v>
       </c>
       <c r="C183" s="45">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>325</v>
-      </c>
-      <c r="D183" s="94"/>
-      <c r="E183" s="94" t="s">
+        <v>4903</v>
+      </c>
+      <c r="D183" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E183" s="86" t="s">
         <v>10</v>
       </c>
       <c r="F183" s="46">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>162.5</v>
-      </c>
-      <c r="G183" s="46">
+        <v>701.5</v>
+      </c>
+      <c r="G183" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H183" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I183" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="J183" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K183" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L183" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M183" s="86"/>
+      <c r="N183" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="O183" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P183" s="86"/>
+      <c r="Q183" s="87">
+        <v>1</v>
+      </c>
+      <c r="R183" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S183" s="87">
+        <v>225</v>
+      </c>
+      <c r="T183" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U183" s="88">
+        <v>0</v>
+      </c>
+      <c r="V183" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="X183" s="46"/>
+      <c r="Y183" s="46"/>
+      <c r="Z183" s="46"/>
+      <c r="AA183" s="46"/>
+      <c r="AB183" s="46"/>
+      <c r="AC183" s="46"/>
+      <c r="AD183" s="46"/>
+    </row>
+    <row r="184" spans="1:30" ht="12.75">
+      <c r="A184" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B184" s="114" t="s">
+        <v>48</v>
+      </c>
+      <c r="C184" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>4903</v>
+      </c>
+      <c r="D184" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E184" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>701.5</v>
+      </c>
+      <c r="G184" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H184" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I184" s="84" t="s">
+        <v>162</v>
+      </c>
+      <c r="J184" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K184" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L184" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M184" s="86"/>
+      <c r="N184" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="O184" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P184" s="86"/>
+      <c r="Q184" s="87">
+        <v>1</v>
+      </c>
+      <c r="R184" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S184" s="87">
+        <v>225</v>
+      </c>
+      <c r="T184" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U184" s="88">
+        <v>0</v>
+      </c>
+      <c r="V184" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="X184" s="46"/>
+      <c r="Y184" s="46"/>
+      <c r="Z184" s="46"/>
+      <c r="AA184" s="46"/>
+      <c r="AB184" s="46"/>
+      <c r="AC184" s="46"/>
+      <c r="AD184" s="46"/>
+    </row>
+    <row r="185" spans="1:30" ht="12.75" hidden="1">
+      <c r="A185" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B185" s="114" t="s">
+        <v>649</v>
+      </c>
+      <c r="C185" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D185" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E185" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G185" s="116">
+        <v>3362.5</v>
+      </c>
+      <c r="H185" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I185" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="J185" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
+      </c>
+      <c r="K185" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="L185" s="52">
+        <v>4990</v>
+      </c>
+      <c r="M185" s="86"/>
+      <c r="N185" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O185" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P185" s="86"/>
+      <c r="Q185" s="87">
+        <v>1</v>
+      </c>
+      <c r="R185" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S185" s="87">
+        <v>325</v>
+      </c>
+      <c r="T185" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U185" s="88">
+        <v>0</v>
+      </c>
+      <c r="V185" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="X185" s="46"/>
+      <c r="Y185" s="46"/>
+      <c r="Z185" s="46"/>
+      <c r="AA185" s="46"/>
+      <c r="AB185" s="46"/>
+      <c r="AC185" s="46"/>
+      <c r="AD185" s="46"/>
+    </row>
+    <row r="186" spans="1:30" ht="12.75" hidden="1">
+      <c r="A186" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B186" s="115" t="s">
+        <v>649</v>
+      </c>
+      <c r="C186" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D186" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E186" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G186" s="116">
+        <v>3362.5</v>
+      </c>
+      <c r="H186" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I186" s="84" t="s">
+        <v>162</v>
+      </c>
+      <c r="J186" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
+      </c>
+      <c r="K186" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="L186" s="52">
+        <v>4990</v>
+      </c>
+      <c r="M186" s="86"/>
+      <c r="N186" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O186" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P186" s="86"/>
+      <c r="Q186" s="87">
+        <v>1</v>
+      </c>
+      <c r="R186" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S186" s="87">
+        <v>325</v>
+      </c>
+      <c r="T186" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U186" s="88">
+        <v>0</v>
+      </c>
+      <c r="V186" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="X186" s="46"/>
+      <c r="Y186" s="46"/>
+      <c r="Z186" s="46"/>
+      <c r="AA186" s="46"/>
+      <c r="AB186" s="46"/>
+      <c r="AC186" s="46"/>
+      <c r="AD186" s="46"/>
+    </row>
+    <row r="187" spans="1:30" ht="12.75" hidden="1">
+      <c r="A187" s="113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B187" s="114" t="s">
+        <v>649</v>
+      </c>
+      <c r="C187" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D187" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E187" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F187" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G187" s="116">
+        <v>3362.5</v>
+      </c>
+      <c r="H187" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I187" s="84" t="s">
+        <v>164</v>
+      </c>
+      <c r="J187" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
+      </c>
+      <c r="K187" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="L187" s="52">
+        <v>4990</v>
+      </c>
+      <c r="M187" s="86"/>
+      <c r="N187" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O187" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P187" s="86"/>
+      <c r="Q187" s="87">
+        <v>1</v>
+      </c>
+      <c r="R187" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S187" s="87">
+        <v>325</v>
+      </c>
+      <c r="T187" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U187" s="88">
+        <v>0</v>
+      </c>
+      <c r="V187" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="X187" s="46"/>
+      <c r="Y187" s="46"/>
+      <c r="Z187" s="46"/>
+      <c r="AA187" s="46"/>
+      <c r="AB187" s="46"/>
+      <c r="AC187" s="46"/>
+      <c r="AD187" s="46"/>
+    </row>
+    <row r="188" spans="1:30" ht="12.75" hidden="1">
+      <c r="A188" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B188" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C188" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D188" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E188" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G188" s="86">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="H183" s="118"/>
-      <c r="I183" s="119" t="s">
-        <v>159</v>
-      </c>
-      <c r="J183" s="94">
-        <v>875</v>
-      </c>
-      <c r="K183" s="117">
-        <v>3137.5</v>
-      </c>
-      <c r="L183" s="120"/>
-      <c r="M183" s="119"/>
-      <c r="N183" s="117">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>-162.5</v>
-      </c>
-      <c r="O183" s="121">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3300</v>
-      </c>
-      <c r="P183" s="94"/>
-      <c r="Q183" s="96">
+        <v>3362.5</v>
+      </c>
+      <c r="H188" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I188" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="J188" s="48">
+        <v>0</v>
+      </c>
+      <c r="K188" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="L188" s="52"/>
+      <c r="M188" s="86"/>
+      <c r="N188" s="86"/>
+      <c r="O188" s="86"/>
+      <c r="P188" s="86"/>
+      <c r="Q188" s="87">
         <v>1</v>
       </c>
-      <c r="R183" s="96" t="s">
+      <c r="R188" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="S183" s="96">
+      <c r="S188" s="86">
         <v>325</v>
       </c>
-      <c r="T183" s="98" t="s">
+      <c r="T188" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="U183" s="98">
-        <v>0</v>
-      </c>
-      <c r="V183" s="104" t="s">
+      <c r="U188" s="88">
+        <v>0</v>
+      </c>
+      <c r="V188" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="X183" s="48"/>
-      <c r="Y183" s="48"/>
-      <c r="Z183" s="48"/>
-      <c r="AA183" s="48"/>
-      <c r="AB183" s="48"/>
-      <c r="AC183" s="48"/>
-      <c r="AD183" s="46"/>
-    </row>
-    <row r="184" spans="1:30" ht="12.75">
-      <c r="A184" s="44"/>
-      <c r="B184" s="44"/>
-      <c r="C184" s="44"/>
-      <c r="I184" s="46"/>
-      <c r="J184" s="46"/>
-      <c r="K184" s="46"/>
-      <c r="M184" s="48"/>
-      <c r="N184" s="48"/>
-      <c r="O184" s="48"/>
-      <c r="Q184" s="61"/>
-      <c r="U184" s="48"/>
-      <c r="X184" s="48"/>
-      <c r="Y184" s="48"/>
-      <c r="Z184" s="48"/>
-      <c r="AA184" s="48"/>
-      <c r="AB184" s="48"/>
-      <c r="AC184" s="48"/>
-      <c r="AD184" s="46"/>
-    </row>
-    <row r="185" spans="1:30" ht="12.75">
-      <c r="A185" s="44"/>
-      <c r="B185" s="44"/>
-      <c r="C185" s="44"/>
-      <c r="I185" s="46"/>
-      <c r="J185" s="46"/>
-      <c r="K185" s="46"/>
-      <c r="M185" s="79"/>
-      <c r="N185" s="48"/>
-      <c r="O185" s="48"/>
-      <c r="Q185" s="61"/>
-      <c r="U185" s="48"/>
-      <c r="X185" s="48"/>
-      <c r="Y185" s="48"/>
-      <c r="Z185" s="48"/>
-      <c r="AA185" s="48"/>
-      <c r="AB185" s="48"/>
-      <c r="AC185" s="48"/>
-      <c r="AD185" s="7"/>
-    </row>
-    <row r="186" spans="1:30" ht="12.75">
-      <c r="A186" s="44"/>
-      <c r="B186" s="44"/>
-      <c r="C186" s="44"/>
-      <c r="I186" s="46"/>
-      <c r="J186" s="46"/>
-      <c r="K186" s="46"/>
-      <c r="M186" s="46"/>
-      <c r="N186" s="48"/>
-      <c r="O186" s="48"/>
-      <c r="Q186" s="61"/>
-      <c r="U186" s="48"/>
-      <c r="X186" s="48"/>
-      <c r="Y186" s="48"/>
-      <c r="Z186" s="48"/>
-      <c r="AA186" s="48"/>
-      <c r="AB186" s="48"/>
-      <c r="AC186" s="48"/>
-      <c r="AD186" s="7"/>
-    </row>
-    <row r="187" spans="1:30" ht="12.75">
-      <c r="A187" s="44"/>
-      <c r="B187" s="44"/>
-      <c r="C187" s="44"/>
-      <c r="I187" s="46"/>
-      <c r="J187" s="46"/>
-      <c r="K187" s="46"/>
-      <c r="M187" s="46"/>
-      <c r="N187" s="48"/>
-      <c r="O187" s="48"/>
-      <c r="Q187" s="61"/>
-      <c r="U187" s="48"/>
-      <c r="X187" s="48"/>
-      <c r="Y187" s="48"/>
-      <c r="Z187" s="48"/>
-      <c r="AA187" s="48"/>
-      <c r="AB187" s="48"/>
-      <c r="AC187" s="48"/>
-      <c r="AD187" s="7"/>
-    </row>
-    <row r="188" spans="1:30" ht="12.75">
-      <c r="A188" s="44"/>
-      <c r="B188" s="44"/>
-      <c r="C188" s="44"/>
-      <c r="I188" s="46"/>
-      <c r="J188" s="46"/>
-      <c r="K188" s="46"/>
-      <c r="M188" s="46"/>
-      <c r="N188" s="48"/>
-      <c r="O188" s="48"/>
-      <c r="Q188" s="61"/>
-      <c r="U188" s="48"/>
-      <c r="X188" s="79"/>
-      <c r="Y188" s="79"/>
-      <c r="Z188" s="79"/>
-      <c r="AA188" s="79"/>
-      <c r="AB188" s="79"/>
-      <c r="AD188" s="16"/>
-    </row>
-    <row r="189" spans="1:30" ht="12.75">
-      <c r="A189" s="44"/>
-      <c r="B189" s="44"/>
-      <c r="C189" s="44"/>
-      <c r="I189" s="46"/>
-      <c r="J189" s="46"/>
-      <c r="K189" s="46"/>
-      <c r="M189" s="46"/>
-      <c r="N189" s="48"/>
-      <c r="O189" s="48"/>
-      <c r="Q189" s="61"/>
-      <c r="U189" s="48"/>
+      <c r="X188" s="46"/>
+      <c r="Y188" s="46"/>
+      <c r="Z188" s="46"/>
+      <c r="AA188" s="46"/>
+      <c r="AB188" s="46"/>
+      <c r="AC188" s="46"/>
+      <c r="AD188" s="46"/>
+    </row>
+    <row r="189" spans="1:30" ht="12.75" hidden="1">
+      <c r="A189" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B189" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C189" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D189" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E189" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F189" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G189" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="H189" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I189" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="J189" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K189" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="L189" s="52">
+        <v>7050</v>
+      </c>
+      <c r="M189" s="86"/>
+      <c r="N189" s="86"/>
+      <c r="O189" s="86"/>
+      <c r="P189" s="86"/>
+      <c r="Q189" s="87">
+        <v>1</v>
+      </c>
+      <c r="R189" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S189" s="86">
+        <v>325</v>
+      </c>
+      <c r="T189" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="U189" s="86">
+        <v>0</v>
+      </c>
+      <c r="V189" s="59" t="s">
+        <v>56</v>
+      </c>
       <c r="X189" s="46"/>
       <c r="Y189" s="46"/>
       <c r="Z189" s="46"/>
@@ -17659,18 +18185,70 @@
       <c r="AC189" s="46"/>
       <c r="AD189" s="46"/>
     </row>
-    <row r="190" spans="1:30" ht="12.75">
-      <c r="A190" s="44"/>
-      <c r="B190" s="44"/>
-      <c r="C190" s="44"/>
-      <c r="I190" s="46"/>
-      <c r="J190" s="46"/>
-      <c r="K190" s="46"/>
-      <c r="M190" s="46"/>
-      <c r="N190" s="48"/>
-      <c r="O190" s="48"/>
-      <c r="Q190" s="61"/>
-      <c r="U190" s="48"/>
+    <row r="190" spans="1:30" ht="12.75" hidden="1">
+      <c r="A190" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B190" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C190" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D190" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E190" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F190" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G190" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="H190" s="40">
+        <v>7050</v>
+      </c>
+      <c r="I190" s="84" t="s">
+        <v>137</v>
+      </c>
+      <c r="J190" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>700</v>
+      </c>
+      <c r="K190" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2662.5</v>
+      </c>
+      <c r="L190" s="55">
+        <v>5650</v>
+      </c>
+      <c r="M190" s="86"/>
+      <c r="N190" s="86"/>
+      <c r="O190" s="86"/>
+      <c r="P190" s="86"/>
+      <c r="Q190" s="87">
+        <v>1</v>
+      </c>
+      <c r="R190" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S190" s="107">
+        <v>325</v>
+      </c>
+      <c r="T190" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U190" s="88">
+        <v>0</v>
+      </c>
+      <c r="V190" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X190" s="46"/>
       <c r="Y190" s="46"/>
       <c r="Z190" s="46"/>
@@ -17680,17 +18258,74 @@
       <c r="AD190" s="46"/>
     </row>
     <row r="191" spans="1:30" ht="12.75">
-      <c r="A191" s="44"/>
-      <c r="B191" s="44"/>
-      <c r="C191" s="44"/>
-      <c r="I191" s="79"/>
-      <c r="J191" s="79"/>
-      <c r="K191" s="79"/>
-      <c r="M191" s="46"/>
-      <c r="N191" s="79"/>
-      <c r="O191" s="79"/>
-      <c r="Q191" s="61"/>
-      <c r="U191" s="79"/>
+      <c r="A191" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B191" s="115" t="s">
+        <v>48</v>
+      </c>
+      <c r="C191" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>4903</v>
+      </c>
+      <c r="D191" s="86">
+        <v>2339</v>
+      </c>
+      <c r="E191" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>701.5</v>
+      </c>
+      <c r="G191" s="116">
+        <v>1637.5</v>
+      </c>
+      <c r="H191" s="53">
+        <v>3500</v>
+      </c>
+      <c r="I191" s="84" t="s">
+        <v>164</v>
+      </c>
+      <c r="J191" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K191" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="L191" s="52">
+        <v>3500</v>
+      </c>
+      <c r="M191" s="86"/>
+      <c r="N191" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>1637.5</v>
+      </c>
+      <c r="O191" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P191" s="86"/>
+      <c r="Q191" s="87">
+        <v>1</v>
+      </c>
+      <c r="R191" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="S191" s="87">
+        <v>225</v>
+      </c>
+      <c r="T191" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="U191" s="88">
+        <v>0</v>
+      </c>
+      <c r="V191" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X191" s="46"/>
       <c r="Y191" s="46"/>
       <c r="Z191" s="46"/>
@@ -17699,18 +18334,70 @@
       <c r="AC191" s="46"/>
       <c r="AD191" s="46"/>
     </row>
-    <row r="192" spans="1:30" ht="12.75">
-      <c r="A192" s="44"/>
-      <c r="B192" s="44"/>
-      <c r="C192" s="44"/>
-      <c r="I192" s="46"/>
-      <c r="J192" s="46"/>
-      <c r="K192" s="46"/>
-      <c r="M192" s="46"/>
-      <c r="N192" s="46"/>
-      <c r="O192" s="46"/>
-      <c r="Q192" s="61"/>
-      <c r="U192" s="46"/>
+    <row r="192" spans="1:30" ht="12.75" hidden="1">
+      <c r="A192" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B192" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C192" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D192" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E192" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G192" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="H192" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I192" s="90" t="s">
+        <v>141</v>
+      </c>
+      <c r="J192" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K192" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="L192" s="52">
+        <v>7050</v>
+      </c>
+      <c r="M192" s="86"/>
+      <c r="N192" s="86"/>
+      <c r="O192" s="86"/>
+      <c r="P192" s="86"/>
+      <c r="Q192" s="87">
+        <v>1</v>
+      </c>
+      <c r="R192" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S192" s="86">
+        <v>325</v>
+      </c>
+      <c r="T192" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U192" s="88">
+        <v>0</v>
+      </c>
+      <c r="V192" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X192" s="46"/>
       <c r="Y192" s="46"/>
       <c r="Z192" s="46"/>
@@ -17719,18 +18406,71 @@
       <c r="AC192" s="46"/>
       <c r="AD192" s="46"/>
     </row>
-    <row r="193" spans="1:30" ht="12.75">
-      <c r="A193" s="44"/>
-      <c r="B193" s="44"/>
-      <c r="C193" s="44"/>
-      <c r="I193" s="46"/>
-      <c r="J193" s="46"/>
-      <c r="K193" s="46"/>
-      <c r="M193" s="46"/>
-      <c r="N193" s="46"/>
-      <c r="O193" s="46"/>
-      <c r="Q193" s="61"/>
-      <c r="U193" s="46"/>
+    <row r="193" spans="1:30" ht="12.75" hidden="1">
+      <c r="A193" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B193" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C193" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D193" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E193" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F193" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G193" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="H193" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I193" s="90" t="s">
+        <v>156</v>
+      </c>
+      <c r="J193" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>500</v>
+      </c>
+      <c r="K193" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2862.5</v>
+      </c>
+      <c r="L193" s="52">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>6050</v>
+      </c>
+      <c r="M193" s="86"/>
+      <c r="N193" s="86"/>
+      <c r="O193" s="86"/>
+      <c r="P193" s="86"/>
+      <c r="Q193" s="87">
+        <v>1</v>
+      </c>
+      <c r="R193" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S193" s="86">
+        <v>325</v>
+      </c>
+      <c r="T193" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U193" s="88">
+        <v>0</v>
+      </c>
+      <c r="V193" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X193" s="46"/>
       <c r="Y193" s="46"/>
       <c r="Z193" s="46"/>
@@ -17739,18 +18479,70 @@
       <c r="AC193" s="46"/>
       <c r="AD193" s="46"/>
     </row>
-    <row r="194" spans="1:30" ht="12.75">
-      <c r="A194" s="44"/>
-      <c r="B194" s="44"/>
-      <c r="C194" s="44"/>
-      <c r="I194" s="46"/>
-      <c r="J194" s="46"/>
-      <c r="K194" s="46"/>
-      <c r="M194" s="46"/>
-      <c r="N194" s="46"/>
-      <c r="O194" s="46"/>
-      <c r="Q194" s="61"/>
-      <c r="U194" s="46"/>
+    <row r="194" spans="1:30" ht="12.75" hidden="1">
+      <c r="A194" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B194" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C194" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>7703</v>
+      </c>
+      <c r="D194" s="86">
+        <v>3689</v>
+      </c>
+      <c r="E194" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F194" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>326.5</v>
+      </c>
+      <c r="G194" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>3362.5</v>
+      </c>
+      <c r="H194" s="52">
+        <v>7050</v>
+      </c>
+      <c r="I194" s="90" t="s">
+        <v>159</v>
+      </c>
+      <c r="J194" s="48">
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>625</v>
+      </c>
+      <c r="K194" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2737.5</v>
+      </c>
+      <c r="L194" s="52">
+        <v>5800</v>
+      </c>
+      <c r="M194" s="90"/>
+      <c r="N194" s="86"/>
+      <c r="O194" s="111"/>
+      <c r="P194" s="86"/>
+      <c r="Q194" s="87">
+        <v>1</v>
+      </c>
+      <c r="R194" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S194" s="86">
+        <v>325</v>
+      </c>
+      <c r="T194" s="110" t="s">
+        <v>55</v>
+      </c>
+      <c r="U194" s="20">
+        <v>0</v>
+      </c>
+      <c r="V194" s="108" t="s">
+        <v>56</v>
+      </c>
       <c r="X194" s="46"/>
       <c r="Y194" s="46"/>
       <c r="Z194" s="46"/>
@@ -17759,18 +18551,75 @@
       <c r="AC194" s="46"/>
       <c r="AD194" s="46"/>
     </row>
-    <row r="195" spans="1:30" ht="12.75">
-      <c r="A195" s="44"/>
-      <c r="B195" s="44"/>
-      <c r="C195" s="44"/>
-      <c r="I195" s="46"/>
-      <c r="J195" s="46"/>
-      <c r="K195" s="46"/>
-      <c r="M195" s="46"/>
-      <c r="N195" s="46"/>
-      <c r="O195" s="46"/>
-      <c r="Q195" s="61"/>
-      <c r="U195" s="46"/>
+    <row r="195" spans="1:30" ht="12.75" hidden="1">
+      <c r="A195" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B195" s="114" t="s">
+        <v>651</v>
+      </c>
+      <c r="C195" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D195" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E195" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G195" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H195" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I195" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="J195" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K195" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L195" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M195" s="86"/>
+      <c r="N195" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O195" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P195" s="86"/>
+      <c r="Q195" s="87">
+        <v>1</v>
+      </c>
+      <c r="R195" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S195" s="87">
+        <v>325</v>
+      </c>
+      <c r="T195" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U195" s="88">
+        <v>0</v>
+      </c>
+      <c r="V195" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X195" s="46"/>
       <c r="Y195" s="46"/>
       <c r="Z195" s="46"/>
@@ -17779,18 +18628,75 @@
       <c r="AC195" s="46"/>
       <c r="AD195" s="46"/>
     </row>
-    <row r="196" spans="1:30" ht="12.75">
-      <c r="A196" s="44"/>
-      <c r="B196" s="44"/>
-      <c r="C196" s="44"/>
-      <c r="I196" s="46"/>
-      <c r="J196" s="46"/>
-      <c r="K196" s="46"/>
-      <c r="M196" s="46"/>
-      <c r="N196" s="46"/>
-      <c r="O196" s="46"/>
-      <c r="Q196" s="61"/>
-      <c r="U196" s="46"/>
+    <row r="196" spans="1:30" ht="12.75" hidden="1">
+      <c r="A196" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B196" s="115" t="s">
+        <v>651</v>
+      </c>
+      <c r="C196" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D196" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E196" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G196" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H196" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I196" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="J196" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K196" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L196" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M196" s="86"/>
+      <c r="N196" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O196" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P196" s="86"/>
+      <c r="Q196" s="87">
+        <v>1</v>
+      </c>
+      <c r="R196" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S196" s="87">
+        <v>325</v>
+      </c>
+      <c r="T196" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U196" s="88">
+        <v>0</v>
+      </c>
+      <c r="V196" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X196" s="46"/>
       <c r="Y196" s="46"/>
       <c r="Z196" s="46"/>
@@ -17799,18 +18705,75 @@
       <c r="AC196" s="46"/>
       <c r="AD196" s="46"/>
     </row>
-    <row r="197" spans="1:30" ht="12.75">
-      <c r="A197" s="44"/>
-      <c r="B197" s="44"/>
-      <c r="C197" s="44"/>
-      <c r="I197" s="46"/>
-      <c r="J197" s="46"/>
-      <c r="K197" s="46"/>
-      <c r="M197" s="46"/>
-      <c r="N197" s="46"/>
-      <c r="O197" s="46"/>
-      <c r="Q197" s="61"/>
-      <c r="U197" s="46"/>
+    <row r="197" spans="1:30" ht="12.75" hidden="1">
+      <c r="A197" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B197" s="114" t="s">
+        <v>651</v>
+      </c>
+      <c r="C197" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D197" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E197" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F197" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G197" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H197" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I197" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="J197" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K197" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L197" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M197" s="86"/>
+      <c r="N197" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O197" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P197" s="86"/>
+      <c r="Q197" s="87">
+        <v>1</v>
+      </c>
+      <c r="R197" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S197" s="87">
+        <v>325</v>
+      </c>
+      <c r="T197" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U197" s="88">
+        <v>0</v>
+      </c>
+      <c r="V197" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X197" s="46"/>
       <c r="Y197" s="46"/>
       <c r="Z197" s="46"/>
@@ -17819,18 +18782,75 @@
       <c r="AC197" s="46"/>
       <c r="AD197" s="46"/>
     </row>
-    <row r="198" spans="1:30" ht="12.75">
-      <c r="A198" s="44"/>
-      <c r="B198" s="44"/>
-      <c r="C198" s="44"/>
-      <c r="I198" s="46"/>
-      <c r="J198" s="46"/>
-      <c r="K198" s="46"/>
-      <c r="M198" s="46"/>
-      <c r="N198" s="46"/>
-      <c r="O198" s="46"/>
-      <c r="Q198" s="61"/>
-      <c r="U198" s="46"/>
+    <row r="198" spans="1:30" ht="12.75" hidden="1">
+      <c r="A198" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B198" s="114" t="s">
+        <v>651</v>
+      </c>
+      <c r="C198" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D198" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E198" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G198" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H198" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I198" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="J198" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K198" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L198" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M198" s="86"/>
+      <c r="N198" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O198" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P198" s="86"/>
+      <c r="Q198" s="87">
+        <v>1</v>
+      </c>
+      <c r="R198" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S198" s="87">
+        <v>325</v>
+      </c>
+      <c r="T198" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U198" s="88">
+        <v>0</v>
+      </c>
+      <c r="V198" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X198" s="46"/>
       <c r="Y198" s="46"/>
       <c r="Z198" s="46"/>
@@ -17839,18 +18859,75 @@
       <c r="AC198" s="46"/>
       <c r="AD198" s="46"/>
     </row>
-    <row r="199" spans="1:30" ht="12.75">
-      <c r="A199" s="44"/>
-      <c r="B199" s="44"/>
-      <c r="C199" s="44"/>
-      <c r="I199" s="46"/>
-      <c r="J199" s="46"/>
-      <c r="K199" s="46"/>
-      <c r="M199" s="46"/>
-      <c r="N199" s="46"/>
-      <c r="O199" s="46"/>
-      <c r="Q199" s="61"/>
-      <c r="U199" s="46"/>
+    <row r="199" spans="1:30" ht="12.75" hidden="1">
+      <c r="A199" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B199" s="115" t="s">
+        <v>651</v>
+      </c>
+      <c r="C199" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D199" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E199" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G199" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H199" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I199" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="J199" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K199" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L199" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M199" s="86"/>
+      <c r="N199" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O199" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P199" s="86"/>
+      <c r="Q199" s="87">
+        <v>1</v>
+      </c>
+      <c r="R199" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S199" s="87">
+        <v>325</v>
+      </c>
+      <c r="T199" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U199" s="88">
+        <v>0</v>
+      </c>
+      <c r="V199" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X199" s="46"/>
       <c r="Y199" s="46"/>
       <c r="Z199" s="46"/>
@@ -17859,18 +18936,75 @@
       <c r="AC199" s="46"/>
       <c r="AD199" s="46"/>
     </row>
-    <row r="200" spans="1:30" ht="12.75">
-      <c r="A200" s="44"/>
-      <c r="B200" s="44"/>
-      <c r="C200" s="44"/>
-      <c r="I200" s="46"/>
-      <c r="J200" s="46"/>
-      <c r="K200" s="46"/>
-      <c r="M200" s="46"/>
-      <c r="N200" s="46"/>
-      <c r="O200" s="46"/>
-      <c r="Q200" s="61"/>
-      <c r="U200" s="46"/>
+    <row r="200" spans="1:30" ht="12.75" hidden="1">
+      <c r="A200" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B200" s="114" t="s">
+        <v>651</v>
+      </c>
+      <c r="C200" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D200" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E200" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G200" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H200" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I200" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="J200" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K200" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L200" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M200" s="86"/>
+      <c r="N200" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O200" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P200" s="86"/>
+      <c r="Q200" s="87">
+        <v>1</v>
+      </c>
+      <c r="R200" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S200" s="87">
+        <v>325</v>
+      </c>
+      <c r="T200" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U200" s="88">
+        <v>0</v>
+      </c>
+      <c r="V200" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X200" s="46"/>
       <c r="Y200" s="46"/>
       <c r="Z200" s="46"/>
@@ -17879,18 +19013,75 @@
       <c r="AC200" s="46"/>
       <c r="AD200" s="46"/>
     </row>
-    <row r="201" spans="1:30" ht="12.75">
-      <c r="A201" s="44"/>
-      <c r="B201" s="44"/>
-      <c r="C201" s="44"/>
-      <c r="I201" s="46"/>
-      <c r="J201" s="46"/>
-      <c r="K201" s="46"/>
-      <c r="M201" s="46"/>
-      <c r="N201" s="46"/>
-      <c r="O201" s="46"/>
-      <c r="Q201" s="61"/>
-      <c r="U201" s="46"/>
+    <row r="201" spans="1:30" ht="12.75" hidden="1">
+      <c r="A201" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B201" s="115" t="s">
+        <v>651</v>
+      </c>
+      <c r="C201" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D201" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E201" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G201" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H201" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I201" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="J201" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K201" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L201" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M201" s="86"/>
+      <c r="N201" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O201" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P201" s="86"/>
+      <c r="Q201" s="87">
+        <v>1</v>
+      </c>
+      <c r="R201" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S201" s="87">
+        <v>325</v>
+      </c>
+      <c r="T201" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U201" s="88">
+        <v>0</v>
+      </c>
+      <c r="V201" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X201" s="46"/>
       <c r="Y201" s="46"/>
       <c r="Z201" s="46"/>
@@ -17899,18 +19090,75 @@
       <c r="AC201" s="46"/>
       <c r="AD201" s="46"/>
     </row>
-    <row r="202" spans="1:30" ht="12.75">
-      <c r="A202" s="44"/>
-      <c r="B202" s="44"/>
-      <c r="C202" s="44"/>
-      <c r="I202" s="46"/>
-      <c r="J202" s="46"/>
-      <c r="K202" s="46"/>
-      <c r="M202" s="46"/>
-      <c r="N202" s="46"/>
-      <c r="O202" s="46"/>
-      <c r="Q202" s="61"/>
-      <c r="U202" s="46"/>
+    <row r="202" spans="1:30" ht="12.75" hidden="1">
+      <c r="A202" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B202" s="114" t="s">
+        <v>651</v>
+      </c>
+      <c r="C202" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D202" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E202" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G202" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H202" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I202" s="84" t="s">
+        <v>162</v>
+      </c>
+      <c r="J202" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K202" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L202" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M202" s="86"/>
+      <c r="N202" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O202" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P202" s="86"/>
+      <c r="Q202" s="87">
+        <v>1</v>
+      </c>
+      <c r="R202" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S202" s="87">
+        <v>325</v>
+      </c>
+      <c r="T202" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U202" s="88">
+        <v>0</v>
+      </c>
+      <c r="V202" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X202" s="46"/>
       <c r="Y202" s="46"/>
       <c r="Z202" s="46"/>
@@ -17919,18 +19167,75 @@
       <c r="AC202" s="46"/>
       <c r="AD202" s="46"/>
     </row>
-    <row r="203" spans="1:30" ht="12.75">
-      <c r="A203" s="44"/>
-      <c r="B203" s="44"/>
-      <c r="C203" s="44"/>
-      <c r="I203" s="46"/>
-      <c r="J203" s="46"/>
-      <c r="K203" s="46"/>
-      <c r="M203" s="46"/>
-      <c r="N203" s="46"/>
-      <c r="O203" s="46"/>
-      <c r="Q203" s="61"/>
-      <c r="U203" s="46"/>
+    <row r="203" spans="1:30" ht="12.75" hidden="1">
+      <c r="A203" s="113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B203" s="115" t="s">
+        <v>651</v>
+      </c>
+      <c r="C203" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D203" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E203" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G203" s="116">
+        <v>4012.5</v>
+      </c>
+      <c r="H203" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I203" s="84" t="s">
+        <v>164</v>
+      </c>
+      <c r="J203" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
+      </c>
+      <c r="K203" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="L203" s="52">
+        <v>5790</v>
+      </c>
+      <c r="M203" s="86"/>
+      <c r="N203" s="116">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O203" s="116">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P203" s="86"/>
+      <c r="Q203" s="87">
+        <v>1</v>
+      </c>
+      <c r="R203" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S203" s="87">
+        <v>325</v>
+      </c>
+      <c r="T203" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U203" s="88">
+        <v>0</v>
+      </c>
+      <c r="V203" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X203" s="46"/>
       <c r="Y203" s="46"/>
       <c r="Z203" s="46"/>
@@ -17939,18 +19244,70 @@
       <c r="AC203" s="46"/>
       <c r="AD203" s="46"/>
     </row>
-    <row r="204" spans="1:30" ht="12.75">
-      <c r="A204" s="44"/>
-      <c r="B204" s="44"/>
-      <c r="C204" s="44"/>
-      <c r="I204" s="46"/>
-      <c r="J204" s="46"/>
-      <c r="K204" s="46"/>
-      <c r="M204" s="46"/>
-      <c r="N204" s="46"/>
-      <c r="O204" s="46"/>
-      <c r="Q204" s="61"/>
-      <c r="U204" s="46"/>
+    <row r="204" spans="1:30" ht="12.75" hidden="1">
+      <c r="A204" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B204" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C204" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D204" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E204" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F204" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G204" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="H204" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I204" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="J204" s="48">
+        <v>0</v>
+      </c>
+      <c r="K204" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="L204" s="52">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>8350</v>
+      </c>
+      <c r="M204" s="86"/>
+      <c r="N204" s="86"/>
+      <c r="O204" s="86"/>
+      <c r="P204" s="86"/>
+      <c r="Q204" s="87">
+        <v>1</v>
+      </c>
+      <c r="R204" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S204" s="86">
+        <v>325</v>
+      </c>
+      <c r="T204" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U204" s="88">
+        <v>0</v>
+      </c>
+      <c r="V204" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X204" s="46"/>
       <c r="Y204" s="46"/>
       <c r="Z204" s="46"/>
@@ -17959,18 +19316,70 @@
       <c r="AC204" s="46"/>
       <c r="AD204" s="46"/>
     </row>
-    <row r="205" spans="1:30" ht="12.75">
-      <c r="A205" s="44"/>
-      <c r="B205" s="44"/>
-      <c r="C205" s="44"/>
-      <c r="I205" s="46"/>
-      <c r="J205" s="46"/>
-      <c r="K205" s="46"/>
-      <c r="M205" s="46"/>
-      <c r="N205" s="46"/>
-      <c r="O205" s="46"/>
-      <c r="Q205" s="61"/>
-      <c r="U205" s="46"/>
+    <row r="205" spans="1:30" ht="12.75" hidden="1">
+      <c r="A205" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B205" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C205" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D205" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E205" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G205" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="H205" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I205" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="J205" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K205" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="L205" s="52">
+        <v>8350</v>
+      </c>
+      <c r="M205" s="86"/>
+      <c r="N205" s="86"/>
+      <c r="O205" s="86"/>
+      <c r="P205" s="86"/>
+      <c r="Q205" s="87">
+        <v>1</v>
+      </c>
+      <c r="R205" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S205" s="86">
+        <v>325</v>
+      </c>
+      <c r="T205" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="U205" s="86">
+        <v>0</v>
+      </c>
+      <c r="V205" s="59" t="s">
+        <v>56</v>
+      </c>
       <c r="X205" s="46"/>
       <c r="Y205" s="46"/>
       <c r="Z205" s="46"/>
@@ -17979,18 +19388,70 @@
       <c r="AC205" s="46"/>
       <c r="AD205" s="46"/>
     </row>
-    <row r="206" spans="1:30" ht="12.75">
-      <c r="A206" s="44"/>
-      <c r="B206" s="44"/>
-      <c r="C206" s="44"/>
-      <c r="I206" s="46"/>
-      <c r="J206" s="46"/>
-      <c r="K206" s="46"/>
-      <c r="M206" s="46"/>
-      <c r="N206" s="46"/>
-      <c r="O206" s="46"/>
-      <c r="Q206" s="61"/>
-      <c r="U206" s="46"/>
+    <row r="206" spans="1:30" ht="12.75" hidden="1">
+      <c r="A206" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B206" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C206" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D206" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E206" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G206" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="H206" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I206" s="84" t="s">
+        <v>138</v>
+      </c>
+      <c r="J206" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>700</v>
+      </c>
+      <c r="K206" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3312.5</v>
+      </c>
+      <c r="L206" s="55">
+        <v>6950</v>
+      </c>
+      <c r="M206" s="86"/>
+      <c r="N206" s="86"/>
+      <c r="O206" s="86"/>
+      <c r="P206" s="86"/>
+      <c r="Q206" s="87">
+        <v>1</v>
+      </c>
+      <c r="R206" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="S206" s="107">
+        <v>325</v>
+      </c>
+      <c r="T206" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U206" s="88">
+        <v>0</v>
+      </c>
+      <c r="V206" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X206" s="46"/>
       <c r="Y206" s="46"/>
       <c r="Z206" s="46"/>
@@ -17999,18 +19460,70 @@
       <c r="AC206" s="46"/>
       <c r="AD206" s="46"/>
     </row>
-    <row r="207" spans="1:30" ht="12.75">
-      <c r="A207" s="44"/>
-      <c r="B207" s="44"/>
-      <c r="C207" s="44"/>
-      <c r="I207" s="46"/>
-      <c r="J207" s="46"/>
-      <c r="K207" s="46"/>
-      <c r="M207" s="46"/>
-      <c r="N207" s="46"/>
-      <c r="O207" s="46"/>
-      <c r="Q207" s="61"/>
-      <c r="U207" s="46"/>
+    <row r="207" spans="1:30" ht="12.75" hidden="1">
+      <c r="A207" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B207" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C207" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D207" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E207" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G207" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="H207" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I207" s="90" t="s">
+        <v>141</v>
+      </c>
+      <c r="J207" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>0</v>
+      </c>
+      <c r="K207" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="L207" s="52">
+        <v>8350</v>
+      </c>
+      <c r="M207" s="86"/>
+      <c r="N207" s="86"/>
+      <c r="O207" s="86"/>
+      <c r="P207" s="86"/>
+      <c r="Q207" s="87">
+        <v>1</v>
+      </c>
+      <c r="R207" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S207" s="86">
+        <v>325</v>
+      </c>
+      <c r="T207" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U207" s="88">
+        <v>0</v>
+      </c>
+      <c r="V207" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X207" s="46"/>
       <c r="Y207" s="46"/>
       <c r="Z207" s="46"/>
@@ -18019,18 +19532,71 @@
       <c r="AC207" s="46"/>
       <c r="AD207" s="46"/>
     </row>
-    <row r="208" spans="1:30" ht="12.75">
-      <c r="A208" s="44"/>
-      <c r="B208" s="44"/>
-      <c r="C208" s="44"/>
-      <c r="I208" s="46"/>
-      <c r="J208" s="46"/>
-      <c r="K208" s="46"/>
-      <c r="M208" s="46"/>
-      <c r="N208" s="46"/>
-      <c r="O208" s="46"/>
-      <c r="Q208" s="61"/>
-      <c r="U208" s="46"/>
+    <row r="208" spans="1:30" ht="12.75" hidden="1">
+      <c r="A208" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B208" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="C208" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D208" s="86">
+        <v>4679</v>
+      </c>
+      <c r="E208" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F208" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G208" s="86">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="H208" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I208" s="90" t="s">
+        <v>156</v>
+      </c>
+      <c r="J208" s="48">
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>500</v>
+      </c>
+      <c r="K208" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3512.5</v>
+      </c>
+      <c r="L208" s="52">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>7350</v>
+      </c>
+      <c r="M208" s="86"/>
+      <c r="N208" s="86"/>
+      <c r="O208" s="86"/>
+      <c r="P208" s="86"/>
+      <c r="Q208" s="87">
+        <v>1</v>
+      </c>
+      <c r="R208" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="S208" s="86">
+        <v>325</v>
+      </c>
+      <c r="T208" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="U208" s="88">
+        <v>0</v>
+      </c>
+      <c r="V208" s="89" t="s">
+        <v>56</v>
+      </c>
       <c r="X208" s="46"/>
       <c r="Y208" s="46"/>
       <c r="Z208" s="46"/>
@@ -18039,18 +19605,70 @@
       <c r="AC208" s="46"/>
       <c r="AD208" s="46"/>
     </row>
-    <row r="209" spans="1:30" ht="12.75">
-      <c r="A209" s="44"/>
-      <c r="B209" s="44"/>
-      <c r="C209" s="44"/>
-      <c r="I209" s="46"/>
-      <c r="J209" s="46"/>
-      <c r="K209" s="46"/>
-      <c r="M209" s="46"/>
-      <c r="N209" s="46"/>
-      <c r="O209" s="46"/>
-      <c r="Q209" s="61"/>
-      <c r="U209" s="46"/>
+    <row r="209" spans="1:30" ht="12.75" hidden="1">
+      <c r="A209" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="B209" s="129" t="s">
+        <v>60</v>
+      </c>
+      <c r="C209" s="45">
+        <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
+        <v>9683</v>
+      </c>
+      <c r="D209" s="92">
+        <v>4679</v>
+      </c>
+      <c r="E209" s="92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="46">
+        <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>666.5</v>
+      </c>
+      <c r="G209" s="92">
+        <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
+        <v>4012.5</v>
+      </c>
+      <c r="H209" s="52">
+        <v>8350</v>
+      </c>
+      <c r="I209" s="93" t="s">
+        <v>159</v>
+      </c>
+      <c r="J209" s="48">
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>875</v>
+      </c>
+      <c r="K209" s="48">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3137.5</v>
+      </c>
+      <c r="L209" s="52">
+        <v>6600</v>
+      </c>
+      <c r="M209" s="93"/>
+      <c r="N209" s="92"/>
+      <c r="O209" s="130"/>
+      <c r="P209" s="92"/>
+      <c r="Q209" s="94">
+        <v>1</v>
+      </c>
+      <c r="R209" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="S209" s="92">
+        <v>325</v>
+      </c>
+      <c r="T209" s="132" t="s">
+        <v>55</v>
+      </c>
+      <c r="U209" s="25">
+        <v>0</v>
+      </c>
+      <c r="V209" s="133" t="s">
+        <v>56</v>
+      </c>
       <c r="X209" s="46"/>
       <c r="Y209" s="46"/>
       <c r="Z209" s="46"/>
@@ -18226,7 +19844,6 @@
       <c r="I218" s="46"/>
       <c r="J218" s="46"/>
       <c r="K218" s="46"/>
-      <c r="M218" s="46"/>
       <c r="N218" s="46"/>
       <c r="O218" s="46"/>
       <c r="Q218" s="61"/>
@@ -18246,7 +19863,6 @@
       <c r="I219" s="46"/>
       <c r="J219" s="46"/>
       <c r="K219" s="46"/>
-      <c r="M219" s="46"/>
       <c r="N219" s="46"/>
       <c r="O219" s="46"/>
       <c r="Q219" s="61"/>
@@ -18266,7 +19882,6 @@
       <c r="I220" s="46"/>
       <c r="J220" s="46"/>
       <c r="K220" s="46"/>
-      <c r="M220" s="46"/>
       <c r="N220" s="46"/>
       <c r="O220" s="46"/>
       <c r="Q220" s="61"/>
@@ -18286,18 +19901,10 @@
       <c r="I221" s="46"/>
       <c r="J221" s="46"/>
       <c r="K221" s="46"/>
-      <c r="M221" s="46"/>
       <c r="N221" s="46"/>
       <c r="O221" s="46"/>
       <c r="Q221" s="61"/>
       <c r="U221" s="46"/>
-      <c r="X221" s="46"/>
-      <c r="Y221" s="46"/>
-      <c r="Z221" s="46"/>
-      <c r="AA221" s="46"/>
-      <c r="AB221" s="46"/>
-      <c r="AC221" s="46"/>
-      <c r="AD221" s="46"/>
     </row>
     <row r="222" spans="1:30" ht="12.75">
       <c r="A222" s="44"/>
@@ -18306,18 +19913,10 @@
       <c r="I222" s="46"/>
       <c r="J222" s="46"/>
       <c r="K222" s="46"/>
-      <c r="M222" s="46"/>
       <c r="N222" s="46"/>
       <c r="O222" s="46"/>
       <c r="Q222" s="61"/>
       <c r="U222" s="46"/>
-      <c r="X222" s="46"/>
-      <c r="Y222" s="46"/>
-      <c r="Z222" s="46"/>
-      <c r="AA222" s="46"/>
-      <c r="AB222" s="46"/>
-      <c r="AC222" s="46"/>
-      <c r="AD222" s="46"/>
     </row>
     <row r="223" spans="1:30" ht="12.75">
       <c r="A223" s="44"/>
@@ -18326,191 +19925,10 @@
       <c r="I223" s="46"/>
       <c r="J223" s="46"/>
       <c r="K223" s="46"/>
-      <c r="M223" s="46"/>
       <c r="N223" s="46"/>
       <c r="O223" s="46"/>
       <c r="Q223" s="61"/>
       <c r="U223" s="46"/>
-      <c r="X223" s="46"/>
-      <c r="Y223" s="46"/>
-      <c r="Z223" s="46"/>
-      <c r="AA223" s="46"/>
-      <c r="AB223" s="46"/>
-      <c r="AC223" s="46"/>
-      <c r="AD223" s="46"/>
-    </row>
-    <row r="224" spans="1:30" ht="12.75">
-      <c r="A224" s="44"/>
-      <c r="B224" s="44"/>
-      <c r="C224" s="44"/>
-      <c r="I224" s="46"/>
-      <c r="J224" s="46"/>
-      <c r="K224" s="46"/>
-      <c r="M224" s="46"/>
-      <c r="N224" s="46"/>
-      <c r="O224" s="46"/>
-      <c r="Q224" s="61"/>
-      <c r="U224" s="46"/>
-      <c r="X224" s="46"/>
-      <c r="Y224" s="46"/>
-      <c r="Z224" s="46"/>
-      <c r="AA224" s="46"/>
-      <c r="AB224" s="46"/>
-      <c r="AC224" s="46"/>
-      <c r="AD224" s="46"/>
-    </row>
-    <row r="225" spans="1:30" ht="12.75">
-      <c r="A225" s="44"/>
-      <c r="B225" s="44"/>
-      <c r="C225" s="44"/>
-      <c r="I225" s="46"/>
-      <c r="J225" s="46"/>
-      <c r="K225" s="46"/>
-      <c r="M225" s="46"/>
-      <c r="N225" s="46"/>
-      <c r="O225" s="46"/>
-      <c r="Q225" s="61"/>
-      <c r="U225" s="46"/>
-      <c r="X225" s="46"/>
-      <c r="Y225" s="46"/>
-      <c r="Z225" s="46"/>
-      <c r="AA225" s="46"/>
-      <c r="AB225" s="46"/>
-      <c r="AC225" s="46"/>
-      <c r="AD225" s="46"/>
-    </row>
-    <row r="226" spans="1:30" ht="12.75">
-      <c r="A226" s="44"/>
-      <c r="B226" s="44"/>
-      <c r="C226" s="44"/>
-      <c r="I226" s="46"/>
-      <c r="J226" s="46"/>
-      <c r="K226" s="46"/>
-      <c r="M226" s="46"/>
-      <c r="N226" s="46"/>
-      <c r="O226" s="46"/>
-      <c r="Q226" s="61"/>
-      <c r="U226" s="46"/>
-      <c r="X226" s="46"/>
-      <c r="Y226" s="46"/>
-      <c r="Z226" s="46"/>
-      <c r="AA226" s="46"/>
-      <c r="AB226" s="46"/>
-      <c r="AC226" s="46"/>
-      <c r="AD226" s="46"/>
-    </row>
-    <row r="227" spans="1:30" ht="12.75">
-      <c r="A227" s="44"/>
-      <c r="B227" s="44"/>
-      <c r="C227" s="44"/>
-      <c r="I227" s="46"/>
-      <c r="J227" s="46"/>
-      <c r="K227" s="46"/>
-      <c r="M227" s="46"/>
-      <c r="N227" s="46"/>
-      <c r="O227" s="46"/>
-      <c r="Q227" s="61"/>
-      <c r="U227" s="46"/>
-      <c r="X227" s="46"/>
-      <c r="Y227" s="46"/>
-      <c r="Z227" s="46"/>
-      <c r="AA227" s="46"/>
-      <c r="AB227" s="46"/>
-      <c r="AC227" s="46"/>
-      <c r="AD227" s="46"/>
-    </row>
-    <row r="228" spans="1:30" ht="12.75">
-      <c r="A228" s="44"/>
-      <c r="B228" s="44"/>
-      <c r="C228" s="44"/>
-      <c r="I228" s="46"/>
-      <c r="J228" s="46"/>
-      <c r="K228" s="46"/>
-      <c r="N228" s="46"/>
-      <c r="O228" s="46"/>
-      <c r="Q228" s="61"/>
-      <c r="U228" s="46"/>
-      <c r="X228" s="46"/>
-      <c r="Y228" s="46"/>
-      <c r="Z228" s="46"/>
-      <c r="AA228" s="46"/>
-      <c r="AB228" s="46"/>
-      <c r="AC228" s="46"/>
-      <c r="AD228" s="46"/>
-    </row>
-    <row r="229" spans="1:30" ht="12.75">
-      <c r="A229" s="44"/>
-      <c r="B229" s="44"/>
-      <c r="C229" s="44"/>
-      <c r="I229" s="46"/>
-      <c r="J229" s="46"/>
-      <c r="K229" s="46"/>
-      <c r="N229" s="46"/>
-      <c r="O229" s="46"/>
-      <c r="Q229" s="61"/>
-      <c r="U229" s="46"/>
-      <c r="X229" s="46"/>
-      <c r="Y229" s="46"/>
-      <c r="Z229" s="46"/>
-      <c r="AA229" s="46"/>
-      <c r="AB229" s="46"/>
-      <c r="AC229" s="46"/>
-      <c r="AD229" s="46"/>
-    </row>
-    <row r="230" spans="1:30" ht="12.75">
-      <c r="A230" s="44"/>
-      <c r="B230" s="44"/>
-      <c r="C230" s="44"/>
-      <c r="I230" s="46"/>
-      <c r="J230" s="46"/>
-      <c r="K230" s="46"/>
-      <c r="N230" s="46"/>
-      <c r="O230" s="46"/>
-      <c r="Q230" s="61"/>
-      <c r="U230" s="46"/>
-      <c r="X230" s="46"/>
-      <c r="Y230" s="46"/>
-      <c r="Z230" s="46"/>
-      <c r="AA230" s="46"/>
-      <c r="AB230" s="46"/>
-      <c r="AC230" s="46"/>
-      <c r="AD230" s="46"/>
-    </row>
-    <row r="231" spans="1:30" ht="12.75">
-      <c r="A231" s="44"/>
-      <c r="B231" s="44"/>
-      <c r="C231" s="44"/>
-      <c r="I231" s="46"/>
-      <c r="J231" s="46"/>
-      <c r="K231" s="46"/>
-      <c r="N231" s="46"/>
-      <c r="O231" s="46"/>
-      <c r="Q231" s="61"/>
-      <c r="U231" s="46"/>
-    </row>
-    <row r="232" spans="1:30" ht="12.75">
-      <c r="A232" s="44"/>
-      <c r="B232" s="44"/>
-      <c r="C232" s="44"/>
-      <c r="I232" s="46"/>
-      <c r="J232" s="46"/>
-      <c r="K232" s="46"/>
-      <c r="N232" s="46"/>
-      <c r="O232" s="46"/>
-      <c r="Q232" s="61"/>
-      <c r="U232" s="46"/>
-    </row>
-    <row r="233" spans="1:30" ht="12.75">
-      <c r="A233" s="44"/>
-      <c r="B233" s="44"/>
-      <c r="C233" s="44"/>
-      <c r="I233" s="46"/>
-      <c r="J233" s="46"/>
-      <c r="K233" s="46"/>
-      <c r="N233" s="46"/>
-      <c r="O233" s="46"/>
-      <c r="Q233" s="61"/>
-      <c r="U233" s="46"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1501" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D08B815-DF3C-4513-8BD4-299C8B456746}"/>
+  <xr:revisionPtr revIDLastSave="1504" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17F4F3F9-AA11-47A4-BD6D-B35BEF960371}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="4110" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -3419,16 +3419,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Beltone RIE Digital Illuminate 17 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Illuminate 4 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Illuminate 6 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Illuminate 9 62S-DRWC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A101:V193">
     <sortCondition ref="I1:I199"/>
   </sortState>
@@ -4530,7 +4521,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="12.75" hidden="1">
+    <row r="2" spans="1:31" ht="12.75">
       <c r="A2" s="43" t="s">
         <v>130</v>
       </c>
@@ -4600,7 +4591,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="12.75" hidden="1">
+    <row r="3" spans="1:31" ht="12.75">
       <c r="A3" s="43" t="s">
         <v>130</v>
       </c>
@@ -4669,7 +4660,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="12.75" hidden="1">
+    <row r="4" spans="1:31" ht="12.75">
       <c r="A4" s="43" t="s">
         <v>130</v>
       </c>
@@ -4741,7 +4732,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="12.75" hidden="1">
+    <row r="5" spans="1:31" ht="12.75">
       <c r="A5" s="43" t="s">
         <v>130</v>
       </c>
@@ -4813,7 +4804,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="12.75" hidden="1">
+    <row r="6" spans="1:31" ht="12.75">
       <c r="A6" s="43" t="s">
         <v>120</v>
       </c>
@@ -4880,7 +4871,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="12.75" hidden="1">
+    <row r="7" spans="1:31" ht="12.75">
       <c r="A7" s="43" t="s">
         <v>120</v>
       </c>
@@ -4944,7 +4935,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="12.75" hidden="1">
+    <row r="8" spans="1:31" ht="12.75">
       <c r="A8" s="43" t="s">
         <v>61</v>
       </c>
@@ -5013,7 +5004,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="12.75" hidden="1">
+    <row r="9" spans="1:31" ht="12.75">
       <c r="A9" s="43" t="s">
         <v>64</v>
       </c>
@@ -5082,7 +5073,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="12.75" hidden="1">
+    <row r="10" spans="1:31" ht="12.75">
       <c r="A10" s="43" t="s">
         <v>66</v>
       </c>
@@ -5151,7 +5142,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="12.75" hidden="1">
+    <row r="11" spans="1:31" ht="12.75">
       <c r="A11" s="43" t="s">
         <v>70</v>
       </c>
@@ -5220,7 +5211,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="12.75" hidden="1">
+    <row r="12" spans="1:31" ht="12.75">
       <c r="A12" s="43" t="s">
         <v>72</v>
       </c>
@@ -5289,7 +5280,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="12.75" hidden="1">
+    <row r="13" spans="1:31" ht="12.75">
       <c r="A13" s="43" t="s">
         <v>75</v>
       </c>
@@ -5358,7 +5349,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="12.75" hidden="1">
+    <row r="14" spans="1:31" ht="12.75">
       <c r="A14" s="43" t="s">
         <v>77</v>
       </c>
@@ -5425,7 +5416,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="12.75" hidden="1">
+    <row r="15" spans="1:31" ht="12.75">
       <c r="A15" s="43" t="s">
         <v>80</v>
       </c>
@@ -5493,7 +5484,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="12.75" hidden="1">
+    <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="43" t="s">
         <v>82</v>
       </c>
@@ -5563,7 +5554,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="12.75" hidden="1">
+    <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="43" t="s">
         <v>84</v>
       </c>
@@ -5632,7 +5623,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="12.75" hidden="1">
+    <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="43" t="s">
         <v>86</v>
       </c>
@@ -5701,7 +5692,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="12.75" hidden="1">
+    <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="43" t="s">
         <v>88</v>
       </c>
@@ -5770,7 +5761,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="12.75" hidden="1">
+    <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="43" t="s">
         <v>90</v>
       </c>
@@ -5839,7 +5830,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="12.75" hidden="1">
+    <row r="21" spans="1:31" ht="12.75">
       <c r="A21" s="43" t="s">
         <v>92</v>
       </c>
@@ -5908,7 +5899,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="12.75" hidden="1">
+    <row r="22" spans="1:31" ht="12.75">
       <c r="A22" s="43" t="s">
         <v>94</v>
       </c>
@@ -5977,7 +5968,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="12.75" hidden="1">
+    <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="43" t="s">
         <v>96</v>
       </c>
@@ -6043,7 +6034,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="12.75" hidden="1">
+    <row r="24" spans="1:31" ht="12.75">
       <c r="A24" s="43" t="s">
         <v>98</v>
       </c>
@@ -6110,7 +6101,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="12.75" hidden="1">
+    <row r="25" spans="1:31" ht="12.75">
       <c r="A25" s="43" t="s">
         <v>100</v>
       </c>
@@ -6178,7 +6169,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="12.75" hidden="1">
+    <row r="26" spans="1:31" ht="12.75">
       <c r="A26" s="43" t="s">
         <v>102</v>
       </c>
@@ -6248,7 +6239,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="12.75" hidden="1">
+    <row r="27" spans="1:31" ht="12.75">
       <c r="A27" s="43" t="s">
         <v>104</v>
       </c>
@@ -6318,7 +6309,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="12.75" hidden="1">
+    <row r="28" spans="1:31" ht="12.75">
       <c r="A28" s="43" t="s">
         <v>106</v>
       </c>
@@ -6387,7 +6378,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="12.75" hidden="1">
+    <row r="29" spans="1:31" ht="12.75">
       <c r="A29" s="43" t="s">
         <v>108</v>
       </c>
@@ -6456,7 +6447,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="12.75" hidden="1">
+    <row r="30" spans="1:31" ht="12.75">
       <c r="A30" s="43" t="s">
         <v>110</v>
       </c>
@@ -6525,7 +6516,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="12.75" hidden="1">
+    <row r="31" spans="1:31" ht="12.75">
       <c r="A31" s="43" t="s">
         <v>112</v>
       </c>
@@ -6594,7 +6585,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="12.75" hidden="1">
+    <row r="32" spans="1:31" ht="12.75">
       <c r="A32" s="43" t="s">
         <v>114</v>
       </c>
@@ -6661,7 +6652,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="12.75" hidden="1">
+    <row r="33" spans="1:31" ht="12.75">
       <c r="A33" s="43" t="s">
         <v>116</v>
       </c>
@@ -6728,7 +6719,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="12.75" hidden="1">
+    <row r="34" spans="1:31" ht="12.75">
       <c r="A34" s="43" t="s">
         <v>118</v>
       </c>
@@ -6795,7 +6786,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="12.75" hidden="1">
+    <row r="35" spans="1:31" ht="12.75">
       <c r="A35" s="43" t="s">
         <v>132</v>
       </c>
@@ -6864,7 +6855,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="12.75" hidden="1">
+    <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="43" t="s">
         <v>132</v>
       </c>
@@ -6934,7 +6925,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="12.75" hidden="1">
+    <row r="37" spans="1:31" ht="12.75">
       <c r="A37" s="43" t="s">
         <v>123</v>
       </c>
@@ -7006,7 +6997,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="12.75" hidden="1">
+    <row r="38" spans="1:31" ht="12.75">
       <c r="A38" s="43" t="s">
         <v>125</v>
       </c>
@@ -7078,7 +7069,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="12.75" hidden="1">
+    <row r="39" spans="1:31" ht="12.75">
       <c r="A39" s="43" t="s">
         <v>127</v>
       </c>
@@ -7150,7 +7141,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="12.75" hidden="1">
+    <row r="40" spans="1:31" ht="12.75">
       <c r="A40" s="43" t="s">
         <v>132</v>
       </c>
@@ -7222,7 +7213,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="12.75" hidden="1">
+    <row r="41" spans="1:31" ht="12.75">
       <c r="A41" s="43" t="s">
         <v>132</v>
       </c>
@@ -7294,7 +7285,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="12.75" hidden="1">
+    <row r="42" spans="1:31" ht="12.75">
       <c r="A42" s="43" t="s">
         <v>134</v>
       </c>
@@ -7363,7 +7354,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="12.75" hidden="1">
+    <row r="43" spans="1:31" ht="12.75">
       <c r="A43" s="43" t="s">
         <v>134</v>
       </c>
@@ -7432,7 +7423,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="12.75" hidden="1">
+    <row r="44" spans="1:31" ht="12.75">
       <c r="A44" s="43" t="s">
         <v>134</v>
       </c>
@@ -7504,7 +7495,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="12.75" hidden="1">
+    <row r="45" spans="1:31" ht="12.75">
       <c r="A45" s="43" t="s">
         <v>134</v>
       </c>
@@ -7576,7 +7567,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="12.75" hidden="1">
+    <row r="46" spans="1:31" ht="12.75">
       <c r="A46" s="43" t="s">
         <v>43</v>
       </c>
@@ -7639,7 +7630,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="12.75" hidden="1">
+    <row r="47" spans="1:31" ht="12.75">
       <c r="A47" s="43" t="s">
         <v>43</v>
       </c>
@@ -7711,7 +7702,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="12.75" hidden="1">
+    <row r="48" spans="1:31" ht="12.75">
       <c r="A48" s="43" t="s">
         <v>47</v>
       </c>
@@ -7782,7 +7773,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="12.75" hidden="1">
+    <row r="49" spans="1:32" ht="12.75">
       <c r="A49" s="43" t="s">
         <v>139</v>
       </c>
@@ -7855,7 +7846,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="12.75" hidden="1">
+    <row r="50" spans="1:32" ht="12.75">
       <c r="A50" s="43" t="s">
         <v>142</v>
       </c>
@@ -7928,7 +7919,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="12.75" hidden="1">
+    <row r="51" spans="1:32" ht="12.75">
       <c r="A51" s="43" t="s">
         <v>144</v>
       </c>
@@ -8001,7 +7992,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="12.75" hidden="1">
+    <row r="52" spans="1:32" ht="12.75">
       <c r="A52" s="43" t="s">
         <v>146</v>
       </c>
@@ -8074,7 +8065,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="12.75" hidden="1">
+    <row r="53" spans="1:32" ht="12.75">
       <c r="A53" s="43" t="s">
         <v>148</v>
       </c>
@@ -8147,7 +8138,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="12.75" hidden="1">
+    <row r="54" spans="1:32" ht="12.75">
       <c r="A54" s="43" t="s">
         <v>150</v>
       </c>
@@ -8220,7 +8211,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="12.75" hidden="1">
+    <row r="55" spans="1:32" ht="12.75">
       <c r="A55" s="43" t="s">
         <v>47</v>
       </c>
@@ -8293,7 +8284,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="12.75" hidden="1">
+    <row r="56" spans="1:32" ht="12.75">
       <c r="A56" s="43" t="s">
         <v>47</v>
       </c>
@@ -8366,7 +8357,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="12.75" hidden="1">
+    <row r="57" spans="1:32" ht="12.75">
       <c r="A57" s="43" t="s">
         <v>47</v>
       </c>
@@ -8439,7 +8430,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="12.75" hidden="1">
+    <row r="58" spans="1:32" ht="12.75">
       <c r="A58" s="43" t="s">
         <v>61</v>
       </c>
@@ -8512,7 +8503,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="12.75" hidden="1">
+    <row r="59" spans="1:32" ht="12.75">
       <c r="A59" s="43" t="s">
         <v>64</v>
       </c>
@@ -8584,7 +8575,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="12.75" hidden="1">
+    <row r="60" spans="1:32" ht="12.75">
       <c r="A60" s="43" t="s">
         <v>66</v>
       </c>
@@ -8656,7 +8647,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="12.75" hidden="1">
+    <row r="61" spans="1:32" ht="12.75">
       <c r="A61" s="43" t="s">
         <v>70</v>
       </c>
@@ -8729,7 +8720,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="12.75" hidden="1">
+    <row r="62" spans="1:32" ht="12.75">
       <c r="A62" s="43" t="s">
         <v>72</v>
       </c>
@@ -8802,7 +8793,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="12.75" hidden="1">
+    <row r="63" spans="1:32" ht="12.75">
       <c r="A63" s="43" t="s">
         <v>75</v>
       </c>
@@ -8875,7 +8866,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="12.75" hidden="1">
+    <row r="64" spans="1:32" ht="12.75">
       <c r="A64" s="43" t="s">
         <v>77</v>
       </c>
@@ -8946,7 +8937,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="12.75" hidden="1">
+    <row r="65" spans="1:31" ht="12.75">
       <c r="A65" s="43" t="s">
         <v>80</v>
       </c>
@@ -9017,7 +9008,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="12.75" hidden="1">
+    <row r="66" spans="1:31" ht="12.75">
       <c r="A66" s="43" t="s">
         <v>82</v>
       </c>
@@ -9090,7 +9081,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="12.75" hidden="1">
+    <row r="67" spans="1:31" ht="12.75">
       <c r="A67" s="43" t="s">
         <v>84</v>
       </c>
@@ -9163,7 +9154,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="12.75" hidden="1">
+    <row r="68" spans="1:31" ht="12.75">
       <c r="A68" s="43" t="s">
         <v>86</v>
       </c>
@@ -9236,7 +9227,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="12.75" hidden="1">
+    <row r="69" spans="1:31" ht="12.75">
       <c r="A69" s="43" t="s">
         <v>88</v>
       </c>
@@ -9309,7 +9300,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="12.75" hidden="1">
+    <row r="70" spans="1:31" ht="12.75">
       <c r="A70" s="43" t="s">
         <v>90</v>
       </c>
@@ -9382,7 +9373,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="12.75" hidden="1">
+    <row r="71" spans="1:31" ht="12.75">
       <c r="A71" s="43" t="s">
         <v>92</v>
       </c>
@@ -9455,7 +9446,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="12.75" hidden="1">
+    <row r="72" spans="1:31" ht="12.75">
       <c r="A72" s="43" t="s">
         <v>94</v>
       </c>
@@ -9528,7 +9519,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="12.75" hidden="1">
+    <row r="73" spans="1:31" ht="12.75">
       <c r="A73" s="43" t="s">
         <v>96</v>
       </c>
@@ -9599,7 +9590,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="12.75" hidden="1">
+    <row r="74" spans="1:31" ht="12.75">
       <c r="A74" s="43" t="s">
         <v>98</v>
       </c>
@@ -9670,7 +9661,7 @@
       <c r="AD74"/>
       <c r="AE74"/>
     </row>
-    <row r="75" spans="1:31" ht="12.75" hidden="1">
+    <row r="75" spans="1:31" ht="12.75">
       <c r="A75" s="43" t="s">
         <v>100</v>
       </c>
@@ -9741,7 +9732,7 @@
       <c r="AD75"/>
       <c r="AE75"/>
     </row>
-    <row r="76" spans="1:31" ht="12.75" hidden="1">
+    <row r="76" spans="1:31" ht="12.75">
       <c r="A76" s="43" t="s">
         <v>102</v>
       </c>
@@ -9814,7 +9805,7 @@
       <c r="AD76"/>
       <c r="AE76"/>
     </row>
-    <row r="77" spans="1:31" ht="12.75" hidden="1">
+    <row r="77" spans="1:31" ht="12.75">
       <c r="A77" s="43" t="s">
         <v>104</v>
       </c>
@@ -9887,7 +9878,7 @@
       <c r="AD77"/>
       <c r="AE77"/>
     </row>
-    <row r="78" spans="1:31" ht="12.75" hidden="1">
+    <row r="78" spans="1:31" ht="12.75">
       <c r="A78" s="43" t="s">
         <v>106</v>
       </c>
@@ -9960,7 +9951,7 @@
       <c r="AD78"/>
       <c r="AE78"/>
     </row>
-    <row r="79" spans="1:31" ht="12.75" hidden="1">
+    <row r="79" spans="1:31" ht="12.75">
       <c r="A79" s="43" t="s">
         <v>108</v>
       </c>
@@ -10033,7 +10024,7 @@
       <c r="AD79"/>
       <c r="AE79"/>
     </row>
-    <row r="80" spans="1:31" ht="12.75" hidden="1">
+    <row r="80" spans="1:31" ht="12.75">
       <c r="A80" s="43" t="s">
         <v>110</v>
       </c>
@@ -10106,7 +10097,7 @@
       <c r="AD80"/>
       <c r="AE80"/>
     </row>
-    <row r="81" spans="1:31" ht="12.75" hidden="1">
+    <row r="81" spans="1:31" ht="12.75">
       <c r="A81" s="43" t="s">
         <v>112</v>
       </c>
@@ -10179,7 +10170,7 @@
       <c r="AD81"/>
       <c r="AE81"/>
     </row>
-    <row r="82" spans="1:31" ht="12.75" hidden="1">
+    <row r="82" spans="1:31" ht="12.75">
       <c r="A82" s="43" t="s">
         <v>114</v>
       </c>
@@ -10250,7 +10241,7 @@
       <c r="AD82"/>
       <c r="AE82"/>
     </row>
-    <row r="83" spans="1:31" ht="12.75" hidden="1">
+    <row r="83" spans="1:31" ht="12.75">
       <c r="A83" s="43" t="s">
         <v>116</v>
       </c>
@@ -10321,7 +10312,7 @@
       <c r="AD83"/>
       <c r="AE83"/>
     </row>
-    <row r="84" spans="1:31" ht="12.75" hidden="1">
+    <row r="84" spans="1:31" ht="12.75">
       <c r="A84" s="43" t="s">
         <v>118</v>
       </c>
@@ -10392,7 +10383,7 @@
       <c r="AD84"/>
       <c r="AE84"/>
     </row>
-    <row r="85" spans="1:31" ht="12.75" hidden="1">
+    <row r="85" spans="1:31" ht="12.75">
       <c r="A85" s="43" t="s">
         <v>123</v>
       </c>
@@ -10465,7 +10456,7 @@
       <c r="AD85"/>
       <c r="AE85"/>
     </row>
-    <row r="86" spans="1:31" ht="12.75" hidden="1">
+    <row r="86" spans="1:31" ht="12.75">
       <c r="A86" s="43" t="s">
         <v>125</v>
       </c>
@@ -10538,7 +10529,7 @@
       <c r="AD86"/>
       <c r="AE86"/>
     </row>
-    <row r="87" spans="1:31" ht="12.75" hidden="1">
+    <row r="87" spans="1:31" ht="12.75">
       <c r="A87" s="43" t="s">
         <v>127</v>
       </c>
@@ -10611,7 +10602,7 @@
       <c r="AD87"/>
       <c r="AE87"/>
     </row>
-    <row r="88" spans="1:31" ht="12.75" hidden="1">
+    <row r="88" spans="1:31" ht="12.75">
       <c r="A88" s="43" t="s">
         <v>47</v>
       </c>
@@ -10684,7 +10675,7 @@
       <c r="AD88"/>
       <c r="AE88"/>
     </row>
-    <row r="89" spans="1:31" ht="12.75" hidden="1">
+    <row r="89" spans="1:31" ht="12.75">
       <c r="A89" s="43" t="s">
         <v>47</v>
       </c>
@@ -10757,7 +10748,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="12.75" hidden="1">
+    <row r="90" spans="1:31" ht="12.75">
       <c r="A90" s="43" t="s">
         <v>47</v>
       </c>
@@ -10830,7 +10821,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="12.75" hidden="1">
+    <row r="91" spans="1:31" ht="12.75">
       <c r="A91" s="43" t="s">
         <v>123</v>
       </c>
@@ -10902,7 +10893,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="12.75" hidden="1">
+    <row r="92" spans="1:31" ht="12.75">
       <c r="A92" s="43" t="s">
         <v>125</v>
       </c>
@@ -10974,7 +10965,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="12.75" hidden="1">
+    <row r="93" spans="1:31" ht="12.75">
       <c r="A93" s="43" t="s">
         <v>127</v>
       </c>
@@ -11046,7 +11037,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="12.75" hidden="1">
+    <row r="94" spans="1:31" ht="12.75">
       <c r="A94" s="43" t="s">
         <v>123</v>
       </c>
@@ -11118,7 +11109,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="12.75" hidden="1">
+    <row r="95" spans="1:31" ht="12.75">
       <c r="A95" s="43" t="s">
         <v>125</v>
       </c>
@@ -11190,7 +11181,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="12.75" hidden="1">
+    <row r="96" spans="1:31" ht="12.75">
       <c r="A96" s="43" t="s">
         <v>127</v>
       </c>
@@ -11263,7 +11254,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="12.75" hidden="1">
+    <row r="97" spans="1:31" ht="12.75">
       <c r="A97" s="43" t="s">
         <v>47</v>
       </c>
@@ -11335,7 +11326,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="12.75" hidden="1">
+    <row r="98" spans="1:31" ht="12.75">
       <c r="A98" s="43" t="s">
         <v>123</v>
       </c>
@@ -11407,7 +11398,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="12.75" hidden="1">
+    <row r="99" spans="1:31" ht="12.75">
       <c r="A99" s="43" t="s">
         <v>125</v>
       </c>
@@ -11479,7 +11470,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="12.75" hidden="1">
+    <row r="100" spans="1:31" ht="12.75">
       <c r="A100" s="43" t="s">
         <v>127</v>
       </c>
@@ -11551,7 +11542,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="12.75" hidden="1">
+    <row r="101" spans="1:31" ht="12.75">
       <c r="A101" s="43" t="s">
         <v>646</v>
       </c>
@@ -11628,7 +11619,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="12.75" hidden="1">
+    <row r="102" spans="1:31" ht="12.75">
       <c r="A102" s="43" t="s">
         <v>123</v>
       </c>
@@ -11700,7 +11691,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="12.75" hidden="1">
+    <row r="103" spans="1:31" ht="12.75">
       <c r="A103" s="43" t="s">
         <v>125</v>
       </c>
@@ -11772,7 +11763,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="12.75" hidden="1">
+    <row r="104" spans="1:31" ht="12.75">
       <c r="A104" s="43" t="s">
         <v>127</v>
       </c>
@@ -11844,7 +11835,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="12.75" hidden="1">
+    <row r="105" spans="1:31" ht="12.75">
       <c r="A105" s="43" t="s">
         <v>139</v>
       </c>
@@ -11917,7 +11908,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="12.75" hidden="1">
+    <row r="106" spans="1:31" ht="12.75">
       <c r="A106" s="43" t="s">
         <v>142</v>
       </c>
@@ -11990,7 +11981,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="12.75" hidden="1">
+    <row r="107" spans="1:31" ht="12.75">
       <c r="A107" s="43" t="s">
         <v>144</v>
       </c>
@@ -12063,7 +12054,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="12.75" hidden="1">
+    <row r="108" spans="1:31" ht="12.75">
       <c r="A108" s="43" t="s">
         <v>146</v>
       </c>
@@ -12136,7 +12127,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="12.75" hidden="1">
+    <row r="109" spans="1:31" ht="12.75">
       <c r="A109" s="43" t="s">
         <v>148</v>
       </c>
@@ -12209,7 +12200,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="12.75" hidden="1">
+    <row r="110" spans="1:31" ht="12.75">
       <c r="A110" s="43" t="s">
         <v>150</v>
       </c>
@@ -12282,7 +12273,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="12.75" hidden="1">
+    <row r="111" spans="1:31" ht="12.75">
       <c r="A111" s="43" t="s">
         <v>648</v>
       </c>
@@ -12359,7 +12350,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="12.75" hidden="1">
+    <row r="112" spans="1:31" ht="12.75">
       <c r="A112" s="43" t="s">
         <v>650</v>
       </c>
@@ -12436,7 +12427,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="12.75" hidden="1">
+    <row r="113" spans="1:31" ht="12.75">
       <c r="A113" s="43" t="s">
         <v>646</v>
       </c>
@@ -12513,7 +12504,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="12.75" hidden="1">
+    <row r="114" spans="1:31" ht="12.75">
       <c r="A114" s="43" t="s">
         <v>123</v>
       </c>
@@ -12586,7 +12577,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="12.75" hidden="1">
+    <row r="115" spans="1:31" ht="12.75">
       <c r="A115" s="43" t="s">
         <v>125</v>
       </c>
@@ -12659,7 +12650,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="12.75" hidden="1">
+    <row r="116" spans="1:31" ht="12.75">
       <c r="A116" s="43" t="s">
         <v>127</v>
       </c>
@@ -12733,7 +12724,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="12.75" hidden="1">
+    <row r="117" spans="1:31" ht="12.75">
       <c r="A117" s="43" t="s">
         <v>648</v>
       </c>
@@ -12811,7 +12802,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="12.75" hidden="1">
+    <row r="118" spans="1:31" ht="12.75">
       <c r="A118" s="43" t="s">
         <v>650</v>
       </c>
@@ -12889,7 +12880,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="12.75" hidden="1">
+    <row r="119" spans="1:31" ht="12.75">
       <c r="A119" s="43" t="s">
         <v>646</v>
       </c>
@@ -12967,7 +12958,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="12.75" hidden="1">
+    <row r="120" spans="1:31" ht="12.75">
       <c r="A120" s="43" t="s">
         <v>648</v>
       </c>
@@ -13045,7 +13036,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="12.75" hidden="1">
+    <row r="121" spans="1:31" ht="12.75">
       <c r="A121" s="43" t="s">
         <v>123</v>
       </c>
@@ -13118,7 +13109,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="12.75" hidden="1">
+    <row r="122" spans="1:31" ht="12.75">
       <c r="A122" s="43" t="s">
         <v>125</v>
       </c>
@@ -13191,7 +13182,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="12.75" hidden="1">
+    <row r="123" spans="1:31" ht="12.75">
       <c r="A123" s="43" t="s">
         <v>127</v>
       </c>
@@ -13264,7 +13255,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="12.75" hidden="1">
+    <row r="124" spans="1:31" ht="12.75">
       <c r="A124" s="43" t="s">
         <v>650</v>
       </c>
@@ -13342,7 +13333,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="12.75" hidden="1">
+    <row r="125" spans="1:31" ht="12.75">
       <c r="A125" s="43" t="s">
         <v>123</v>
       </c>
@@ -13415,7 +13406,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="12.75" hidden="1">
+    <row r="126" spans="1:31" ht="12.75">
       <c r="A126" s="43" t="s">
         <v>125</v>
       </c>
@@ -13488,7 +13479,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="12.75" hidden="1">
+    <row r="127" spans="1:31" ht="12.75">
       <c r="A127" s="43" t="s">
         <v>127</v>
       </c>
@@ -13561,7 +13552,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="12.75" hidden="1">
+    <row r="128" spans="1:31" ht="12.75">
       <c r="A128" s="43" t="s">
         <v>53</v>
       </c>
@@ -13631,7 +13622,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="12.75" hidden="1">
+    <row r="129" spans="1:31" ht="12.75">
       <c r="A129" s="43" t="s">
         <v>53</v>
       </c>
@@ -13704,7 +13695,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="12.75" hidden="1">
+    <row r="130" spans="1:31" ht="12.75">
       <c r="A130" s="43" t="s">
         <v>53</v>
       </c>
@@ -13777,7 +13768,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="12.75" hidden="1">
+    <row r="131" spans="1:31" ht="12.75">
       <c r="A131" s="43" t="s">
         <v>53</v>
       </c>
@@ -13850,7 +13841,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="12.75" hidden="1">
+    <row r="132" spans="1:31" ht="12.75">
       <c r="A132" s="43" t="s">
         <v>53</v>
       </c>
@@ -13924,7 +13915,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="12.75" hidden="1">
+    <row r="133" spans="1:31" ht="12.75">
       <c r="A133" s="84" t="s">
         <v>53</v>
       </c>
@@ -13996,7 +13987,7 @@
       <c r="AC133" s="47"/>
       <c r="AD133" s="47"/>
     </row>
-    <row r="134" spans="1:31" ht="12.75" hidden="1">
+    <row r="134" spans="1:31" ht="12.75">
       <c r="A134" s="84" t="s">
         <v>50</v>
       </c>
@@ -14067,7 +14058,7 @@
       <c r="AC134" s="47"/>
       <c r="AD134" s="47"/>
     </row>
-    <row r="135" spans="1:31" ht="12.75" hidden="1">
+    <row r="135" spans="1:31" ht="12.75">
       <c r="A135" s="84" t="s">
         <v>123</v>
       </c>
@@ -14139,7 +14130,7 @@
       <c r="AC135" s="47"/>
       <c r="AD135" s="45"/>
     </row>
-    <row r="136" spans="1:31" ht="12.75" hidden="1">
+    <row r="136" spans="1:31" ht="12.75">
       <c r="A136" s="84" t="s">
         <v>125</v>
       </c>
@@ -14211,7 +14202,7 @@
       <c r="AC136" s="47"/>
       <c r="AD136" s="45"/>
     </row>
-    <row r="137" spans="1:31" ht="12.75" hidden="1">
+    <row r="137" spans="1:31" ht="12.75">
       <c r="A137" s="84" t="s">
         <v>127</v>
       </c>
@@ -14283,7 +14274,7 @@
       <c r="AC137" s="47"/>
       <c r="AD137" s="45"/>
     </row>
-    <row r="138" spans="1:31" ht="12.75" hidden="1">
+    <row r="138" spans="1:31" ht="12.75">
       <c r="A138" s="84" t="s">
         <v>50</v>
       </c>
@@ -14355,7 +14346,7 @@
       <c r="AC138" s="47"/>
       <c r="AD138" s="45"/>
     </row>
-    <row r="139" spans="1:31" ht="12.75" hidden="1">
+    <row r="139" spans="1:31" ht="12.75">
       <c r="A139" s="84" t="s">
         <v>123</v>
       </c>
@@ -14428,7 +14419,7 @@
       <c r="AD139" s="45"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="12.75" hidden="1">
+    <row r="140" spans="1:31" ht="12.75">
       <c r="A140" s="84" t="s">
         <v>125</v>
       </c>
@@ -14501,7 +14492,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="12.75" hidden="1">
+    <row r="141" spans="1:31" ht="12.75">
       <c r="A141" s="84" t="s">
         <v>127</v>
       </c>
@@ -14574,7 +14565,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="12.75" hidden="1">
+    <row r="142" spans="1:31" ht="12.75">
       <c r="A142" s="84" t="s">
         <v>646</v>
       </c>
@@ -14651,7 +14642,7 @@
       <c r="AC142" s="47"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="12.75" hidden="1">
+    <row r="143" spans="1:31" ht="12.75">
       <c r="A143" s="84" t="s">
         <v>123</v>
       </c>
@@ -14723,7 +14714,7 @@
       <c r="AC143" s="47"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="12.75" hidden="1">
+    <row r="144" spans="1:31" ht="12.75">
       <c r="A144" s="84" t="s">
         <v>125</v>
       </c>
@@ -14795,7 +14786,7 @@
       <c r="AC144" s="47"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="12.75" hidden="1">
+    <row r="145" spans="1:31" ht="12.75">
       <c r="A145" s="84" t="s">
         <v>127</v>
       </c>
@@ -14867,7 +14858,7 @@
       <c r="AC145" s="47"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="12.75" hidden="1">
+    <row r="146" spans="1:31" ht="12.75">
       <c r="A146" s="90" t="s">
         <v>648</v>
       </c>
@@ -14944,7 +14935,7 @@
       <c r="AC146" s="47"/>
       <c r="AD146" s="45"/>
     </row>
-    <row r="147" spans="1:31" ht="12.75" hidden="1">
+    <row r="147" spans="1:31" ht="12.75">
       <c r="A147" s="43" t="s">
         <v>123</v>
       </c>
@@ -15016,7 +15007,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="12.75" hidden="1">
+    <row r="148" spans="1:31" ht="12.75">
       <c r="A148" s="43" t="s">
         <v>125</v>
       </c>
@@ -15088,7 +15079,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="12.75" hidden="1">
+    <row r="149" spans="1:31" ht="12.75">
       <c r="A149" s="43" t="s">
         <v>127</v>
       </c>
@@ -15160,7 +15151,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="12.75" hidden="1">
+    <row r="150" spans="1:31" ht="12.75">
       <c r="A150" s="43" t="s">
         <v>650</v>
       </c>
@@ -15237,7 +15228,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="12.75" hidden="1">
+    <row r="151" spans="1:31" ht="12.75">
       <c r="A151" s="43" t="s">
         <v>123</v>
       </c>
@@ -15309,7 +15300,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="12.75" hidden="1">
+    <row r="152" spans="1:31" ht="12.75">
       <c r="A152" s="43" t="s">
         <v>125</v>
       </c>
@@ -15382,7 +15373,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="12.75" hidden="1">
+    <row r="153" spans="1:31" ht="12.75">
       <c r="A153" s="43" t="s">
         <v>127</v>
       </c>
@@ -15453,7 +15444,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="12.75" hidden="1">
+    <row r="154" spans="1:31" ht="12.75">
       <c r="A154" s="43" t="s">
         <v>165</v>
       </c>
@@ -15488,7 +15479,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>1935</v>
       </c>
-      <c r="K154" s="45">
+      <c r="K154" s="47">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1086.5</v>
       </c>
@@ -15532,7 +15523,7 @@
       <c r="AC154" s="47"/>
       <c r="AD154" s="47"/>
     </row>
-    <row r="155" spans="1:31" ht="12.75" hidden="1">
+    <row r="155" spans="1:31" ht="12.75">
       <c r="A155" s="43" t="s">
         <v>167</v>
       </c>
@@ -15567,7 +15558,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>2095</v>
       </c>
-      <c r="K155" s="45">
+      <c r="K155" s="47">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1636.5</v>
       </c>
@@ -15611,7 +15602,7 @@
       <c r="AC155" s="47"/>
       <c r="AD155" s="45"/>
     </row>
-    <row r="156" spans="1:31" ht="12.75" hidden="1">
+    <row r="156" spans="1:31" ht="12.75">
       <c r="A156" s="43" t="s">
         <v>169</v>
       </c>
@@ -15646,7 +15637,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>2575</v>
       </c>
-      <c r="K156" s="45">
+      <c r="K156" s="47">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2086.5</v>
       </c>
@@ -15690,7 +15681,7 @@
       <c r="AC156" s="47"/>
       <c r="AD156" s="45"/>
     </row>
-    <row r="157" spans="1:31" ht="12.75" hidden="1">
+    <row r="157" spans="1:31" ht="12.75">
       <c r="A157" s="43" t="s">
         <v>1</v>
       </c>
@@ -15725,7 +15716,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
         <v>3405</v>
       </c>
-      <c r="K157" s="45">
+      <c r="K157" s="47">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2336.5</v>
       </c>
@@ -15803,8 +15794,9 @@
       <c r="J158" s="85">
         <v>0</v>
       </c>
-      <c r="K158" s="85">
-        <v>4562.5</v>
+      <c r="K158" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4662.5</v>
       </c>
       <c r="L158" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
@@ -15874,8 +15866,9 @@
       <c r="J159" s="85">
         <v>500</v>
       </c>
-      <c r="K159" s="85">
-        <v>4062.5</v>
+      <c r="K159" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4162.5</v>
       </c>
       <c r="L159" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
@@ -15945,8 +15938,9 @@
       <c r="J160" s="85">
         <v>925</v>
       </c>
-      <c r="K160" s="85">
-        <v>3637.5</v>
+      <c r="K160" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3737.5</v>
       </c>
       <c r="L160" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
@@ -16016,8 +16010,9 @@
       <c r="J161" s="85">
         <v>0</v>
       </c>
-      <c r="K161" s="85">
-        <v>2362.5</v>
+      <c r="K161" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2512.5</v>
       </c>
       <c r="L161" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
@@ -16087,8 +16082,9 @@
       <c r="J162" s="85">
         <v>0</v>
       </c>
-      <c r="K162" s="85">
-        <v>3362.5</v>
+      <c r="K162" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3562.5</v>
       </c>
       <c r="L162" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
@@ -16158,8 +16154,9 @@
       <c r="J163" s="85">
         <v>500</v>
       </c>
-      <c r="K163" s="85">
-        <v>2862.5</v>
+      <c r="K163" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3062.5</v>
       </c>
       <c r="L163" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
@@ -16229,8 +16226,9 @@
       <c r="J164" s="85">
         <v>625</v>
       </c>
-      <c r="K164" s="85">
-        <v>2737.5</v>
+      <c r="K164" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>2937.5</v>
       </c>
       <c r="L164" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
@@ -16300,8 +16298,9 @@
       <c r="J165" s="85">
         <v>0</v>
       </c>
-      <c r="K165" s="85">
-        <v>4012.5</v>
+      <c r="K165" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>4112.5</v>
       </c>
       <c r="L165" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
@@ -16371,8 +16370,9 @@
       <c r="J166" s="85">
         <v>500</v>
       </c>
-      <c r="K166" s="85">
-        <v>3512.5</v>
+      <c r="K166" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3612.5</v>
       </c>
       <c r="L166" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
@@ -16442,8 +16442,9 @@
       <c r="J167" s="91">
         <v>875</v>
       </c>
-      <c r="K167" s="91">
-        <v>3137.5</v>
+      <c r="K167" s="47">
+        <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
+        <v>3237.5</v>
       </c>
       <c r="L167" s="101">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
@@ -16479,7 +16480,7 @@
       <c r="AC167" s="47"/>
       <c r="AD167" s="45"/>
     </row>
-    <row r="168" spans="1:30" ht="12.75" hidden="1">
+    <row r="168" spans="1:30" ht="12.75">
       <c r="A168" s="84" t="s">
         <v>646</v>
       </c>
@@ -16521,13 +16522,10 @@
         <v>6690</v>
       </c>
       <c r="M168" s="85"/>
-      <c r="N168" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="N168" s="85"/>
       <c r="O168" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P168" s="85"/>
       <c r="Q168" s="86">
@@ -16556,7 +16554,7 @@
       <c r="AC168" s="47"/>
       <c r="AD168" s="45"/>
     </row>
-    <row r="169" spans="1:30" ht="12.75" hidden="1">
+    <row r="169" spans="1:30" ht="12.75">
       <c r="A169" s="84" t="s">
         <v>648</v>
       </c>
@@ -16598,13 +16596,10 @@
         <v>4990</v>
       </c>
       <c r="M169" s="85"/>
-      <c r="N169" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N169" s="85"/>
       <c r="O169" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2332.5</v>
       </c>
       <c r="P169" s="85"/>
       <c r="Q169" s="86">
@@ -16633,7 +16628,7 @@
       <c r="AC169" s="47"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="12.75" hidden="1">
+    <row r="170" spans="1:30" ht="12.75">
       <c r="A170" s="84" t="s">
         <v>650</v>
       </c>
@@ -16675,13 +16670,10 @@
         <v>5790</v>
       </c>
       <c r="M170" s="85"/>
-      <c r="N170" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N170" s="85"/>
       <c r="O170" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2732.5</v>
       </c>
       <c r="P170" s="85"/>
       <c r="Q170" s="86">
@@ -16710,7 +16702,7 @@
       <c r="AC170" s="47"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="12.75" hidden="1">
+    <row r="171" spans="1:30" ht="12.75">
       <c r="A171" s="84" t="s">
         <v>47</v>
       </c>
@@ -16781,7 +16773,7 @@
       <c r="AB171" s="78"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="12.75" hidden="1">
+    <row r="172" spans="1:30" ht="12.75">
       <c r="A172" s="84" t="s">
         <v>47</v>
       </c>
@@ -16853,7 +16845,7 @@
       <c r="AC172" s="45"/>
       <c r="AD172" s="45"/>
     </row>
-    <row r="173" spans="1:30" ht="12.75" hidden="1">
+    <row r="173" spans="1:30" ht="12.75">
       <c r="A173" s="84" t="s">
         <v>47</v>
       </c>
@@ -16925,7 +16917,7 @@
       <c r="AC173" s="45"/>
       <c r="AD173" s="45"/>
     </row>
-    <row r="174" spans="1:30" ht="12.75" hidden="1">
+    <row r="174" spans="1:30" ht="12.75">
       <c r="A174" s="84" t="s">
         <v>47</v>
       </c>
@@ -16997,7 +16989,7 @@
       <c r="AC174" s="45"/>
       <c r="AD174" s="45"/>
     </row>
-    <row r="175" spans="1:30" ht="12.75" hidden="1">
+    <row r="175" spans="1:30" ht="12.75">
       <c r="A175" s="84" t="s">
         <v>47</v>
       </c>
@@ -17069,7 +17061,7 @@
       <c r="AC175" s="45"/>
       <c r="AD175" s="45"/>
     </row>
-    <row r="176" spans="1:30" ht="12.75" hidden="1">
+    <row r="176" spans="1:30" ht="12.75">
       <c r="A176" s="84" t="s">
         <v>646</v>
       </c>
@@ -17111,13 +17103,10 @@
         <v>6690</v>
       </c>
       <c r="M176" s="85"/>
-      <c r="N176" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="N176" s="85"/>
       <c r="O176" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P176" s="85"/>
       <c r="Q176" s="86">
@@ -17146,7 +17135,7 @@
       <c r="AC176" s="45"/>
       <c r="AD176" s="45"/>
     </row>
-    <row r="177" spans="1:30" ht="12.75" hidden="1">
+    <row r="177" spans="1:30" ht="12.75">
       <c r="A177" s="84" t="s">
         <v>648</v>
       </c>
@@ -17188,13 +17177,10 @@
         <v>4990</v>
       </c>
       <c r="M177" s="85"/>
-      <c r="N177" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N177" s="85"/>
       <c r="O177" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2332.5</v>
       </c>
       <c r="P177" s="85"/>
       <c r="Q177" s="86">
@@ -17223,7 +17209,7 @@
       <c r="AC177" s="45"/>
       <c r="AD177" s="45"/>
     </row>
-    <row r="178" spans="1:30" ht="12.75" hidden="1">
+    <row r="178" spans="1:30" ht="12.75">
       <c r="A178" s="84" t="s">
         <v>650</v>
       </c>
@@ -17265,13 +17251,10 @@
         <v>5790</v>
       </c>
       <c r="M178" s="85"/>
-      <c r="N178" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N178" s="85"/>
       <c r="O178" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2732.5</v>
       </c>
       <c r="P178" s="85"/>
       <c r="Q178" s="86">
@@ -17300,7 +17283,7 @@
       <c r="AC178" s="45"/>
       <c r="AD178" s="45"/>
     </row>
-    <row r="179" spans="1:30" ht="12.75" hidden="1">
+    <row r="179" spans="1:30" ht="12.75">
       <c r="A179" s="84" t="s">
         <v>57</v>
       </c>
@@ -17369,7 +17352,7 @@
       <c r="AC179" s="45"/>
       <c r="AD179" s="45"/>
     </row>
-    <row r="180" spans="1:30" ht="12.75" hidden="1">
+    <row r="180" spans="1:30" ht="12.75">
       <c r="A180" s="84" t="s">
         <v>57</v>
       </c>
@@ -17441,7 +17424,7 @@
       <c r="AC180" s="45"/>
       <c r="AD180" s="45"/>
     </row>
-    <row r="181" spans="1:30" ht="12.75" hidden="1">
+    <row r="181" spans="1:30" ht="12.75">
       <c r="A181" s="84" t="s">
         <v>57</v>
       </c>
@@ -17513,7 +17496,7 @@
       <c r="AC181" s="45"/>
       <c r="AD181" s="45"/>
     </row>
-    <row r="182" spans="1:30" ht="12.75" hidden="1">
+    <row r="182" spans="1:30" ht="12.75">
       <c r="A182" s="84" t="s">
         <v>57</v>
       </c>
@@ -17585,7 +17568,7 @@
       <c r="AC182" s="45"/>
       <c r="AD182" s="45"/>
     </row>
-    <row r="183" spans="1:30" ht="12.75" hidden="1">
+    <row r="183" spans="1:30" ht="12.75">
       <c r="A183" s="84" t="s">
         <v>57</v>
       </c>
@@ -17658,7 +17641,7 @@
       <c r="AC183" s="45"/>
       <c r="AD183" s="45"/>
     </row>
-    <row r="184" spans="1:30" ht="12.75" hidden="1">
+    <row r="184" spans="1:30" ht="12.75">
       <c r="A184" s="84" t="s">
         <v>57</v>
       </c>
@@ -17730,7 +17713,7 @@
       <c r="AC184" s="45"/>
       <c r="AD184" s="45"/>
     </row>
-    <row r="185" spans="1:30" ht="12.75" hidden="1">
+    <row r="185" spans="1:30" ht="12.75">
       <c r="A185" s="84" t="s">
         <v>646</v>
       </c>
@@ -17772,13 +17755,10 @@
         <v>6690</v>
       </c>
       <c r="M185" s="85"/>
-      <c r="N185" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="N185" s="85"/>
       <c r="O185" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P185" s="85"/>
       <c r="Q185" s="86">
@@ -17807,7 +17787,7 @@
       <c r="AC185" s="45"/>
       <c r="AD185" s="45"/>
     </row>
-    <row r="186" spans="1:30" ht="12.75" hidden="1">
+    <row r="186" spans="1:30" ht="12.75">
       <c r="A186" s="84" t="s">
         <v>648</v>
       </c>
@@ -17849,13 +17829,10 @@
         <v>4990</v>
       </c>
       <c r="M186" s="85"/>
-      <c r="N186" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N186" s="85"/>
       <c r="O186" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2332.5</v>
       </c>
       <c r="P186" s="85"/>
       <c r="Q186" s="86">
@@ -17884,7 +17861,7 @@
       <c r="AC186" s="45"/>
       <c r="AD186" s="45"/>
     </row>
-    <row r="187" spans="1:30" ht="12.75" hidden="1">
+    <row r="187" spans="1:30" ht="12.75">
       <c r="A187" s="84" t="s">
         <v>650</v>
       </c>
@@ -17926,13 +17903,10 @@
         <v>5790</v>
       </c>
       <c r="M187" s="85"/>
-      <c r="N187" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N187" s="85"/>
       <c r="O187" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2732.5</v>
       </c>
       <c r="P187" s="85"/>
       <c r="Q187" s="86">
@@ -17961,7 +17935,7 @@
       <c r="AC187" s="45"/>
       <c r="AD187" s="45"/>
     </row>
-    <row r="188" spans="1:30" ht="12.75" hidden="1">
+    <row r="188" spans="1:30" ht="12.75">
       <c r="A188" s="84" t="s">
         <v>646</v>
       </c>
@@ -18003,13 +17977,10 @@
         <v>6690</v>
       </c>
       <c r="M188" s="85"/>
-      <c r="N188" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="N188" s="85"/>
       <c r="O188" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P188" s="85"/>
       <c r="Q188" s="86">
@@ -18038,7 +18009,7 @@
       <c r="AC188" s="45"/>
       <c r="AD188" s="45"/>
     </row>
-    <row r="189" spans="1:30" ht="12.75" hidden="1">
+    <row r="189" spans="1:30" ht="12.75">
       <c r="A189" s="84" t="s">
         <v>648</v>
       </c>
@@ -18080,13 +18051,10 @@
         <v>4990</v>
       </c>
       <c r="M189" s="85"/>
-      <c r="N189" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N189" s="85"/>
       <c r="O189" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2332.5</v>
       </c>
       <c r="P189" s="85"/>
       <c r="Q189" s="86">
@@ -18115,7 +18083,7 @@
       <c r="AC189" s="45"/>
       <c r="AD189" s="45"/>
     </row>
-    <row r="190" spans="1:30" ht="12.75" hidden="1">
+    <row r="190" spans="1:30" ht="12.75">
       <c r="A190" s="84" t="s">
         <v>650</v>
       </c>
@@ -18157,13 +18125,10 @@
         <v>5790</v>
       </c>
       <c r="M190" s="85"/>
-      <c r="N190" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N190" s="85"/>
       <c r="O190" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2732.5</v>
       </c>
       <c r="P190" s="85"/>
       <c r="Q190" s="86">
@@ -18192,7 +18157,7 @@
       <c r="AC190" s="45"/>
       <c r="AD190" s="45"/>
     </row>
-    <row r="191" spans="1:30" ht="12.75" hidden="1">
+    <row r="191" spans="1:30" ht="12.75">
       <c r="A191" s="84" t="s">
         <v>646</v>
       </c>
@@ -18234,13 +18199,10 @@
         <v>6690</v>
       </c>
       <c r="M191" s="85"/>
-      <c r="N191" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="N191" s="85"/>
       <c r="O191" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P191" s="85"/>
       <c r="Q191" s="86">
@@ -18269,7 +18231,7 @@
       <c r="AC191" s="45"/>
       <c r="AD191" s="45"/>
     </row>
-    <row r="192" spans="1:30" ht="12.75" hidden="1">
+    <row r="192" spans="1:30" ht="12.75">
       <c r="A192" s="84" t="s">
         <v>648</v>
       </c>
@@ -18311,13 +18273,10 @@
         <v>4990</v>
       </c>
       <c r="M192" s="85"/>
-      <c r="N192" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N192" s="85"/>
       <c r="O192" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2332.5</v>
       </c>
       <c r="P192" s="85"/>
       <c r="Q192" s="86">
@@ -18346,7 +18305,7 @@
       <c r="AC192" s="45"/>
       <c r="AD192" s="45"/>
     </row>
-    <row r="193" spans="1:30" ht="12.75" hidden="1">
+    <row r="193" spans="1:30" ht="12.75">
       <c r="A193" s="84" t="s">
         <v>650</v>
       </c>
@@ -18388,13 +18347,10 @@
         <v>5790</v>
       </c>
       <c r="M193" s="85"/>
-      <c r="N193" s="85">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N193" s="85"/>
       <c r="O193" s="85">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>2732.5</v>
       </c>
       <c r="P193" s="85"/>
       <c r="Q193" s="86">
@@ -18423,7 +18379,7 @@
       <c r="AC193" s="45"/>
       <c r="AD193" s="45"/>
     </row>
-    <row r="194" spans="1:30" ht="12.75" hidden="1">
+    <row r="194" spans="1:30" ht="12.75">
       <c r="A194" s="84" t="s">
         <v>59</v>
       </c>
@@ -18495,7 +18451,7 @@
       <c r="AC194" s="45"/>
       <c r="AD194" s="45"/>
     </row>
-    <row r="195" spans="1:30" ht="12.75" hidden="1">
+    <row r="195" spans="1:30" ht="12.75">
       <c r="A195" s="84" t="s">
         <v>59</v>
       </c>
@@ -18567,7 +18523,7 @@
       <c r="AC195" s="45"/>
       <c r="AD195" s="45"/>
     </row>
-    <row r="196" spans="1:30" ht="12.75" hidden="1">
+    <row r="196" spans="1:30" ht="12.75">
       <c r="A196" s="84" t="s">
         <v>59</v>
       </c>
@@ -18639,7 +18595,7 @@
       <c r="AC196" s="45"/>
       <c r="AD196" s="45"/>
     </row>
-    <row r="197" spans="1:30" ht="12.75" hidden="1">
+    <row r="197" spans="1:30" ht="12.75">
       <c r="A197" s="84" t="s">
         <v>59</v>
       </c>
@@ -18711,7 +18667,7 @@
       <c r="AC197" s="45"/>
       <c r="AD197" s="45"/>
     </row>
-    <row r="198" spans="1:30" ht="12.75" hidden="1">
+    <row r="198" spans="1:30" ht="12.75">
       <c r="A198" s="84" t="s">
         <v>59</v>
       </c>
@@ -18784,7 +18740,7 @@
       <c r="AC198" s="45"/>
       <c r="AD198" s="45"/>
     </row>
-    <row r="199" spans="1:30" ht="12.75" hidden="1">
+    <row r="199" spans="1:30" ht="12.75">
       <c r="A199" s="90" t="s">
         <v>59</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1513" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB4CDEA-4BA3-4656-87AF-4962C7F8A6A1}"/>
+  <xr:revisionPtr revIDLastSave="1521" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DF51AE1-3CD8-480D-B60C-70D004FB9EB3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="1035" yWindow="4110" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="648">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -2002,18 +2002,6 @@
   </si>
   <si>
     <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone RIE Digital Envision 17 62SDRWC</t>
-  </si>
-  <si>
-    <t>Beltone Envision 17 62SDRWC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone RIE Digital Envision 6 62SDRWC</t>
-  </si>
-  <si>
-    <t>Beltone Envision 6 62SDRWC Digital RIE</t>
   </si>
   <si>
     <t>Beltone RIE Digital Envision 9 62SDRWC</t>
@@ -2380,7 +2368,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2574,6 +2562,19 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="6" borderId="19" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="11" fillId="6" borderId="19" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2590,20 +2591,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="6" borderId="19" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="11" fillId="6" borderId="19" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3372,8 +3363,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:V193">
-    <sortCondition ref="I1:I199"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:V199">
+    <sortCondition ref="B1:B199"/>
   </sortState>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{A759776D-F1C7-439A-A017-B16601DE8834}" name="haModel" dataDxfId="56"/>
@@ -3824,10 +3815,10 @@
       <c r="A3" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="119"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
       <c r="F3" s="42"/>
@@ -3848,10 +3839,10 @@
       <c r="A5" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="118">
         <v>2</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="119"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
       <c r="F5" s="42"/>
@@ -3872,10 +3863,10 @@
       <c r="A7" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="109" t="s">
+      <c r="B7" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="110"/>
+      <c r="C7" s="119"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42"/>
       <c r="F7" s="42"/>
@@ -4234,9 +4225,9 @@
       <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="108"/>
-      <c r="B30" s="108"/>
-      <c r="C30" s="108"/>
+      <c r="A30" s="117"/>
+      <c r="B30" s="117"/>
+      <c r="C30" s="117"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="26"/>
@@ -4484,7 +4475,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11863</v>
       </c>
-      <c r="D2" s="122">
+      <c r="D2" s="115">
         <v>5819</v>
       </c>
       <c r="E2" s="46" t="s">
@@ -4498,7 +4489,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4612.5</v>
       </c>
-      <c r="H2" s="122">
+      <c r="H2" s="115">
         <v>9450</v>
       </c>
       <c r="I2" s="77" t="s">
@@ -4509,7 +4500,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4612.5</v>
       </c>
-      <c r="L2" s="122">
+      <c r="L2" s="115">
         <v>9450</v>
       </c>
       <c r="M2" s="46"/>
@@ -4554,7 +4545,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11863</v>
       </c>
-      <c r="D3" s="122">
+      <c r="D3" s="115">
         <v>5819</v>
       </c>
       <c r="E3" s="46" t="s">
@@ -4568,7 +4559,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4612.5</v>
       </c>
-      <c r="H3" s="122">
+      <c r="H3" s="115">
         <v>9450</v>
       </c>
       <c r="I3" s="77" t="s">
@@ -4579,7 +4570,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4612.5</v>
       </c>
-      <c r="L3" s="122">
+      <c r="L3" s="115">
         <v>9450</v>
       </c>
       <c r="M3" s="46"/>
@@ -4623,7 +4614,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11863</v>
       </c>
-      <c r="D4" s="122">
+      <c r="D4" s="115">
         <v>5819</v>
       </c>
       <c r="E4" s="46" t="s">
@@ -4637,7 +4628,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4612.5</v>
       </c>
-      <c r="H4" s="122">
+      <c r="H4" s="115">
         <v>9450</v>
       </c>
       <c r="I4" s="77" t="s">
@@ -4651,7 +4642,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4112.5</v>
       </c>
-      <c r="L4" s="122">
+      <c r="L4" s="115">
         <v>8450</v>
       </c>
       <c r="M4" s="46"/>
@@ -4695,7 +4686,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11863</v>
       </c>
-      <c r="D5" s="122">
+      <c r="D5" s="115">
         <v>5819</v>
       </c>
       <c r="E5" s="46" t="s">
@@ -4709,7 +4700,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4612.5</v>
       </c>
-      <c r="H5" s="122">
+      <c r="H5" s="115">
         <v>9450</v>
       </c>
       <c r="I5" s="77" t="s">
@@ -4723,7 +4714,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3687.5</v>
       </c>
-      <c r="L5" s="122">
+      <c r="L5" s="115">
         <v>7600</v>
       </c>
       <c r="M5" s="77"/>
@@ -4767,7 +4758,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6283</v>
       </c>
-      <c r="D6" s="122">
+      <c r="D6" s="115">
         <v>3029</v>
       </c>
       <c r="E6" s="46" t="s">
@@ -4781,7 +4772,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2412.5</v>
       </c>
-      <c r="H6" s="122">
+      <c r="H6" s="115">
         <v>5050</v>
       </c>
       <c r="I6" s="77" t="s">
@@ -4795,7 +4786,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2412.5</v>
       </c>
-      <c r="L6" s="122">
+      <c r="L6" s="115">
         <v>5050</v>
       </c>
       <c r="M6" s="46"/>
@@ -4834,7 +4825,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6283</v>
       </c>
-      <c r="D7" s="122">
+      <c r="D7" s="115">
         <v>3029</v>
       </c>
       <c r="E7" s="46" t="s">
@@ -4848,7 +4839,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2412.5</v>
       </c>
-      <c r="H7" s="122">
+      <c r="H7" s="115">
         <v>5050</v>
       </c>
       <c r="I7" s="77" t="s">
@@ -4859,7 +4850,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2412.5</v>
       </c>
-      <c r="L7" s="122">
+      <c r="L7" s="115">
         <v>5050</v>
       </c>
       <c r="M7" s="46"/>
@@ -4898,7 +4889,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D8" s="122">
+      <c r="D8" s="115">
         <v>1960</v>
       </c>
       <c r="E8" s="44" t="s">
@@ -4912,7 +4903,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H8" s="122">
+      <c r="H8" s="115">
         <v>3100</v>
       </c>
       <c r="I8" s="55" t="s">
@@ -4925,7 +4916,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L8" s="122"/>
+      <c r="L8" s="115"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
       <c r="O8" s="46"/>
@@ -4967,7 +4958,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D9" s="122">
+      <c r="D9" s="115">
         <v>1960</v>
       </c>
       <c r="E9" s="44" t="s">
@@ -4981,7 +4972,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H9" s="122">
+      <c r="H9" s="115">
         <v>3100</v>
       </c>
       <c r="I9" s="55" t="s">
@@ -4994,7 +4985,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L9" s="122"/>
+      <c r="L9" s="115"/>
       <c r="M9" s="46"/>
       <c r="N9" s="46"/>
       <c r="O9" s="46"/>
@@ -5036,7 +5027,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="115">
         <v>1960</v>
       </c>
       <c r="E10" s="44" t="s">
@@ -5050,7 +5041,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H10" s="122">
+      <c r="H10" s="115">
         <v>3100</v>
       </c>
       <c r="I10" s="55" t="s">
@@ -5063,7 +5054,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L10" s="122"/>
+      <c r="L10" s="115"/>
       <c r="M10" s="46"/>
       <c r="N10" s="46"/>
       <c r="O10" s="46"/>
@@ -5105,7 +5096,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D11" s="122">
+      <c r="D11" s="115">
         <v>1960</v>
       </c>
       <c r="E11" s="44" t="s">
@@ -5119,7 +5110,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H11" s="122">
+      <c r="H11" s="115">
         <v>3100</v>
       </c>
       <c r="I11" s="55" t="s">
@@ -5132,7 +5123,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L11" s="122"/>
+      <c r="L11" s="115"/>
       <c r="M11" s="46"/>
       <c r="N11" s="46"/>
       <c r="O11" s="46"/>
@@ -5174,7 +5165,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D12" s="122">
+      <c r="D12" s="115">
         <v>1960</v>
       </c>
       <c r="E12" s="44" t="s">
@@ -5188,7 +5179,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H12" s="122">
+      <c r="H12" s="115">
         <v>3100</v>
       </c>
       <c r="I12" s="55" t="s">
@@ -5201,7 +5192,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L12" s="122"/>
+      <c r="L12" s="115"/>
       <c r="M12" s="46"/>
       <c r="N12" s="46"/>
       <c r="O12" s="46"/>
@@ -5243,7 +5234,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D13" s="122">
+      <c r="D13" s="115">
         <v>1960</v>
       </c>
       <c r="E13" s="44" t="s">
@@ -5257,7 +5248,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H13" s="122">
+      <c r="H13" s="115">
         <v>3100</v>
       </c>
       <c r="I13" s="55" t="s">
@@ -5270,7 +5261,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L13" s="122"/>
+      <c r="L13" s="115"/>
       <c r="M13" s="46"/>
       <c r="N13" s="46"/>
       <c r="O13" s="46"/>
@@ -5312,7 +5303,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D14" s="122">
+      <c r="D14" s="115">
         <v>1960</v>
       </c>
       <c r="E14" s="44" t="s">
@@ -5326,7 +5317,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H14" s="122">
+      <c r="H14" s="115">
         <v>3100</v>
       </c>
       <c r="I14" s="55" t="s">
@@ -5339,7 +5330,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L14" s="122"/>
+      <c r="L14" s="115"/>
       <c r="M14" s="46"/>
       <c r="N14" s="46"/>
       <c r="O14" s="46"/>
@@ -5379,7 +5370,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D15" s="122">
+      <c r="D15" s="115">
         <v>1960</v>
       </c>
       <c r="E15" s="44" t="s">
@@ -5393,7 +5384,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H15" s="122">
+      <c r="H15" s="115">
         <v>3100</v>
       </c>
       <c r="I15" s="55" t="s">
@@ -5406,7 +5397,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L15" s="122"/>
+      <c r="L15" s="115"/>
       <c r="M15" s="46"/>
       <c r="N15" s="46"/>
       <c r="O15" s="46"/>
@@ -5447,7 +5438,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D16" s="122">
+      <c r="D16" s="115">
         <v>2345</v>
       </c>
       <c r="E16" s="44" t="s">
@@ -5461,7 +5452,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H16" s="122">
+      <c r="H16" s="115">
         <v>3500</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -5474,7 +5465,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L16" s="122"/>
+      <c r="L16" s="115"/>
       <c r="M16" s="46"/>
       <c r="N16" s="46"/>
       <c r="O16" s="46"/>
@@ -5517,7 +5508,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4915</v>
       </c>
-      <c r="D17" s="122">
+      <c r="D17" s="115">
         <v>2345</v>
       </c>
       <c r="E17" s="44" t="s">
@@ -5531,7 +5522,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1637.5</v>
       </c>
-      <c r="H17" s="122">
+      <c r="H17" s="115">
         <v>3500</v>
       </c>
       <c r="I17" s="55" t="s">
@@ -5544,7 +5535,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1637.5</v>
       </c>
-      <c r="L17" s="122"/>
+      <c r="L17" s="115"/>
       <c r="M17" s="46"/>
       <c r="N17" s="46"/>
       <c r="O17" s="46"/>
@@ -5586,7 +5577,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D18" s="122">
+      <c r="D18" s="115">
         <v>2345</v>
       </c>
       <c r="E18" s="44" t="s">
@@ -5600,7 +5591,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H18" s="122">
+      <c r="H18" s="115">
         <v>3500</v>
       </c>
       <c r="I18" s="55" t="s">
@@ -5613,7 +5604,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L18" s="122"/>
+      <c r="L18" s="115"/>
       <c r="M18" s="46"/>
       <c r="N18" s="46"/>
       <c r="O18" s="46"/>
@@ -5655,7 +5646,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D19" s="122">
+      <c r="D19" s="115">
         <v>2345</v>
       </c>
       <c r="E19" s="44" t="s">
@@ -5669,7 +5660,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H19" s="122">
+      <c r="H19" s="115">
         <v>3500</v>
       </c>
       <c r="I19" s="55" t="s">
@@ -5682,7 +5673,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L19" s="122"/>
+      <c r="L19" s="115"/>
       <c r="M19" s="46"/>
       <c r="N19" s="46"/>
       <c r="O19" s="46"/>
@@ -5724,7 +5715,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="115">
         <v>2345</v>
       </c>
       <c r="E20" s="44" t="s">
@@ -5738,7 +5729,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H20" s="122">
+      <c r="H20" s="115">
         <v>3500</v>
       </c>
       <c r="I20" s="55" t="s">
@@ -5751,7 +5742,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L20" s="122"/>
+      <c r="L20" s="115"/>
       <c r="M20" s="46"/>
       <c r="N20" s="46"/>
       <c r="O20" s="46"/>
@@ -5793,7 +5784,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D21" s="122">
+      <c r="D21" s="115">
         <v>2345</v>
       </c>
       <c r="E21" s="44" t="s">
@@ -5807,7 +5798,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H21" s="122">
+      <c r="H21" s="115">
         <v>3500</v>
       </c>
       <c r="I21" s="55" t="s">
@@ -5820,7 +5811,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L21" s="122"/>
+      <c r="L21" s="115"/>
       <c r="M21" s="46"/>
       <c r="N21" s="46"/>
       <c r="O21" s="46"/>
@@ -5862,7 +5853,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D22" s="122">
+      <c r="D22" s="115">
         <v>2345</v>
       </c>
       <c r="E22" s="44" t="s">
@@ -5876,7 +5867,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H22" s="122">
+      <c r="H22" s="115">
         <v>3500</v>
       </c>
       <c r="I22" s="55" t="s">
@@ -5889,7 +5880,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L22" s="122"/>
+      <c r="L22" s="115"/>
       <c r="M22" s="46"/>
       <c r="N22" s="46"/>
       <c r="O22" s="46"/>
@@ -5931,7 +5922,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D23" s="122">
+      <c r="D23" s="115">
         <v>2345</v>
       </c>
       <c r="E23" s="44" t="s">
@@ -5945,7 +5936,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H23" s="122">
+      <c r="H23" s="115">
         <v>3500</v>
       </c>
       <c r="I23" s="55" t="s">
@@ -5958,7 +5949,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L23" s="122"/>
+      <c r="L23" s="115"/>
       <c r="M23" s="46"/>
       <c r="N23" s="46"/>
       <c r="O23" s="46"/>
@@ -5997,7 +5988,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D24" s="122">
+      <c r="D24" s="115">
         <v>2345</v>
       </c>
       <c r="E24" s="44" t="s">
@@ -6011,7 +6002,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H24" s="122">
+      <c r="H24" s="115">
         <v>3500</v>
       </c>
       <c r="I24" s="55" t="s">
@@ -6024,7 +6015,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L24" s="122"/>
+      <c r="L24" s="115"/>
       <c r="M24" s="46"/>
       <c r="N24" s="46"/>
       <c r="O24" s="46"/>
@@ -6064,7 +6055,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D25" s="122">
+      <c r="D25" s="115">
         <v>2345</v>
       </c>
       <c r="E25" s="44" t="s">
@@ -6078,7 +6069,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H25" s="122">
+      <c r="H25" s="115">
         <v>3500</v>
       </c>
       <c r="I25" s="55" t="s">
@@ -6091,7 +6082,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L25" s="122"/>
+      <c r="L25" s="115"/>
       <c r="M25" s="46"/>
       <c r="N25" s="46"/>
       <c r="O25" s="46"/>
@@ -6132,7 +6123,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6283</v>
       </c>
-      <c r="D26" s="122">
+      <c r="D26" s="115">
         <v>3029</v>
       </c>
       <c r="E26" s="44" t="s">
@@ -6146,7 +6137,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2412.5</v>
       </c>
-      <c r="H26" s="122">
+      <c r="H26" s="115">
         <v>5050</v>
       </c>
       <c r="I26" s="55" t="s">
@@ -6159,7 +6150,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2412.5</v>
       </c>
-      <c r="L26" s="122"/>
+      <c r="L26" s="115"/>
       <c r="M26" s="46"/>
       <c r="N26" s="46"/>
       <c r="O26" s="46"/>
@@ -6202,7 +6193,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D27" s="122">
+      <c r="D27" s="115">
         <v>3029</v>
       </c>
       <c r="E27" s="44" t="s">
@@ -6216,7 +6207,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H27" s="122">
+      <c r="H27" s="115">
         <v>5050</v>
       </c>
       <c r="I27" s="55" t="s">
@@ -6229,7 +6220,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L27" s="122"/>
+      <c r="L27" s="115"/>
       <c r="M27" s="46"/>
       <c r="N27" s="46"/>
       <c r="O27" s="46"/>
@@ -6272,7 +6263,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D28" s="122">
+      <c r="D28" s="115">
         <v>3029</v>
       </c>
       <c r="E28" s="44" t="s">
@@ -6286,7 +6277,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H28" s="122">
+      <c r="H28" s="115">
         <v>5050</v>
       </c>
       <c r="I28" s="55" t="s">
@@ -6299,7 +6290,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L28" s="122"/>
+      <c r="L28" s="115"/>
       <c r="M28" s="46"/>
       <c r="N28" s="46"/>
       <c r="O28" s="46"/>
@@ -6341,7 +6332,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D29" s="122">
+      <c r="D29" s="115">
         <v>3029</v>
       </c>
       <c r="E29" s="44" t="s">
@@ -6355,7 +6346,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H29" s="122">
+      <c r="H29" s="115">
         <v>5050</v>
       </c>
       <c r="I29" s="55" t="s">
@@ -6368,7 +6359,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L29" s="122"/>
+      <c r="L29" s="115"/>
       <c r="M29" s="46"/>
       <c r="N29" s="46"/>
       <c r="O29" s="46"/>
@@ -6410,7 +6401,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D30" s="122">
+      <c r="D30" s="115">
         <v>3029</v>
       </c>
       <c r="E30" s="44" t="s">
@@ -6424,7 +6415,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H30" s="122">
+      <c r="H30" s="115">
         <v>5050</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -6437,7 +6428,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L30" s="122"/>
+      <c r="L30" s="115"/>
       <c r="M30" s="46"/>
       <c r="N30" s="46"/>
       <c r="O30" s="46"/>
@@ -6479,7 +6470,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D31" s="122">
+      <c r="D31" s="115">
         <v>3029</v>
       </c>
       <c r="E31" s="44" t="s">
@@ -6493,7 +6484,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H31" s="122">
+      <c r="H31" s="115">
         <v>5050</v>
       </c>
       <c r="I31" s="55" t="s">
@@ -6506,7 +6497,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L31" s="122"/>
+      <c r="L31" s="115"/>
       <c r="M31" s="46"/>
       <c r="N31" s="46"/>
       <c r="O31" s="46"/>
@@ -6548,7 +6539,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D32" s="122">
+      <c r="D32" s="115">
         <v>3029</v>
       </c>
       <c r="E32" s="44" t="s">
@@ -6562,7 +6553,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H32" s="122">
+      <c r="H32" s="115">
         <v>5050</v>
       </c>
       <c r="I32" s="55" t="s">
@@ -6575,7 +6566,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L32" s="122"/>
+      <c r="L32" s="115"/>
       <c r="M32" s="46"/>
       <c r="N32" s="46"/>
       <c r="O32" s="46"/>
@@ -6615,7 +6606,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D33" s="122">
+      <c r="D33" s="115">
         <v>3029</v>
       </c>
       <c r="E33" s="44" t="s">
@@ -6629,7 +6620,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H33" s="122">
+      <c r="H33" s="115">
         <v>5050</v>
       </c>
       <c r="I33" s="55" t="s">
@@ -6642,7 +6633,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L33" s="122"/>
+      <c r="L33" s="115"/>
       <c r="M33" s="46"/>
       <c r="N33" s="46"/>
       <c r="O33" s="46"/>
@@ -6682,7 +6673,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D34" s="122">
+      <c r="D34" s="115">
         <v>3029</v>
       </c>
       <c r="E34" s="44" t="s">
@@ -6696,7 +6687,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H34" s="122">
+      <c r="H34" s="115">
         <v>5050</v>
       </c>
       <c r="I34" s="55" t="s">
@@ -6709,7 +6700,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L34" s="122"/>
+      <c r="L34" s="115"/>
       <c r="M34" s="46"/>
       <c r="N34" s="46"/>
       <c r="O34" s="46"/>
@@ -6749,7 +6740,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7603</v>
       </c>
-      <c r="D35" s="122">
+      <c r="D35" s="115">
         <v>3689</v>
       </c>
       <c r="E35" s="46" t="s">
@@ -6763,7 +6754,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3412.5</v>
       </c>
-      <c r="H35" s="122">
+      <c r="H35" s="115">
         <v>7050</v>
       </c>
       <c r="I35" s="77" t="s">
@@ -6774,7 +6765,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3412.5</v>
       </c>
-      <c r="L35" s="122">
+      <c r="L35" s="115">
         <v>7050</v>
       </c>
       <c r="M35" s="46"/>
@@ -6818,7 +6809,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7603</v>
       </c>
-      <c r="D36" s="122">
+      <c r="D36" s="115">
         <v>3689</v>
       </c>
       <c r="E36" s="46" t="s">
@@ -6832,7 +6823,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4062.5</v>
       </c>
-      <c r="H36" s="122">
+      <c r="H36" s="115">
         <v>8350</v>
       </c>
       <c r="I36" s="77" t="s">
@@ -6843,7 +6834,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4062.5</v>
       </c>
-      <c r="L36" s="122">
+      <c r="L36" s="115">
         <v>8350</v>
       </c>
       <c r="M36" s="46"/>
@@ -6888,7 +6879,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D37" s="122">
+      <c r="D37" s="115">
         <v>2459</v>
       </c>
       <c r="E37" s="44" t="s">
@@ -6902,7 +6893,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H37" s="122">
+      <c r="H37" s="115">
         <v>3990</v>
       </c>
       <c r="I37" s="55" t="s">
@@ -6916,7 +6907,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L37" s="122">
+      <c r="L37" s="115">
         <v>3390</v>
       </c>
       <c r="M37" s="46"/>
@@ -6951,16 +6942,16 @@
     </row>
     <row r="38" spans="1:31" ht="15">
       <c r="A38" s="42" t="s">
-        <v>646</v>
+        <v>53</v>
       </c>
       <c r="B38" s="102" t="s">
-        <v>647</v>
+        <v>54</v>
       </c>
       <c r="C38" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D38" s="122">
+      <c r="D38" s="115">
         <v>5939</v>
       </c>
       <c r="E38" s="46" t="s">
@@ -6974,7 +6965,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H38" s="122">
+      <c r="H38" s="115">
         <v>9450</v>
       </c>
       <c r="I38" s="77" t="s">
@@ -6988,7 +6979,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L38" s="122">
+      <c r="L38" s="115">
         <v>6690</v>
       </c>
       <c r="M38" s="46"/>
@@ -7029,50 +7020,50 @@
     </row>
     <row r="39" spans="1:31" ht="15">
       <c r="A39" s="42" t="s">
-        <v>648</v>
+        <v>53</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>649</v>
+        <v>54</v>
       </c>
       <c r="C39" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D39" s="122">
-        <v>3839</v>
+        <v>12203</v>
+      </c>
+      <c r="D39" s="115">
+        <v>5939</v>
       </c>
       <c r="E39" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>1376.5</v>
       </c>
       <c r="G39" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H39" s="122">
-        <v>7050</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H39" s="115">
+        <v>9450</v>
       </c>
       <c r="I39" s="77" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J39" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>1380</v>
       </c>
       <c r="K39" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L39" s="122">
-        <v>4990</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L39" s="115">
+        <v>6690</v>
       </c>
       <c r="M39" s="46"/>
       <c r="N39" s="46">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
+        <v>3182.5</v>
       </c>
       <c r="O39" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
@@ -7116,7 +7107,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7603</v>
       </c>
-      <c r="D40" s="122">
+      <c r="D40" s="115">
         <v>3689</v>
       </c>
       <c r="E40" s="46" t="s">
@@ -7130,7 +7121,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3412.5</v>
       </c>
-      <c r="H40" s="122">
+      <c r="H40" s="115">
         <v>7050</v>
       </c>
       <c r="I40" s="77" t="s">
@@ -7144,7 +7135,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2912.5</v>
       </c>
-      <c r="L40" s="122">
+      <c r="L40" s="115">
         <v>6050</v>
       </c>
       <c r="M40" s="46"/>
@@ -7188,7 +7179,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7603</v>
       </c>
-      <c r="D41" s="122">
+      <c r="D41" s="115">
         <v>3689</v>
       </c>
       <c r="E41" s="46" t="s">
@@ -7202,7 +7193,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3412.5</v>
       </c>
-      <c r="H41" s="122">
+      <c r="H41" s="115">
         <v>7050</v>
       </c>
       <c r="I41" s="77" t="s">
@@ -7216,7 +7207,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2787.5</v>
       </c>
-      <c r="L41" s="122">
+      <c r="L41" s="115">
         <v>5800</v>
       </c>
       <c r="M41" s="77"/>
@@ -7260,7 +7251,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9583</v>
       </c>
-      <c r="D42" s="122">
+      <c r="D42" s="115">
         <v>4679</v>
       </c>
       <c r="E42" s="46" t="s">
@@ -7274,7 +7265,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4062.5</v>
       </c>
-      <c r="H42" s="122">
+      <c r="H42" s="115">
         <v>8350</v>
       </c>
       <c r="I42" s="77" t="s">
@@ -7285,7 +7276,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4062.5</v>
       </c>
-      <c r="L42" s="122">
+      <c r="L42" s="115">
         <v>8350</v>
       </c>
       <c r="M42" s="46"/>
@@ -7329,7 +7320,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9583</v>
       </c>
-      <c r="D43" s="122">
+      <c r="D43" s="115">
         <v>4679</v>
       </c>
       <c r="E43" s="46" t="s">
@@ -7343,7 +7334,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3412.5</v>
       </c>
-      <c r="H43" s="122">
+      <c r="H43" s="115">
         <v>7050</v>
       </c>
       <c r="I43" s="77" t="s">
@@ -7354,7 +7345,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3412.5</v>
       </c>
-      <c r="L43" s="122">
+      <c r="L43" s="115">
         <v>7050</v>
       </c>
       <c r="M43" s="46"/>
@@ -7398,7 +7389,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9583</v>
       </c>
-      <c r="D44" s="122">
+      <c r="D44" s="115">
         <v>4679</v>
       </c>
       <c r="E44" s="46" t="s">
@@ -7412,7 +7403,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4062.5</v>
       </c>
-      <c r="H44" s="122">
+      <c r="H44" s="115">
         <v>8350</v>
       </c>
       <c r="I44" s="77" t="s">
@@ -7426,7 +7417,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3562.5</v>
       </c>
-      <c r="L44" s="122">
+      <c r="L44" s="115">
         <v>7350</v>
       </c>
       <c r="M44" s="46"/>
@@ -7470,7 +7461,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9583</v>
       </c>
-      <c r="D45" s="122">
+      <c r="D45" s="115">
         <v>4679</v>
       </c>
       <c r="E45" s="46" t="s">
@@ -7484,7 +7475,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4062.5</v>
       </c>
-      <c r="H45" s="122">
+      <c r="H45" s="115">
         <v>8350</v>
       </c>
       <c r="I45" s="77" t="s">
@@ -7498,7 +7489,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3187.5</v>
       </c>
-      <c r="L45" s="122">
+      <c r="L45" s="115">
         <v>6600</v>
       </c>
       <c r="M45" s="77"/>
@@ -7542,7 +7533,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3718</v>
       </c>
-      <c r="D46" s="122">
+      <c r="D46" s="115">
         <v>1859</v>
       </c>
       <c r="E46" s="44" t="s">
@@ -7556,7 +7547,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H46" s="122">
+      <c r="H46" s="115">
         <v>3100</v>
       </c>
       <c r="I46" s="55" t="s">
@@ -7569,7 +7560,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L46" s="122"/>
+      <c r="L46" s="115"/>
       <c r="M46" s="46"/>
       <c r="N46" s="46"/>
       <c r="O46" s="46"/>
@@ -7605,7 +7596,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3718</v>
       </c>
-      <c r="D47" s="122">
+      <c r="D47" s="115">
         <v>1859</v>
       </c>
       <c r="E47" s="44" t="s">
@@ -7619,7 +7610,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H47" s="122">
+      <c r="H47" s="115">
         <v>3100</v>
       </c>
       <c r="I47" s="55" t="s">
@@ -7633,7 +7624,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L47" s="122">
+      <c r="L47" s="115">
         <v>3100</v>
       </c>
       <c r="M47" s="46"/>
@@ -7677,7 +7668,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D48" s="122">
+      <c r="D48" s="115">
         <v>2459</v>
       </c>
       <c r="E48" s="44" t="s">
@@ -7691,7 +7682,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H48" s="122">
+      <c r="H48" s="115">
         <v>3990</v>
       </c>
       <c r="I48" s="55" t="s">
@@ -7704,7 +7695,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1882.5</v>
       </c>
-      <c r="L48" s="122">
+      <c r="L48" s="115">
         <v>3990</v>
       </c>
       <c r="M48" s="46"/>
@@ -7748,7 +7739,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11638</v>
       </c>
-      <c r="D49" s="122">
+      <c r="D49" s="115">
         <v>5819</v>
       </c>
       <c r="E49" s="44" t="s">
@@ -7762,7 +7753,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4725</v>
       </c>
-      <c r="H49" s="122">
+      <c r="H49" s="115">
         <v>9450</v>
       </c>
       <c r="I49" s="55" t="s">
@@ -7776,7 +7767,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4725</v>
       </c>
-      <c r="L49" s="122">
+      <c r="L49" s="115">
         <v>9450</v>
       </c>
       <c r="M49" s="46"/>
@@ -7821,7 +7812,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11638</v>
       </c>
-      <c r="D50" s="122">
+      <c r="D50" s="115">
         <v>5819</v>
       </c>
       <c r="E50" s="44" t="s">
@@ -7835,7 +7826,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4725</v>
       </c>
-      <c r="H50" s="122">
+      <c r="H50" s="115">
         <v>9450</v>
       </c>
       <c r="I50" s="55" t="s">
@@ -7849,7 +7840,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4725</v>
       </c>
-      <c r="L50" s="122">
+      <c r="L50" s="115">
         <v>9450</v>
       </c>
       <c r="M50" s="46"/>
@@ -7894,7 +7885,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7378</v>
       </c>
-      <c r="D51" s="122">
+      <c r="D51" s="115">
         <v>3689</v>
       </c>
       <c r="E51" s="44" t="s">
@@ -7908,7 +7899,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3525</v>
       </c>
-      <c r="H51" s="122">
+      <c r="H51" s="115">
         <v>7050</v>
       </c>
       <c r="I51" s="55" t="s">
@@ -7922,7 +7913,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3525</v>
       </c>
-      <c r="L51" s="122">
+      <c r="L51" s="115">
         <v>7050</v>
       </c>
       <c r="M51" s="46"/>
@@ -7967,7 +7958,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7378</v>
       </c>
-      <c r="D52" s="122">
+      <c r="D52" s="115">
         <v>3689</v>
       </c>
       <c r="E52" s="44" t="s">
@@ -7981,7 +7972,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3525</v>
       </c>
-      <c r="H52" s="122">
+      <c r="H52" s="115">
         <v>7050</v>
       </c>
       <c r="I52" s="55" t="s">
@@ -7995,7 +7986,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3525</v>
       </c>
-      <c r="L52" s="122">
+      <c r="L52" s="115">
         <v>7050</v>
       </c>
       <c r="M52" s="46"/>
@@ -8040,7 +8031,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9358</v>
       </c>
-      <c r="D53" s="122">
+      <c r="D53" s="115">
         <v>4679</v>
       </c>
       <c r="E53" s="44" t="s">
@@ -8054,7 +8045,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4175</v>
       </c>
-      <c r="H53" s="122">
+      <c r="H53" s="115">
         <v>8350</v>
       </c>
       <c r="I53" s="55" t="s">
@@ -8068,7 +8059,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4175</v>
       </c>
-      <c r="L53" s="122">
+      <c r="L53" s="115">
         <v>8350</v>
       </c>
       <c r="M53" s="46"/>
@@ -8113,7 +8104,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9358</v>
       </c>
-      <c r="D54" s="122">
+      <c r="D54" s="115">
         <v>4679</v>
       </c>
       <c r="E54" s="44" t="s">
@@ -8127,7 +8118,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4175</v>
       </c>
-      <c r="H54" s="122">
+      <c r="H54" s="115">
         <v>8350</v>
       </c>
       <c r="I54" s="55" t="s">
@@ -8141,7 +8132,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4175</v>
       </c>
-      <c r="L54" s="122">
+      <c r="L54" s="115">
         <v>8350</v>
       </c>
       <c r="M54" s="46"/>
@@ -8177,50 +8168,50 @@
     </row>
     <row r="55" spans="1:32" ht="15">
       <c r="A55" s="42" t="s">
-        <v>650</v>
+        <v>53</v>
       </c>
       <c r="B55" s="102" t="s">
-        <v>651</v>
+        <v>54</v>
       </c>
       <c r="C55" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D55" s="122">
-        <v>5039</v>
+        <v>12203</v>
+      </c>
+      <c r="D55" s="115">
+        <v>5939</v>
       </c>
       <c r="E55" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>1376.5</v>
       </c>
       <c r="G55" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H55" s="122">
-        <v>8350</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H55" s="115">
+        <v>9450</v>
       </c>
       <c r="I55" s="77" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="J55" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>1380</v>
       </c>
       <c r="K55" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L55" s="122">
-        <v>5790</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L55" s="115">
+        <v>6690</v>
       </c>
       <c r="M55" s="46"/>
       <c r="N55" s="46">
         <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
+        <v>3182.5</v>
       </c>
       <c r="O55" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
@@ -8255,7 +8246,7 @@
       <c r="AE55"/>
     </row>
     <row r="56" spans="1:32" ht="15">
-      <c r="A56" s="111" t="s">
+      <c r="A56" s="42" t="s">
         <v>123</v>
       </c>
       <c r="B56" s="42" t="s">
@@ -8265,7 +8256,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D56" s="122">
+      <c r="D56" s="115">
         <v>5819</v>
       </c>
       <c r="E56" s="46" t="s">
@@ -8279,10 +8270,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H56" s="122">
+      <c r="H56" s="115">
         <v>9450</v>
       </c>
-      <c r="I56" s="113" t="s">
+      <c r="I56" s="55" t="s">
         <v>122</v>
       </c>
       <c r="J56" s="46">
@@ -8293,7 +8284,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L56" s="122">
+      <c r="L56" s="115">
         <v>6690</v>
       </c>
       <c r="M56" s="46"/>
@@ -8309,7 +8300,7 @@
       <c r="S56" s="46">
         <v>325</v>
       </c>
-      <c r="T56" s="118" t="s">
+      <c r="T56" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U56" s="46">
@@ -8328,17 +8319,17 @@
       <c r="AE56"/>
     </row>
     <row r="57" spans="1:32" ht="15">
-      <c r="A57" s="111" t="s">
+      <c r="A57" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="B57" s="111" t="s">
+      <c r="B57" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C57" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D57" s="122">
+      <c r="D57" s="115">
         <v>3689</v>
       </c>
       <c r="E57" s="46" t="s">
@@ -8352,10 +8343,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H57" s="122">
+      <c r="H57" s="115">
         <v>7050</v>
       </c>
-      <c r="I57" s="113" t="s">
+      <c r="I57" s="55" t="s">
         <v>122</v>
       </c>
       <c r="J57" s="46">
@@ -8366,7 +8357,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L57" s="122">
+      <c r="L57" s="115">
         <v>4890</v>
       </c>
       <c r="M57" s="46"/>
@@ -8382,7 +8373,7 @@
       <c r="S57" s="46">
         <v>325</v>
       </c>
-      <c r="T57" s="118" t="s">
+      <c r="T57" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U57" s="46">
@@ -8411,7 +8402,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D58" s="122">
+      <c r="D58" s="115">
         <v>1960</v>
       </c>
       <c r="E58" s="44" t="s">
@@ -8425,7 +8416,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H58" s="122">
+      <c r="H58" s="115">
         <v>3100</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -8439,7 +8430,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L58" s="122">
+      <c r="L58" s="115">
         <v>3100</v>
       </c>
       <c r="M58" s="46"/>
@@ -8484,7 +8475,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D59" s="122">
+      <c r="D59" s="115">
         <v>1960</v>
       </c>
       <c r="E59" s="44" t="s">
@@ -8498,7 +8489,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H59" s="122">
+      <c r="H59" s="115">
         <v>3100</v>
       </c>
       <c r="I59" s="55" t="s">
@@ -8512,7 +8503,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L59" s="122">
+      <c r="L59" s="115">
         <v>3100</v>
       </c>
       <c r="M59" s="46"/>
@@ -8556,7 +8547,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D60" s="122">
+      <c r="D60" s="115">
         <v>1960</v>
       </c>
       <c r="E60" s="44" t="s">
@@ -8570,7 +8561,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H60" s="122">
+      <c r="H60" s="115">
         <v>3100</v>
       </c>
       <c r="I60" s="55" t="s">
@@ -8584,7 +8575,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L60" s="122">
+      <c r="L60" s="115">
         <v>3100</v>
       </c>
       <c r="M60" s="46"/>
@@ -8628,7 +8619,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D61" s="122">
+      <c r="D61" s="115">
         <v>1960</v>
       </c>
       <c r="E61" s="44" t="s">
@@ -8642,7 +8633,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H61" s="122">
+      <c r="H61" s="115">
         <v>3100</v>
       </c>
       <c r="I61" s="55" t="s">
@@ -8656,7 +8647,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L61" s="122">
+      <c r="L61" s="115">
         <v>3100</v>
       </c>
       <c r="M61" s="46"/>
@@ -8701,7 +8692,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D62" s="122">
+      <c r="D62" s="115">
         <v>1960</v>
       </c>
       <c r="E62" s="44" t="s">
@@ -8715,7 +8706,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H62" s="122">
+      <c r="H62" s="115">
         <v>3100</v>
       </c>
       <c r="I62" s="55" t="s">
@@ -8729,7 +8720,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L62" s="122">
+      <c r="L62" s="115">
         <v>3100</v>
       </c>
       <c r="M62" s="46"/>
@@ -8774,7 +8765,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D63" s="122">
+      <c r="D63" s="115">
         <v>1960</v>
       </c>
       <c r="E63" s="44" t="s">
@@ -8788,7 +8779,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H63" s="122">
+      <c r="H63" s="115">
         <v>3100</v>
       </c>
       <c r="I63" s="55" t="s">
@@ -8802,7 +8793,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L63" s="122">
+      <c r="L63" s="115">
         <v>3100</v>
       </c>
       <c r="M63" s="46"/>
@@ -8847,7 +8838,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D64" s="122">
+      <c r="D64" s="115">
         <v>1960</v>
       </c>
       <c r="E64" s="44" t="s">
@@ -8861,7 +8852,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H64" s="122">
+      <c r="H64" s="115">
         <v>3100</v>
       </c>
       <c r="I64" s="55" t="s">
@@ -8875,7 +8866,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L64" s="122">
+      <c r="L64" s="115">
         <v>3100</v>
       </c>
       <c r="M64" s="46"/>
@@ -8918,7 +8909,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>3920</v>
       </c>
-      <c r="D65" s="122">
+      <c r="D65" s="115">
         <v>1960</v>
       </c>
       <c r="E65" s="44" t="s">
@@ -8932,7 +8923,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1550</v>
       </c>
-      <c r="H65" s="122">
+      <c r="H65" s="115">
         <v>3100</v>
       </c>
       <c r="I65" s="55" t="s">
@@ -8946,7 +8937,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1550</v>
       </c>
-      <c r="L65" s="122">
+      <c r="L65" s="115">
         <v>3100</v>
       </c>
       <c r="M65" s="46"/>
@@ -8989,7 +8980,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D66" s="122">
+      <c r="D66" s="115">
         <v>2345</v>
       </c>
       <c r="E66" s="44" t="s">
@@ -9003,7 +8994,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H66" s="122">
+      <c r="H66" s="115">
         <v>3500</v>
       </c>
       <c r="I66" s="55" t="s">
@@ -9017,7 +9008,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L66" s="122">
+      <c r="L66" s="115">
         <v>3500</v>
       </c>
       <c r="M66" s="46"/>
@@ -9062,7 +9053,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4915</v>
       </c>
-      <c r="D67" s="122">
+      <c r="D67" s="115">
         <v>2345</v>
       </c>
       <c r="E67" s="44" t="s">
@@ -9076,7 +9067,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1637.5</v>
       </c>
-      <c r="H67" s="122">
+      <c r="H67" s="115">
         <v>3500</v>
       </c>
       <c r="I67" s="55" t="s">
@@ -9090,7 +9081,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1637.5</v>
       </c>
-      <c r="L67" s="122">
+      <c r="L67" s="115">
         <v>3500</v>
       </c>
       <c r="M67" s="46"/>
@@ -9135,7 +9126,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D68" s="122">
+      <c r="D68" s="115">
         <v>2345</v>
       </c>
       <c r="E68" s="44" t="s">
@@ -9149,7 +9140,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H68" s="122">
+      <c r="H68" s="115">
         <v>3500</v>
       </c>
       <c r="I68" s="55" t="s">
@@ -9163,7 +9154,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L68" s="122">
+      <c r="L68" s="115">
         <v>3500</v>
       </c>
       <c r="M68" s="46"/>
@@ -9208,7 +9199,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D69" s="122">
+      <c r="D69" s="115">
         <v>2345</v>
       </c>
       <c r="E69" s="44" t="s">
@@ -9222,7 +9213,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H69" s="122">
+      <c r="H69" s="115">
         <v>3500</v>
       </c>
       <c r="I69" s="55" t="s">
@@ -9236,7 +9227,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L69" s="122">
+      <c r="L69" s="115">
         <v>3500</v>
       </c>
       <c r="M69" s="46"/>
@@ -9281,7 +9272,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D70" s="122">
+      <c r="D70" s="115">
         <v>2345</v>
       </c>
       <c r="E70" s="44" t="s">
@@ -9295,7 +9286,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H70" s="122">
+      <c r="H70" s="115">
         <v>3500</v>
       </c>
       <c r="I70" s="55" t="s">
@@ -9309,7 +9300,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L70" s="122">
+      <c r="L70" s="115">
         <v>3500</v>
       </c>
       <c r="M70" s="46"/>
@@ -9354,7 +9345,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D71" s="122">
+      <c r="D71" s="115">
         <v>2345</v>
       </c>
       <c r="E71" s="44" t="s">
@@ -9368,7 +9359,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H71" s="122">
+      <c r="H71" s="115">
         <v>3500</v>
       </c>
       <c r="I71" s="55" t="s">
@@ -9382,7 +9373,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L71" s="122">
+      <c r="L71" s="115">
         <v>3500</v>
       </c>
       <c r="M71" s="46"/>
@@ -9427,7 +9418,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D72" s="122">
+      <c r="D72" s="115">
         <v>2345</v>
       </c>
       <c r="E72" s="44" t="s">
@@ -9441,7 +9432,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H72" s="122">
+      <c r="H72" s="115">
         <v>3500</v>
       </c>
       <c r="I72" s="55" t="s">
@@ -9455,7 +9446,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L72" s="122">
+      <c r="L72" s="115">
         <v>3500</v>
       </c>
       <c r="M72" s="46"/>
@@ -9500,7 +9491,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D73" s="122">
+      <c r="D73" s="115">
         <v>2345</v>
       </c>
       <c r="E73" s="44" t="s">
@@ -9514,7 +9505,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H73" s="122">
+      <c r="H73" s="115">
         <v>3500</v>
       </c>
       <c r="I73" s="55" t="s">
@@ -9528,7 +9519,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L73" s="122">
+      <c r="L73" s="115">
         <v>3500</v>
       </c>
       <c r="M73" s="46"/>
@@ -9571,7 +9562,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D74" s="122">
+      <c r="D74" s="115">
         <v>2345</v>
       </c>
       <c r="E74" s="44" t="s">
@@ -9585,7 +9576,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H74" s="122">
+      <c r="H74" s="115">
         <v>3500</v>
       </c>
       <c r="I74" s="55" t="s">
@@ -9599,7 +9590,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L74" s="122">
+      <c r="L74" s="115">
         <v>3500</v>
       </c>
       <c r="M74" s="46"/>
@@ -9642,7 +9633,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>4690</v>
       </c>
-      <c r="D75" s="122">
+      <c r="D75" s="115">
         <v>2345</v>
       </c>
       <c r="E75" s="44" t="s">
@@ -9656,7 +9647,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1750</v>
       </c>
-      <c r="H75" s="122">
+      <c r="H75" s="115">
         <v>3500</v>
       </c>
       <c r="I75" s="55" t="s">
@@ -9670,7 +9661,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1750</v>
       </c>
-      <c r="L75" s="122">
+      <c r="L75" s="115">
         <v>3500</v>
       </c>
       <c r="M75" s="46"/>
@@ -9713,7 +9704,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6283</v>
       </c>
-      <c r="D76" s="122">
+      <c r="D76" s="115">
         <v>3029</v>
       </c>
       <c r="E76" s="44" t="s">
@@ -9727,7 +9718,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2412.5</v>
       </c>
-      <c r="H76" s="122">
+      <c r="H76" s="115">
         <v>5050</v>
       </c>
       <c r="I76" s="55" t="s">
@@ -9741,7 +9732,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2412.5</v>
       </c>
-      <c r="L76" s="122">
+      <c r="L76" s="115">
         <v>5050</v>
       </c>
       <c r="M76" s="46"/>
@@ -9786,7 +9777,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D77" s="122">
+      <c r="D77" s="115">
         <v>3029</v>
       </c>
       <c r="E77" s="44" t="s">
@@ -9800,7 +9791,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H77" s="122">
+      <c r="H77" s="115">
         <v>5050</v>
       </c>
       <c r="I77" s="55" t="s">
@@ -9814,7 +9805,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L77" s="122">
+      <c r="L77" s="115">
         <v>5050</v>
       </c>
       <c r="M77" s="46"/>
@@ -9859,7 +9850,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D78" s="122">
+      <c r="D78" s="115">
         <v>3029</v>
       </c>
       <c r="E78" s="44" t="s">
@@ -9873,7 +9864,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H78" s="122">
+      <c r="H78" s="115">
         <v>5050</v>
       </c>
       <c r="I78" s="55" t="s">
@@ -9887,7 +9878,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L78" s="122">
+      <c r="L78" s="115">
         <v>5050</v>
       </c>
       <c r="M78" s="46"/>
@@ -9932,7 +9923,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D79" s="122">
+      <c r="D79" s="115">
         <v>3029</v>
       </c>
       <c r="E79" s="44" t="s">
@@ -9946,7 +9937,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H79" s="122">
+      <c r="H79" s="115">
         <v>5050</v>
       </c>
       <c r="I79" s="55" t="s">
@@ -9960,7 +9951,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L79" s="122">
+      <c r="L79" s="115">
         <v>5050</v>
       </c>
       <c r="M79" s="46"/>
@@ -10005,7 +9996,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D80" s="122">
+      <c r="D80" s="115">
         <v>3029</v>
       </c>
       <c r="E80" s="44" t="s">
@@ -10019,7 +10010,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H80" s="122">
+      <c r="H80" s="115">
         <v>5050</v>
       </c>
       <c r="I80" s="55" t="s">
@@ -10033,7 +10024,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L80" s="122">
+      <c r="L80" s="115">
         <v>5050</v>
       </c>
       <c r="M80" s="46"/>
@@ -10078,7 +10069,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D81" s="122">
+      <c r="D81" s="115">
         <v>3029</v>
       </c>
       <c r="E81" s="44" t="s">
@@ -10092,7 +10083,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H81" s="122">
+      <c r="H81" s="115">
         <v>5050</v>
       </c>
       <c r="I81" s="55" t="s">
@@ -10106,7 +10097,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L81" s="122">
+      <c r="L81" s="115">
         <v>5050</v>
       </c>
       <c r="M81" s="46"/>
@@ -10151,7 +10142,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D82" s="122">
+      <c r="D82" s="115">
         <v>3029</v>
       </c>
       <c r="E82" s="44" t="s">
@@ -10165,7 +10156,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H82" s="122">
+      <c r="H82" s="115">
         <v>5050</v>
       </c>
       <c r="I82" s="55" t="s">
@@ -10179,7 +10170,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L82" s="122">
+      <c r="L82" s="115">
         <v>5050</v>
       </c>
       <c r="M82" s="46"/>
@@ -10222,7 +10213,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D83" s="122">
+      <c r="D83" s="115">
         <v>3029</v>
       </c>
       <c r="E83" s="44" t="s">
@@ -10236,7 +10227,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H83" s="122">
+      <c r="H83" s="115">
         <v>5050</v>
       </c>
       <c r="I83" s="55" t="s">
@@ -10250,7 +10241,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L83" s="122">
+      <c r="L83" s="115">
         <v>5050</v>
       </c>
       <c r="M83" s="46"/>
@@ -10293,7 +10284,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6058</v>
       </c>
-      <c r="D84" s="122">
+      <c r="D84" s="115">
         <v>3029</v>
       </c>
       <c r="E84" s="44" t="s">
@@ -10307,7 +10298,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2525</v>
       </c>
-      <c r="H84" s="122">
+      <c r="H84" s="115">
         <v>5050</v>
       </c>
       <c r="I84" s="55" t="s">
@@ -10321,7 +10312,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2525</v>
       </c>
-      <c r="L84" s="122">
+      <c r="L84" s="115">
         <v>5050</v>
       </c>
       <c r="M84" s="46"/>
@@ -10364,7 +10355,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D85" s="122">
+      <c r="D85" s="115">
         <v>5819</v>
       </c>
       <c r="E85" s="44" t="s">
@@ -10378,7 +10369,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H85" s="122">
+      <c r="H85" s="115">
         <v>9450</v>
       </c>
       <c r="I85" s="55" t="s">
@@ -10392,7 +10383,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4562.5</v>
       </c>
-      <c r="L85" s="122">
+      <c r="L85" s="115">
         <v>9450</v>
       </c>
       <c r="M85" s="46"/>
@@ -10437,7 +10428,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D86" s="122">
+      <c r="D86" s="115">
         <v>3689</v>
       </c>
       <c r="E86" s="44" t="s">
@@ -10451,7 +10442,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H86" s="122">
+      <c r="H86" s="115">
         <v>7050</v>
       </c>
       <c r="I86" s="55" t="s">
@@ -10465,7 +10456,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3362.5</v>
       </c>
-      <c r="L86" s="122">
+      <c r="L86" s="115">
         <v>7050</v>
       </c>
       <c r="M86" s="46"/>
@@ -10510,7 +10501,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D87" s="122">
+      <c r="D87" s="115">
         <v>4679</v>
       </c>
       <c r="E87" s="44" t="s">
@@ -10524,7 +10515,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H87" s="122">
+      <c r="H87" s="115">
         <v>8350</v>
       </c>
       <c r="I87" s="55" t="s">
@@ -10538,7 +10529,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4012.5</v>
       </c>
-      <c r="L87" s="122">
+      <c r="L87" s="115">
         <v>8350</v>
       </c>
       <c r="M87" s="46"/>
@@ -10573,17 +10564,17 @@
       <c r="AE87"/>
     </row>
     <row r="88" spans="1:31" ht="15">
-      <c r="A88" s="111" t="s">
+      <c r="A88" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="111" t="s">
+      <c r="B88" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C88" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D88" s="122">
+      <c r="D88" s="115">
         <v>4679</v>
       </c>
       <c r="E88" s="46" t="s">
@@ -10597,10 +10588,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H88" s="122">
+      <c r="H88" s="115">
         <v>8350</v>
       </c>
-      <c r="I88" s="113" t="s">
+      <c r="I88" s="55" t="s">
         <v>122</v>
       </c>
       <c r="J88" s="46">
@@ -10611,7 +10602,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L88" s="122">
+      <c r="L88" s="115">
         <v>5690</v>
       </c>
       <c r="M88" s="46"/>
@@ -10627,7 +10618,7 @@
       <c r="S88" s="46">
         <v>325</v>
       </c>
-      <c r="T88" s="118" t="s">
+      <c r="T88" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U88" s="46">
@@ -10656,7 +10647,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D89" s="122">
+      <c r="D89" s="115">
         <v>2459</v>
       </c>
       <c r="E89" s="44" t="s">
@@ -10670,7 +10661,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H89" s="122">
+      <c r="H89" s="115">
         <v>3990</v>
       </c>
       <c r="I89" s="55" t="s">
@@ -10684,7 +10675,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L89" s="122">
+      <c r="L89" s="115">
         <v>3390</v>
       </c>
       <c r="M89" s="46"/>
@@ -10729,7 +10720,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D90" s="122">
+      <c r="D90" s="115">
         <v>2459</v>
       </c>
       <c r="E90" s="44" t="s">
@@ -10743,7 +10734,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H90" s="122">
+      <c r="H90" s="115">
         <v>3990</v>
       </c>
       <c r="I90" s="55" t="s">
@@ -10757,7 +10748,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L90" s="122">
+      <c r="L90" s="115">
         <v>3390</v>
       </c>
       <c r="M90" s="46"/>
@@ -10793,16 +10784,16 @@
     </row>
     <row r="91" spans="1:31" ht="15">
       <c r="A91" s="42" t="s">
-        <v>646</v>
-      </c>
-      <c r="B91" s="42" t="s">
-        <v>647</v>
+        <v>53</v>
+      </c>
+      <c r="B91" s="102" t="s">
+        <v>54</v>
       </c>
       <c r="C91" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D91" s="122">
+      <c r="D91" s="115">
         <v>5939</v>
       </c>
       <c r="E91" s="46" t="s">
@@ -10816,11 +10807,11 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H91" s="122">
+      <c r="H91" s="115">
         <v>9450</v>
       </c>
       <c r="I91" s="77" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J91" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -10830,7 +10821,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L91" s="122">
+      <c r="L91" s="115">
         <v>6690</v>
       </c>
       <c r="M91" s="46"/>
@@ -10871,54 +10862,51 @@
     </row>
     <row r="92" spans="1:31" ht="15">
       <c r="A92" s="42" t="s">
-        <v>648</v>
-      </c>
-      <c r="B92" s="102" t="s">
-        <v>649</v>
+        <v>53</v>
+      </c>
+      <c r="B92" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C92" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D92" s="122">
-        <v>3839</v>
+        <v>12203</v>
+      </c>
+      <c r="D92" s="115">
+        <v>5939</v>
       </c>
       <c r="E92" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>1376.5</v>
       </c>
       <c r="G92" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H92" s="122">
-        <v>7050</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H92" s="115">
+        <v>9450</v>
       </c>
       <c r="I92" s="77" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J92" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>1380</v>
       </c>
       <c r="K92" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L92" s="122">
-        <v>4990</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L92" s="115">
+        <v>6690</v>
       </c>
       <c r="M92" s="46"/>
-      <c r="N92" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N92" s="46"/>
       <c r="O92" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P92" s="46"/>
       <c r="Q92" s="47">
@@ -10948,55 +10936,52 @@
       <c r="AE92"/>
     </row>
     <row r="93" spans="1:31" ht="15">
-      <c r="A93" s="42" t="s">
-        <v>650</v>
-      </c>
-      <c r="B93" s="42" t="s">
-        <v>651</v>
+      <c r="A93" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="B93" s="102" t="s">
+        <v>54</v>
       </c>
       <c r="C93" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D93" s="122">
-        <v>5039</v>
+        <v>12203</v>
+      </c>
+      <c r="D93" s="115">
+        <v>5939</v>
       </c>
       <c r="E93" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>1376.5</v>
       </c>
       <c r="G93" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H93" s="122">
-        <v>8350</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H93" s="115">
+        <v>9450</v>
       </c>
       <c r="I93" s="77" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J93" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>1380</v>
       </c>
       <c r="K93" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L93" s="122">
-        <v>5790</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L93" s="115">
+        <v>6690</v>
       </c>
       <c r="M93" s="46"/>
-      <c r="N93" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N93" s="46"/>
       <c r="O93" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P93" s="46"/>
       <c r="Q93" s="47">
@@ -11026,7 +11011,7 @@
       <c r="AE93"/>
     </row>
     <row r="94" spans="1:31" ht="15">
-      <c r="A94" s="111" t="s">
+      <c r="A94" s="42" t="s">
         <v>123</v>
       </c>
       <c r="B94" s="42" t="s">
@@ -11036,7 +11021,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D94" s="122">
+      <c r="D94" s="115">
         <v>5819</v>
       </c>
       <c r="E94" s="46" t="s">
@@ -11050,10 +11035,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H94" s="122">
+      <c r="H94" s="115">
         <v>9450</v>
       </c>
-      <c r="I94" s="113" t="s">
+      <c r="I94" s="55" t="s">
         <v>152</v>
       </c>
       <c r="J94" s="46">
@@ -11064,7 +11049,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L94" s="122">
+      <c r="L94" s="115">
         <v>6690</v>
       </c>
       <c r="M94" s="46"/>
@@ -11080,7 +11065,7 @@
       <c r="S94" s="46">
         <v>325</v>
       </c>
-      <c r="T94" s="118" t="s">
+      <c r="T94" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U94" s="46">
@@ -11098,17 +11083,17 @@
       <c r="AE94"/>
     </row>
     <row r="95" spans="1:31" ht="15">
-      <c r="A95" s="111" t="s">
+      <c r="A95" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="B95" s="111" t="s">
+      <c r="B95" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C95" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D95" s="122">
+      <c r="D95" s="115">
         <v>3689</v>
       </c>
       <c r="E95" s="46" t="s">
@@ -11122,10 +11107,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H95" s="122">
+      <c r="H95" s="115">
         <v>7050</v>
       </c>
-      <c r="I95" s="113" t="s">
+      <c r="I95" s="55" t="s">
         <v>152</v>
       </c>
       <c r="J95" s="46">
@@ -11136,7 +11121,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L95" s="122">
+      <c r="L95" s="115">
         <v>4890</v>
       </c>
       <c r="M95" s="46"/>
@@ -11152,7 +11137,7 @@
       <c r="S95" s="46">
         <v>325</v>
       </c>
-      <c r="T95" s="118" t="s">
+      <c r="T95" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U95" s="46">
@@ -11170,17 +11155,17 @@
       <c r="AE95"/>
     </row>
     <row r="96" spans="1:31" ht="15">
-      <c r="A96" s="111" t="s">
+      <c r="A96" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B96" s="111" t="s">
+      <c r="B96" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C96" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D96" s="122">
+      <c r="D96" s="115">
         <v>4679</v>
       </c>
       <c r="E96" s="46" t="s">
@@ -11194,10 +11179,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H96" s="122">
+      <c r="H96" s="115">
         <v>8350</v>
       </c>
-      <c r="I96" s="113" t="s">
+      <c r="I96" s="55" t="s">
         <v>152</v>
       </c>
       <c r="J96" s="46">
@@ -11208,7 +11193,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L96" s="122">
+      <c r="L96" s="115">
         <v>5690</v>
       </c>
       <c r="M96" s="46"/>
@@ -11224,7 +11209,7 @@
       <c r="S96" s="46">
         <v>325</v>
       </c>
-      <c r="T96" s="118" t="s">
+      <c r="T96" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U96" s="46">
@@ -11253,7 +11238,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D97" s="122">
+      <c r="D97" s="115">
         <v>2459</v>
       </c>
       <c r="E97" s="44" t="s">
@@ -11267,7 +11252,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H97" s="122">
+      <c r="H97" s="115">
         <v>3990</v>
       </c>
       <c r="I97" s="55" t="s">
@@ -11281,7 +11266,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L97" s="122">
+      <c r="L97" s="115">
         <v>3390</v>
       </c>
       <c r="M97" s="46"/>
@@ -11316,16 +11301,16 @@
     </row>
     <row r="98" spans="1:31" ht="15">
       <c r="A98" s="42" t="s">
-        <v>646</v>
-      </c>
-      <c r="B98" s="102" t="s">
-        <v>647</v>
+        <v>53</v>
+      </c>
+      <c r="B98" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C98" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D98" s="122">
+      <c r="D98" s="115">
         <v>5939</v>
       </c>
       <c r="E98" s="46" t="s">
@@ -11339,11 +11324,11 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H98" s="122">
+      <c r="H98" s="115">
         <v>9450</v>
       </c>
       <c r="I98" s="77" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="J98" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -11353,17 +11338,14 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L98" s="122">
+      <c r="L98" s="115">
         <v>6690</v>
       </c>
       <c r="M98" s="46"/>
-      <c r="N98" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="N98" s="46"/>
       <c r="O98" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P98" s="46"/>
       <c r="Q98" s="47">
@@ -11393,55 +11375,52 @@
       <c r="AE98"/>
     </row>
     <row r="99" spans="1:31" ht="15">
-      <c r="A99" s="42" t="s">
-        <v>648</v>
-      </c>
-      <c r="B99" s="42" t="s">
-        <v>649</v>
+      <c r="A99" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="B99" s="121" t="s">
+        <v>54</v>
       </c>
       <c r="C99" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D99" s="122">
-        <v>3839</v>
+        <v>12203</v>
+      </c>
+      <c r="D99" s="115">
+        <v>5939</v>
       </c>
       <c r="E99" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>1376.5</v>
       </c>
       <c r="G99" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H99" s="122">
-        <v>7050</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H99" s="115">
+        <v>9450</v>
       </c>
       <c r="I99" s="77" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J99" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>1380</v>
       </c>
       <c r="K99" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L99" s="122">
-        <v>4990</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L99" s="115">
+        <v>6690</v>
       </c>
       <c r="M99" s="46"/>
-      <c r="N99" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="N99" s="46"/>
       <c r="O99" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P99" s="46"/>
       <c r="Q99" s="47">
@@ -11471,55 +11450,52 @@
       <c r="AE99"/>
     </row>
     <row r="100" spans="1:31" ht="15">
-      <c r="A100" s="42" t="s">
-        <v>650</v>
-      </c>
-      <c r="B100" s="102" t="s">
-        <v>651</v>
+      <c r="A100" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="B100" s="120" t="s">
+        <v>54</v>
       </c>
       <c r="C100" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D100" s="122">
-        <v>5039</v>
+        <v>12203</v>
+      </c>
+      <c r="D100" s="115">
+        <v>5939</v>
       </c>
       <c r="E100" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F100" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>1376.5</v>
       </c>
       <c r="G100" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H100" s="122">
-        <v>8350</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H100" s="115">
+        <v>9450</v>
       </c>
       <c r="I100" s="77" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J100" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>1380</v>
       </c>
       <c r="K100" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L100" s="122">
-        <v>5790</v>
+        <v>3182.5</v>
+      </c>
+      <c r="L100" s="115">
+        <v>6690</v>
       </c>
       <c r="M100" s="46"/>
-      <c r="N100" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="N100" s="46"/>
       <c r="O100" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
+        <v>3182.5</v>
       </c>
       <c r="P100" s="46"/>
       <c r="Q100" s="47">
@@ -11549,7 +11525,7 @@
       <c r="AE100"/>
     </row>
     <row r="101" spans="1:31" ht="15">
-      <c r="A101" s="111" t="s">
+      <c r="A101" s="42" t="s">
         <v>123</v>
       </c>
       <c r="B101" s="42" t="s">
@@ -11559,7 +11535,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D101" s="122">
+      <c r="D101" s="115">
         <v>5819</v>
       </c>
       <c r="E101" s="46" t="s">
@@ -11573,10 +11549,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H101" s="122">
+      <c r="H101" s="115">
         <v>9450</v>
       </c>
-      <c r="I101" s="113" t="s">
+      <c r="I101" s="55" t="s">
         <v>153</v>
       </c>
       <c r="J101" s="46">
@@ -11587,7 +11563,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L101" s="122">
+      <c r="L101" s="115">
         <v>6690</v>
       </c>
       <c r="M101" s="46"/>
@@ -11603,7 +11579,7 @@
       <c r="S101" s="46">
         <v>325</v>
       </c>
-      <c r="T101" s="118" t="s">
+      <c r="T101" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U101" s="46">
@@ -11631,7 +11607,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D102" s="122">
+      <c r="D102" s="115">
         <v>5819</v>
       </c>
       <c r="E102" s="44" t="s">
@@ -11645,7 +11621,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H102" s="122">
+      <c r="H102" s="115">
         <v>9450</v>
       </c>
       <c r="I102" s="55" t="s">
@@ -11659,7 +11635,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L102" s="122">
+      <c r="L102" s="115">
         <v>6690</v>
       </c>
       <c r="M102" s="46"/>
@@ -11703,7 +11679,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D103" s="122">
+      <c r="D103" s="115">
         <v>3689</v>
       </c>
       <c r="E103" s="44" t="s">
@@ -11717,7 +11693,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H103" s="122">
+      <c r="H103" s="115">
         <v>7050</v>
       </c>
       <c r="I103" s="55" t="s">
@@ -11731,7 +11707,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L103" s="122">
+      <c r="L103" s="115">
         <v>4890</v>
       </c>
       <c r="M103" s="46"/>
@@ -11775,7 +11751,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D104" s="122">
+      <c r="D104" s="115">
         <v>4679</v>
       </c>
       <c r="E104" s="44" t="s">
@@ -11789,7 +11765,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3512.5</v>
       </c>
-      <c r="H104" s="122">
+      <c r="H104" s="115">
         <v>7350</v>
       </c>
       <c r="I104" s="55" t="s">
@@ -11803,7 +11779,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L104" s="122">
+      <c r="L104" s="115">
         <v>5690</v>
       </c>
       <c r="M104" s="46"/>
@@ -11847,7 +11823,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11638</v>
       </c>
-      <c r="D105" s="122">
+      <c r="D105" s="115">
         <v>5819</v>
       </c>
       <c r="E105" s="44" t="s">
@@ -11861,7 +11837,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4725</v>
       </c>
-      <c r="H105" s="122">
+      <c r="H105" s="115">
         <v>9450</v>
       </c>
       <c r="I105" s="55" t="s">
@@ -11875,7 +11851,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4225</v>
       </c>
-      <c r="L105" s="122">
+      <c r="L105" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8450</v>
       </c>
@@ -11920,7 +11896,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11638</v>
       </c>
-      <c r="D106" s="122">
+      <c r="D106" s="115">
         <v>5819</v>
       </c>
       <c r="E106" s="44" t="s">
@@ -11934,7 +11910,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4725</v>
       </c>
-      <c r="H106" s="122">
+      <c r="H106" s="115">
         <v>9450</v>
       </c>
       <c r="I106" s="55" t="s">
@@ -11948,7 +11924,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4225</v>
       </c>
-      <c r="L106" s="122">
+      <c r="L106" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8450</v>
       </c>
@@ -11993,7 +11969,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7378</v>
       </c>
-      <c r="D107" s="122">
+      <c r="D107" s="115">
         <v>3689</v>
       </c>
       <c r="E107" s="44" t="s">
@@ -12007,7 +11983,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3525</v>
       </c>
-      <c r="H107" s="122">
+      <c r="H107" s="115">
         <v>7050</v>
       </c>
       <c r="I107" s="55" t="s">
@@ -12021,7 +11997,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3025</v>
       </c>
-      <c r="L107" s="122">
+      <c r="L107" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6050</v>
       </c>
@@ -12066,7 +12042,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7378</v>
       </c>
-      <c r="D108" s="122">
+      <c r="D108" s="115">
         <v>3689</v>
       </c>
       <c r="E108" s="44" t="s">
@@ -12080,7 +12056,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3525</v>
       </c>
-      <c r="H108" s="122">
+      <c r="H108" s="115">
         <v>7050</v>
       </c>
       <c r="I108" s="55" t="s">
@@ -12094,7 +12070,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3025</v>
       </c>
-      <c r="L108" s="122">
+      <c r="L108" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6050</v>
       </c>
@@ -12139,7 +12115,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9358</v>
       </c>
-      <c r="D109" s="122">
+      <c r="D109" s="115">
         <v>4679</v>
       </c>
       <c r="E109" s="44" t="s">
@@ -12153,7 +12129,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4175</v>
       </c>
-      <c r="H109" s="122">
+      <c r="H109" s="115">
         <v>8350</v>
       </c>
       <c r="I109" s="55" t="s">
@@ -12167,7 +12143,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3675</v>
       </c>
-      <c r="L109" s="122">
+      <c r="L109" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7350</v>
       </c>
@@ -12212,7 +12188,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9358</v>
       </c>
-      <c r="D110" s="122">
+      <c r="D110" s="115">
         <v>4679</v>
       </c>
       <c r="E110" s="44" t="s">
@@ -12226,7 +12202,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4175</v>
       </c>
-      <c r="H110" s="122">
+      <c r="H110" s="115">
         <v>8350</v>
       </c>
       <c r="I110" s="55" t="s">
@@ -12240,7 +12216,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3675</v>
       </c>
-      <c r="L110" s="122">
+      <c r="L110" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7350</v>
       </c>
@@ -12275,17 +12251,17 @@
       <c r="AE110"/>
     </row>
     <row r="111" spans="1:31" ht="15">
-      <c r="A111" s="111" t="s">
+      <c r="A111" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="111" t="s">
+      <c r="B111" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D111" s="122">
+      <c r="D111" s="115">
         <v>3689</v>
       </c>
       <c r="E111" s="46" t="s">
@@ -12299,10 +12275,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H111" s="122">
+      <c r="H111" s="115">
         <v>7050</v>
       </c>
-      <c r="I111" s="113" t="s">
+      <c r="I111" s="55" t="s">
         <v>153</v>
       </c>
       <c r="J111" s="46">
@@ -12313,7 +12289,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L111" s="122">
+      <c r="L111" s="115">
         <v>4890</v>
       </c>
       <c r="M111" s="46"/>
@@ -12329,7 +12305,7 @@
       <c r="S111" s="46">
         <v>325</v>
       </c>
-      <c r="T111" s="118" t="s">
+      <c r="T111" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U111" s="46">
@@ -12347,17 +12323,17 @@
       <c r="AE111"/>
     </row>
     <row r="112" spans="1:31" ht="15">
-      <c r="A112" s="111" t="s">
+      <c r="A112" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B112" s="111" t="s">
+      <c r="B112" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C112" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D112" s="122">
+      <c r="D112" s="115">
         <v>4679</v>
       </c>
       <c r="E112" s="46" t="s">
@@ -12371,10 +12347,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H112" s="122">
+      <c r="H112" s="115">
         <v>8350</v>
       </c>
-      <c r="I112" s="113" t="s">
+      <c r="I112" s="55" t="s">
         <v>153</v>
       </c>
       <c r="J112" s="46">
@@ -12385,7 +12361,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L112" s="122">
+      <c r="L112" s="115">
         <v>5690</v>
       </c>
       <c r="M112" s="46"/>
@@ -12401,7 +12377,7 @@
       <c r="S112" s="46">
         <v>325</v>
       </c>
-      <c r="T112" s="118" t="s">
+      <c r="T112" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U112" s="46">
@@ -12429,7 +12405,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D113" s="122">
+      <c r="D113" s="115">
         <v>2459</v>
       </c>
       <c r="E113" s="44" t="s">
@@ -12443,7 +12419,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H113" s="122">
+      <c r="H113" s="115">
         <v>3990</v>
       </c>
       <c r="I113" s="55" t="s">
@@ -12457,7 +12433,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L113" s="122">
+      <c r="L113" s="115">
         <v>3390</v>
       </c>
       <c r="M113" s="46"/>
@@ -12501,7 +12477,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D114" s="122">
+      <c r="D114" s="115">
         <v>5819</v>
       </c>
       <c r="E114" s="44" t="s">
@@ -12515,7 +12491,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H114" s="122">
+      <c r="H114" s="115">
         <v>9450</v>
       </c>
       <c r="I114" s="55" t="s">
@@ -12529,7 +12505,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4062.5</v>
       </c>
-      <c r="L114" s="122">
+      <c r="L114" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8450</v>
       </c>
@@ -12574,7 +12550,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D115" s="122">
+      <c r="D115" s="115">
         <v>3689</v>
       </c>
       <c r="E115" s="44" t="s">
@@ -12588,7 +12564,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H115" s="122">
+      <c r="H115" s="115">
         <v>7050</v>
       </c>
       <c r="I115" s="55" t="s">
@@ -12602,7 +12578,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2862.5</v>
       </c>
-      <c r="L115" s="122">
+      <c r="L115" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6050</v>
       </c>
@@ -12647,7 +12623,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D116" s="122">
+      <c r="D116" s="115">
         <v>4679</v>
       </c>
       <c r="E116" s="44" t="s">
@@ -12661,7 +12637,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H116" s="122">
+      <c r="H116" s="115">
         <v>8350</v>
       </c>
       <c r="I116" s="55" t="s">
@@ -12675,7 +12651,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3512.5</v>
       </c>
-      <c r="L116" s="122">
+      <c r="L116" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7350</v>
       </c>
@@ -12711,73 +12687,64 @@
       <c r="AE116"/>
     </row>
     <row r="117" spans="1:31" ht="15">
-      <c r="A117" s="111" t="s">
-        <v>646</v>
-      </c>
-      <c r="B117" s="102" t="s">
-        <v>647</v>
+      <c r="A117" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B117" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C117" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
-      </c>
-      <c r="D117" s="122">
-        <v>5939</v>
-      </c>
-      <c r="E117" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D117" s="115">
+        <v>5819</v>
+      </c>
+      <c r="E117" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F117" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1376.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G117" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H117" s="122">
+      <c r="H117" s="115">
         <v>9450</v>
       </c>
-      <c r="I117" s="77" t="s">
-        <v>154</v>
+      <c r="I117" s="55" t="s">
+        <v>45</v>
       </c>
       <c r="J117" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="K117" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L117" s="122">
-        <v>6690</v>
-      </c>
+        <v>4562.5</v>
+      </c>
+      <c r="L117" s="115"/>
       <c r="M117" s="46"/>
-      <c r="N117" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="O117" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
+      <c r="N117" s="46"/>
+      <c r="O117" s="46"/>
       <c r="P117" s="46"/>
       <c r="Q117" s="47">
         <v>1</v>
       </c>
-      <c r="R117" s="47" t="s">
+      <c r="R117" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S117" s="47">
+      <c r="S117" s="46">
         <v>325</v>
       </c>
-      <c r="T117" s="49" t="s">
+      <c r="T117" s="48" t="s">
         <v>55</v>
       </c>
       <c r="U117" s="49">
         <v>0</v>
       </c>
-      <c r="V117" s="49" t="s">
+      <c r="V117" s="48" t="s">
         <v>56</v>
       </c>
       <c r="W117" s="46"/>
@@ -12790,73 +12757,67 @@
       <c r="AE117"/>
     </row>
     <row r="118" spans="1:31" ht="15">
-      <c r="A118" s="111" t="s">
-        <v>648</v>
+      <c r="A118" s="42" t="s">
+        <v>53</v>
       </c>
       <c r="B118" s="42" t="s">
-        <v>649</v>
+        <v>54</v>
       </c>
       <c r="C118" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D118" s="122">
-        <v>3839</v>
-      </c>
-      <c r="E118" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D118" s="115">
+        <v>5819</v>
+      </c>
+      <c r="E118" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F118" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G118" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H118" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I118" s="77" t="s">
-        <v>154</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H118" s="115">
+        <v>9450</v>
+      </c>
+      <c r="I118" s="55" t="s">
+        <v>129</v>
       </c>
       <c r="J118" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="K118" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L118" s="122">
-        <v>4990</v>
+        <v>4562.5</v>
+      </c>
+      <c r="L118" s="115">
+        <v>9450</v>
       </c>
       <c r="M118" s="46"/>
-      <c r="N118" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="O118" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
+      <c r="N118" s="46"/>
+      <c r="O118" s="46"/>
       <c r="P118" s="46"/>
       <c r="Q118" s="47">
         <v>1</v>
       </c>
-      <c r="R118" s="47" t="s">
+      <c r="R118" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S118" s="47">
+      <c r="S118" s="46">
         <v>325</v>
       </c>
-      <c r="T118" s="49" t="s">
+      <c r="T118" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="U118" s="49">
-        <v>0</v>
-      </c>
-      <c r="V118" s="49" t="s">
+      <c r="U118" s="46">
+        <v>0</v>
+      </c>
+      <c r="V118" s="51" t="s">
         <v>56</v>
       </c>
       <c r="W118" s="46"/>
@@ -12870,55 +12831,49 @@
     </row>
     <row r="119" spans="1:31" ht="15">
       <c r="A119" s="42" t="s">
-        <v>650</v>
-      </c>
-      <c r="B119" s="102" t="s">
-        <v>651</v>
+        <v>53</v>
+      </c>
+      <c r="B119" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C119" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D119" s="122">
-        <v>5039</v>
-      </c>
-      <c r="E119" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D119" s="115">
+        <v>5819</v>
+      </c>
+      <c r="E119" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F119" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G119" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H119" s="122">
-        <v>8350</v>
-      </c>
-      <c r="I119" s="77" t="s">
-        <v>154</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H119" s="116">
+        <v>9450</v>
+      </c>
+      <c r="I119" s="45" t="s">
+        <v>136</v>
       </c>
       <c r="J119" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>750</v>
       </c>
       <c r="K119" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L119" s="122">
-        <v>5790</v>
+        <v>3812.5</v>
+      </c>
+      <c r="L119" s="116">
+        <v>7950</v>
       </c>
       <c r="M119" s="46"/>
-      <c r="N119" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="O119" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
+      <c r="N119" s="46"/>
+      <c r="O119" s="46"/>
       <c r="P119" s="46"/>
       <c r="Q119" s="47">
         <v>1</v>
@@ -12926,16 +12881,16 @@
       <c r="R119" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S119" s="47">
+      <c r="S119" s="73">
         <v>325</v>
       </c>
-      <c r="T119" s="49" t="s">
+      <c r="T119" s="48" t="s">
         <v>55</v>
       </c>
       <c r="U119" s="49">
         <v>0</v>
       </c>
-      <c r="V119" s="49" t="s">
+      <c r="V119" s="48" t="s">
         <v>56</v>
       </c>
       <c r="W119" s="4"/>
@@ -12948,7 +12903,7 @@
       <c r="AE119"/>
     </row>
     <row r="120" spans="1:31" ht="15">
-      <c r="A120" s="111" t="s">
+      <c r="A120" s="42" t="s">
         <v>123</v>
       </c>
       <c r="B120" s="42" t="s">
@@ -12958,7 +12913,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D120" s="122">
+      <c r="D120" s="115">
         <v>5819</v>
       </c>
       <c r="E120" s="46" t="s">
@@ -12972,10 +12927,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H120" s="122">
+      <c r="H120" s="115">
         <v>9450</v>
       </c>
-      <c r="I120" s="113" t="s">
+      <c r="I120" s="55" t="s">
         <v>154</v>
       </c>
       <c r="J120" s="46">
@@ -12986,7 +12941,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L120" s="122">
+      <c r="L120" s="115">
         <v>6690</v>
       </c>
       <c r="M120" s="46"/>
@@ -13002,7 +12957,7 @@
       <c r="S120" s="46">
         <v>325</v>
       </c>
-      <c r="T120" s="118" t="s">
+      <c r="T120" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U120" s="46">
@@ -13021,17 +12976,17 @@
       <c r="AE120"/>
     </row>
     <row r="121" spans="1:31" ht="15">
-      <c r="A121" s="111" t="s">
+      <c r="A121" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="B121" s="111" t="s">
+      <c r="B121" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C121" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D121" s="122">
+      <c r="D121" s="115">
         <v>3689</v>
       </c>
       <c r="E121" s="46" t="s">
@@ -13045,10 +13000,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H121" s="122">
+      <c r="H121" s="115">
         <v>7050</v>
       </c>
-      <c r="I121" s="113" t="s">
+      <c r="I121" s="55" t="s">
         <v>154</v>
       </c>
       <c r="J121" s="46">
@@ -13059,7 +13014,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L121" s="122">
+      <c r="L121" s="115">
         <v>4890</v>
       </c>
       <c r="M121" s="46"/>
@@ -13075,7 +13030,7 @@
       <c r="S121" s="46">
         <v>325</v>
       </c>
-      <c r="T121" s="118" t="s">
+      <c r="T121" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U121" s="46">
@@ -13094,17 +13049,17 @@
       <c r="AE121"/>
     </row>
     <row r="122" spans="1:31" ht="15">
-      <c r="A122" s="111" t="s">
+      <c r="A122" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="111" t="s">
+      <c r="B122" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C122" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D122" s="122">
+      <c r="D122" s="115">
         <v>4679</v>
       </c>
       <c r="E122" s="46" t="s">
@@ -13118,10 +13073,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H122" s="122">
+      <c r="H122" s="115">
         <v>8350</v>
       </c>
-      <c r="I122" s="113" t="s">
+      <c r="I122" s="55" t="s">
         <v>154</v>
       </c>
       <c r="J122" s="46">
@@ -13132,7 +13087,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L122" s="122">
+      <c r="L122" s="115">
         <v>5690</v>
       </c>
       <c r="M122" s="46"/>
@@ -13148,7 +13103,7 @@
       <c r="S122" s="46">
         <v>325</v>
       </c>
-      <c r="T122" s="118" t="s">
+      <c r="T122" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U122" s="46">
@@ -13177,7 +13132,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D123" s="122">
+      <c r="D123" s="115">
         <v>2459</v>
       </c>
       <c r="E123" s="44" t="s">
@@ -13191,7 +13146,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H123" s="122">
+      <c r="H123" s="115">
         <v>3990</v>
       </c>
       <c r="I123" s="55" t="s">
@@ -13205,7 +13160,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L123" s="122">
+      <c r="L123" s="115">
         <v>3390</v>
       </c>
       <c r="M123" s="46"/>
@@ -13240,70 +13195,67 @@
       <c r="AE123"/>
     </row>
     <row r="124" spans="1:31" ht="15">
-      <c r="A124" s="111" t="s">
-        <v>646</v>
-      </c>
-      <c r="B124" s="111" t="s">
-        <v>647</v>
+      <c r="A124" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B124" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C124" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
-      </c>
-      <c r="D124" s="122">
-        <v>5939</v>
-      </c>
-      <c r="E124" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D124" s="115">
+        <v>5819</v>
+      </c>
+      <c r="E124" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F124" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1376.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G124" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H124" s="122">
+      <c r="H124" s="115">
         <v>9450</v>
       </c>
-      <c r="I124" s="77" t="s">
-        <v>157</v>
+      <c r="I124" s="55" t="s">
+        <v>141</v>
       </c>
       <c r="J124" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="K124" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L124" s="122">
-        <v>6690</v>
+        <v>4562.5</v>
+      </c>
+      <c r="L124" s="115">
+        <v>9450</v>
       </c>
       <c r="M124" s="46"/>
       <c r="N124" s="46"/>
-      <c r="O124" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="O124" s="46"/>
       <c r="P124" s="46"/>
       <c r="Q124" s="47">
         <v>1</v>
       </c>
-      <c r="R124" s="47" t="s">
+      <c r="R124" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S124" s="47">
+      <c r="S124" s="46">
         <v>325</v>
       </c>
-      <c r="T124" s="49" t="s">
+      <c r="T124" s="48" t="s">
         <v>55</v>
       </c>
       <c r="U124" s="49">
         <v>0</v>
       </c>
-      <c r="V124" s="49" t="s">
+      <c r="V124" s="48" t="s">
         <v>56</v>
       </c>
       <c r="W124" s="4"/>
@@ -13316,70 +13268,68 @@
       <c r="AE124"/>
     </row>
     <row r="125" spans="1:31" ht="15">
-      <c r="A125" s="111" t="s">
-        <v>648</v>
-      </c>
-      <c r="B125" s="112" t="s">
-        <v>649</v>
+      <c r="A125" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B125" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C125" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D125" s="122">
-        <v>3839</v>
-      </c>
-      <c r="E125" s="46" t="s">
+        <v>11963</v>
+      </c>
+      <c r="D125" s="115">
+        <v>5819</v>
+      </c>
+      <c r="E125" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G125" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H125" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I125" s="77" t="s">
-        <v>157</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H125" s="115">
+        <v>9450</v>
+      </c>
+      <c r="I125" s="55" t="s">
+        <v>156</v>
       </c>
       <c r="J125" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>500</v>
       </c>
       <c r="K125" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L125" s="122">
-        <v>4990</v>
+        <v>4062.5</v>
+      </c>
+      <c r="L125" s="115">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>8450</v>
       </c>
       <c r="M125" s="46"/>
       <c r="N125" s="46"/>
-      <c r="O125" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="O125" s="46"/>
       <c r="P125" s="46"/>
       <c r="Q125" s="47">
         <v>1</v>
       </c>
-      <c r="R125" s="47" t="s">
+      <c r="R125" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S125" s="47">
+      <c r="S125" s="46">
         <v>325</v>
       </c>
-      <c r="T125" s="49" t="s">
+      <c r="T125" s="48" t="s">
         <v>55</v>
       </c>
       <c r="U125" s="49">
         <v>0</v>
       </c>
-      <c r="V125" s="49" t="s">
+      <c r="V125" s="48" t="s">
         <v>56</v>
       </c>
       <c r="W125" s="4"/>
@@ -13392,70 +13342,67 @@
       <c r="AE125"/>
     </row>
     <row r="126" spans="1:31" ht="15">
-      <c r="A126" s="111" t="s">
-        <v>650</v>
-      </c>
-      <c r="B126" s="111" t="s">
-        <v>651</v>
+      <c r="A126" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="B126" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="C126" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D126" s="122">
-        <v>5039</v>
+        <v>11963</v>
+      </c>
+      <c r="D126" s="115">
+        <v>5819</v>
       </c>
       <c r="E126" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F126" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>1256.5</v>
       </c>
       <c r="G126" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H126" s="122">
-        <v>8350</v>
-      </c>
-      <c r="I126" s="77" t="s">
-        <v>157</v>
+        <v>4562.5</v>
+      </c>
+      <c r="H126" s="115">
+        <v>9450</v>
+      </c>
+      <c r="I126" s="122" t="s">
+        <v>159</v>
       </c>
       <c r="J126" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>925</v>
       </c>
       <c r="K126" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L126" s="122">
-        <v>5790</v>
-      </c>
-      <c r="M126" s="46"/>
+        <v>3637.5</v>
+      </c>
+      <c r="L126" s="115">
+        <v>7600</v>
+      </c>
+      <c r="M126" s="122"/>
       <c r="N126" s="46"/>
-      <c r="O126" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="O126" s="123"/>
       <c r="P126" s="46"/>
       <c r="Q126" s="47">
         <v>1</v>
       </c>
-      <c r="R126" s="47" t="s">
+      <c r="R126" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S126" s="47">
+      <c r="S126" s="46">
         <v>325</v>
       </c>
-      <c r="T126" s="49" t="s">
+      <c r="T126" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="U126" s="49">
-        <v>0</v>
-      </c>
-      <c r="V126" s="49" t="s">
+      <c r="U126" s="21">
+        <v>0</v>
+      </c>
+      <c r="V126" s="113" t="s">
         <v>56</v>
       </c>
       <c r="W126" s="4"/>
@@ -13468,7 +13415,7 @@
       <c r="AE126"/>
     </row>
     <row r="127" spans="1:31" ht="15">
-      <c r="A127" s="111" t="s">
+      <c r="A127" s="42" t="s">
         <v>123</v>
       </c>
       <c r="B127" s="42" t="s">
@@ -13478,7 +13425,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D127" s="122">
+      <c r="D127" s="115">
         <v>5819</v>
       </c>
       <c r="E127" s="46" t="s">
@@ -13492,10 +13439,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H127" s="122">
+      <c r="H127" s="115">
         <v>9450</v>
       </c>
-      <c r="I127" s="113" t="s">
+      <c r="I127" s="55" t="s">
         <v>157</v>
       </c>
       <c r="J127" s="46">
@@ -13506,7 +13453,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L127" s="122">
+      <c r="L127" s="115">
         <v>6690</v>
       </c>
       <c r="M127" s="46"/>
@@ -13522,7 +13469,7 @@
       <c r="S127" s="46">
         <v>325</v>
       </c>
-      <c r="T127" s="118" t="s">
+      <c r="T127" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U127" s="46">
@@ -13541,34 +13488,34 @@
       <c r="AE127"/>
     </row>
     <row r="128" spans="1:31" ht="15">
-      <c r="A128" s="42" t="s">
-        <v>53</v>
+      <c r="A128" s="120" t="s">
+        <v>50</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C128" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D128" s="122">
-        <v>5819</v>
-      </c>
-      <c r="E128" s="44" t="s">
+        <v>6383</v>
+      </c>
+      <c r="D128" s="115">
+        <v>3029</v>
+      </c>
+      <c r="E128" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F128" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
+        <v>666.5</v>
       </c>
       <c r="G128" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H128" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I128" s="55" t="s">
+        <v>2362.5</v>
+      </c>
+      <c r="H128" s="115">
+        <v>5050</v>
+      </c>
+      <c r="I128" s="122" t="s">
         <v>45</v>
       </c>
       <c r="J128" s="46">
@@ -13576,9 +13523,11 @@
       </c>
       <c r="K128" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="L128" s="122"/>
+        <v>2362.5</v>
+      </c>
+      <c r="L128" s="115">
+        <v>5050</v>
+      </c>
       <c r="M128" s="46"/>
       <c r="N128" s="46"/>
       <c r="O128" s="46"/>
@@ -13586,19 +13535,19 @@
       <c r="Q128" s="47">
         <v>1</v>
       </c>
-      <c r="R128" s="46" t="s">
+      <c r="R128" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="S128" s="46">
+      <c r="S128" s="73">
         <v>325</v>
       </c>
-      <c r="T128" s="48" t="s">
+      <c r="T128" s="49" t="s">
         <v>55</v>
       </c>
       <c r="U128" s="49">
         <v>0</v>
       </c>
-      <c r="V128" s="48" t="s">
+      <c r="V128" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W128" s="4"/>
@@ -13611,35 +13560,35 @@
       <c r="AE128"/>
     </row>
     <row r="129" spans="1:31" ht="15">
-      <c r="A129" s="42" t="s">
-        <v>53</v>
+      <c r="A129" s="120" t="s">
+        <v>50</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C129" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D129" s="122">
-        <v>5819</v>
-      </c>
-      <c r="E129" s="44" t="s">
+        <v>6383</v>
+      </c>
+      <c r="D129" s="115">
+        <v>3029</v>
+      </c>
+      <c r="E129" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F129" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
+        <v>666.5</v>
       </c>
       <c r="G129" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H129" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I129" s="55" t="s">
-        <v>129</v>
+        <v>2362.5</v>
+      </c>
+      <c r="H129" s="115">
+        <v>5050</v>
+      </c>
+      <c r="I129" s="122" t="s">
+        <v>141</v>
       </c>
       <c r="J129" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -13647,10 +13596,10 @@
       </c>
       <c r="K129" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="L129" s="122">
-        <v>9450</v>
+        <v>2362.5</v>
+      </c>
+      <c r="L129" s="115">
+        <v>5050</v>
       </c>
       <c r="M129" s="46"/>
       <c r="N129" s="46"/>
@@ -13659,19 +13608,19 @@
       <c r="Q129" s="47">
         <v>1</v>
       </c>
-      <c r="R129" s="46" t="s">
+      <c r="R129" s="72" t="s">
         <v>52</v>
       </c>
       <c r="S129" s="46">
         <v>325</v>
       </c>
-      <c r="T129" s="6" t="s">
+      <c r="T129" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="U129" s="46">
-        <v>0</v>
-      </c>
-      <c r="V129" s="51" t="s">
+      <c r="U129" s="49">
+        <v>0</v>
+      </c>
+      <c r="V129" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W129" s="4"/>
@@ -13685,49 +13634,55 @@
     </row>
     <row r="130" spans="1:31" ht="15">
       <c r="A130" s="42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B130" s="42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C130" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D130" s="122">
-        <v>5819</v>
-      </c>
-      <c r="E130" s="44" t="s">
+        <v>8003</v>
+      </c>
+      <c r="D130" s="115">
+        <v>3839</v>
+      </c>
+      <c r="E130" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F130" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
+        <v>476.5</v>
       </c>
       <c r="G130" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H130" s="123">
-        <v>9450</v>
-      </c>
-      <c r="I130" s="45" t="s">
-        <v>136</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H130" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I130" s="77" t="s">
+        <v>122</v>
       </c>
       <c r="J130" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>750</v>
+        <v>1030</v>
       </c>
       <c r="K130" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3812.5</v>
-      </c>
-      <c r="L130" s="123">
-        <v>7950</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L130" s="115">
+        <v>4990</v>
       </c>
       <c r="M130" s="46"/>
-      <c r="N130" s="46"/>
-      <c r="O130" s="46"/>
+      <c r="N130" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O130" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P130" s="46"/>
       <c r="Q130" s="47">
         <v>1</v>
@@ -13735,16 +13690,16 @@
       <c r="R130" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S130" s="73">
+      <c r="S130" s="47">
         <v>325</v>
       </c>
-      <c r="T130" s="48" t="s">
+      <c r="T130" s="49" t="s">
         <v>55</v>
       </c>
       <c r="U130" s="49">
         <v>0</v>
       </c>
-      <c r="V130" s="48" t="s">
+      <c r="V130" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W130" s="4"/>
@@ -13758,66 +13713,72 @@
     </row>
     <row r="131" spans="1:31" ht="15">
       <c r="A131" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="B131" s="42" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="B131" s="102" t="s">
+        <v>58</v>
       </c>
       <c r="C131" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D131" s="122">
-        <v>5819</v>
-      </c>
-      <c r="E131" s="44" t="s">
+        <v>8003</v>
+      </c>
+      <c r="D131" s="115">
+        <v>3839</v>
+      </c>
+      <c r="E131" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F131" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
+        <v>476.5</v>
       </c>
       <c r="G131" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H131" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I131" s="55" t="s">
-        <v>141</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H131" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I131" s="77" t="s">
+        <v>152</v>
       </c>
       <c r="J131" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="K131" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="L131" s="122">
-        <v>9450</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L131" s="115">
+        <v>4990</v>
       </c>
       <c r="M131" s="80"/>
-      <c r="N131" s="46"/>
-      <c r="O131" s="46"/>
+      <c r="N131" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O131" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P131" s="46"/>
       <c r="Q131" s="47">
         <v>1</v>
       </c>
-      <c r="R131" s="46" t="s">
+      <c r="R131" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S131" s="46">
+      <c r="S131" s="47">
         <v>325</v>
       </c>
-      <c r="T131" s="48" t="s">
+      <c r="T131" s="49" t="s">
         <v>55</v>
       </c>
       <c r="U131" s="49">
         <v>0</v>
       </c>
-      <c r="V131" s="48" t="s">
+      <c r="V131" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W131" s="4"/>
@@ -13831,67 +13792,72 @@
     </row>
     <row r="132" spans="1:31" ht="15">
       <c r="A132" s="42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B132" s="42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C132" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D132" s="122">
-        <v>5819</v>
-      </c>
-      <c r="E132" s="44" t="s">
+        <v>8003</v>
+      </c>
+      <c r="D132" s="115">
+        <v>3839</v>
+      </c>
+      <c r="E132" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F132" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
+        <v>476.5</v>
       </c>
       <c r="G132" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H132" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I132" s="55" t="s">
-        <v>156</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H132" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I132" s="77" t="s">
+        <v>153</v>
       </c>
       <c r="J132" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>500</v>
+        <v>1030</v>
       </c>
       <c r="K132" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4062.5</v>
-      </c>
-      <c r="L132" s="122">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>8450</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L132" s="115">
+        <v>4990</v>
       </c>
       <c r="M132" s="80"/>
-      <c r="N132" s="46"/>
-      <c r="O132" s="46"/>
+      <c r="N132" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O132" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P132" s="46"/>
       <c r="Q132" s="47">
         <v>1</v>
       </c>
-      <c r="R132" s="46" t="s">
+      <c r="R132" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S132" s="46">
+      <c r="S132" s="47">
         <v>325</v>
       </c>
-      <c r="T132" s="48" t="s">
+      <c r="T132" s="49" t="s">
         <v>55</v>
       </c>
       <c r="U132" s="49">
         <v>0</v>
       </c>
-      <c r="V132" s="48" t="s">
+      <c r="V132" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W132" s="4"/>
@@ -13905,66 +13871,72 @@
     </row>
     <row r="133" spans="1:31" ht="15">
       <c r="A133" s="79" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B133" s="42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C133" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>11963</v>
-      </c>
-      <c r="D133" s="122">
-        <v>5819</v>
+        <v>8003</v>
+      </c>
+      <c r="D133" s="115">
+        <v>3839</v>
       </c>
       <c r="E133" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F133" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1256.5</v>
+        <v>476.5</v>
       </c>
       <c r="G133" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H133" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I133" s="84" t="s">
-        <v>159</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H133" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I133" s="78" t="s">
+        <v>154</v>
       </c>
       <c r="J133" s="46">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>925</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
       </c>
       <c r="K133" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3637.5</v>
-      </c>
-      <c r="L133" s="122">
-        <v>7600</v>
-      </c>
-      <c r="M133" s="84"/>
-      <c r="N133" s="46"/>
-      <c r="O133" s="97"/>
+        <v>2332.5</v>
+      </c>
+      <c r="L133" s="115">
+        <v>4990</v>
+      </c>
+      <c r="M133" s="80"/>
+      <c r="N133" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2332.5</v>
+      </c>
+      <c r="O133" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P133" s="80"/>
       <c r="Q133" s="81">
         <v>1</v>
       </c>
-      <c r="R133" s="80" t="s">
+      <c r="R133" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S133" s="46">
+      <c r="S133" s="47">
         <v>325</v>
       </c>
-      <c r="T133" s="96" t="s">
+      <c r="T133" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="U133" s="20">
-        <v>0</v>
-      </c>
-      <c r="V133" s="95" t="s">
+      <c r="U133" s="82">
+        <v>0</v>
+      </c>
+      <c r="V133" s="83" t="s">
         <v>56</v>
       </c>
       <c r="X133" s="46"/>
@@ -13977,56 +13949,60 @@
     </row>
     <row r="134" spans="1:31" ht="15">
       <c r="A134" s="79" t="s">
-        <v>50</v>
-      </c>
-      <c r="B134" s="42" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="B134" s="102" t="s">
+        <v>58</v>
       </c>
       <c r="C134" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>6383</v>
-      </c>
-      <c r="D134" s="122">
-        <v>3029</v>
+        <v>8003</v>
+      </c>
+      <c r="D134" s="115">
+        <v>3839</v>
       </c>
       <c r="E134" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F134" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>476.5</v>
       </c>
       <c r="G134" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>2362.5</v>
-      </c>
-      <c r="H134" s="122">
-        <v>5050</v>
-      </c>
-      <c r="I134" s="84" t="s">
-        <v>45</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H134" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I134" s="78" t="s">
+        <v>157</v>
       </c>
       <c r="J134" s="46">
-        <v>0</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1030</v>
       </c>
       <c r="K134" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2362.5</v>
-      </c>
-      <c r="L134" s="122">
-        <v>5050</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L134" s="115">
+        <v>4990</v>
       </c>
       <c r="M134" s="80"/>
       <c r="N134" s="46"/>
-      <c r="O134" s="80"/>
+      <c r="O134" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2332.5</v>
+      </c>
       <c r="P134" s="80"/>
       <c r="Q134" s="81">
         <v>1</v>
       </c>
-      <c r="R134" s="98" t="s">
+      <c r="R134" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S134" s="73">
+      <c r="S134" s="47">
         <v>325</v>
       </c>
       <c r="T134" s="82" t="s">
@@ -14057,7 +14033,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D135" s="122">
+      <c r="D135" s="115">
         <v>5819</v>
       </c>
       <c r="E135" s="80" t="s">
@@ -14071,7 +14047,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H135" s="122">
+      <c r="H135" s="115">
         <v>9450</v>
       </c>
       <c r="I135" s="84" t="s">
@@ -14085,7 +14061,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L135" s="122">
+      <c r="L135" s="115">
         <v>6690</v>
       </c>
       <c r="M135" s="80"/>
@@ -14129,7 +14105,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D136" s="122">
+      <c r="D136" s="115">
         <v>3689</v>
       </c>
       <c r="E136" s="80" t="s">
@@ -14143,7 +14119,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H136" s="122">
+      <c r="H136" s="115">
         <v>7050</v>
       </c>
       <c r="I136" s="84" t="s">
@@ -14157,7 +14133,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L136" s="122">
+      <c r="L136" s="115">
         <v>4890</v>
       </c>
       <c r="M136" s="80"/>
@@ -14201,7 +14177,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D137" s="122">
+      <c r="D137" s="115">
         <v>4679</v>
       </c>
       <c r="E137" s="80" t="s">
@@ -14215,7 +14191,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3512.5</v>
       </c>
-      <c r="H137" s="122">
+      <c r="H137" s="115">
         <v>7350</v>
       </c>
       <c r="I137" s="84" t="s">
@@ -14229,7 +14205,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L137" s="122">
+      <c r="L137" s="115">
         <v>5690</v>
       </c>
       <c r="M137" s="80"/>
@@ -14264,57 +14240,60 @@
     </row>
     <row r="138" spans="1:31" ht="15">
       <c r="A138" s="79" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B138" s="42" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C138" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>6383</v>
-      </c>
-      <c r="D138" s="122">
-        <v>3029</v>
+        <v>8003</v>
+      </c>
+      <c r="D138" s="115">
+        <v>3839</v>
       </c>
       <c r="E138" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F138" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>476.5</v>
       </c>
       <c r="G138" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>2362.5</v>
-      </c>
-      <c r="H138" s="122">
-        <v>5050</v>
-      </c>
-      <c r="I138" s="84" t="s">
-        <v>141</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H138" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I138" s="78" t="s">
+        <v>158</v>
       </c>
       <c r="J138" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="K138" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2362.5</v>
-      </c>
-      <c r="L138" s="122">
-        <v>5050</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L138" s="115">
+        <v>4990</v>
       </c>
       <c r="M138" s="80"/>
       <c r="N138" s="46"/>
-      <c r="O138" s="80"/>
+      <c r="O138" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2332.5</v>
+      </c>
       <c r="P138" s="80"/>
       <c r="Q138" s="81">
         <v>1</v>
       </c>
-      <c r="R138" s="104" t="s">
+      <c r="R138" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S138" s="46">
+      <c r="S138" s="47">
         <v>325</v>
       </c>
       <c r="T138" s="82" t="s">
@@ -14338,14 +14317,14 @@
       <c r="A139" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="B139" s="111" t="s">
+      <c r="B139" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C139" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D139" s="122">
+      <c r="D139" s="115">
         <v>3689</v>
       </c>
       <c r="E139" s="80" t="s">
@@ -14359,7 +14338,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H139" s="122">
+      <c r="H139" s="115">
         <v>7050</v>
       </c>
       <c r="I139" s="84" t="s">
@@ -14373,7 +14352,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L139" s="122">
+      <c r="L139" s="115">
         <v>4890</v>
       </c>
       <c r="M139" s="80"/>
@@ -14411,14 +14390,14 @@
       <c r="A140" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="B140" s="111" t="s">
+      <c r="B140" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C140" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D140" s="122">
+      <c r="D140" s="115">
         <v>4679</v>
       </c>
       <c r="E140" s="80" t="s">
@@ -14432,7 +14411,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H140" s="122">
+      <c r="H140" s="115">
         <v>8350</v>
       </c>
       <c r="I140" s="84" t="s">
@@ -14446,7 +14425,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L140" s="122">
+      <c r="L140" s="115">
         <v>5690</v>
       </c>
       <c r="M140" s="80"/>
@@ -14491,7 +14470,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D141" s="122">
+      <c r="D141" s="115">
         <v>2459</v>
       </c>
       <c r="E141" s="80" t="s">
@@ -14505,7 +14484,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H141" s="122">
+      <c r="H141" s="115">
         <v>3990</v>
       </c>
       <c r="I141" s="84" t="s">
@@ -14519,7 +14498,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L141" s="122">
+      <c r="L141" s="115">
         <v>3390</v>
       </c>
       <c r="M141" s="80"/>
@@ -14555,51 +14534,51 @@
     </row>
     <row r="142" spans="1:31" ht="15">
       <c r="A142" s="79" t="s">
-        <v>646</v>
-      </c>
-      <c r="B142" s="112" t="s">
-        <v>647</v>
+        <v>57</v>
+      </c>
+      <c r="B142" s="102" t="s">
+        <v>58</v>
       </c>
       <c r="C142" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
-      </c>
-      <c r="D142" s="122">
-        <v>5939</v>
+        <v>8003</v>
+      </c>
+      <c r="D142" s="115">
+        <v>3839</v>
       </c>
       <c r="E142" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F142" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1376.5</v>
+        <v>476.5</v>
       </c>
       <c r="G142" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H142" s="122">
-        <v>9450</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H142" s="115">
+        <v>7050</v>
       </c>
       <c r="I142" s="78" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J142" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>1030</v>
       </c>
       <c r="K142" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L142" s="122">
-        <v>6690</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L142" s="115">
+        <v>4990</v>
       </c>
       <c r="M142" s="80"/>
       <c r="N142" s="46"/>
       <c r="O142" s="80">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3182.5</v>
+        <v>2332.5</v>
       </c>
       <c r="P142" s="80"/>
       <c r="Q142" s="81">
@@ -14630,16 +14609,16 @@
     </row>
     <row r="143" spans="1:31" ht="15">
       <c r="A143" s="79" t="s">
-        <v>648</v>
-      </c>
-      <c r="B143" s="111" t="s">
-        <v>649</v>
+        <v>57</v>
+      </c>
+      <c r="B143" s="120" t="s">
+        <v>58</v>
       </c>
       <c r="C143" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D143" s="122">
+      <c r="D143" s="115">
         <v>3839</v>
       </c>
       <c r="E143" s="80" t="s">
@@ -14653,11 +14632,11 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H143" s="122">
+      <c r="H143" s="115">
         <v>7050</v>
       </c>
       <c r="I143" s="78" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J143" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -14667,7 +14646,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2332.5</v>
       </c>
-      <c r="L143" s="122">
+      <c r="L143" s="115">
         <v>4990</v>
       </c>
       <c r="M143" s="80"/>
@@ -14705,51 +14684,51 @@
     </row>
     <row r="144" spans="1:31" ht="15">
       <c r="A144" s="79" t="s">
-        <v>650</v>
-      </c>
-      <c r="B144" s="112" t="s">
-        <v>651</v>
+        <v>57</v>
+      </c>
+      <c r="B144" s="121" t="s">
+        <v>58</v>
       </c>
       <c r="C144" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D144" s="122">
-        <v>5039</v>
+        <v>8003</v>
+      </c>
+      <c r="D144" s="115">
+        <v>3839</v>
       </c>
       <c r="E144" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F144" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>476.5</v>
       </c>
       <c r="G144" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H144" s="122">
-        <v>8350</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H144" s="115">
+        <v>7050</v>
       </c>
       <c r="I144" s="78" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J144" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>1030</v>
       </c>
       <c r="K144" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L144" s="122">
-        <v>5790</v>
+        <v>2332.5</v>
+      </c>
+      <c r="L144" s="115">
+        <v>4990</v>
       </c>
       <c r="M144" s="80"/>
       <c r="N144" s="46"/>
       <c r="O144" s="80">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
+        <v>2332.5</v>
       </c>
       <c r="P144" s="80"/>
       <c r="Q144" s="81">
@@ -14789,7 +14768,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D145" s="122">
+      <c r="D145" s="115">
         <v>5819</v>
       </c>
       <c r="E145" s="80" t="s">
@@ -14803,7 +14782,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H145" s="122">
+      <c r="H145" s="115">
         <v>9450</v>
       </c>
       <c r="I145" s="84" t="s">
@@ -14817,7 +14796,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L145" s="122">
+      <c r="L145" s="115">
         <v>6690</v>
       </c>
       <c r="M145" s="80"/>
@@ -14854,14 +14833,14 @@
       <c r="A146" s="85" t="s">
         <v>125</v>
       </c>
-      <c r="B146" s="111" t="s">
+      <c r="B146" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C146" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D146" s="122">
+      <c r="D146" s="115">
         <v>3689</v>
       </c>
       <c r="E146" s="86" t="s">
@@ -14875,7 +14854,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H146" s="122">
+      <c r="H146" s="115">
         <v>7050</v>
       </c>
       <c r="I146" s="87" t="s">
@@ -14889,7 +14868,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L146" s="122">
+      <c r="L146" s="115">
         <v>4890</v>
       </c>
       <c r="M146" s="86"/>
@@ -14905,13 +14884,13 @@
       <c r="S146" s="46">
         <v>325</v>
       </c>
-      <c r="T146" s="119" t="s">
+      <c r="T146" s="112" t="s">
         <v>55</v>
       </c>
       <c r="U146" s="86">
         <v>0</v>
       </c>
-      <c r="V146" s="121" t="s">
+      <c r="V146" s="114" t="s">
         <v>56</v>
       </c>
       <c r="X146" s="46"/>
@@ -14933,7 +14912,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D147" s="122">
+      <c r="D147" s="115">
         <v>5819</v>
       </c>
       <c r="E147" s="46" t="s">
@@ -14947,7 +14926,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H147" s="122">
+      <c r="H147" s="115">
         <v>9450</v>
       </c>
       <c r="I147" s="55" t="s">
@@ -14961,7 +14940,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L147" s="122">
+      <c r="L147" s="115">
         <v>6690</v>
       </c>
       <c r="M147" s="46"/>
@@ -15005,7 +14984,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D148" s="122">
+      <c r="D148" s="115">
         <v>3689</v>
       </c>
       <c r="E148" s="46" t="s">
@@ -15019,7 +14998,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H148" s="122">
+      <c r="H148" s="115">
         <v>7050</v>
       </c>
       <c r="I148" s="55" t="s">
@@ -15033,7 +15012,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L148" s="122">
+      <c r="L148" s="115">
         <v>4890</v>
       </c>
       <c r="M148" s="46"/>
@@ -15077,7 +15056,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D149" s="122">
+      <c r="D149" s="115">
         <v>4679</v>
       </c>
       <c r="E149" s="46" t="s">
@@ -15091,7 +15070,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H149" s="122">
+      <c r="H149" s="115">
         <v>8350</v>
       </c>
       <c r="I149" s="55" t="s">
@@ -15105,7 +15084,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L149" s="122">
+      <c r="L149" s="115">
         <v>5690</v>
       </c>
       <c r="M149" s="46"/>
@@ -15139,17 +15118,17 @@
       <c r="AE149"/>
     </row>
     <row r="150" spans="1:31" ht="15">
-      <c r="A150" s="111" t="s">
+      <c r="A150" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B150" s="111" t="s">
+      <c r="B150" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C150" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D150" s="122">
+      <c r="D150" s="115">
         <v>4679</v>
       </c>
       <c r="E150" s="46" t="s">
@@ -15163,10 +15142,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H150" s="122">
+      <c r="H150" s="115">
         <v>8350</v>
       </c>
-      <c r="I150" s="113" t="s">
+      <c r="I150" s="55" t="s">
         <v>158</v>
       </c>
       <c r="J150" s="46">
@@ -15177,7 +15156,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L150" s="122">
+      <c r="L150" s="115">
         <v>5690</v>
       </c>
       <c r="M150" s="46"/>
@@ -15193,7 +15172,7 @@
       <c r="S150" s="46">
         <v>325</v>
       </c>
-      <c r="T150" s="118" t="s">
+      <c r="T150" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U150" s="46">
@@ -15211,17 +15190,17 @@
       <c r="AE150"/>
     </row>
     <row r="151" spans="1:31" ht="15">
-      <c r="A151" s="111" t="s">
+      <c r="A151" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B151" s="111" t="s">
+      <c r="B151" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C151" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D151" s="122">
+      <c r="D151" s="115">
         <v>2459</v>
       </c>
       <c r="E151" s="46" t="s">
@@ -15235,10 +15214,10 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H151" s="122">
+      <c r="H151" s="115">
         <v>3990</v>
       </c>
-      <c r="I151" s="113" t="s">
+      <c r="I151" s="55" t="s">
         <v>161</v>
       </c>
       <c r="J151" s="46">
@@ -15249,29 +15228,29 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L151" s="122">
+      <c r="L151" s="115">
         <v>3390</v>
       </c>
       <c r="M151" s="46"/>
       <c r="N151" s="46"/>
       <c r="O151" s="46"/>
-      <c r="P151" s="114"/>
-      <c r="Q151" s="115">
+      <c r="P151" s="108"/>
+      <c r="Q151" s="109">
         <v>1</v>
       </c>
-      <c r="R151" s="116" t="s">
+      <c r="R151" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="S151" s="114">
+      <c r="S151" s="108">
         <v>225</v>
       </c>
-      <c r="T151" s="117" t="s">
+      <c r="T151" s="111" t="s">
         <v>63</v>
       </c>
       <c r="U151" s="21">
         <v>0</v>
       </c>
-      <c r="V151" s="120" t="s">
+      <c r="V151" s="113" t="s">
         <v>56</v>
       </c>
       <c r="Y151" s="16"/>
@@ -15283,61 +15262,55 @@
       <c r="AE151"/>
     </row>
     <row r="152" spans="1:31" ht="15">
-      <c r="A152" s="111" t="s">
-        <v>646</v>
-      </c>
-      <c r="B152" s="111" t="s">
-        <v>647</v>
+      <c r="A152" s="120" t="s">
+        <v>57</v>
+      </c>
+      <c r="B152" s="120" t="s">
+        <v>58</v>
       </c>
       <c r="C152" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
-      </c>
-      <c r="D152" s="122">
-        <v>5939</v>
+        <v>7703</v>
+      </c>
+      <c r="D152" s="115">
+        <v>3689</v>
       </c>
       <c r="E152" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F152" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1376.5</v>
+        <v>326.5</v>
       </c>
       <c r="G152" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H152" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I152" s="77" t="s">
-        <v>161</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H152" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I152" s="122" t="s">
+        <v>45</v>
       </c>
       <c r="J152" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="K152" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L152" s="122">
-        <v>6690</v>
-      </c>
+        <v>3362.5</v>
+      </c>
+      <c r="L152" s="115"/>
       <c r="M152" s="46"/>
       <c r="N152" s="46"/>
-      <c r="O152" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="O152" s="46"/>
       <c r="P152" s="46"/>
       <c r="Q152" s="47">
         <v>1</v>
       </c>
-      <c r="R152" s="47" t="s">
+      <c r="R152" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S152" s="47">
+      <c r="S152" s="46">
         <v>325</v>
       </c>
       <c r="T152" s="49" t="s">
@@ -15359,70 +15332,67 @@
       <c r="AE152"/>
     </row>
     <row r="153" spans="1:31" ht="15">
-      <c r="A153" s="111" t="s">
-        <v>648</v>
-      </c>
-      <c r="B153" s="112" t="s">
-        <v>649</v>
+      <c r="A153" s="120" t="s">
+        <v>57</v>
+      </c>
+      <c r="B153" s="120" t="s">
+        <v>58</v>
       </c>
       <c r="C153" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D153" s="122">
-        <v>3839</v>
+        <v>7703</v>
+      </c>
+      <c r="D153" s="115">
+        <v>3689</v>
       </c>
       <c r="E153" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F153" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>326.5</v>
       </c>
       <c r="G153" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H153" s="122">
+      <c r="H153" s="115">
         <v>7050</v>
       </c>
-      <c r="I153" s="77" t="s">
-        <v>161</v>
+      <c r="I153" s="122" t="s">
+        <v>129</v>
       </c>
       <c r="J153" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="K153" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L153" s="122">
-        <v>4990</v>
+        <v>3362.5</v>
+      </c>
+      <c r="L153" s="115">
+        <v>7050</v>
       </c>
       <c r="M153" s="46"/>
       <c r="N153" s="46"/>
-      <c r="O153" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="O153" s="46"/>
       <c r="P153" s="46"/>
       <c r="Q153" s="47">
         <v>1</v>
       </c>
-      <c r="R153" s="47" t="s">
+      <c r="R153" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S153" s="47">
+      <c r="S153" s="46">
         <v>325</v>
       </c>
-      <c r="T153" s="49" t="s">
+      <c r="T153" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="U153" s="49">
-        <v>0</v>
-      </c>
-      <c r="V153" s="49" t="s">
+      <c r="U153" s="46">
+        <v>0</v>
+      </c>
+      <c r="V153" s="54" t="s">
         <v>56</v>
       </c>
       <c r="W153" s="46"/>
@@ -15445,7 +15415,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6043</v>
       </c>
-      <c r="D154" s="122">
+      <c r="D154" s="115">
         <v>2909</v>
       </c>
       <c r="E154" s="44" t="s">
@@ -15459,7 +15429,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3021.5</v>
       </c>
-      <c r="H154" s="122">
+      <c r="H154" s="115">
         <v>6268</v>
       </c>
       <c r="I154" s="45" t="s">
@@ -15473,7 +15443,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1086.5</v>
       </c>
-      <c r="L154" s="123">
+      <c r="L154" s="116">
         <f>1199*2</f>
         <v>2398</v>
       </c>
@@ -15524,7 +15494,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7463</v>
       </c>
-      <c r="D155" s="122">
+      <c r="D155" s="115">
         <v>3569</v>
       </c>
       <c r="E155" s="44" t="s">
@@ -15538,7 +15508,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3731.5</v>
       </c>
-      <c r="H155" s="122">
+      <c r="H155" s="115">
         <v>7788</v>
       </c>
       <c r="I155" s="45" t="s">
@@ -15552,7 +15522,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1636.5</v>
       </c>
-      <c r="L155" s="123">
+      <c r="L155" s="116">
         <f>1799*2</f>
         <v>3598</v>
       </c>
@@ -15603,7 +15573,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9323</v>
       </c>
-      <c r="D156" s="122">
+      <c r="D156" s="115">
         <v>4499</v>
       </c>
       <c r="E156" s="44" t="s">
@@ -15617,7 +15587,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4661.5</v>
       </c>
-      <c r="H156" s="122">
+      <c r="H156" s="115">
         <v>9648</v>
       </c>
       <c r="I156" s="45" t="s">
@@ -15631,7 +15601,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2086.5</v>
       </c>
-      <c r="L156" s="123">
+      <c r="L156" s="116">
         <f>2249*2</f>
         <v>4498</v>
       </c>
@@ -15682,7 +15652,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11483</v>
       </c>
-      <c r="D157" s="122">
+      <c r="D157" s="115">
         <v>5579</v>
       </c>
       <c r="E157" s="44" t="s">
@@ -15696,7 +15666,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>5741.5</v>
       </c>
-      <c r="H157" s="122">
+      <c r="H157" s="115">
         <v>11808</v>
       </c>
       <c r="I157" s="45" t="s">
@@ -15710,7 +15680,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2336.5</v>
       </c>
-      <c r="L157" s="123">
+      <c r="L157" s="116">
         <f>2499*2</f>
         <v>4998</v>
       </c>
@@ -15761,7 +15731,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D158" s="122">
+      <c r="D158" s="115">
         <v>5939</v>
       </c>
       <c r="E158" s="80" t="s">
@@ -15775,7 +15745,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H158" s="122">
+      <c r="H158" s="115">
         <v>9650</v>
       </c>
       <c r="I158" s="78" t="s">
@@ -15788,7 +15758,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4662.5</v>
       </c>
-      <c r="L158" s="123">
+      <c r="L158" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>9650</v>
       </c>
@@ -15833,7 +15803,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D159" s="122">
+      <c r="D159" s="115">
         <v>5939</v>
       </c>
       <c r="E159" s="80" t="s">
@@ -15847,7 +15817,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H159" s="122">
+      <c r="H159" s="115">
         <v>9650</v>
       </c>
       <c r="I159" s="78" t="s">
@@ -15860,7 +15830,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4162.5</v>
       </c>
-      <c r="L159" s="123">
+      <c r="L159" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8650</v>
       </c>
@@ -15905,7 +15875,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>12203</v>
       </c>
-      <c r="D160" s="122">
+      <c r="D160" s="115">
         <v>5939</v>
       </c>
       <c r="E160" s="80" t="s">
@@ -15919,7 +15889,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4662.5</v>
       </c>
-      <c r="H160" s="122">
+      <c r="H160" s="115">
         <v>9650</v>
       </c>
       <c r="I160" s="78" t="s">
@@ -15932,7 +15902,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3737.5</v>
       </c>
-      <c r="L160" s="123">
+      <c r="L160" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>8650</v>
       </c>
@@ -15977,7 +15947,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>6623</v>
       </c>
-      <c r="D161" s="122">
+      <c r="D161" s="115">
         <v>3149</v>
       </c>
       <c r="E161" s="80" t="s">
@@ -15991,7 +15961,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>2512.5</v>
       </c>
-      <c r="H161" s="122">
+      <c r="H161" s="115">
         <v>5350</v>
       </c>
       <c r="I161" s="78" t="s">
@@ -16004,7 +15974,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2512.5</v>
       </c>
-      <c r="L161" s="123">
+      <c r="L161" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>5350</v>
       </c>
@@ -16049,7 +16019,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D162" s="122">
+      <c r="D162" s="115">
         <v>3839</v>
       </c>
       <c r="E162" s="80" t="s">
@@ -16063,7 +16033,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H162" s="122">
+      <c r="H162" s="115">
         <v>7450</v>
       </c>
       <c r="I162" s="78" t="s">
@@ -16076,7 +16046,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3562.5</v>
       </c>
-      <c r="L162" s="123">
+      <c r="L162" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>7450</v>
       </c>
@@ -16121,7 +16091,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D163" s="122">
+      <c r="D163" s="115">
         <v>3839</v>
       </c>
       <c r="E163" s="80" t="s">
@@ -16135,7 +16105,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H163" s="122">
+      <c r="H163" s="115">
         <v>7450</v>
       </c>
       <c r="I163" s="78" t="s">
@@ -16148,7 +16118,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3062.5</v>
       </c>
-      <c r="L163" s="123">
+      <c r="L163" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6450</v>
       </c>
@@ -16193,7 +16163,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>8003</v>
       </c>
-      <c r="D164" s="122">
+      <c r="D164" s="115">
         <v>3839</v>
       </c>
       <c r="E164" s="80" t="s">
@@ -16207,7 +16177,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3562.5</v>
       </c>
-      <c r="H164" s="122">
+      <c r="H164" s="115">
         <v>7450</v>
       </c>
       <c r="I164" s="78" t="s">
@@ -16220,7 +16190,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2937.5</v>
       </c>
-      <c r="L164" s="123">
+      <c r="L164" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>6450</v>
       </c>
@@ -16265,7 +16235,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D165" s="122">
+      <c r="D165" s="115">
         <v>5039</v>
       </c>
       <c r="E165" s="80" t="s">
@@ -16279,7 +16249,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H165" s="122">
+      <c r="H165" s="115">
         <v>8550</v>
       </c>
       <c r="I165" s="78" t="s">
@@ -16292,7 +16262,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4112.5</v>
       </c>
-      <c r="L165" s="123">
+      <c r="L165" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>8550</v>
       </c>
@@ -16337,7 +16307,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D166" s="122">
+      <c r="D166" s="115">
         <v>5039</v>
       </c>
       <c r="E166" s="80" t="s">
@@ -16351,7 +16321,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H166" s="122">
+      <c r="H166" s="115">
         <v>8550</v>
       </c>
       <c r="I166" s="78" t="s">
@@ -16364,7 +16334,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3612.5</v>
       </c>
-      <c r="L166" s="123">
+      <c r="L166" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7550</v>
       </c>
@@ -16409,7 +16379,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D167" s="122">
+      <c r="D167" s="115">
         <v>5039</v>
       </c>
       <c r="E167" s="86" t="s">
@@ -16423,7 +16393,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4112.5</v>
       </c>
-      <c r="H167" s="122">
+      <c r="H167" s="115">
         <v>8550</v>
       </c>
       <c r="I167" s="101" t="s">
@@ -16436,7 +16406,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3237.5</v>
       </c>
-      <c r="L167" s="123">
+      <c r="L167" s="116">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7550</v>
       </c>
@@ -16472,52 +16442,49 @@
     </row>
     <row r="168" spans="1:30" ht="15">
       <c r="A168" s="79" t="s">
-        <v>650</v>
+        <v>57</v>
       </c>
       <c r="B168" s="92" t="s">
-        <v>651</v>
+        <v>58</v>
       </c>
       <c r="C168" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D168" s="122">
-        <v>5039</v>
+        <v>7703</v>
+      </c>
+      <c r="D168" s="115">
+        <v>3689</v>
       </c>
       <c r="E168" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F168" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>326.5</v>
       </c>
       <c r="G168" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H168" s="122">
-        <v>8350</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H168" s="116">
+        <v>7050</v>
       </c>
       <c r="I168" s="78" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="J168" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>700</v>
       </c>
       <c r="K168" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L168" s="122">
-        <v>5790</v>
+        <v>2662.5</v>
+      </c>
+      <c r="L168" s="116">
+        <v>5650</v>
       </c>
       <c r="M168" s="80"/>
       <c r="N168" s="80"/>
-      <c r="O168" s="80">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="O168" s="80"/>
       <c r="P168" s="80"/>
       <c r="Q168" s="81">
         <v>1</v>
@@ -16525,7 +16492,7 @@
       <c r="R168" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S168" s="81">
+      <c r="S168" s="93">
         <v>325</v>
       </c>
       <c r="T168" s="82" t="s">
@@ -16556,7 +16523,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D169" s="122">
+      <c r="D169" s="115">
         <v>5819</v>
       </c>
       <c r="E169" s="80" t="s">
@@ -16570,7 +16537,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H169" s="122">
+      <c r="H169" s="115">
         <v>9450</v>
       </c>
       <c r="I169" s="84" t="s">
@@ -16584,7 +16551,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L169" s="122">
+      <c r="L169" s="115">
         <v>6690</v>
       </c>
       <c r="M169" s="80"/>
@@ -16628,7 +16595,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D170" s="122">
+      <c r="D170" s="115">
         <v>3689</v>
       </c>
       <c r="E170" s="80" t="s">
@@ -16642,7 +16609,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H170" s="122">
+      <c r="H170" s="115">
         <v>7050</v>
       </c>
       <c r="I170" s="84" t="s">
@@ -16656,7 +16623,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L170" s="122">
+      <c r="L170" s="115">
         <v>4890</v>
       </c>
       <c r="M170" s="80"/>
@@ -16700,7 +16667,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D171" s="122">
+      <c r="D171" s="115">
         <v>2459</v>
       </c>
       <c r="E171" s="80" t="s">
@@ -16714,7 +16681,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H171" s="122">
+      <c r="H171" s="115">
         <v>3990</v>
       </c>
       <c r="I171" s="84" t="s">
@@ -16728,7 +16695,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L171" s="122">
+      <c r="L171" s="115">
         <v>3390</v>
       </c>
       <c r="M171" s="80"/>
@@ -16771,7 +16738,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D172" s="122">
+      <c r="D172" s="115">
         <v>4679</v>
       </c>
       <c r="E172" s="80" t="s">
@@ -16785,7 +16752,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H172" s="122">
+      <c r="H172" s="115">
         <v>8350</v>
       </c>
       <c r="I172" s="84" t="s">
@@ -16799,7 +16766,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L172" s="122">
+      <c r="L172" s="115">
         <v>5690</v>
       </c>
       <c r="M172" s="80"/>
@@ -16843,7 +16810,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D173" s="122">
+      <c r="D173" s="115">
         <v>2459</v>
       </c>
       <c r="E173" s="80" t="s">
@@ -16857,7 +16824,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H173" s="122">
+      <c r="H173" s="115">
         <v>3990</v>
       </c>
       <c r="I173" s="78" t="s">
@@ -16871,7 +16838,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L173" s="123">
+      <c r="L173" s="116">
         <v>3390</v>
       </c>
       <c r="M173" s="80"/>
@@ -16915,7 +16882,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D174" s="122">
+      <c r="D174" s="115">
         <v>2459</v>
       </c>
       <c r="E174" s="80" t="s">
@@ -16929,7 +16896,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H174" s="122">
+      <c r="H174" s="115">
         <v>3990</v>
       </c>
       <c r="I174" s="84" t="s">
@@ -16943,7 +16910,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L174" s="122">
+      <c r="L174" s="115">
         <v>3390</v>
       </c>
       <c r="M174" s="80"/>
@@ -16978,60 +16945,57 @@
     </row>
     <row r="175" spans="1:30" ht="15">
       <c r="A175" s="79" t="s">
-        <v>646</v>
-      </c>
-      <c r="B175" s="99" t="s">
-        <v>647</v>
+        <v>57</v>
+      </c>
+      <c r="B175" s="92" t="s">
+        <v>58</v>
       </c>
       <c r="C175" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
-      </c>
-      <c r="D175" s="122">
-        <v>5939</v>
+        <v>7703</v>
+      </c>
+      <c r="D175" s="115">
+        <v>3689</v>
       </c>
       <c r="E175" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F175" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1376.5</v>
+        <v>326.5</v>
       </c>
       <c r="G175" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H175" s="122">
-        <v>9450</v>
-      </c>
-      <c r="I175" s="78" t="s">
-        <v>162</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H175" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I175" s="84" t="s">
+        <v>141</v>
       </c>
       <c r="J175" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="K175" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L175" s="122">
-        <v>6690</v>
+        <v>3362.5</v>
+      </c>
+      <c r="L175" s="115">
+        <v>7050</v>
       </c>
       <c r="M175" s="80"/>
       <c r="N175" s="80"/>
-      <c r="O175" s="80">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3182.5</v>
-      </c>
+      <c r="O175" s="80"/>
       <c r="P175" s="80"/>
       <c r="Q175" s="81">
         <v>1</v>
       </c>
-      <c r="R175" s="81" t="s">
+      <c r="R175" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="S175" s="81">
+      <c r="S175" s="80">
         <v>325</v>
       </c>
       <c r="T175" s="82" t="s">
@@ -17053,60 +17017,58 @@
     </row>
     <row r="176" spans="1:30" ht="15">
       <c r="A176" s="79" t="s">
-        <v>648</v>
+        <v>57</v>
       </c>
       <c r="B176" s="92" t="s">
-        <v>649</v>
+        <v>58</v>
       </c>
       <c r="C176" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D176" s="122">
-        <v>3839</v>
+        <v>7703</v>
+      </c>
+      <c r="D176" s="115">
+        <v>3689</v>
       </c>
       <c r="E176" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F176" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>326.5</v>
       </c>
       <c r="G176" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H176" s="122">
+      <c r="H176" s="115">
         <v>7050</v>
       </c>
-      <c r="I176" s="78" t="s">
-        <v>162</v>
+      <c r="I176" s="84" t="s">
+        <v>156</v>
       </c>
       <c r="J176" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>500</v>
       </c>
       <c r="K176" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L176" s="122">
-        <v>4990</v>
+        <v>2862.5</v>
+      </c>
+      <c r="L176" s="115">
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>6050</v>
       </c>
       <c r="M176" s="80"/>
       <c r="N176" s="80"/>
-      <c r="O176" s="80">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2332.5</v>
-      </c>
+      <c r="O176" s="80"/>
       <c r="P176" s="80"/>
       <c r="Q176" s="81">
         <v>1</v>
       </c>
-      <c r="R176" s="81" t="s">
+      <c r="R176" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="S176" s="81">
+      <c r="S176" s="80">
         <v>325</v>
       </c>
       <c r="T176" s="82" t="s">
@@ -17128,69 +17090,66 @@
     </row>
     <row r="177" spans="1:30" ht="15">
       <c r="A177" s="79" t="s">
-        <v>650</v>
-      </c>
-      <c r="B177" s="99" t="s">
-        <v>651</v>
+        <v>57</v>
+      </c>
+      <c r="B177" s="92" t="s">
+        <v>58</v>
       </c>
       <c r="C177" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
-      </c>
-      <c r="D177" s="122">
-        <v>5039</v>
+        <v>7703</v>
+      </c>
+      <c r="D177" s="115">
+        <v>3689</v>
       </c>
       <c r="E177" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F177" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>326.5</v>
       </c>
       <c r="G177" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4012.5</v>
-      </c>
-      <c r="H177" s="122">
-        <v>8350</v>
-      </c>
-      <c r="I177" s="78" t="s">
-        <v>162</v>
+        <v>3362.5</v>
+      </c>
+      <c r="H177" s="115">
+        <v>7050</v>
+      </c>
+      <c r="I177" s="84" t="s">
+        <v>159</v>
       </c>
       <c r="J177" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>625</v>
       </c>
       <c r="K177" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L177" s="122">
-        <v>5790</v>
-      </c>
-      <c r="M177" s="80"/>
+        <v>2737.5</v>
+      </c>
+      <c r="L177" s="115">
+        <v>5800</v>
+      </c>
+      <c r="M177" s="84"/>
       <c r="N177" s="80"/>
-      <c r="O177" s="80">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="O177" s="97"/>
       <c r="P177" s="80"/>
       <c r="Q177" s="81">
         <v>1</v>
       </c>
-      <c r="R177" s="81" t="s">
+      <c r="R177" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="S177" s="81">
+      <c r="S177" s="80">
         <v>325</v>
       </c>
-      <c r="T177" s="82" t="s">
+      <c r="T177" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="U177" s="82">
-        <v>0</v>
-      </c>
-      <c r="V177" s="83" t="s">
+      <c r="U177" s="20">
+        <v>0</v>
+      </c>
+      <c r="V177" s="95" t="s">
         <v>56</v>
       </c>
       <c r="X177" s="44"/>
@@ -17212,7 +17171,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D178" s="122">
+      <c r="D178" s="115">
         <v>5819</v>
       </c>
       <c r="E178" s="80" t="s">
@@ -17226,7 +17185,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H178" s="123">
+      <c r="H178" s="116">
         <v>9450</v>
       </c>
       <c r="I178" s="78" t="s">
@@ -17240,7 +17199,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L178" s="123">
+      <c r="L178" s="116">
         <v>6690</v>
       </c>
       <c r="M178" s="80"/>
@@ -17275,54 +17234,63 @@
     </row>
     <row r="179" spans="1:30" ht="15">
       <c r="A179" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B179" s="92" t="s">
-        <v>58</v>
+        <v>646</v>
+      </c>
+      <c r="B179" s="99" t="s">
+        <v>647</v>
       </c>
       <c r="C179" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D179" s="122">
-        <v>3689</v>
+        <v>10403</v>
+      </c>
+      <c r="D179" s="115">
+        <v>5039</v>
       </c>
       <c r="E179" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F179" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G179" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H179" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I179" s="84" t="s">
-        <v>45</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H179" s="115">
+        <v>8350</v>
+      </c>
+      <c r="I179" s="78" t="s">
+        <v>122</v>
       </c>
       <c r="J179" s="46">
-        <v>0</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
       </c>
       <c r="K179" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="L179" s="122"/>
+        <v>2732.5</v>
+      </c>
+      <c r="L179" s="115">
+        <v>5790</v>
+      </c>
       <c r="M179" s="80"/>
-      <c r="N179" s="80"/>
-      <c r="O179" s="80"/>
+      <c r="N179" s="80">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O179" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P179" s="80"/>
       <c r="Q179" s="81">
         <v>1</v>
       </c>
-      <c r="R179" s="80" t="s">
+      <c r="R179" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S179" s="80">
+      <c r="S179" s="81">
         <v>325</v>
       </c>
       <c r="T179" s="82" t="s">
@@ -17344,66 +17312,72 @@
     </row>
     <row r="180" spans="1:30" ht="15">
       <c r="A180" s="79" t="s">
-        <v>57</v>
+        <v>646</v>
       </c>
       <c r="B180" s="92" t="s">
-        <v>58</v>
+        <v>647</v>
       </c>
       <c r="C180" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D180" s="122">
-        <v>3689</v>
+        <v>10403</v>
+      </c>
+      <c r="D180" s="115">
+        <v>5039</v>
       </c>
       <c r="E180" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F180" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G180" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H180" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I180" s="84" t="s">
-        <v>129</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H180" s="115">
+        <v>8350</v>
+      </c>
+      <c r="I180" s="78" t="s">
+        <v>152</v>
       </c>
       <c r="J180" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="K180" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="L180" s="122">
-        <v>7050</v>
+        <v>2732.5</v>
+      </c>
+      <c r="L180" s="115">
+        <v>5790</v>
       </c>
       <c r="M180" s="80"/>
-      <c r="N180" s="80"/>
-      <c r="O180" s="80"/>
+      <c r="N180" s="80">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O180" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P180" s="80"/>
       <c r="Q180" s="81">
         <v>1</v>
       </c>
-      <c r="R180" s="80" t="s">
+      <c r="R180" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S180" s="80">
+      <c r="S180" s="81">
         <v>325</v>
       </c>
-      <c r="T180" s="41" t="s">
+      <c r="T180" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="U180" s="80">
-        <v>0</v>
-      </c>
-      <c r="V180" s="53" t="s">
+      <c r="U180" s="82">
+        <v>0</v>
+      </c>
+      <c r="V180" s="83" t="s">
         <v>56</v>
       </c>
       <c r="X180" s="44"/>
@@ -17416,49 +17390,55 @@
     </row>
     <row r="181" spans="1:30" ht="15">
       <c r="A181" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B181" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B181" s="99" t="s">
+        <v>60</v>
       </c>
       <c r="C181" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D181" s="122">
-        <v>3689</v>
+        <v>10403</v>
+      </c>
+      <c r="D181" s="115">
+        <v>5039</v>
       </c>
       <c r="E181" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F181" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G181" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H181" s="123">
-        <v>7050</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H181" s="115">
+        <v>8350</v>
       </c>
       <c r="I181" s="78" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="J181" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>700</v>
+        <v>1280</v>
       </c>
       <c r="K181" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2662.5</v>
-      </c>
-      <c r="L181" s="123">
-        <v>5650</v>
+        <v>2732.5</v>
+      </c>
+      <c r="L181" s="115">
+        <v>5790</v>
       </c>
       <c r="M181" s="80"/>
-      <c r="N181" s="80"/>
-      <c r="O181" s="80"/>
+      <c r="N181" s="80">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O181" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P181" s="80"/>
       <c r="Q181" s="81">
         <v>1</v>
@@ -17466,7 +17446,7 @@
       <c r="R181" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S181" s="93">
+      <c r="S181" s="81">
         <v>325</v>
       </c>
       <c r="T181" s="82" t="s">
@@ -17488,57 +17468,63 @@
     </row>
     <row r="182" spans="1:30" ht="15">
       <c r="A182" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B182" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B182" s="99" t="s">
+        <v>60</v>
       </c>
       <c r="C182" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D182" s="122">
-        <v>3689</v>
+        <v>10403</v>
+      </c>
+      <c r="D182" s="115">
+        <v>5039</v>
       </c>
       <c r="E182" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F182" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G182" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H182" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I182" s="84" t="s">
-        <v>141</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H182" s="115">
+        <v>8350</v>
+      </c>
+      <c r="I182" s="78" t="s">
+        <v>154</v>
       </c>
       <c r="J182" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="K182" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="L182" s="122">
-        <v>7050</v>
+        <v>2732.5</v>
+      </c>
+      <c r="L182" s="115">
+        <v>5790</v>
       </c>
       <c r="M182" s="80"/>
-      <c r="N182" s="80"/>
-      <c r="O182" s="80"/>
+      <c r="N182" s="80">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
+      <c r="O182" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>0</v>
+      </c>
       <c r="P182" s="80"/>
       <c r="Q182" s="81">
         <v>1</v>
       </c>
-      <c r="R182" s="80" t="s">
+      <c r="R182" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S182" s="80">
+      <c r="S182" s="81">
         <v>325</v>
       </c>
       <c r="T182" s="82" t="s">
@@ -17560,58 +17546,60 @@
     </row>
     <row r="183" spans="1:30" ht="15">
       <c r="A183" s="79" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B183" s="92" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C183" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D183" s="122">
-        <v>3689</v>
+        <v>10403</v>
+      </c>
+      <c r="D183" s="115">
+        <v>5039</v>
       </c>
       <c r="E183" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F183" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G183" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H183" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I183" s="84" t="s">
-        <v>156</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H183" s="115">
+        <v>8350</v>
+      </c>
+      <c r="I183" s="78" t="s">
+        <v>157</v>
       </c>
       <c r="J183" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>500</v>
+        <v>1280</v>
       </c>
       <c r="K183" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2862.5</v>
-      </c>
-      <c r="L183" s="122">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>6050</v>
+        <v>2732.5</v>
+      </c>
+      <c r="L183" s="115">
+        <v>5790</v>
       </c>
       <c r="M183" s="80"/>
       <c r="N183" s="80"/>
-      <c r="O183" s="80"/>
+      <c r="O183" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P183" s="80"/>
       <c r="Q183" s="81">
         <v>1</v>
       </c>
-      <c r="R183" s="80" t="s">
+      <c r="R183" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S183" s="80">
+      <c r="S183" s="81">
         <v>325</v>
       </c>
       <c r="T183" s="82" t="s">
@@ -17633,66 +17621,69 @@
     </row>
     <row r="184" spans="1:30" ht="15">
       <c r="A184" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B184" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B184" s="99" t="s">
+        <v>60</v>
       </c>
       <c r="C184" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>7703</v>
-      </c>
-      <c r="D184" s="122">
-        <v>3689</v>
+        <v>10403</v>
+      </c>
+      <c r="D184" s="115">
+        <v>5039</v>
       </c>
       <c r="E184" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F184" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>326.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G184" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H184" s="122">
-        <v>7050</v>
-      </c>
-      <c r="I184" s="84" t="s">
-        <v>159</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H184" s="115">
+        <v>8350</v>
+      </c>
+      <c r="I184" s="78" t="s">
+        <v>158</v>
       </c>
       <c r="J184" s="46">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>625</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
       </c>
       <c r="K184" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2737.5</v>
-      </c>
-      <c r="L184" s="122">
-        <v>5800</v>
-      </c>
-      <c r="M184" s="84"/>
+        <v>2732.5</v>
+      </c>
+      <c r="L184" s="115">
+        <v>5790</v>
+      </c>
+      <c r="M184" s="80"/>
       <c r="N184" s="80"/>
-      <c r="O184" s="97"/>
+      <c r="O184" s="80">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P184" s="80"/>
       <c r="Q184" s="81">
         <v>1</v>
       </c>
-      <c r="R184" s="80" t="s">
+      <c r="R184" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="S184" s="80">
+      <c r="S184" s="81">
         <v>325</v>
       </c>
-      <c r="T184" s="96" t="s">
+      <c r="T184" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="U184" s="20">
-        <v>0</v>
-      </c>
-      <c r="V184" s="95" t="s">
+      <c r="U184" s="82">
+        <v>0</v>
+      </c>
+      <c r="V184" s="83" t="s">
         <v>56</v>
       </c>
       <c r="X184" s="44"/>
@@ -17714,7 +17705,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D185" s="122">
+      <c r="D185" s="115">
         <v>3689</v>
       </c>
       <c r="E185" s="80" t="s">
@@ -17728,7 +17719,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H185" s="123">
+      <c r="H185" s="116">
         <v>7050</v>
       </c>
       <c r="I185" s="78" t="s">
@@ -17742,7 +17733,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L185" s="123">
+      <c r="L185" s="116">
         <v>4890</v>
       </c>
       <c r="M185" s="80"/>
@@ -17786,7 +17777,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D186" s="122">
+      <c r="D186" s="115">
         <v>4679</v>
       </c>
       <c r="E186" s="80" t="s">
@@ -17800,7 +17791,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H186" s="123">
+      <c r="H186" s="116">
         <v>8350</v>
       </c>
       <c r="I186" s="78" t="s">
@@ -17814,7 +17805,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L186" s="123">
+      <c r="L186" s="116">
         <v>5690</v>
       </c>
       <c r="M186" s="80"/>
@@ -17858,7 +17849,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>5143</v>
       </c>
-      <c r="D187" s="122">
+      <c r="D187" s="115">
         <v>2459</v>
       </c>
       <c r="E187" s="80" t="s">
@@ -17872,7 +17863,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>1882.5</v>
       </c>
-      <c r="H187" s="122">
+      <c r="H187" s="115">
         <v>3990</v>
       </c>
       <c r="I187" s="84" t="s">
@@ -17886,7 +17877,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>1582.5</v>
       </c>
-      <c r="L187" s="122">
+      <c r="L187" s="115">
         <v>3390</v>
       </c>
       <c r="M187" s="80"/>
@@ -17921,51 +17912,51 @@
     </row>
     <row r="188" spans="1:30" ht="15">
       <c r="A188" s="79" t="s">
-        <v>646</v>
+        <v>59</v>
       </c>
       <c r="B188" s="92" t="s">
-        <v>647</v>
+        <v>60</v>
       </c>
       <c r="C188" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>12203</v>
-      </c>
-      <c r="D188" s="122">
-        <v>5939</v>
+        <v>10403</v>
+      </c>
+      <c r="D188" s="115">
+        <v>5039</v>
       </c>
       <c r="E188" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F188" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1376.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G188" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>4562.5</v>
-      </c>
-      <c r="H188" s="122">
-        <v>9450</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H188" s="115">
+        <v>8350</v>
       </c>
       <c r="I188" s="78" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J188" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1380</v>
+        <v>1280</v>
       </c>
       <c r="K188" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3182.5</v>
-      </c>
-      <c r="L188" s="122">
-        <v>6690</v>
+        <v>2732.5</v>
+      </c>
+      <c r="L188" s="115">
+        <v>5790</v>
       </c>
       <c r="M188" s="80"/>
       <c r="N188" s="80"/>
       <c r="O188" s="80">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>3182.5</v>
+        <v>2732.5</v>
       </c>
       <c r="P188" s="80"/>
       <c r="Q188" s="81">
@@ -17996,51 +17987,51 @@
     </row>
     <row r="189" spans="1:30" ht="15">
       <c r="A189" s="79" t="s">
-        <v>648</v>
+        <v>59</v>
       </c>
       <c r="B189" s="99" t="s">
-        <v>649</v>
+        <v>60</v>
       </c>
       <c r="C189" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>8003</v>
-      </c>
-      <c r="D189" s="122">
-        <v>3839</v>
+        <v>10403</v>
+      </c>
+      <c r="D189" s="115">
+        <v>5039</v>
       </c>
       <c r="E189" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F189" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>476.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G189" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
-        <v>3362.5</v>
-      </c>
-      <c r="H189" s="122">
-        <v>7050</v>
+        <v>4012.5</v>
+      </c>
+      <c r="H189" s="115">
+        <v>8350</v>
       </c>
       <c r="I189" s="78" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J189" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1030</v>
+        <v>1280</v>
       </c>
       <c r="K189" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2332.5</v>
-      </c>
-      <c r="L189" s="122">
-        <v>4990</v>
+        <v>2732.5</v>
+      </c>
+      <c r="L189" s="115">
+        <v>5790</v>
       </c>
       <c r="M189" s="80"/>
       <c r="N189" s="80"/>
       <c r="O189" s="80">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2332.5</v>
+        <v>2732.5</v>
       </c>
       <c r="P189" s="80"/>
       <c r="Q189" s="81">
@@ -18071,16 +18062,16 @@
     </row>
     <row r="190" spans="1:30" ht="15">
       <c r="A190" s="79" t="s">
-        <v>650</v>
+        <v>59</v>
       </c>
       <c r="B190" s="92" t="s">
-        <v>651</v>
+        <v>60</v>
       </c>
       <c r="C190" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>10403</v>
       </c>
-      <c r="D190" s="122">
+      <c r="D190" s="115">
         <v>5039</v>
       </c>
       <c r="E190" s="80" t="s">
@@ -18094,7 +18085,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H190" s="122">
+      <c r="H190" s="115">
         <v>8350</v>
       </c>
       <c r="I190" s="78" t="s">
@@ -18108,7 +18099,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2732.5</v>
       </c>
-      <c r="L190" s="122">
+      <c r="L190" s="115">
         <v>5790</v>
       </c>
       <c r="M190" s="80"/>
@@ -18155,7 +18146,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>11963</v>
       </c>
-      <c r="D191" s="122">
+      <c r="D191" s="115">
         <v>5819</v>
       </c>
       <c r="E191" s="80" t="s">
@@ -18169,7 +18160,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4562.5</v>
       </c>
-      <c r="H191" s="122">
+      <c r="H191" s="115">
         <v>9450</v>
       </c>
       <c r="I191" s="84" t="s">
@@ -18183,7 +18174,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3182.5</v>
       </c>
-      <c r="L191" s="122">
+      <c r="L191" s="115">
         <v>6690</v>
       </c>
       <c r="M191" s="80"/>
@@ -18227,7 +18218,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>7703</v>
       </c>
-      <c r="D192" s="122">
+      <c r="D192" s="115">
         <v>3689</v>
       </c>
       <c r="E192" s="80" t="s">
@@ -18241,7 +18232,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>3362.5</v>
       </c>
-      <c r="H192" s="122">
+      <c r="H192" s="115">
         <v>7050</v>
       </c>
       <c r="I192" s="84" t="s">
@@ -18255,7 +18246,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2282.5</v>
       </c>
-      <c r="L192" s="122">
+      <c r="L192" s="115">
         <v>4890</v>
       </c>
       <c r="M192" s="80"/>
@@ -18299,7 +18290,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D193" s="122">
+      <c r="D193" s="115">
         <v>4679</v>
       </c>
       <c r="E193" s="80" t="s">
@@ -18313,7 +18304,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>-162.5</v>
       </c>
-      <c r="H193" s="122"/>
+      <c r="H193" s="115"/>
       <c r="I193" s="84" t="s">
         <v>164</v>
       </c>
@@ -18325,7 +18316,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>2682.5</v>
       </c>
-      <c r="L193" s="122">
+      <c r="L193" s="115">
         <v>5690</v>
       </c>
       <c r="M193" s="80"/>
@@ -18369,7 +18360,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D194" s="122">
+      <c r="D194" s="115">
         <v>4679</v>
       </c>
       <c r="E194" s="80" t="s">
@@ -18383,7 +18374,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H194" s="122">
+      <c r="H194" s="115">
         <v>8350</v>
       </c>
       <c r="I194" s="84" t="s">
@@ -18396,7 +18387,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4012.5</v>
       </c>
-      <c r="L194" s="122">
+      <c r="L194" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
         <v>8350</v>
       </c>
@@ -18441,7 +18432,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D195" s="122">
+      <c r="D195" s="115">
         <v>4679</v>
       </c>
       <c r="E195" s="80" t="s">
@@ -18455,7 +18446,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H195" s="122">
+      <c r="H195" s="115">
         <v>8350</v>
       </c>
       <c r="I195" s="84" t="s">
@@ -18469,7 +18460,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4012.5</v>
       </c>
-      <c r="L195" s="122">
+      <c r="L195" s="115">
         <v>8350</v>
       </c>
       <c r="M195" s="80"/>
@@ -18513,7 +18504,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D196" s="122">
+      <c r="D196" s="115">
         <v>4679</v>
       </c>
       <c r="E196" s="80" t="s">
@@ -18527,7 +18518,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H196" s="122">
+      <c r="H196" s="115">
         <v>8350</v>
       </c>
       <c r="I196" s="78" t="s">
@@ -18541,7 +18532,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3312.5</v>
       </c>
-      <c r="L196" s="123">
+      <c r="L196" s="116">
         <v>6950</v>
       </c>
       <c r="M196" s="80"/>
@@ -18585,7 +18576,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D197" s="122">
+      <c r="D197" s="115">
         <v>4679</v>
       </c>
       <c r="E197" s="80" t="s">
@@ -18599,7 +18590,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H197" s="122">
+      <c r="H197" s="115">
         <v>8350</v>
       </c>
       <c r="I197" s="84" t="s">
@@ -18613,7 +18604,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>4012.5</v>
       </c>
-      <c r="L197" s="122">
+      <c r="L197" s="115">
         <v>8350</v>
       </c>
       <c r="M197" s="80"/>
@@ -18657,7 +18648,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D198" s="122">
+      <c r="D198" s="115">
         <v>4679</v>
       </c>
       <c r="E198" s="80" t="s">
@@ -18671,7 +18662,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H198" s="122">
+      <c r="H198" s="115">
         <v>8350</v>
       </c>
       <c r="I198" s="84" t="s">
@@ -18685,7 +18676,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3512.5</v>
       </c>
-      <c r="L198" s="122">
+      <c r="L198" s="115">
         <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
         <v>7350</v>
       </c>
@@ -18730,7 +18721,7 @@
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
         <v>9683</v>
       </c>
-      <c r="D199" s="122">
+      <c r="D199" s="115">
         <v>4679</v>
       </c>
       <c r="E199" s="86" t="s">
@@ -18744,7 +18735,7 @@
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
         <v>4012.5</v>
       </c>
-      <c r="H199" s="122">
+      <c r="H199" s="115">
         <v>8350</v>
       </c>
       <c r="I199" s="87" t="s">
@@ -18758,7 +18749,7 @@
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
         <v>3137.5</v>
       </c>
-      <c r="L199" s="122">
+      <c r="L199" s="115">
         <v>6600</v>
       </c>
       <c r="M199" s="87"/>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1522" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54DA9564-2953-4037-A841-07C2214A7AA8}"/>
+  <xr:revisionPtr revIDLastSave="1529" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F597968-A36B-4021-8664-46EE7F249227}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="3765" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
+    <workbookView xWindow="4185" yWindow="3690" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Price Calculator" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="647">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -2002,9 +2002,6 @@
   </si>
   <si>
     <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone RIE Digital Envision 9 62SDRWC</t>
   </si>
   <si>
     <t>Beltone Envision 9 62SDRWC Digital RIE</t>
@@ -2368,7 +2365,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2560,6 +2557,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2571,16 +2569,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3348,7 +3336,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Beltone RIE Digital Envision 9 62S-DRWC"/>
+        <filter val="Beltone RIE Digital Envision 9 62-SDRWC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V199">
     <sortCondition ref="B1:B199"/>
   </sortState>
@@ -3801,10 +3796,10 @@
       <c r="A3" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
       <c r="F3" s="42"/>
@@ -3825,10 +3820,10 @@
       <c r="A5" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="110">
         <v>2</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="111"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
       <c r="F5" s="42"/>
@@ -3849,10 +3844,10 @@
       <c r="A7" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="109" t="s">
+      <c r="B7" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="110"/>
+      <c r="C7" s="111"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42"/>
       <c r="F7" s="42"/>
@@ -4211,9 +4206,9 @@
       <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
-      <c r="A30" s="108"/>
-      <c r="B30" s="108"/>
-      <c r="C30" s="108"/>
+      <c r="A30" s="109"/>
+      <c r="B30" s="109"/>
+      <c r="C30" s="109"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
       <c r="F30" s="26"/>
@@ -4450,7 +4445,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15">
+    <row r="2" spans="1:31" ht="15" hidden="1">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4520,7 +4515,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15">
+    <row r="3" spans="1:31" ht="15" hidden="1">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4589,7 +4584,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15">
+    <row r="4" spans="1:31" ht="15" hidden="1">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4661,7 +4656,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15">
+    <row r="5" spans="1:31" ht="15" hidden="1">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4733,7 +4728,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15">
+    <row r="6" spans="1:31" ht="15" hidden="1">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4800,7 +4795,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15">
+    <row r="7" spans="1:31" ht="15" hidden="1">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4864,7 +4859,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15">
+    <row r="8" spans="1:31" ht="15" hidden="1">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4933,7 +4928,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15">
+    <row r="9" spans="1:31" ht="15" hidden="1">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -5005,7 +5000,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15">
+    <row r="10" spans="1:31" ht="15" hidden="1">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5077,7 +5072,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15">
+    <row r="11" spans="1:31" ht="15" hidden="1">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5146,7 +5141,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15">
+    <row r="12" spans="1:31" ht="15" hidden="1">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5215,7 +5210,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15">
+    <row r="13" spans="1:31" ht="15" hidden="1">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5284,7 +5279,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15">
+    <row r="14" spans="1:31" ht="15" hidden="1">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5356,7 +5351,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15">
+    <row r="15" spans="1:31" ht="15" hidden="1">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -5429,7 +5424,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15">
+    <row r="16" spans="1:31" ht="15" hidden="1">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5502,7 +5497,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15">
+    <row r="17" spans="1:31" ht="15" hidden="1">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5575,7 +5570,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15">
+    <row r="18" spans="1:31" ht="15" hidden="1">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5647,7 +5642,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15">
+    <row r="19" spans="1:31" ht="15" hidden="1">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5720,7 +5715,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15">
+    <row r="20" spans="1:31" ht="15" hidden="1">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5792,7 +5787,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15">
+    <row r="21" spans="1:31" ht="15" hidden="1">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5865,7 +5860,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15">
+    <row r="22" spans="1:31" ht="15" hidden="1">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5937,7 +5932,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15">
+    <row r="23" spans="1:31" ht="15" hidden="1">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -6009,7 +6004,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15">
+    <row r="24" spans="1:31" ht="15" hidden="1">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6081,7 +6076,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15">
+    <row r="25" spans="1:31" ht="15" hidden="1">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6155,7 +6150,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15">
+    <row r="26" spans="1:31" ht="15" hidden="1">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6228,7 +6223,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15">
+    <row r="27" spans="1:31" ht="15" hidden="1">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6302,7 +6297,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15">
+    <row r="28" spans="1:31" ht="15" hidden="1">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6365,7 +6360,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15">
+    <row r="29" spans="1:31" ht="15" hidden="1">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -6437,7 +6432,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15">
+    <row r="30" spans="1:31" ht="15" hidden="1">
       <c r="A30" s="42" t="s">
         <v>47</v>
       </c>
@@ -6509,7 +6504,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15">
+    <row r="31" spans="1:31" ht="15" hidden="1">
       <c r="A31" s="42" t="s">
         <v>47</v>
       </c>
@@ -6580,7 +6575,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15">
+    <row r="32" spans="1:31" ht="15" hidden="1">
       <c r="A32" s="42" t="s">
         <v>47</v>
       </c>
@@ -6652,7 +6647,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="15">
+    <row r="33" spans="1:31" ht="15" hidden="1">
       <c r="A33" s="42" t="s">
         <v>47</v>
       </c>
@@ -6724,7 +6719,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="15">
+    <row r="34" spans="1:31" ht="15" hidden="1">
       <c r="A34" s="42" t="s">
         <v>47</v>
       </c>
@@ -6796,7 +6791,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="15">
+    <row r="35" spans="1:31" ht="15" hidden="1">
       <c r="A35" s="42" t="s">
         <v>47</v>
       </c>
@@ -6868,7 +6863,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="15">
+    <row r="36" spans="1:31" ht="15" hidden="1">
       <c r="A36" s="42" t="s">
         <v>47</v>
       </c>
@@ -6941,8 +6936,8 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="15">
-      <c r="A37" s="111" t="s">
+    <row r="37" spans="1:31" ht="15" hidden="1">
+      <c r="A37" s="42" t="s">
         <v>47</v>
       </c>
       <c r="B37" s="42" t="s">
@@ -6969,7 +6964,7 @@
       <c r="H37" s="105">
         <v>3990</v>
       </c>
-      <c r="I37" s="113" t="s">
+      <c r="I37" s="55" t="s">
         <v>158</v>
       </c>
       <c r="J37" s="46">
@@ -7013,7 +7008,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="15">
+    <row r="38" spans="1:31" ht="15" hidden="1">
       <c r="A38" s="42" t="s">
         <v>47</v>
       </c>
@@ -7085,11 +7080,11 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="15">
-      <c r="A39" s="111" t="s">
+    <row r="39" spans="1:31" ht="15" hidden="1">
+      <c r="A39" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="111" t="s">
+      <c r="B39" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C39" s="43">
@@ -7113,7 +7108,7 @@
       <c r="H39" s="105">
         <v>3990</v>
       </c>
-      <c r="I39" s="113" t="s">
+      <c r="I39" s="55" t="s">
         <v>160</v>
       </c>
       <c r="J39" s="46">
@@ -7157,11 +7152,11 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="15">
-      <c r="A40" s="111" t="s">
+    <row r="40" spans="1:31" ht="15" hidden="1">
+      <c r="A40" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="111" t="s">
+      <c r="B40" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C40" s="43">
@@ -7229,11 +7224,11 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="15">
-      <c r="A41" s="111" t="s">
+    <row r="41" spans="1:31" ht="15" hidden="1">
+      <c r="A41" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="111" t="s">
+      <c r="B41" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C41" s="43">
@@ -7257,7 +7252,7 @@
       <c r="H41" s="105">
         <v>3990</v>
       </c>
-      <c r="I41" s="113" t="s">
+      <c r="I41" s="55" t="s">
         <v>163</v>
       </c>
       <c r="J41" s="46">
@@ -7301,11 +7296,11 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="15">
-      <c r="A42" s="111" t="s">
+    <row r="42" spans="1:31" ht="15" hidden="1">
+      <c r="A42" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="111" t="s">
+      <c r="B42" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C42" s="43">
@@ -7329,7 +7324,7 @@
       <c r="H42" s="105">
         <v>3990</v>
       </c>
-      <c r="I42" s="113" t="s">
+      <c r="I42" s="55" t="s">
         <v>164</v>
       </c>
       <c r="J42" s="46">
@@ -7373,7 +7368,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15">
+    <row r="43" spans="1:31" ht="15" hidden="1">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7451,7 +7446,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15">
+    <row r="44" spans="1:31" ht="15" hidden="1">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7529,7 +7524,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15">
+    <row r="45" spans="1:31" ht="15" hidden="1">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7607,7 +7602,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15">
+    <row r="46" spans="1:31" ht="15" hidden="1">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7685,7 +7680,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15">
+    <row r="47" spans="1:31" ht="15" hidden="1">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7760,7 +7755,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15">
+    <row r="48" spans="1:31" ht="15" hidden="1">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7835,7 +7830,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15">
+    <row r="49" spans="1:32" ht="15" hidden="1">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7911,7 +7906,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15">
+    <row r="50" spans="1:32" ht="15" hidden="1">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7987,7 +7982,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15">
+    <row r="51" spans="1:32" ht="15" hidden="1">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8063,7 +8058,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15">
+    <row r="52" spans="1:32" ht="15" hidden="1">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8133,7 +8128,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15">
+    <row r="53" spans="1:32" ht="15" hidden="1">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8206,7 +8201,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15">
+    <row r="54" spans="1:32" ht="15" hidden="1">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8279,7 +8274,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15">
+    <row r="55" spans="1:32" ht="15" hidden="1">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8352,7 +8347,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15">
+    <row r="56" spans="1:32" ht="15" hidden="1">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8426,7 +8421,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15">
+    <row r="57" spans="1:32" ht="15" hidden="1">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8499,7 +8494,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15">
+    <row r="58" spans="1:32" ht="15" hidden="1">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8571,7 +8566,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15">
+    <row r="59" spans="1:32" ht="15" hidden="1">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8643,7 +8638,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15">
+    <row r="60" spans="1:32" ht="15" hidden="1">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8721,7 +8716,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15">
+    <row r="61" spans="1:32" ht="15" hidden="1">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8800,7 +8795,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15">
+    <row r="62" spans="1:32" ht="15" hidden="1">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8879,8 +8874,8 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15">
-      <c r="A63" s="111" t="s">
+    <row r="63" spans="1:32" ht="15" hidden="1">
+      <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B63" s="42" t="s">
@@ -8958,8 +8953,8 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15">
-      <c r="A64" s="111" t="s">
+    <row r="64" spans="1:32" ht="15" hidden="1">
+      <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B64" s="95" t="s">
@@ -9034,8 +9029,8 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15">
-      <c r="A65" s="111" t="s">
+    <row r="65" spans="1:31" ht="15" hidden="1">
+      <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B65" s="42" t="s">
@@ -9110,8 +9105,8 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15">
-      <c r="A66" s="111" t="s">
+    <row r="66" spans="1:31" ht="15" hidden="1">
+      <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B66" s="95" t="s">
@@ -9186,8 +9181,8 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15">
-      <c r="A67" s="111" t="s">
+    <row r="67" spans="1:31" ht="15" hidden="1">
+      <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B67" s="42" t="s">
@@ -9262,8 +9257,8 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15">
-      <c r="A68" s="111" t="s">
+    <row r="68" spans="1:31" ht="15" hidden="1">
+      <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B68" s="95" t="s">
@@ -9338,7 +9333,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15">
+    <row r="69" spans="1:31" ht="15" hidden="1">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9408,7 +9403,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15">
+    <row r="70" spans="1:31" ht="15" hidden="1">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9481,11 +9476,11 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15">
-      <c r="A71" s="111" t="s">
+    <row r="71" spans="1:31" ht="15" hidden="1">
+      <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B71" s="111" t="s">
+      <c r="B71" s="42" t="s">
         <v>58</v>
       </c>
       <c r="C71" s="43">
@@ -9554,11 +9549,11 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15">
-      <c r="A72" s="111" t="s">
+    <row r="72" spans="1:31" ht="15" hidden="1">
+      <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B72" s="111" t="s">
+      <c r="B72" s="42" t="s">
         <v>58</v>
       </c>
       <c r="C72" s="43">
@@ -9582,7 +9577,7 @@
       <c r="H72" s="105">
         <v>7050</v>
       </c>
-      <c r="I72" s="113" t="s">
+      <c r="I72" s="55" t="s">
         <v>141</v>
       </c>
       <c r="J72" s="46">
@@ -9627,11 +9622,11 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15">
-      <c r="A73" s="111" t="s">
+    <row r="73" spans="1:31" ht="15" hidden="1">
+      <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B73" s="111" t="s">
+      <c r="B73" s="42" t="s">
         <v>58</v>
       </c>
       <c r="C73" s="43">
@@ -9655,7 +9650,7 @@
       <c r="H73" s="105">
         <v>7050</v>
       </c>
-      <c r="I73" s="113" t="s">
+      <c r="I73" s="55" t="s">
         <v>156</v>
       </c>
       <c r="J73" s="46">
@@ -9701,11 +9696,11 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15">
-      <c r="A74" s="111" t="s">
+    <row r="74" spans="1:31" ht="15" hidden="1">
+      <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B74" s="111" t="s">
+      <c r="B74" s="42" t="s">
         <v>58</v>
       </c>
       <c r="C74" s="43">
@@ -9729,7 +9724,7 @@
       <c r="H74" s="105">
         <v>7050</v>
       </c>
-      <c r="I74" s="113" t="s">
+      <c r="I74" s="55" t="s">
         <v>159</v>
       </c>
       <c r="J74" s="46">
@@ -9743,9 +9738,9 @@
       <c r="L74" s="105">
         <v>5800</v>
       </c>
-      <c r="M74" s="113"/>
+      <c r="M74" s="55"/>
       <c r="N74" s="46"/>
-      <c r="O74" s="114"/>
+      <c r="O74" s="107"/>
       <c r="P74" s="46"/>
       <c r="Q74" s="47">
         <v>1</v>
@@ -9775,11 +9770,11 @@
       <c r="AE74"/>
     </row>
     <row r="75" spans="1:31" ht="15">
-      <c r="A75" s="111" t="s">
+      <c r="A75" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="95" t="s">
         <v>646</v>
-      </c>
-      <c r="B75" s="112" t="s">
-        <v>647</v>
       </c>
       <c r="C75" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
@@ -9854,11 +9849,11 @@
       <c r="AE75"/>
     </row>
     <row r="76" spans="1:31" ht="15">
-      <c r="A76" s="111" t="s">
+      <c r="A76" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76" s="42" t="s">
         <v>646</v>
-      </c>
-      <c r="B76" s="111" t="s">
-        <v>647</v>
       </c>
       <c r="C76" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
@@ -9933,10 +9928,10 @@
       <c r="AE76"/>
     </row>
     <row r="77" spans="1:31" ht="15">
-      <c r="A77" s="111" t="s">
+      <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B77" s="112" t="s">
+      <c r="B77" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C77" s="43">
@@ -10012,10 +10007,10 @@
       <c r="AE77"/>
     </row>
     <row r="78" spans="1:31" ht="15">
-      <c r="A78" s="111" t="s">
+      <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B78" s="112" t="s">
+      <c r="B78" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C78" s="43">
@@ -10091,10 +10086,10 @@
       <c r="AE78"/>
     </row>
     <row r="79" spans="1:31" ht="15">
-      <c r="A79" s="111" t="s">
+      <c r="A79" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B79" s="111" t="s">
+      <c r="B79" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C79" s="43">
@@ -10167,10 +10162,10 @@
       <c r="AE79"/>
     </row>
     <row r="80" spans="1:31" ht="15">
-      <c r="A80" s="111" t="s">
+      <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B80" s="112" t="s">
+      <c r="B80" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C80" s="43">
@@ -10243,10 +10238,10 @@
       <c r="AE80"/>
     </row>
     <row r="81" spans="1:31" ht="15">
-      <c r="A81" s="111" t="s">
+      <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B81" s="111" t="s">
+      <c r="B81" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C81" s="43">
@@ -10319,10 +10314,10 @@
       <c r="AE81"/>
     </row>
     <row r="82" spans="1:31" ht="15">
-      <c r="A82" s="111" t="s">
+      <c r="A82" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B82" s="112" t="s">
+      <c r="B82" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C82" s="43">
@@ -10395,10 +10390,10 @@
       <c r="AE82"/>
     </row>
     <row r="83" spans="1:31" ht="15">
-      <c r="A83" s="111" t="s">
+      <c r="A83" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B83" s="111" t="s">
+      <c r="B83" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C83" s="43">
@@ -10471,10 +10466,10 @@
       <c r="AE83"/>
     </row>
     <row r="84" spans="1:31" ht="15">
-      <c r="A84" s="111" t="s">
+      <c r="A84" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B84" s="111" t="s">
+      <c r="B84" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C84" s="43">
@@ -10498,7 +10493,7 @@
       <c r="H84" s="105">
         <v>8350</v>
       </c>
-      <c r="I84" s="113" t="s">
+      <c r="I84" s="55" t="s">
         <v>45</v>
       </c>
       <c r="J84" s="46">
@@ -10544,10 +10539,10 @@
       <c r="AE84"/>
     </row>
     <row r="85" spans="1:31" ht="15">
-      <c r="A85" s="111" t="s">
+      <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B85" s="111" t="s">
+      <c r="B85" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C85" s="43">
@@ -10571,7 +10566,7 @@
       <c r="H85" s="105">
         <v>8350</v>
       </c>
-      <c r="I85" s="113" t="s">
+      <c r="I85" s="55" t="s">
         <v>129</v>
       </c>
       <c r="J85" s="46">
@@ -10598,7 +10593,7 @@
       <c r="S85" s="46">
         <v>325</v>
       </c>
-      <c r="T85" s="115" t="s">
+      <c r="T85" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U85" s="46">
@@ -10617,10 +10612,10 @@
       <c r="AE85"/>
     </row>
     <row r="86" spans="1:31" ht="15">
-      <c r="A86" s="111" t="s">
+      <c r="A86" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B86" s="111" t="s">
+      <c r="B86" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C86" s="43">
@@ -10690,10 +10685,10 @@
       <c r="AE86"/>
     </row>
     <row r="87" spans="1:31" ht="15">
-      <c r="A87" s="111" t="s">
+      <c r="A87" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B87" s="111" t="s">
+      <c r="B87" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C87" s="43">
@@ -10717,7 +10712,7 @@
       <c r="H87" s="105">
         <v>8350</v>
       </c>
-      <c r="I87" s="113" t="s">
+      <c r="I87" s="55" t="s">
         <v>141</v>
       </c>
       <c r="J87" s="46">
@@ -10763,10 +10758,10 @@
       <c r="AE87"/>
     </row>
     <row r="88" spans="1:31" ht="15">
-      <c r="A88" s="111" t="s">
+      <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B88" s="111" t="s">
+      <c r="B88" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="43">
@@ -10790,7 +10785,7 @@
       <c r="H88" s="105">
         <v>8350</v>
       </c>
-      <c r="I88" s="113" t="s">
+      <c r="I88" s="55" t="s">
         <v>156</v>
       </c>
       <c r="J88" s="46">
@@ -10837,10 +10832,10 @@
       <c r="AE88"/>
     </row>
     <row r="89" spans="1:31" ht="15">
-      <c r="A89" s="111" t="s">
+      <c r="A89" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B89" s="111" t="s">
+      <c r="B89" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="43">
@@ -10864,7 +10859,7 @@
       <c r="H89" s="105">
         <v>8350</v>
       </c>
-      <c r="I89" s="113" t="s">
+      <c r="I89" s="55" t="s">
         <v>159</v>
       </c>
       <c r="J89" s="46">
@@ -10878,9 +10873,9 @@
       <c r="L89" s="105">
         <v>6600</v>
       </c>
-      <c r="M89" s="113"/>
+      <c r="M89" s="55"/>
       <c r="N89" s="46"/>
-      <c r="O89" s="114"/>
+      <c r="O89" s="107"/>
       <c r="P89" s="46"/>
       <c r="Q89" s="47">
         <v>1</v>
@@ -10909,11 +10904,11 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="15">
-      <c r="A90" s="111" t="s">
+    <row r="90" spans="1:31" ht="15" hidden="1">
+      <c r="A90" s="42" t="s">
         <v>638</v>
       </c>
-      <c r="B90" s="112" t="s">
+      <c r="B90" s="95" t="s">
         <v>639</v>
       </c>
       <c r="C90" s="43">
@@ -10982,11 +10977,11 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="15">
-      <c r="A91" s="111" t="s">
+    <row r="91" spans="1:31" ht="15" hidden="1">
+      <c r="A91" s="42" t="s">
         <v>638</v>
       </c>
-      <c r="B91" s="112" t="s">
+      <c r="B91" s="95" t="s">
         <v>639</v>
       </c>
       <c r="C91" s="43">
@@ -11054,11 +11049,11 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="15">
-      <c r="A92" s="111" t="s">
+    <row r="92" spans="1:31" ht="15" hidden="1">
+      <c r="A92" s="42" t="s">
         <v>638</v>
       </c>
-      <c r="B92" s="111" t="s">
+      <c r="B92" s="42" t="s">
         <v>639</v>
       </c>
       <c r="C92" s="43">
@@ -11126,11 +11121,11 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="15">
-      <c r="A93" s="111" t="s">
+    <row r="93" spans="1:31" ht="15" hidden="1">
+      <c r="A93" s="42" t="s">
         <v>640</v>
       </c>
-      <c r="B93" s="112" t="s">
+      <c r="B93" s="95" t="s">
         <v>641</v>
       </c>
       <c r="C93" s="43">
@@ -11198,11 +11193,11 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="15">
-      <c r="A94" s="111" t="s">
+    <row r="94" spans="1:31" ht="15" hidden="1">
+      <c r="A94" s="42" t="s">
         <v>642</v>
       </c>
-      <c r="B94" s="112" t="s">
+      <c r="B94" s="95" t="s">
         <v>643</v>
       </c>
       <c r="C94" s="43">
@@ -11270,11 +11265,11 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="15">
-      <c r="A95" s="111" t="s">
+    <row r="95" spans="1:31" ht="15" hidden="1">
+      <c r="A95" s="42" t="s">
         <v>642</v>
       </c>
-      <c r="B95" s="112" t="s">
+      <c r="B95" s="95" t="s">
         <v>643</v>
       </c>
       <c r="C95" s="43">
@@ -11342,11 +11337,11 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="15">
-      <c r="A96" s="111" t="s">
+    <row r="96" spans="1:31" ht="15" hidden="1">
+      <c r="A96" s="42" t="s">
         <v>642</v>
       </c>
-      <c r="B96" s="111" t="s">
+      <c r="B96" s="42" t="s">
         <v>643</v>
       </c>
       <c r="C96" s="43">
@@ -11415,11 +11410,11 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="15">
-      <c r="A97" s="111" t="s">
+    <row r="97" spans="1:31" ht="15" hidden="1">
+      <c r="A97" s="42" t="s">
         <v>644</v>
       </c>
-      <c r="B97" s="112" t="s">
+      <c r="B97" s="95" t="s">
         <v>645</v>
       </c>
       <c r="C97" s="43">
@@ -11487,11 +11482,11 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="15">
-      <c r="A98" s="111" t="s">
+    <row r="98" spans="1:31" ht="15" hidden="1">
+      <c r="A98" s="42" t="s">
         <v>644</v>
       </c>
-      <c r="B98" s="112" t="s">
+      <c r="B98" s="95" t="s">
         <v>645</v>
       </c>
       <c r="C98" s="43">
@@ -11559,11 +11554,11 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="15">
-      <c r="A99" s="111" t="s">
+    <row r="99" spans="1:31" ht="15" hidden="1">
+      <c r="A99" s="42" t="s">
         <v>644</v>
       </c>
-      <c r="B99" s="111" t="s">
+      <c r="B99" s="42" t="s">
         <v>645</v>
       </c>
       <c r="C99" s="43">
@@ -11631,7 +11626,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15">
+    <row r="100" spans="1:31" ht="15" hidden="1">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11700,7 +11695,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15">
+    <row r="101" spans="1:31" ht="15" hidden="1">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11772,7 +11767,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15">
+    <row r="102" spans="1:31" ht="15" hidden="1">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11841,7 +11836,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15">
+    <row r="103" spans="1:31" ht="15" hidden="1">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11913,7 +11908,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15">
+    <row r="104" spans="1:31" ht="15" hidden="1">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11982,7 +11977,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15">
+    <row r="105" spans="1:31" ht="15" hidden="1">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12054,7 +12049,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15">
+    <row r="106" spans="1:31" ht="15" hidden="1">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12123,7 +12118,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15">
+    <row r="107" spans="1:31" ht="15" hidden="1">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12195,7 +12190,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15">
+    <row r="108" spans="1:31" ht="15" hidden="1">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12264,7 +12259,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15">
+    <row r="109" spans="1:31" ht="15" hidden="1">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12336,7 +12331,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15">
+    <row r="110" spans="1:31" ht="15" hidden="1">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12405,7 +12400,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15">
+    <row r="111" spans="1:31" ht="15" hidden="1">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12477,7 +12472,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15">
+    <row r="112" spans="1:31" ht="15" hidden="1">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12544,7 +12539,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15">
+    <row r="113" spans="1:31" ht="15" hidden="1">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12614,7 +12609,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15">
+    <row r="114" spans="1:31" ht="15" hidden="1">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12681,7 +12676,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15">
+    <row r="115" spans="1:31" ht="15" hidden="1">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12751,7 +12746,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15">
+    <row r="116" spans="1:31" ht="15" hidden="1">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12821,7 +12816,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15">
+    <row r="117" spans="1:31" ht="15" hidden="1">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12894,7 +12889,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15">
+    <row r="118" spans="1:31" ht="15" hidden="1">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12964,7 +12959,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15">
+    <row r="119" spans="1:31" ht="15" hidden="1">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13037,7 +13032,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15">
+    <row r="120" spans="1:31" ht="15" hidden="1">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13107,7 +13102,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15">
+    <row r="121" spans="1:31" ht="15" hidden="1">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13180,7 +13175,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15">
+    <row r="122" spans="1:31" ht="15" hidden="1">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13250,7 +13245,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15">
+    <row r="123" spans="1:31" ht="15" hidden="1">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13323,7 +13318,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15">
+    <row r="124" spans="1:31" ht="15" hidden="1">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13393,7 +13388,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15">
+    <row r="125" spans="1:31" ht="15" hidden="1">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13466,7 +13461,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15">
+    <row r="126" spans="1:31" ht="15" hidden="1">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13536,7 +13531,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15">
+    <row r="127" spans="1:31" ht="15" hidden="1">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13609,7 +13604,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15">
+    <row r="128" spans="1:31" ht="15" hidden="1">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13679,7 +13674,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15">
+    <row r="129" spans="1:31" ht="15" hidden="1">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13752,7 +13747,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15">
+    <row r="130" spans="1:31" ht="15" hidden="1">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13820,7 +13815,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15">
+    <row r="131" spans="1:31" ht="15" hidden="1">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13891,7 +13886,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15">
+    <row r="132" spans="1:31" ht="15" hidden="1">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13959,7 +13954,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15">
+    <row r="133" spans="1:31" ht="15" hidden="1">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14029,7 +14024,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15">
+    <row r="134" spans="1:31" ht="15" hidden="1">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14096,7 +14091,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15">
+    <row r="135" spans="1:31" ht="15" hidden="1">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14166,7 +14161,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15">
+    <row r="136" spans="1:31" ht="15" hidden="1">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14235,7 +14230,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15">
+    <row r="137" spans="1:31" ht="15" hidden="1">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14307,7 +14302,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15">
+    <row r="138" spans="1:31" ht="15" hidden="1">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14376,7 +14371,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15">
+    <row r="139" spans="1:31" ht="15" hidden="1">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14449,7 +14444,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15">
+    <row r="140" spans="1:31" ht="15" hidden="1">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14519,7 +14514,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15">
+    <row r="141" spans="1:31" ht="15" hidden="1">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14592,7 +14587,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15">
+    <row r="142" spans="1:31" ht="15" hidden="1">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14661,7 +14656,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15">
+    <row r="143" spans="1:31" ht="15" hidden="1">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14733,7 +14728,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15">
+    <row r="144" spans="1:31" ht="15" hidden="1">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14802,7 +14797,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15">
+    <row r="145" spans="1:31" ht="15" hidden="1">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14874,7 +14869,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15">
+    <row r="146" spans="1:31" ht="15" hidden="1">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14929,7 +14924,7 @@
       <c r="T146" s="89" t="s">
         <v>74</v>
       </c>
-      <c r="U146" s="116">
+      <c r="U146" s="108">
         <v>0</v>
       </c>
       <c r="V146" s="104" t="s">
@@ -14943,7 +14938,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15">
+    <row r="147" spans="1:31" ht="15" hidden="1">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -15015,7 +15010,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15">
+    <row r="148" spans="1:31" ht="15" hidden="1">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15082,7 +15077,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15">
+    <row r="149" spans="1:31" ht="15" hidden="1">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15152,7 +15147,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15">
+    <row r="150" spans="1:31" ht="15" hidden="1">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15219,7 +15214,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15">
+    <row r="151" spans="1:31" ht="15" hidden="1">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15289,7 +15284,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15">
+    <row r="152" spans="1:31" ht="15" hidden="1">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15357,7 +15352,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15">
+    <row r="153" spans="1:31" ht="15" hidden="1">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15428,7 +15423,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15">
+    <row r="154" spans="1:31" ht="15" hidden="1">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15500,7 +15495,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15">
+    <row r="155" spans="1:31" ht="15" hidden="1">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15572,7 +15567,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15">
+    <row r="156" spans="1:31" ht="15" hidden="1">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15644,7 +15639,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15">
+    <row r="157" spans="1:31" ht="15" hidden="1">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15716,7 +15711,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15">
+    <row r="158" spans="1:31" ht="15" hidden="1">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15788,7 +15783,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15">
+    <row r="159" spans="1:31" ht="15" hidden="1">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15861,7 +15856,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15">
+    <row r="160" spans="1:31" ht="15" hidden="1">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15933,7 +15928,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15">
+    <row r="161" spans="1:30" ht="15" hidden="1">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -16005,7 +16000,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15">
+    <row r="162" spans="1:30" ht="15" hidden="1">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16077,7 +16072,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15">
+    <row r="163" spans="1:30" ht="15" hidden="1">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16149,7 +16144,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15">
+    <row r="164" spans="1:30" ht="15" hidden="1">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16221,7 +16216,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15">
+    <row r="165" spans="1:30" ht="15" hidden="1">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16293,7 +16288,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15">
+    <row r="166" spans="1:30" ht="15" hidden="1">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16365,7 +16360,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15">
+    <row r="167" spans="1:30" ht="15" hidden="1">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16437,7 +16432,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15">
+    <row r="168" spans="1:30" ht="15" hidden="1">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16509,7 +16504,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15">
+    <row r="169" spans="1:30" ht="15" hidden="1">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16581,7 +16576,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15">
+    <row r="170" spans="1:30" ht="15" hidden="1">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16653,7 +16648,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15">
+    <row r="171" spans="1:30" ht="15" hidden="1">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16724,7 +16719,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15">
+    <row r="172" spans="1:30" ht="15" hidden="1">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16796,7 +16791,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15">
+    <row r="173" spans="1:30" ht="15" hidden="1">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16869,7 +16864,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15">
+    <row r="174" spans="1:30" ht="15" hidden="1">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16941,7 +16936,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15">
+    <row r="175" spans="1:30" ht="15" hidden="1">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -17013,7 +17008,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15">
+    <row r="176" spans="1:30" ht="15" hidden="1">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17085,7 +17080,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15">
+    <row r="177" spans="1:30" ht="15" hidden="1">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17157,7 +17152,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15">
+    <row r="178" spans="1:30" ht="15" hidden="1">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17229,7 +17224,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15">
+    <row r="179" spans="1:30" ht="15" hidden="1">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17301,7 +17296,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15">
+    <row r="180" spans="1:30" ht="15" hidden="1">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17373,7 +17368,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15">
+    <row r="181" spans="1:30" ht="15" hidden="1">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17445,7 +17440,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15">
+    <row r="182" spans="1:30" ht="15" hidden="1">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17517,7 +17512,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15">
+    <row r="183" spans="1:30" ht="15" hidden="1">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17589,7 +17584,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15">
+    <row r="184" spans="1:30" ht="15" hidden="1">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17661,7 +17656,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15">
+    <row r="185" spans="1:30" ht="15" hidden="1">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17733,7 +17728,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15">
+    <row r="186" spans="1:30" ht="15" hidden="1">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17805,7 +17800,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15">
+    <row r="187" spans="1:30" ht="15" hidden="1">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17878,7 +17873,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15">
+    <row r="188" spans="1:30" ht="15" hidden="1">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17950,7 +17945,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15">
+    <row r="189" spans="1:30" ht="15" hidden="1">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18022,7 +18017,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15">
+    <row r="190" spans="1:30" ht="15" hidden="1">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18094,7 +18089,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15">
+    <row r="191" spans="1:30" ht="15" hidden="1">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18166,7 +18161,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15">
+    <row r="192" spans="1:30" ht="15" hidden="1">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18238,7 +18233,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15">
+    <row r="193" spans="1:30" ht="15" hidden="1">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18310,7 +18305,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15">
+    <row r="194" spans="1:30" ht="15" hidden="1">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18382,7 +18377,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15">
+    <row r="195" spans="1:30" ht="15" hidden="1">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18452,7 +18447,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15">
+    <row r="196" spans="1:30" ht="15" hidden="1">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18531,7 +18526,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15">
+    <row r="197" spans="1:30" ht="15" hidden="1">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18610,7 +18605,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15">
+    <row r="198" spans="1:30" ht="15" hidden="1">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18689,7 +18684,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15">
+    <row r="199" spans="1:30" ht="15" hidden="1">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>

--- a/downloaded_file.xlsx
+++ b/downloaded_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beltonene-my.sharepoint.com/personal/helpdesk_beltonene_com/Documents/HelpDesk_Shared/Inner Ear/Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1529" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F597968-A36B-4021-8664-46EE7F249227}"/>
+  <xr:revisionPtr revIDLastSave="1533" documentId="8_{964C585B-190F-46EC-9553-F8D486DF59FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB1AF40E-3D95-484D-BC98-43B1E38C4A87}"/>
   <bookViews>
     <workbookView xWindow="4185" yWindow="3690" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{117CC408-EBB5-49DC-AD42-2C9AA08047CD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="646">
   <si>
     <t>Choose Hearing Aid Model</t>
   </si>
@@ -2002,9 +2002,6 @@
   </si>
   <si>
     <t>Beltone Illuminate 9 62S-DRWC Digital RIE</t>
-  </si>
-  <si>
-    <t>Beltone Envision 9 62SDRWC Digital RIE</t>
   </si>
 </sst>
 </file>
@@ -3336,16 +3333,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}" name="HearingAids7" displayName="HearingAids7" ref="A1:V199" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Beltone RIE Digital Envision 9 62S-DRWC"/>
-        <filter val="Beltone RIE Digital Envision 9 62-SDRWC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V199">
-    <sortCondition ref="B1:B199"/>
+  <autoFilter ref="A1:V199" xr:uid="{DDE93EFC-1E30-486E-83F2-F1CC19CD90C0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A75:V89">
+    <sortCondition ref="I1:I199"/>
   </sortState>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{A759776D-F1C7-439A-A017-B16601DE8834}" name="haModel" dataDxfId="56"/>
@@ -4445,7 +4435,7 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" ht="15" hidden="1">
+    <row r="2" spans="1:31" ht="15">
       <c r="A2" s="42" t="s">
         <v>130</v>
       </c>
@@ -4515,7 +4505,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" ht="15" hidden="1">
+    <row r="3" spans="1:31" ht="15">
       <c r="A3" s="42" t="s">
         <v>130</v>
       </c>
@@ -4584,7 +4574,7 @@
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" ht="15" hidden="1">
+    <row r="4" spans="1:31" ht="15">
       <c r="A4" s="42" t="s">
         <v>130</v>
       </c>
@@ -4656,7 +4646,7 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" ht="15" hidden="1">
+    <row r="5" spans="1:31" ht="15">
       <c r="A5" s="42" t="s">
         <v>130</v>
       </c>
@@ -4728,7 +4718,7 @@
       <c r="AD5"/>
       <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31" ht="15" hidden="1">
+    <row r="6" spans="1:31" ht="15">
       <c r="A6" s="42" t="s">
         <v>120</v>
       </c>
@@ -4795,7 +4785,7 @@
       <c r="AD6"/>
       <c r="AE6"/>
     </row>
-    <row r="7" spans="1:31" ht="15" hidden="1">
+    <row r="7" spans="1:31" ht="15">
       <c r="A7" s="42" t="s">
         <v>120</v>
       </c>
@@ -4859,7 +4849,7 @@
       <c r="AD7"/>
       <c r="AE7"/>
     </row>
-    <row r="8" spans="1:31" ht="15" hidden="1">
+    <row r="8" spans="1:31" ht="15">
       <c r="A8" s="42" t="s">
         <v>132</v>
       </c>
@@ -4928,7 +4918,7 @@
       <c r="AD8"/>
       <c r="AE8"/>
     </row>
-    <row r="9" spans="1:31" ht="15" hidden="1">
+    <row r="9" spans="1:31" ht="15">
       <c r="A9" s="42" t="s">
         <v>132</v>
       </c>
@@ -5000,7 +4990,7 @@
       <c r="AD9"/>
       <c r="AE9"/>
     </row>
-    <row r="10" spans="1:31" ht="15" hidden="1">
+    <row r="10" spans="1:31" ht="15">
       <c r="A10" s="42" t="s">
         <v>132</v>
       </c>
@@ -5072,7 +5062,7 @@
       <c r="AD10"/>
       <c r="AE10"/>
     </row>
-    <row r="11" spans="1:31" ht="15" hidden="1">
+    <row r="11" spans="1:31" ht="15">
       <c r="A11" s="42" t="s">
         <v>134</v>
       </c>
@@ -5141,7 +5131,7 @@
       <c r="AD11"/>
       <c r="AE11"/>
     </row>
-    <row r="12" spans="1:31" ht="15" hidden="1">
+    <row r="12" spans="1:31" ht="15">
       <c r="A12" s="42" t="s">
         <v>132</v>
       </c>
@@ -5210,7 +5200,7 @@
       <c r="AD12"/>
       <c r="AE12"/>
     </row>
-    <row r="13" spans="1:31" ht="15" hidden="1">
+    <row r="13" spans="1:31" ht="15">
       <c r="A13" s="42" t="s">
         <v>134</v>
       </c>
@@ -5279,7 +5269,7 @@
       <c r="AD13"/>
       <c r="AE13"/>
     </row>
-    <row r="14" spans="1:31" ht="15" hidden="1">
+    <row r="14" spans="1:31" ht="15">
       <c r="A14" s="42" t="s">
         <v>134</v>
       </c>
@@ -5351,7 +5341,7 @@
       <c r="AD14"/>
       <c r="AE14"/>
     </row>
-    <row r="15" spans="1:31" ht="15" hidden="1">
+    <row r="15" spans="1:31" ht="15">
       <c r="A15" s="42" t="s">
         <v>134</v>
       </c>
@@ -5424,7 +5414,7 @@
       <c r="AD15"/>
       <c r="AE15"/>
     </row>
-    <row r="16" spans="1:31" ht="15" hidden="1">
+    <row r="16" spans="1:31" ht="15">
       <c r="A16" s="42" t="s">
         <v>139</v>
       </c>
@@ -5497,7 +5487,7 @@
       <c r="AD16"/>
       <c r="AE16"/>
     </row>
-    <row r="17" spans="1:31" ht="15" hidden="1">
+    <row r="17" spans="1:31" ht="15">
       <c r="A17" s="42" t="s">
         <v>139</v>
       </c>
@@ -5570,7 +5560,7 @@
       <c r="AD17"/>
       <c r="AE17"/>
     </row>
-    <row r="18" spans="1:31" ht="15" hidden="1">
+    <row r="18" spans="1:31" ht="15">
       <c r="A18" s="42" t="s">
         <v>142</v>
       </c>
@@ -5642,7 +5632,7 @@
       <c r="AD18"/>
       <c r="AE18"/>
     </row>
-    <row r="19" spans="1:31" ht="15" hidden="1">
+    <row r="19" spans="1:31" ht="15">
       <c r="A19" s="42" t="s">
         <v>142</v>
       </c>
@@ -5715,7 +5705,7 @@
       <c r="AD19"/>
       <c r="AE19"/>
     </row>
-    <row r="20" spans="1:31" ht="15" hidden="1">
+    <row r="20" spans="1:31" ht="15">
       <c r="A20" s="42" t="s">
         <v>144</v>
       </c>
@@ -5787,7 +5777,7 @@
       <c r="AD20"/>
       <c r="AE20"/>
     </row>
-    <row r="21" spans="1:31" ht="15" hidden="1">
+    <row r="21" spans="1:31" ht="15">
       <c r="A21" s="42" t="s">
         <v>144</v>
       </c>
@@ -5860,7 +5850,7 @@
       <c r="AD21"/>
       <c r="AE21"/>
     </row>
-    <row r="22" spans="1:31" ht="15" hidden="1">
+    <row r="22" spans="1:31" ht="15">
       <c r="A22" s="42" t="s">
         <v>146</v>
       </c>
@@ -5932,7 +5922,7 @@
       <c r="AD22"/>
       <c r="AE22"/>
     </row>
-    <row r="23" spans="1:31" ht="15" hidden="1">
+    <row r="23" spans="1:31" ht="15">
       <c r="A23" s="42" t="s">
         <v>146</v>
       </c>
@@ -6004,7 +5994,7 @@
       <c r="AD23"/>
       <c r="AE23"/>
     </row>
-    <row r="24" spans="1:31" ht="15" hidden="1">
+    <row r="24" spans="1:31" ht="15">
       <c r="A24" s="42" t="s">
         <v>148</v>
       </c>
@@ -6076,7 +6066,7 @@
       <c r="AD24"/>
       <c r="AE24"/>
     </row>
-    <row r="25" spans="1:31" ht="15" hidden="1">
+    <row r="25" spans="1:31" ht="15">
       <c r="A25" s="42" t="s">
         <v>148</v>
       </c>
@@ -6150,7 +6140,7 @@
       <c r="AD25"/>
       <c r="AE25"/>
     </row>
-    <row r="26" spans="1:31" ht="15" hidden="1">
+    <row r="26" spans="1:31" ht="15">
       <c r="A26" s="42" t="s">
         <v>150</v>
       </c>
@@ -6223,7 +6213,7 @@
       <c r="AD26"/>
       <c r="AE26"/>
     </row>
-    <row r="27" spans="1:31" ht="15" hidden="1">
+    <row r="27" spans="1:31" ht="15">
       <c r="A27" s="42" t="s">
         <v>150</v>
       </c>
@@ -6297,7 +6287,7 @@
       <c r="AD27"/>
       <c r="AE27"/>
     </row>
-    <row r="28" spans="1:31" ht="15" hidden="1">
+    <row r="28" spans="1:31" ht="15">
       <c r="A28" s="42" t="s">
         <v>43</v>
       </c>
@@ -6360,7 +6350,7 @@
       <c r="AD28"/>
       <c r="AE28"/>
     </row>
-    <row r="29" spans="1:31" ht="15" hidden="1">
+    <row r="29" spans="1:31" ht="15">
       <c r="A29" s="42" t="s">
         <v>43</v>
       </c>
@@ -6432,7 +6422,7 @@
       <c r="AD29"/>
       <c r="AE29"/>
     </row>
-    <row r="30" spans="1:31" ht="15" hidden="1">
+    <row r="30" spans="1:31" ht="15">
       <c r="A30" s="42" t="s">
         <v>47</v>
       </c>
@@ -6504,7 +6494,7 @@
       <c r="AD30"/>
       <c r="AE30"/>
     </row>
-    <row r="31" spans="1:31" ht="15" hidden="1">
+    <row r="31" spans="1:31" ht="15">
       <c r="A31" s="42" t="s">
         <v>47</v>
       </c>
@@ -6575,7 +6565,7 @@
       <c r="AD31"/>
       <c r="AE31"/>
     </row>
-    <row r="32" spans="1:31" ht="15" hidden="1">
+    <row r="32" spans="1:31" ht="15">
       <c r="A32" s="42" t="s">
         <v>47</v>
       </c>
@@ -6647,7 +6637,7 @@
       <c r="AD32"/>
       <c r="AE32"/>
     </row>
-    <row r="33" spans="1:31" ht="15" hidden="1">
+    <row r="33" spans="1:31" ht="15">
       <c r="A33" s="42" t="s">
         <v>47</v>
       </c>
@@ -6719,7 +6709,7 @@
       <c r="AD33"/>
       <c r="AE33"/>
     </row>
-    <row r="34" spans="1:31" ht="15" hidden="1">
+    <row r="34" spans="1:31" ht="15">
       <c r="A34" s="42" t="s">
         <v>47</v>
       </c>
@@ -6791,7 +6781,7 @@
       <c r="AD34"/>
       <c r="AE34"/>
     </row>
-    <row r="35" spans="1:31" ht="15" hidden="1">
+    <row r="35" spans="1:31" ht="15">
       <c r="A35" s="42" t="s">
         <v>47</v>
       </c>
@@ -6863,7 +6853,7 @@
       <c r="AD35"/>
       <c r="AE35"/>
     </row>
-    <row r="36" spans="1:31" ht="15" hidden="1">
+    <row r="36" spans="1:31" ht="15">
       <c r="A36" s="42" t="s">
         <v>47</v>
       </c>
@@ -6936,7 +6926,7 @@
       <c r="AD36"/>
       <c r="AE36"/>
     </row>
-    <row r="37" spans="1:31" ht="15" hidden="1">
+    <row r="37" spans="1:31" ht="15">
       <c r="A37" s="42" t="s">
         <v>47</v>
       </c>
@@ -7008,7 +6998,7 @@
       <c r="AD37"/>
       <c r="AE37"/>
     </row>
-    <row r="38" spans="1:31" ht="15" hidden="1">
+    <row r="38" spans="1:31" ht="15">
       <c r="A38" s="42" t="s">
         <v>47</v>
       </c>
@@ -7080,7 +7070,7 @@
       <c r="AD38"/>
       <c r="AE38"/>
     </row>
-    <row r="39" spans="1:31" ht="15" hidden="1">
+    <row r="39" spans="1:31" ht="15">
       <c r="A39" s="42" t="s">
         <v>47</v>
       </c>
@@ -7152,7 +7142,7 @@
       <c r="AD39"/>
       <c r="AE39"/>
     </row>
-    <row r="40" spans="1:31" ht="15" hidden="1">
+    <row r="40" spans="1:31" ht="15">
       <c r="A40" s="42" t="s">
         <v>47</v>
       </c>
@@ -7224,7 +7214,7 @@
       <c r="AD40"/>
       <c r="AE40"/>
     </row>
-    <row r="41" spans="1:31" ht="15" hidden="1">
+    <row r="41" spans="1:31" ht="15">
       <c r="A41" s="42" t="s">
         <v>47</v>
       </c>
@@ -7296,7 +7286,7 @@
       <c r="AD41"/>
       <c r="AE41"/>
     </row>
-    <row r="42" spans="1:31" ht="15" hidden="1">
+    <row r="42" spans="1:31" ht="15">
       <c r="A42" s="42" t="s">
         <v>47</v>
       </c>
@@ -7368,7 +7358,7 @@
       <c r="AD42"/>
       <c r="AE42"/>
     </row>
-    <row r="43" spans="1:31" ht="15" hidden="1">
+    <row r="43" spans="1:31" ht="15">
       <c r="A43" s="42" t="s">
         <v>53</v>
       </c>
@@ -7446,7 +7436,7 @@
       <c r="AD43"/>
       <c r="AE43"/>
     </row>
-    <row r="44" spans="1:31" ht="15" hidden="1">
+    <row r="44" spans="1:31" ht="15">
       <c r="A44" s="42" t="s">
         <v>53</v>
       </c>
@@ -7524,7 +7514,7 @@
       <c r="AD44"/>
       <c r="AE44"/>
     </row>
-    <row r="45" spans="1:31" ht="15" hidden="1">
+    <row r="45" spans="1:31" ht="15">
       <c r="A45" s="42" t="s">
         <v>53</v>
       </c>
@@ -7602,7 +7592,7 @@
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
-    <row r="46" spans="1:31" ht="15" hidden="1">
+    <row r="46" spans="1:31" ht="15">
       <c r="A46" s="42" t="s">
         <v>53</v>
       </c>
@@ -7680,7 +7670,7 @@
       <c r="AD46"/>
       <c r="AE46"/>
     </row>
-    <row r="47" spans="1:31" ht="15" hidden="1">
+    <row r="47" spans="1:31" ht="15">
       <c r="A47" s="42" t="s">
         <v>53</v>
       </c>
@@ -7755,7 +7745,7 @@
       <c r="AD47"/>
       <c r="AE47"/>
     </row>
-    <row r="48" spans="1:31" ht="15" hidden="1">
+    <row r="48" spans="1:31" ht="15">
       <c r="A48" s="42" t="s">
         <v>53</v>
       </c>
@@ -7830,7 +7820,7 @@
       <c r="AD48"/>
       <c r="AE48"/>
     </row>
-    <row r="49" spans="1:32" ht="15" hidden="1">
+    <row r="49" spans="1:32" ht="15">
       <c r="A49" s="42" t="s">
         <v>53</v>
       </c>
@@ -7906,7 +7896,7 @@
       <c r="AD49"/>
       <c r="AE49"/>
     </row>
-    <row r="50" spans="1:32" ht="15" hidden="1">
+    <row r="50" spans="1:32" ht="15">
       <c r="A50" s="42" t="s">
         <v>53</v>
       </c>
@@ -7982,7 +7972,7 @@
       <c r="AD50"/>
       <c r="AE50"/>
     </row>
-    <row r="51" spans="1:32" ht="15" hidden="1">
+    <row r="51" spans="1:32" ht="15">
       <c r="A51" s="42" t="s">
         <v>53</v>
       </c>
@@ -8058,7 +8048,7 @@
       <c r="AD51"/>
       <c r="AE51"/>
     </row>
-    <row r="52" spans="1:32" ht="15" hidden="1">
+    <row r="52" spans="1:32" ht="15">
       <c r="A52" s="42" t="s">
         <v>53</v>
       </c>
@@ -8128,7 +8118,7 @@
       <c r="AD52"/>
       <c r="AE52"/>
     </row>
-    <row r="53" spans="1:32" ht="15" hidden="1">
+    <row r="53" spans="1:32" ht="15">
       <c r="A53" s="42" t="s">
         <v>53</v>
       </c>
@@ -8201,7 +8191,7 @@
       <c r="AD53"/>
       <c r="AE53"/>
     </row>
-    <row r="54" spans="1:32" ht="15" hidden="1">
+    <row r="54" spans="1:32" ht="15">
       <c r="A54" s="42" t="s">
         <v>53</v>
       </c>
@@ -8274,7 +8264,7 @@
       <c r="AD54"/>
       <c r="AE54"/>
     </row>
-    <row r="55" spans="1:32" ht="15" hidden="1">
+    <row r="55" spans="1:32" ht="15">
       <c r="A55" s="42" t="s">
         <v>53</v>
       </c>
@@ -8347,7 +8337,7 @@
       <c r="AD55"/>
       <c r="AE55"/>
     </row>
-    <row r="56" spans="1:32" ht="15" hidden="1">
+    <row r="56" spans="1:32" ht="15">
       <c r="A56" s="42" t="s">
         <v>53</v>
       </c>
@@ -8421,7 +8411,7 @@
       <c r="AD56"/>
       <c r="AE56"/>
     </row>
-    <row r="57" spans="1:32" ht="15" hidden="1">
+    <row r="57" spans="1:32" ht="15">
       <c r="A57" s="42" t="s">
         <v>53</v>
       </c>
@@ -8494,7 +8484,7 @@
       <c r="AE57" s="16"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" ht="15" hidden="1">
+    <row r="58" spans="1:32" ht="15">
       <c r="A58" s="42" t="s">
         <v>50</v>
       </c>
@@ -8566,7 +8556,7 @@
       <c r="AE58" s="16"/>
       <c r="AF58" s="16"/>
     </row>
-    <row r="59" spans="1:32" ht="15" hidden="1">
+    <row r="59" spans="1:32" ht="15">
       <c r="A59" s="42" t="s">
         <v>50</v>
       </c>
@@ -8638,7 +8628,7 @@
       <c r="AE59" s="16"/>
       <c r="AF59" s="16"/>
     </row>
-    <row r="60" spans="1:32" ht="15" hidden="1">
+    <row r="60" spans="1:32" ht="15">
       <c r="A60" s="42" t="s">
         <v>57</v>
       </c>
@@ -8716,7 +8706,7 @@
       <c r="AE60" s="16"/>
       <c r="AF60" s="16"/>
     </row>
-    <row r="61" spans="1:32" ht="15" hidden="1">
+    <row r="61" spans="1:32" ht="15">
       <c r="A61" s="42" t="s">
         <v>57</v>
       </c>
@@ -8795,7 +8785,7 @@
       <c r="AD61"/>
       <c r="AE61"/>
     </row>
-    <row r="62" spans="1:32" ht="15" hidden="1">
+    <row r="62" spans="1:32" ht="15">
       <c r="A62" s="42" t="s">
         <v>57</v>
       </c>
@@ -8874,7 +8864,7 @@
       <c r="AD62"/>
       <c r="AE62"/>
     </row>
-    <row r="63" spans="1:32" ht="15" hidden="1">
+    <row r="63" spans="1:32" ht="15">
       <c r="A63" s="42" t="s">
         <v>57</v>
       </c>
@@ -8953,7 +8943,7 @@
       <c r="AD63"/>
       <c r="AE63"/>
     </row>
-    <row r="64" spans="1:32" ht="15" hidden="1">
+    <row r="64" spans="1:32" ht="15">
       <c r="A64" s="42" t="s">
         <v>57</v>
       </c>
@@ -9029,7 +9019,7 @@
       <c r="AD64"/>
       <c r="AE64"/>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1">
+    <row r="65" spans="1:31" ht="15">
       <c r="A65" s="42" t="s">
         <v>57</v>
       </c>
@@ -9105,7 +9095,7 @@
       <c r="AD65"/>
       <c r="AE65"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1">
+    <row r="66" spans="1:31" ht="15">
       <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
@@ -9181,7 +9171,7 @@
       <c r="AD66"/>
       <c r="AE66"/>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1">
+    <row r="67" spans="1:31" ht="15">
       <c r="A67" s="42" t="s">
         <v>57</v>
       </c>
@@ -9257,7 +9247,7 @@
       <c r="AD67"/>
       <c r="AE67"/>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1">
+    <row r="68" spans="1:31" ht="15">
       <c r="A68" s="42" t="s">
         <v>57</v>
       </c>
@@ -9333,7 +9323,7 @@
       <c r="AD68"/>
       <c r="AE68"/>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1">
+    <row r="69" spans="1:31" ht="15">
       <c r="A69" s="42" t="s">
         <v>57</v>
       </c>
@@ -9403,7 +9393,7 @@
       <c r="AD69"/>
       <c r="AE69"/>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1">
+    <row r="70" spans="1:31" ht="15">
       <c r="A70" s="42" t="s">
         <v>57</v>
       </c>
@@ -9476,7 +9466,7 @@
       <c r="AD70"/>
       <c r="AE70"/>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1">
+    <row r="71" spans="1:31" ht="15">
       <c r="A71" s="42" t="s">
         <v>57</v>
       </c>
@@ -9549,7 +9539,7 @@
       <c r="AD71"/>
       <c r="AE71"/>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1">
+    <row r="72" spans="1:31" ht="15">
       <c r="A72" s="42" t="s">
         <v>57</v>
       </c>
@@ -9622,7 +9612,7 @@
       <c r="AD72"/>
       <c r="AE72"/>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1">
+    <row r="73" spans="1:31" ht="15">
       <c r="A73" s="42" t="s">
         <v>57</v>
       </c>
@@ -9696,7 +9686,7 @@
       <c r="AD73"/>
       <c r="AE73"/>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1">
+    <row r="74" spans="1:31" ht="15">
       <c r="A74" s="42" t="s">
         <v>57</v>
       </c>
@@ -9773,22 +9763,22 @@
       <c r="A75" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B75" s="95" t="s">
-        <v>646</v>
+      <c r="B75" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="C75" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>9683</v>
       </c>
       <c r="D75" s="105">
-        <v>5039</v>
+        <v>4679</v>
       </c>
       <c r="E75" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>666.5</v>
       </c>
       <c r="G75" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -9797,37 +9787,31 @@
       <c r="H75" s="105">
         <v>8350</v>
       </c>
-      <c r="I75" s="77" t="s">
-        <v>122</v>
+      <c r="I75" s="55" t="s">
+        <v>45</v>
       </c>
       <c r="J75" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="K75" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
+        <v>4012.5</v>
       </c>
       <c r="L75" s="105">
-        <v>5790</v>
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
+        <v>8350</v>
       </c>
       <c r="M75" s="46"/>
-      <c r="N75" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="O75" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
+      <c r="N75" s="46"/>
+      <c r="O75" s="46"/>
       <c r="P75" s="46"/>
       <c r="Q75" s="47">
         <v>1</v>
       </c>
-      <c r="R75" s="47" t="s">
+      <c r="R75" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S75" s="47">
+      <c r="S75" s="46">
         <v>325</v>
       </c>
       <c r="T75" s="49" t="s">
@@ -9852,8 +9836,8 @@
       <c r="A76" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B76" s="42" t="s">
-        <v>646</v>
+      <c r="B76" s="95" t="s">
+        <v>60</v>
       </c>
       <c r="C76" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
@@ -9877,7 +9861,7 @@
         <v>8350</v>
       </c>
       <c r="I76" s="77" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="J76" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -9931,22 +9915,22 @@
       <c r="A77" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B77" s="95" t="s">
+      <c r="B77" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C77" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>9683</v>
       </c>
       <c r="D77" s="105">
-        <v>5039</v>
+        <v>4679</v>
       </c>
       <c r="E77" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>666.5</v>
       </c>
       <c r="G77" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -9955,46 +9939,40 @@
       <c r="H77" s="105">
         <v>8350</v>
       </c>
-      <c r="I77" s="77" t="s">
-        <v>153</v>
+      <c r="I77" s="55" t="s">
+        <v>129</v>
       </c>
       <c r="J77" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="K77" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
+        <v>4012.5</v>
       </c>
       <c r="L77" s="105">
-        <v>5790</v>
+        <v>8350</v>
       </c>
       <c r="M77" s="46"/>
-      <c r="N77" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="O77" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
+      <c r="N77" s="46"/>
+      <c r="O77" s="46"/>
       <c r="P77" s="46"/>
       <c r="Q77" s="47">
         <v>1</v>
       </c>
-      <c r="R77" s="47" t="s">
+      <c r="R77" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S77" s="47">
+      <c r="S77" s="46">
         <v>325</v>
       </c>
-      <c r="T77" s="49" t="s">
+      <c r="T77" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="U77" s="49">
-        <v>0</v>
-      </c>
-      <c r="V77" s="49" t="s">
+      <c r="U77" s="46">
+        <v>0</v>
+      </c>
+      <c r="V77" s="54" t="s">
         <v>56</v>
       </c>
       <c r="W77" s="4"/>
@@ -10010,22 +9988,22 @@
       <c r="A78" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B78" s="95" t="s">
+      <c r="B78" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C78" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>9683</v>
       </c>
       <c r="D78" s="105">
-        <v>5039</v>
+        <v>4679</v>
       </c>
       <c r="E78" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>666.5</v>
       </c>
       <c r="G78" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10035,28 +10013,22 @@
         <v>8350</v>
       </c>
       <c r="I78" s="77" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="J78" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>700</v>
       </c>
       <c r="K78" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="L78" s="105">
-        <v>5790</v>
+        <v>3312.5</v>
+      </c>
+      <c r="L78" s="106">
+        <v>6950</v>
       </c>
       <c r="M78" s="46"/>
-      <c r="N78" s="46">
-        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
-        <v>2732.5</v>
-      </c>
-      <c r="O78" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>0</v>
-      </c>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
       <c r="P78" s="46"/>
       <c r="Q78" s="47">
         <v>1</v>
@@ -10064,7 +10036,7 @@
       <c r="R78" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S78" s="47">
+      <c r="S78" s="98">
         <v>325</v>
       </c>
       <c r="T78" s="49" t="s">
@@ -10094,17 +10066,17 @@
       </c>
       <c r="C79" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>9683</v>
       </c>
       <c r="D79" s="105">
-        <v>5039</v>
+        <v>4679</v>
       </c>
       <c r="E79" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F79" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>666.5</v>
       </c>
       <c r="G79" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10113,34 +10085,31 @@
       <c r="H79" s="105">
         <v>8350</v>
       </c>
-      <c r="I79" s="77" t="s">
-        <v>157</v>
+      <c r="I79" s="55" t="s">
+        <v>141</v>
       </c>
       <c r="J79" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="K79" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
+        <v>4012.5</v>
       </c>
       <c r="L79" s="105">
-        <v>5790</v>
+        <v>8350</v>
       </c>
       <c r="M79" s="46"/>
       <c r="N79" s="46"/>
-      <c r="O79" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="O79" s="46"/>
       <c r="P79" s="46"/>
       <c r="Q79" s="47">
         <v>1</v>
       </c>
-      <c r="R79" s="47" t="s">
+      <c r="R79" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S79" s="47">
+      <c r="S79" s="46">
         <v>325</v>
       </c>
       <c r="T79" s="49" t="s">
@@ -10165,7 +10134,7 @@
       <c r="A80" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B80" s="95" t="s">
+      <c r="B80" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C80" s="43">
@@ -10190,7 +10159,7 @@
         <v>8350</v>
       </c>
       <c r="I80" s="77" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J80" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -10204,10 +10173,13 @@
         <v>5790</v>
       </c>
       <c r="M80" s="46"/>
-      <c r="N80" s="46"/>
+      <c r="N80" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="O80" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
+        <v>0</v>
       </c>
       <c r="P80" s="46"/>
       <c r="Q80" s="47">
@@ -10241,7 +10213,7 @@
       <c r="A81" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B81" s="42" t="s">
+      <c r="B81" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C81" s="43">
@@ -10266,7 +10238,7 @@
         <v>8350</v>
       </c>
       <c r="I81" s="77" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="J81" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -10280,10 +10252,13 @@
         <v>5790</v>
       </c>
       <c r="M81" s="46"/>
-      <c r="N81" s="46"/>
+      <c r="N81" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="O81" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
+        <v>0</v>
       </c>
       <c r="P81" s="46"/>
       <c r="Q81" s="47">
@@ -10342,7 +10317,7 @@
         <v>8350</v>
       </c>
       <c r="I82" s="77" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J82" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
@@ -10356,10 +10331,13 @@
         <v>5790</v>
       </c>
       <c r="M82" s="46"/>
-      <c r="N82" s="46"/>
+      <c r="N82" s="46">
+        <f>((HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)-HearingAids7[[#This Row],[haNetPriceBinural2]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="O82" s="46">
         <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
+        <v>0</v>
       </c>
       <c r="P82" s="46"/>
       <c r="Q82" s="47">
@@ -10398,17 +10376,17 @@
       </c>
       <c r="C83" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>10403</v>
+        <v>9683</v>
       </c>
       <c r="D83" s="105">
-        <v>5039</v>
+        <v>4679</v>
       </c>
       <c r="E83" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>1026.5</v>
+        <v>666.5</v>
       </c>
       <c r="G83" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10417,34 +10395,32 @@
       <c r="H83" s="105">
         <v>8350</v>
       </c>
-      <c r="I83" s="77" t="s">
-        <v>164</v>
+      <c r="I83" s="55" t="s">
+        <v>156</v>
       </c>
       <c r="J83" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>1280</v>
+        <v>500</v>
       </c>
       <c r="K83" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>2732.5</v>
+        <v>3512.5</v>
       </c>
       <c r="L83" s="105">
-        <v>5790</v>
+        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
+        <v>7350</v>
       </c>
       <c r="M83" s="46"/>
       <c r="N83" s="46"/>
-      <c r="O83" s="46">
-        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
-        <v>2732.5</v>
-      </c>
+      <c r="O83" s="46"/>
       <c r="P83" s="46"/>
       <c r="Q83" s="47">
         <v>1</v>
       </c>
-      <c r="R83" s="47" t="s">
+      <c r="R83" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S83" s="47">
+      <c r="S83" s="46">
         <v>325</v>
       </c>
       <c r="T83" s="49" t="s">
@@ -10474,17 +10450,17 @@
       </c>
       <c r="C84" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
+        <v>10403</v>
       </c>
       <c r="D84" s="105">
-        <v>4679</v>
+        <v>5039</v>
       </c>
       <c r="E84" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F84" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G84" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10493,31 +10469,34 @@
       <c r="H84" s="105">
         <v>8350</v>
       </c>
-      <c r="I84" s="55" t="s">
-        <v>45</v>
+      <c r="I84" s="77" t="s">
+        <v>157</v>
       </c>
       <c r="J84" s="46">
-        <v>0</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
       </c>
       <c r="K84" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4012.5</v>
+        <v>2732.5</v>
       </c>
       <c r="L84" s="105">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]</f>
-        <v>8350</v>
+        <v>5790</v>
       </c>
       <c r="M84" s="46"/>
       <c r="N84" s="46"/>
-      <c r="O84" s="46"/>
+      <c r="O84" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P84" s="46"/>
       <c r="Q84" s="47">
         <v>1</v>
       </c>
-      <c r="R84" s="46" t="s">
+      <c r="R84" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S84" s="46">
+      <c r="S84" s="47">
         <v>325</v>
       </c>
       <c r="T84" s="49" t="s">
@@ -10542,22 +10521,22 @@
       <c r="A85" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B85" s="42" t="s">
+      <c r="B85" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C85" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
+        <v>10403</v>
       </c>
       <c r="D85" s="105">
-        <v>4679</v>
+        <v>5039</v>
       </c>
       <c r="E85" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G85" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10566,40 +10545,43 @@
       <c r="H85" s="105">
         <v>8350</v>
       </c>
-      <c r="I85" s="55" t="s">
-        <v>129</v>
+      <c r="I85" s="77" t="s">
+        <v>158</v>
       </c>
       <c r="J85" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="K85" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4012.5</v>
+        <v>2732.5</v>
       </c>
       <c r="L85" s="105">
-        <v>8350</v>
+        <v>5790</v>
       </c>
       <c r="M85" s="46"/>
       <c r="N85" s="46"/>
-      <c r="O85" s="46"/>
+      <c r="O85" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P85" s="46"/>
       <c r="Q85" s="47">
         <v>1</v>
       </c>
-      <c r="R85" s="46" t="s">
+      <c r="R85" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S85" s="46">
+      <c r="S85" s="47">
         <v>325</v>
       </c>
-      <c r="T85" s="6" t="s">
+      <c r="T85" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="U85" s="46">
-        <v>0</v>
-      </c>
-      <c r="V85" s="54" t="s">
+      <c r="U85" s="49">
+        <v>0</v>
+      </c>
+      <c r="V85" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W85" s="4"/>
@@ -10639,40 +10621,40 @@
       <c r="H86" s="105">
         <v>8350</v>
       </c>
-      <c r="I86" s="77" t="s">
-        <v>138</v>
+      <c r="I86" s="55" t="s">
+        <v>159</v>
       </c>
       <c r="J86" s="46">
-        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>700</v>
+        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
+        <v>875</v>
       </c>
       <c r="K86" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3312.5</v>
-      </c>
-      <c r="L86" s="106">
-        <v>6950</v>
-      </c>
-      <c r="M86" s="46"/>
+        <v>3137.5</v>
+      </c>
+      <c r="L86" s="105">
+        <v>6600</v>
+      </c>
+      <c r="M86" s="55"/>
       <c r="N86" s="46"/>
-      <c r="O86" s="46"/>
+      <c r="O86" s="107"/>
       <c r="P86" s="46"/>
       <c r="Q86" s="47">
         <v>1</v>
       </c>
-      <c r="R86" s="47" t="s">
+      <c r="R86" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="S86" s="98">
+      <c r="S86" s="46">
         <v>325</v>
       </c>
-      <c r="T86" s="49" t="s">
+      <c r="T86" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="U86" s="49">
-        <v>0</v>
-      </c>
-      <c r="V86" s="49" t="s">
+      <c r="U86" s="21">
+        <v>0</v>
+      </c>
+      <c r="V86" s="103" t="s">
         <v>56</v>
       </c>
       <c r="W86" s="4"/>
@@ -10693,17 +10675,17 @@
       </c>
       <c r="C87" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
+        <v>10403</v>
       </c>
       <c r="D87" s="105">
-        <v>4679</v>
+        <v>5039</v>
       </c>
       <c r="E87" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G87" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10712,31 +10694,34 @@
       <c r="H87" s="105">
         <v>8350</v>
       </c>
-      <c r="I87" s="55" t="s">
-        <v>141</v>
+      <c r="I87" s="77" t="s">
+        <v>161</v>
       </c>
       <c r="J87" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="K87" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>4012.5</v>
+        <v>2732.5</v>
       </c>
       <c r="L87" s="105">
-        <v>8350</v>
+        <v>5790</v>
       </c>
       <c r="M87" s="46"/>
       <c r="N87" s="46"/>
-      <c r="O87" s="46"/>
+      <c r="O87" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P87" s="46"/>
       <c r="Q87" s="47">
         <v>1</v>
       </c>
-      <c r="R87" s="46" t="s">
+      <c r="R87" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S87" s="46">
+      <c r="S87" s="47">
         <v>325</v>
       </c>
       <c r="T87" s="49" t="s">
@@ -10761,22 +10746,22 @@
       <c r="A88" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B88" s="42" t="s">
+      <c r="B88" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
+        <v>10403</v>
       </c>
       <c r="D88" s="105">
-        <v>4679</v>
+        <v>5039</v>
       </c>
       <c r="E88" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F88" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G88" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10785,32 +10770,34 @@
       <c r="H88" s="105">
         <v>8350</v>
       </c>
-      <c r="I88" s="55" t="s">
-        <v>156</v>
+      <c r="I88" s="77" t="s">
+        <v>162</v>
       </c>
       <c r="J88" s="46">
         <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
-        <v>500</v>
+        <v>1280</v>
       </c>
       <c r="K88" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3512.5</v>
+        <v>2732.5</v>
       </c>
       <c r="L88" s="105">
-        <f>HearingAids7[[#This Row],[ListPriceBinural]]-1000</f>
-        <v>7350</v>
+        <v>5790</v>
       </c>
       <c r="M88" s="46"/>
       <c r="N88" s="46"/>
-      <c r="O88" s="46"/>
+      <c r="O88" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P88" s="46"/>
       <c r="Q88" s="47">
         <v>1</v>
       </c>
-      <c r="R88" s="46" t="s">
+      <c r="R88" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S88" s="46">
+      <c r="S88" s="47">
         <v>325</v>
       </c>
       <c r="T88" s="49" t="s">
@@ -10840,17 +10827,17 @@
       </c>
       <c r="C89" s="43">
         <f>(HearingAids7[[#This Row],[haMSRP]]*2)+HearingAids7[[#This Row],[chargerPrice]]</f>
-        <v>9683</v>
+        <v>10403</v>
       </c>
       <c r="D89" s="105">
-        <v>4679</v>
+        <v>5039</v>
       </c>
       <c r="E89" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-((HearingAids7[[#This Row],[ListPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>666.5</v>
+        <v>1026.5</v>
       </c>
       <c r="G89" s="44">
         <f>HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]]</f>
@@ -10859,40 +10846,43 @@
       <c r="H89" s="105">
         <v>8350</v>
       </c>
-      <c r="I89" s="55" t="s">
-        <v>159</v>
+      <c r="I89" s="77" t="s">
+        <v>164</v>
       </c>
       <c r="J89" s="46">
-        <f>((HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2)</f>
-        <v>875</v>
+        <f>(HearingAids7[[#This Row],[haMSRP]]-HearingAids7[[#This Row],[Discount Amount 1]])-(HearingAids7[[#This Row],[haNetPriceBinural]]-HearingAids7[[#This Row],[chargerPrice]])/2</f>
+        <v>1280</v>
       </c>
       <c r="K89" s="46">
         <f>HearingAids7[[#This Row],[HAListPrice]]-HearingAids7[[#This Row],[Discount Amount 2]]</f>
-        <v>3137.5</v>
+        <v>2732.5</v>
       </c>
       <c r="L89" s="105">
-        <v>6600</v>
-      </c>
-      <c r="M89" s="55"/>
+        <v>5790</v>
+      </c>
+      <c r="M89" s="46"/>
       <c r="N89" s="46"/>
-      <c r="O89" s="107"/>
+      <c r="O89" s="46">
+        <f>HearingAids7[[#This Row],[haNetPrice]]-HearingAids7[[#This Row],[Discount Amount 3]]</f>
+        <v>2732.5</v>
+      </c>
       <c r="P89" s="46"/>
       <c r="Q89" s="47">
         <v>1</v>
       </c>
-      <c r="R89" s="46" t="s">
+      <c r="R89" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="S89" s="46">
+      <c r="S89" s="47">
         <v>325</v>
       </c>
-      <c r="T89" s="101" t="s">
+      <c r="T89" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="U89" s="21">
-        <v>0</v>
-      </c>
-      <c r="V89" s="103" t="s">
+      <c r="U89" s="49">
+        <v>0</v>
+      </c>
+      <c r="V89" s="49" t="s">
         <v>56</v>
       </c>
       <c r="W89" s="4"/>
@@ -10904,7 +10894,7 @@
       <c r="AD89"/>
       <c r="AE89"/>
     </row>
-    <row r="90" spans="1:31" ht="15" hidden="1">
+    <row r="90" spans="1:31" ht="15">
       <c r="A90" s="42" t="s">
         <v>638</v>
       </c>
@@ -10977,7 +10967,7 @@
       <c r="AD90"/>
       <c r="AE90"/>
     </row>
-    <row r="91" spans="1:31" ht="15" hidden="1">
+    <row r="91" spans="1:31" ht="15">
       <c r="A91" s="42" t="s">
         <v>638</v>
       </c>
@@ -11049,7 +11039,7 @@
       <c r="AD91"/>
       <c r="AE91"/>
     </row>
-    <row r="92" spans="1:31" ht="15" hidden="1">
+    <row r="92" spans="1:31" ht="15">
       <c r="A92" s="42" t="s">
         <v>638</v>
       </c>
@@ -11121,7 +11111,7 @@
       <c r="AD92"/>
       <c r="AE92"/>
     </row>
-    <row r="93" spans="1:31" ht="15" hidden="1">
+    <row r="93" spans="1:31" ht="15">
       <c r="A93" s="42" t="s">
         <v>640</v>
       </c>
@@ -11193,7 +11183,7 @@
       <c r="AD93"/>
       <c r="AE93"/>
     </row>
-    <row r="94" spans="1:31" ht="15" hidden="1">
+    <row r="94" spans="1:31" ht="15">
       <c r="A94" s="42" t="s">
         <v>642</v>
       </c>
@@ -11265,7 +11255,7 @@
       <c r="AD94"/>
       <c r="AE94"/>
     </row>
-    <row r="95" spans="1:31" ht="15" hidden="1">
+    <row r="95" spans="1:31" ht="15">
       <c r="A95" s="42" t="s">
         <v>642</v>
       </c>
@@ -11337,7 +11327,7 @@
       <c r="AD95"/>
       <c r="AE95"/>
     </row>
-    <row r="96" spans="1:31" ht="15" hidden="1">
+    <row r="96" spans="1:31" ht="15">
       <c r="A96" s="42" t="s">
         <v>642</v>
       </c>
@@ -11410,7 +11400,7 @@
       <c r="AD96"/>
       <c r="AE96"/>
     </row>
-    <row r="97" spans="1:31" ht="15" hidden="1">
+    <row r="97" spans="1:31" ht="15">
       <c r="A97" s="42" t="s">
         <v>644</v>
       </c>
@@ -11482,7 +11472,7 @@
       <c r="AD97"/>
       <c r="AE97"/>
     </row>
-    <row r="98" spans="1:31" ht="15" hidden="1">
+    <row r="98" spans="1:31" ht="15">
       <c r="A98" s="42" t="s">
         <v>644</v>
       </c>
@@ -11554,7 +11544,7 @@
       <c r="AD98"/>
       <c r="AE98"/>
     </row>
-    <row r="99" spans="1:31" ht="15" hidden="1">
+    <row r="99" spans="1:31" ht="15">
       <c r="A99" s="42" t="s">
         <v>644</v>
       </c>
@@ -11626,7 +11616,7 @@
       <c r="AD99"/>
       <c r="AE99"/>
     </row>
-    <row r="100" spans="1:31" ht="15" hidden="1">
+    <row r="100" spans="1:31" ht="15">
       <c r="A100" s="42" t="s">
         <v>61</v>
       </c>
@@ -11695,7 +11685,7 @@
       <c r="AD100"/>
       <c r="AE100"/>
     </row>
-    <row r="101" spans="1:31" ht="15" hidden="1">
+    <row r="101" spans="1:31" ht="15">
       <c r="A101" s="42" t="s">
         <v>61</v>
       </c>
@@ -11767,7 +11757,7 @@
       <c r="AD101"/>
       <c r="AE101"/>
     </row>
-    <row r="102" spans="1:31" ht="15" hidden="1">
+    <row r="102" spans="1:31" ht="15">
       <c r="A102" s="42" t="s">
         <v>64</v>
       </c>
@@ -11836,7 +11826,7 @@
       <c r="AD102"/>
       <c r="AE102"/>
     </row>
-    <row r="103" spans="1:31" ht="15" hidden="1">
+    <row r="103" spans="1:31" ht="15">
       <c r="A103" s="42" t="s">
         <v>64</v>
       </c>
@@ -11908,7 +11898,7 @@
       <c r="AD103"/>
       <c r="AE103"/>
     </row>
-    <row r="104" spans="1:31" ht="15" hidden="1">
+    <row r="104" spans="1:31" ht="15">
       <c r="A104" s="42" t="s">
         <v>66</v>
       </c>
@@ -11977,7 +11967,7 @@
       <c r="AD104"/>
       <c r="AE104"/>
     </row>
-    <row r="105" spans="1:31" ht="15" hidden="1">
+    <row r="105" spans="1:31" ht="15">
       <c r="A105" s="42" t="s">
         <v>66</v>
       </c>
@@ -12049,7 +12039,7 @@
       <c r="AD105"/>
       <c r="AE105"/>
     </row>
-    <row r="106" spans="1:31" ht="15" hidden="1">
+    <row r="106" spans="1:31" ht="15">
       <c r="A106" s="42" t="s">
         <v>70</v>
       </c>
@@ -12118,7 +12108,7 @@
       <c r="AD106"/>
       <c r="AE106"/>
     </row>
-    <row r="107" spans="1:31" ht="15" hidden="1">
+    <row r="107" spans="1:31" ht="15">
       <c r="A107" s="42" t="s">
         <v>70</v>
       </c>
@@ -12190,7 +12180,7 @@
       <c r="AD107"/>
       <c r="AE107"/>
     </row>
-    <row r="108" spans="1:31" ht="15" hidden="1">
+    <row r="108" spans="1:31" ht="15">
       <c r="A108" s="42" t="s">
         <v>72</v>
       </c>
@@ -12259,7 +12249,7 @@
       <c r="AD108"/>
       <c r="AE108"/>
     </row>
-    <row r="109" spans="1:31" ht="15" hidden="1">
+    <row r="109" spans="1:31" ht="15">
       <c r="A109" s="42" t="s">
         <v>72</v>
       </c>
@@ -12331,7 +12321,7 @@
       <c r="AD109"/>
       <c r="AE109"/>
     </row>
-    <row r="110" spans="1:31" ht="15" hidden="1">
+    <row r="110" spans="1:31" ht="15">
       <c r="A110" s="42" t="s">
         <v>75</v>
       </c>
@@ -12400,7 +12390,7 @@
       <c r="AD110"/>
       <c r="AE110"/>
     </row>
-    <row r="111" spans="1:31" ht="15" hidden="1">
+    <row r="111" spans="1:31" ht="15">
       <c r="A111" s="42" t="s">
         <v>75</v>
       </c>
@@ -12472,7 +12462,7 @@
       <c r="AD111"/>
       <c r="AE111"/>
     </row>
-    <row r="112" spans="1:31" ht="15" hidden="1">
+    <row r="112" spans="1:31" ht="15">
       <c r="A112" s="42" t="s">
         <v>77</v>
       </c>
@@ -12539,7 +12529,7 @@
       <c r="AD112"/>
       <c r="AE112"/>
     </row>
-    <row r="113" spans="1:31" ht="15" hidden="1">
+    <row r="113" spans="1:31" ht="15">
       <c r="A113" s="42" t="s">
         <v>77</v>
       </c>
@@ -12609,7 +12599,7 @@
       <c r="AD113"/>
       <c r="AE113"/>
     </row>
-    <row r="114" spans="1:31" ht="15" hidden="1">
+    <row r="114" spans="1:31" ht="15">
       <c r="A114" s="42" t="s">
         <v>80</v>
       </c>
@@ -12676,7 +12666,7 @@
       <c r="AD114"/>
       <c r="AE114"/>
     </row>
-    <row r="115" spans="1:31" ht="15" hidden="1">
+    <row r="115" spans="1:31" ht="15">
       <c r="A115" s="42" t="s">
         <v>80</v>
       </c>
@@ -12746,7 +12736,7 @@
       <c r="AD115"/>
       <c r="AE115"/>
     </row>
-    <row r="116" spans="1:31" ht="15" hidden="1">
+    <row r="116" spans="1:31" ht="15">
       <c r="A116" s="42" t="s">
         <v>82</v>
       </c>
@@ -12816,7 +12806,7 @@
       <c r="AD116"/>
       <c r="AE116"/>
     </row>
-    <row r="117" spans="1:31" ht="15" hidden="1">
+    <row r="117" spans="1:31" ht="15">
       <c r="A117" s="42" t="s">
         <v>82</v>
       </c>
@@ -12889,7 +12879,7 @@
       <c r="AD117"/>
       <c r="AE117"/>
     </row>
-    <row r="118" spans="1:31" ht="15" hidden="1">
+    <row r="118" spans="1:31" ht="15">
       <c r="A118" s="42" t="s">
         <v>84</v>
       </c>
@@ -12959,7 +12949,7 @@
       <c r="AD118"/>
       <c r="AE118"/>
     </row>
-    <row r="119" spans="1:31" ht="15" hidden="1">
+    <row r="119" spans="1:31" ht="15">
       <c r="A119" s="42" t="s">
         <v>84</v>
       </c>
@@ -13032,7 +13022,7 @@
       <c r="AD119"/>
       <c r="AE119"/>
     </row>
-    <row r="120" spans="1:31" ht="15" hidden="1">
+    <row r="120" spans="1:31" ht="15">
       <c r="A120" s="42" t="s">
         <v>86</v>
       </c>
@@ -13102,7 +13092,7 @@
       <c r="AD120"/>
       <c r="AE120"/>
     </row>
-    <row r="121" spans="1:31" ht="15" hidden="1">
+    <row r="121" spans="1:31" ht="15">
       <c r="A121" s="42" t="s">
         <v>86</v>
       </c>
@@ -13175,7 +13165,7 @@
       <c r="AD121"/>
       <c r="AE121"/>
     </row>
-    <row r="122" spans="1:31" ht="15" hidden="1">
+    <row r="122" spans="1:31" ht="15">
       <c r="A122" s="42" t="s">
         <v>88</v>
       </c>
@@ -13245,7 +13235,7 @@
       <c r="AD122"/>
       <c r="AE122"/>
     </row>
-    <row r="123" spans="1:31" ht="15" hidden="1">
+    <row r="123" spans="1:31" ht="15">
       <c r="A123" s="42" t="s">
         <v>88</v>
       </c>
@@ -13318,7 +13308,7 @@
       <c r="AD123"/>
       <c r="AE123"/>
     </row>
-    <row r="124" spans="1:31" ht="15" hidden="1">
+    <row r="124" spans="1:31" ht="15">
       <c r="A124" s="42" t="s">
         <v>90</v>
       </c>
@@ -13388,7 +13378,7 @@
       <c r="AD124"/>
       <c r="AE124"/>
     </row>
-    <row r="125" spans="1:31" ht="15" hidden="1">
+    <row r="125" spans="1:31" ht="15">
       <c r="A125" s="42" t="s">
         <v>90</v>
       </c>
@@ -13461,7 +13451,7 @@
       <c r="AD125"/>
       <c r="AE125"/>
     </row>
-    <row r="126" spans="1:31" ht="15" hidden="1">
+    <row r="126" spans="1:31" ht="15">
       <c r="A126" s="42" t="s">
         <v>92</v>
       </c>
@@ -13531,7 +13521,7 @@
       <c r="AD126"/>
       <c r="AE126"/>
     </row>
-    <row r="127" spans="1:31" ht="15" hidden="1">
+    <row r="127" spans="1:31" ht="15">
       <c r="A127" s="42" t="s">
         <v>92</v>
       </c>
@@ -13604,7 +13594,7 @@
       <c r="AD127"/>
       <c r="AE127"/>
     </row>
-    <row r="128" spans="1:31" ht="15" hidden="1">
+    <row r="128" spans="1:31" ht="15">
       <c r="A128" s="42" t="s">
         <v>94</v>
       </c>
@@ -13674,7 +13664,7 @@
       <c r="AD128"/>
       <c r="AE128"/>
     </row>
-    <row r="129" spans="1:31" ht="15" hidden="1">
+    <row r="129" spans="1:31" ht="15">
       <c r="A129" s="42" t="s">
         <v>94</v>
       </c>
@@ -13747,7 +13737,7 @@
       <c r="AD129"/>
       <c r="AE129"/>
     </row>
-    <row r="130" spans="1:31" ht="15" hidden="1">
+    <row r="130" spans="1:31" ht="15">
       <c r="A130" s="42" t="s">
         <v>96</v>
       </c>
@@ -13815,7 +13805,7 @@
       <c r="AD130"/>
       <c r="AE130"/>
     </row>
-    <row r="131" spans="1:31" ht="15" hidden="1">
+    <row r="131" spans="1:31" ht="15">
       <c r="A131" s="42" t="s">
         <v>96</v>
       </c>
@@ -13886,7 +13876,7 @@
       <c r="AD131"/>
       <c r="AE131"/>
     </row>
-    <row r="132" spans="1:31" ht="15" hidden="1">
+    <row r="132" spans="1:31" ht="15">
       <c r="A132" s="42" t="s">
         <v>98</v>
       </c>
@@ -13954,7 +13944,7 @@
       <c r="AD132"/>
       <c r="AE132"/>
     </row>
-    <row r="133" spans="1:31" ht="15" hidden="1">
+    <row r="133" spans="1:31" ht="15">
       <c r="A133" s="79" t="s">
         <v>98</v>
       </c>
@@ -14024,7 +14014,7 @@
       <c r="AC133" s="46"/>
       <c r="AD133" s="46"/>
     </row>
-    <row r="134" spans="1:31" ht="15" hidden="1">
+    <row r="134" spans="1:31" ht="15">
       <c r="A134" s="79" t="s">
         <v>100</v>
       </c>
@@ -14091,7 +14081,7 @@
       <c r="AC134" s="46"/>
       <c r="AD134" s="46"/>
     </row>
-    <row r="135" spans="1:31" ht="15" hidden="1">
+    <row r="135" spans="1:31" ht="15">
       <c r="A135" s="79" t="s">
         <v>100</v>
       </c>
@@ -14161,7 +14151,7 @@
       <c r="AC135" s="46"/>
       <c r="AD135" s="44"/>
     </row>
-    <row r="136" spans="1:31" ht="15" hidden="1">
+    <row r="136" spans="1:31" ht="15">
       <c r="A136" s="79" t="s">
         <v>102</v>
       </c>
@@ -14230,7 +14220,7 @@
       <c r="AC136" s="46"/>
       <c r="AD136" s="44"/>
     </row>
-    <row r="137" spans="1:31" ht="15" hidden="1">
+    <row r="137" spans="1:31" ht="15">
       <c r="A137" s="79" t="s">
         <v>102</v>
       </c>
@@ -14302,7 +14292,7 @@
       <c r="AC137" s="46"/>
       <c r="AD137" s="44"/>
     </row>
-    <row r="138" spans="1:31" ht="15" hidden="1">
+    <row r="138" spans="1:31" ht="15">
       <c r="A138" s="79" t="s">
         <v>104</v>
       </c>
@@ -14371,7 +14361,7 @@
       <c r="AC138" s="46"/>
       <c r="AD138" s="44"/>
     </row>
-    <row r="139" spans="1:31" ht="15" hidden="1">
+    <row r="139" spans="1:31" ht="15">
       <c r="A139" s="79" t="s">
         <v>104</v>
       </c>
@@ -14444,7 +14434,7 @@
       <c r="AD139" s="44"/>
       <c r="AE139" s="16"/>
     </row>
-    <row r="140" spans="1:31" ht="15" hidden="1">
+    <row r="140" spans="1:31" ht="15">
       <c r="A140" s="79" t="s">
         <v>106</v>
       </c>
@@ -14514,7 +14504,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="16"/>
     </row>
-    <row r="141" spans="1:31" ht="15" hidden="1">
+    <row r="141" spans="1:31" ht="15">
       <c r="A141" s="79" t="s">
         <v>106</v>
       </c>
@@ -14587,7 +14577,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="16"/>
     </row>
-    <row r="142" spans="1:31" ht="15" hidden="1">
+    <row r="142" spans="1:31" ht="15">
       <c r="A142" s="79" t="s">
         <v>108</v>
       </c>
@@ -14656,7 +14646,7 @@
       <c r="AC142" s="46"/>
       <c r="AD142" s="7"/>
     </row>
-    <row r="143" spans="1:31" ht="15" hidden="1">
+    <row r="143" spans="1:31" ht="15">
       <c r="A143" s="79" t="s">
         <v>108</v>
       </c>
@@ -14728,7 +14718,7 @@
       <c r="AC143" s="46"/>
       <c r="AD143" s="7"/>
     </row>
-    <row r="144" spans="1:31" ht="15" hidden="1">
+    <row r="144" spans="1:31" ht="15">
       <c r="A144" s="79" t="s">
         <v>110</v>
       </c>
@@ -14797,7 +14787,7 @@
       <c r="AC144" s="46"/>
       <c r="AD144" s="7"/>
     </row>
-    <row r="145" spans="1:31" ht="15" hidden="1">
+    <row r="145" spans="1:31" ht="15">
       <c r="A145" s="79" t="s">
         <v>110</v>
       </c>
@@ -14869,7 +14859,7 @@
       <c r="AC145" s="46"/>
       <c r="AD145" s="7"/>
     </row>
-    <row r="146" spans="1:31" ht="15" hidden="1">
+    <row r="146" spans="1:31" ht="15">
       <c r="A146" s="85" t="s">
         <v>112</v>
       </c>
@@ -14938,7 +14928,7 @@
       <c r="AC146" s="46"/>
       <c r="AD146" s="44"/>
     </row>
-    <row r="147" spans="1:31" ht="15" hidden="1">
+    <row r="147" spans="1:31" ht="15">
       <c r="A147" s="42" t="s">
         <v>112</v>
       </c>
@@ -15010,7 +15000,7 @@
       <c r="AD147"/>
       <c r="AE147"/>
     </row>
-    <row r="148" spans="1:31" ht="15" hidden="1">
+    <row r="148" spans="1:31" ht="15">
       <c r="A148" s="42" t="s">
         <v>114</v>
       </c>
@@ -15077,7 +15067,7 @@
       <c r="AD148"/>
       <c r="AE148"/>
     </row>
-    <row r="149" spans="1:31" ht="15" hidden="1">
+    <row r="149" spans="1:31" ht="15">
       <c r="A149" s="42" t="s">
         <v>114</v>
       </c>
@@ -15147,7 +15137,7 @@
       <c r="AD149"/>
       <c r="AE149"/>
     </row>
-    <row r="150" spans="1:31" ht="15" hidden="1">
+    <row r="150" spans="1:31" ht="15">
       <c r="A150" s="42" t="s">
         <v>116</v>
       </c>
@@ -15214,7 +15204,7 @@
       <c r="AD150"/>
       <c r="AE150"/>
     </row>
-    <row r="151" spans="1:31" ht="15" hidden="1">
+    <row r="151" spans="1:31" ht="15">
       <c r="A151" s="42" t="s">
         <v>116</v>
       </c>
@@ -15284,7 +15274,7 @@
       <c r="AD151"/>
       <c r="AE151"/>
     </row>
-    <row r="152" spans="1:31" ht="15" hidden="1">
+    <row r="152" spans="1:31" ht="15">
       <c r="A152" s="42" t="s">
         <v>118</v>
       </c>
@@ -15352,7 +15342,7 @@
       <c r="AD152"/>
       <c r="AE152"/>
     </row>
-    <row r="153" spans="1:31" ht="15" hidden="1">
+    <row r="153" spans="1:31" ht="15">
       <c r="A153" s="42" t="s">
         <v>118</v>
       </c>
@@ -15423,7 +15413,7 @@
       <c r="AD153"/>
       <c r="AE153"/>
     </row>
-    <row r="154" spans="1:31" ht="15" hidden="1">
+    <row r="154" spans="1:31" ht="15">
       <c r="A154" s="42" t="s">
         <v>123</v>
       </c>
@@ -15495,7 +15485,7 @@
       <c r="AC154" s="46"/>
       <c r="AD154" s="46"/>
     </row>
-    <row r="155" spans="1:31" ht="15" hidden="1">
+    <row r="155" spans="1:31" ht="15">
       <c r="A155" s="42" t="s">
         <v>123</v>
       </c>
@@ -15567,7 +15557,7 @@
       <c r="AC155" s="46"/>
       <c r="AD155" s="44"/>
     </row>
-    <row r="156" spans="1:31" ht="15" hidden="1">
+    <row r="156" spans="1:31" ht="15">
       <c r="A156" s="42" t="s">
         <v>123</v>
       </c>
@@ -15639,7 +15629,7 @@
       <c r="AC156" s="46"/>
       <c r="AD156" s="44"/>
     </row>
-    <row r="157" spans="1:31" ht="15" hidden="1">
+    <row r="157" spans="1:31" ht="15">
       <c r="A157" s="42" t="s">
         <v>123</v>
       </c>
@@ -15711,7 +15701,7 @@
       <c r="AC157" s="46"/>
       <c r="AD157" s="7"/>
     </row>
-    <row r="158" spans="1:31" ht="15" hidden="1">
+    <row r="158" spans="1:31" ht="15">
       <c r="A158" s="79" t="s">
         <v>123</v>
       </c>
@@ -15783,7 +15773,7 @@
       <c r="AC158" s="46"/>
       <c r="AD158" s="7"/>
     </row>
-    <row r="159" spans="1:31" ht="15" hidden="1">
+    <row r="159" spans="1:31" ht="15">
       <c r="A159" s="79" t="s">
         <v>123</v>
       </c>
@@ -15856,7 +15846,7 @@
       <c r="AC159" s="46"/>
       <c r="AD159" s="7"/>
     </row>
-    <row r="160" spans="1:31" ht="15" hidden="1">
+    <row r="160" spans="1:31" ht="15">
       <c r="A160" s="79" t="s">
         <v>123</v>
       </c>
@@ -15928,7 +15918,7 @@
       <c r="AC160" s="46"/>
       <c r="AD160" s="7"/>
     </row>
-    <row r="161" spans="1:30" ht="15" hidden="1">
+    <row r="161" spans="1:30" ht="15">
       <c r="A161" s="79" t="s">
         <v>123</v>
       </c>
@@ -16000,7 +15990,7 @@
       <c r="AC161" s="46"/>
       <c r="AD161" s="46"/>
     </row>
-    <row r="162" spans="1:30" ht="15" hidden="1">
+    <row r="162" spans="1:30" ht="15">
       <c r="A162" s="79" t="s">
         <v>123</v>
       </c>
@@ -16072,7 +16062,7 @@
       <c r="AC162" s="46"/>
       <c r="AD162" s="7"/>
     </row>
-    <row r="163" spans="1:30" ht="15" hidden="1">
+    <row r="163" spans="1:30" ht="15">
       <c r="A163" s="79" t="s">
         <v>123</v>
       </c>
@@ -16144,7 +16134,7 @@
       <c r="AC163" s="46"/>
       <c r="AD163" s="46"/>
     </row>
-    <row r="164" spans="1:30" ht="15" hidden="1">
+    <row r="164" spans="1:30" ht="15">
       <c r="A164" s="79" t="s">
         <v>123</v>
       </c>
@@ -16216,7 +16206,7 @@
       <c r="AC164" s="46"/>
       <c r="AD164" s="44"/>
     </row>
-    <row r="165" spans="1:30" ht="15" hidden="1">
+    <row r="165" spans="1:30" ht="15">
       <c r="A165" s="79" t="s">
         <v>123</v>
       </c>
@@ -16288,7 +16278,7 @@
       <c r="AC165" s="46"/>
       <c r="AD165" s="44"/>
     </row>
-    <row r="166" spans="1:30" ht="15" hidden="1">
+    <row r="166" spans="1:30" ht="15">
       <c r="A166" s="79" t="s">
         <v>123</v>
       </c>
@@ -16360,7 +16350,7 @@
       <c r="AC166" s="46"/>
       <c r="AD166" s="44"/>
     </row>
-    <row r="167" spans="1:30" ht="15" hidden="1">
+    <row r="167" spans="1:30" ht="15">
       <c r="A167" s="85" t="s">
         <v>123</v>
       </c>
@@ -16432,7 +16422,7 @@
       <c r="AC167" s="46"/>
       <c r="AD167" s="44"/>
     </row>
-    <row r="168" spans="1:30" ht="15" hidden="1">
+    <row r="168" spans="1:30" ht="15">
       <c r="A168" s="79" t="s">
         <v>125</v>
       </c>
@@ -16504,7 +16494,7 @@
       <c r="AC168" s="46"/>
       <c r="AD168" s="44"/>
     </row>
-    <row r="169" spans="1:30" ht="15" hidden="1">
+    <row r="169" spans="1:30" ht="15">
       <c r="A169" s="79" t="s">
         <v>125</v>
       </c>
@@ -16576,7 +16566,7 @@
       <c r="AC169" s="46"/>
       <c r="AD169" s="7"/>
     </row>
-    <row r="170" spans="1:30" ht="15" hidden="1">
+    <row r="170" spans="1:30" ht="15">
       <c r="A170" s="79" t="s">
         <v>125</v>
       </c>
@@ -16648,7 +16638,7 @@
       <c r="AC170" s="46"/>
       <c r="AD170" s="7"/>
     </row>
-    <row r="171" spans="1:30" ht="15" hidden="1">
+    <row r="171" spans="1:30" ht="15">
       <c r="A171" s="79" t="s">
         <v>125</v>
       </c>
@@ -16719,7 +16709,7 @@
       <c r="AB171" s="73"/>
       <c r="AD171" s="16"/>
     </row>
-    <row r="172" spans="1:30" ht="15" hidden="1">
+    <row r="172" spans="1:30" ht="15">
       <c r="A172" s="79" t="s">
         <v>125</v>
       </c>
@@ -16791,7 +16781,7 @@
       <c r="AC172" s="44"/>
       <c r="AD172" s="44"/>
     </row>
-    <row r="173" spans="1:30" ht="15" hidden="1">
+    <row r="173" spans="1:30" ht="15">
       <c r="A173" s="79" t="s">
         <v>125</v>
       </c>
@@ -16864,7 +16854,7 @@
       <c r="AC173" s="44"/>
       <c r="AD173" s="44"/>
     </row>
-    <row r="174" spans="1:30" ht="15" hidden="1">
+    <row r="174" spans="1:30" ht="15">
       <c r="A174" s="79" t="s">
         <v>125</v>
       </c>
@@ -16936,7 +16926,7 @@
       <c r="AC174" s="44"/>
       <c r="AD174" s="44"/>
     </row>
-    <row r="175" spans="1:30" ht="15" hidden="1">
+    <row r="175" spans="1:30" ht="15">
       <c r="A175" s="79" t="s">
         <v>125</v>
       </c>
@@ -17008,7 +16998,7 @@
       <c r="AC175" s="44"/>
       <c r="AD175" s="44"/>
     </row>
-    <row r="176" spans="1:30" ht="15" hidden="1">
+    <row r="176" spans="1:30" ht="15">
       <c r="A176" s="79" t="s">
         <v>125</v>
       </c>
@@ -17080,7 +17070,7 @@
       <c r="AC176" s="44"/>
       <c r="AD176" s="44"/>
     </row>
-    <row r="177" spans="1:30" ht="15" hidden="1">
+    <row r="177" spans="1:30" ht="15">
       <c r="A177" s="79" t="s">
         <v>125</v>
       </c>
@@ -17152,7 +17142,7 @@
       <c r="AC177" s="44"/>
       <c r="AD177" s="44"/>
     </row>
-    <row r="178" spans="1:30" ht="15" hidden="1">
+    <row r="178" spans="1:30" ht="15">
       <c r="A178" s="79" t="s">
         <v>125</v>
       </c>
@@ -17224,7 +17214,7 @@
       <c r="AC178" s="44"/>
       <c r="AD178" s="44"/>
     </row>
-    <row r="179" spans="1:30" ht="15" hidden="1">
+    <row r="179" spans="1:30" ht="15">
       <c r="A179" s="79" t="s">
         <v>125</v>
       </c>
@@ -17296,7 +17286,7 @@
       <c r="AC179" s="44"/>
       <c r="AD179" s="44"/>
     </row>
-    <row r="180" spans="1:30" ht="15" hidden="1">
+    <row r="180" spans="1:30" ht="15">
       <c r="A180" s="79" t="s">
         <v>125</v>
       </c>
@@ -17368,7 +17358,7 @@
       <c r="AC180" s="44"/>
       <c r="AD180" s="44"/>
     </row>
-    <row r="181" spans="1:30" ht="15" hidden="1">
+    <row r="181" spans="1:30" ht="15">
       <c r="A181" s="79" t="s">
         <v>125</v>
       </c>
@@ -17440,7 +17430,7 @@
       <c r="AC181" s="44"/>
       <c r="AD181" s="44"/>
     </row>
-    <row r="182" spans="1:30" ht="15" hidden="1">
+    <row r="182" spans="1:30" ht="15">
       <c r="A182" s="79" t="s">
         <v>127</v>
       </c>
@@ -17512,7 +17502,7 @@
       <c r="AC182" s="44"/>
       <c r="AD182" s="44"/>
     </row>
-    <row r="183" spans="1:30" ht="15" hidden="1">
+    <row r="183" spans="1:30" ht="15">
       <c r="A183" s="79" t="s">
         <v>127</v>
       </c>
@@ -17584,7 +17574,7 @@
       <c r="AC183" s="44"/>
       <c r="AD183" s="44"/>
     </row>
-    <row r="184" spans="1:30" ht="15" hidden="1">
+    <row r="184" spans="1:30" ht="15">
       <c r="A184" s="79" t="s">
         <v>127</v>
       </c>
@@ -17656,7 +17646,7 @@
       <c r="AC184" s="44"/>
       <c r="AD184" s="44"/>
     </row>
-    <row r="185" spans="1:30" ht="15" hidden="1">
+    <row r="185" spans="1:30" ht="15">
       <c r="A185" s="79" t="s">
         <v>127</v>
       </c>
@@ -17728,7 +17718,7 @@
       <c r="AC185" s="44"/>
       <c r="AD185" s="44"/>
     </row>
-    <row r="186" spans="1:30" ht="15" hidden="1">
+    <row r="186" spans="1:30" ht="15">
       <c r="A186" s="79" t="s">
         <v>127</v>
       </c>
@@ -17800,7 +17790,7 @@
       <c r="AC186" s="44"/>
       <c r="AD186" s="44"/>
     </row>
-    <row r="187" spans="1:30" ht="15" hidden="1">
+    <row r="187" spans="1:30" ht="15">
       <c r="A187" s="79" t="s">
         <v>127</v>
       </c>
@@ -17873,7 +17863,7 @@
       <c r="AC187" s="44"/>
       <c r="AD187" s="44"/>
     </row>
-    <row r="188" spans="1:30" ht="15" hidden="1">
+    <row r="188" spans="1:30" ht="15">
       <c r="A188" s="79" t="s">
         <v>127</v>
       </c>
@@ -17945,7 +17935,7 @@
       <c r="AC188" s="44"/>
       <c r="AD188" s="44"/>
     </row>
-    <row r="189" spans="1:30" ht="15" hidden="1">
+    <row r="189" spans="1:30" ht="15">
       <c r="A189" s="79" t="s">
         <v>127</v>
       </c>
@@ -18017,7 +18007,7 @@
       <c r="AC189" s="44"/>
       <c r="AD189" s="44"/>
     </row>
-    <row r="190" spans="1:30" ht="15" hidden="1">
+    <row r="190" spans="1:30" ht="15">
       <c r="A190" s="79" t="s">
         <v>127</v>
       </c>
@@ -18089,7 +18079,7 @@
       <c r="AC190" s="44"/>
       <c r="AD190" s="44"/>
     </row>
-    <row r="191" spans="1:30" ht="15" hidden="1">
+    <row r="191" spans="1:30" ht="15">
       <c r="A191" s="79" t="s">
         <v>127</v>
       </c>
@@ -18161,7 +18151,7 @@
       <c r="AC191" s="44"/>
       <c r="AD191" s="44"/>
     </row>
-    <row r="192" spans="1:30" ht="15" hidden="1">
+    <row r="192" spans="1:30" ht="15">
       <c r="A192" s="79" t="s">
         <v>127</v>
       </c>
@@ -18233,7 +18223,7 @@
       <c r="AC192" s="44"/>
       <c r="AD192" s="44"/>
     </row>
-    <row r="193" spans="1:30" ht="15" hidden="1">
+    <row r="193" spans="1:30" ht="15">
       <c r="A193" s="79" t="s">
         <v>127</v>
       </c>
@@ -18305,7 +18295,7 @@
       <c r="AC193" s="44"/>
       <c r="AD193" s="44"/>
     </row>
-    <row r="194" spans="1:30" ht="15" hidden="1">
+    <row r="194" spans="1:30" ht="15">
       <c r="A194" s="79" t="s">
         <v>127</v>
       </c>
@@ -18377,7 +18367,7 @@
       <c r="AC194" s="44"/>
       <c r="AD194" s="44"/>
     </row>
-    <row r="195" spans="1:30" ht="15" hidden="1">
+    <row r="195" spans="1:30" ht="15">
       <c r="A195" s="79" t="s">
         <v>127</v>
       </c>
@@ -18447,7 +18437,7 @@
       <c r="AC195" s="44"/>
       <c r="AD195" s="44"/>
     </row>
-    <row r="196" spans="1:30" ht="15" hidden="1">
+    <row r="196" spans="1:30" ht="15">
       <c r="A196" s="79" t="s">
         <v>165</v>
       </c>
@@ -18526,7 +18516,7 @@
       <c r="AC196" s="44"/>
       <c r="AD196" s="44"/>
     </row>
-    <row r="197" spans="1:30" ht="15" hidden="1">
+    <row r="197" spans="1:30" ht="15">
       <c r="A197" s="79" t="s">
         <v>167</v>
       </c>
@@ -18605,7 +18595,7 @@
       <c r="AC197" s="44"/>
       <c r="AD197" s="44"/>
     </row>
-    <row r="198" spans="1:30" ht="15" hidden="1">
+    <row r="198" spans="1:30" ht="15">
       <c r="A198" s="79" t="s">
         <v>169</v>
       </c>
@@ -18684,7 +18674,7 @@
       <c r="AC198" s="44"/>
       <c r="AD198" s="44"/>
     </row>
-    <row r="199" spans="1:30" ht="15" hidden="1">
+    <row r="199" spans="1:30" ht="15">
       <c r="A199" s="85" t="s">
         <v>1</v>
       </c>
